--- a/community-help-api/docs/api/community-help-api-test.xlsx
+++ b/community-help-api/docs/api/community-help-api-test.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="873" uniqueCount="475">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="965" uniqueCount="520">
   <si>
     <t>Community Help API — Plan de Pruebas Swagger</t>
   </si>
@@ -452,6 +452,144 @@
     <t>Verificar que el filtro JWT rechaza la petición</t>
   </si>
   <si>
+    <t>Verificación de email</t>
+  </si>
+  <si>
+    <t>A-12</t>
+  </si>
+  <si>
+    <t>Verificar email con OTP válido</t>
+  </si>
+  <si>
+    <t>/api/v1/auth/verify-email</t>
+  </si>
+  <si>
+    <t>{"email":"ana@test.com","code":"XXXXXX"}</t>
+  </si>
+  <si>
+    <t>200 OK</t>
+  </si>
+  <si>
+    <t>Consultar el OTP real con: SELECT code FROM otp_codes WHERE email='ana@test.com' AND used=false</t>
+  </si>
+  <si>
+    <t>A-13</t>
+  </si>
+  <si>
+    <t>Verificar email con OTP expirado</t>
+  </si>
+  <si>
+    <t>Forzar expiración: UPDATE otp_codes SET expires_at = now() - interval '1 hour'</t>
+  </si>
+  <si>
+    <t>A-14</t>
+  </si>
+  <si>
+    <t>Verificar email con OTP incorrecto</t>
+  </si>
+  <si>
+    <t>{"email":"ana@test.com","code":"000000"}</t>
+  </si>
+  <si>
+    <t>Código inventado, debe rechazarse</t>
+  </si>
+  <si>
+    <t>Recuperación de contraseña</t>
+  </si>
+  <si>
+    <t>A-17</t>
+  </si>
+  <si>
+    <t>Solicitar reset (email existe)</t>
+  </si>
+  <si>
+    <t>/api/v1/auth/forgot-password</t>
+  </si>
+  <si>
+    <t>{"email":"ana@test.com"}</t>
+  </si>
+  <si>
+    <t>Comprobar que llega email y se crea registro en otp_codes</t>
+  </si>
+  <si>
+    <t>A-18</t>
+  </si>
+  <si>
+    <t>Solicitar reset (email no existe)</t>
+  </si>
+  <si>
+    <t>{"email":"noexiste@test.com"}</t>
+  </si>
+  <si>
+    <t>404 Not Found</t>
+  </si>
+  <si>
+    <t>Debe lanzar EntityNotFoundException</t>
+  </si>
+  <si>
+    <t>A-19</t>
+  </si>
+  <si>
+    <t>Resetear contraseña con OTP válido</t>
+  </si>
+  <si>
+    <t>/api/v1/auth/reset-password</t>
+  </si>
+  <si>
+    <t>{"email":"ana@test.com","code":"XXXXXX","newPassword":"NuevoPass1!"}</t>
+  </si>
+  <si>
+    <t>Verificar login posterior con la nueva contraseña (ver A-20)</t>
+  </si>
+  <si>
+    <t>A-20</t>
+  </si>
+  <si>
+    <t>Login con nueva contraseña tras reset</t>
+  </si>
+  <si>
+    <t>{"email":"ana@test.com","password":"NuevoPass1!"}</t>
+  </si>
+  <si>
+    <t>Confirmar que el cambio de contraseña fue efectivo</t>
+  </si>
+  <si>
+    <t>A-21</t>
+  </si>
+  <si>
+    <t>Login con contraseña antigua tras reset</t>
+  </si>
+  <si>
+    <t>La contraseña antigua ya no debe funcionar</t>
+  </si>
+  <si>
+    <t>A-22</t>
+  </si>
+  <si>
+    <t>Resetear contraseña con OTP incorrecto</t>
+  </si>
+  <si>
+    <t>{"email":"ana@test.com","code":"000000","newPassword":"NuevoPass1!"}</t>
+  </si>
+  <si>
+    <t>Código inventado</t>
+  </si>
+  <si>
+    <t>A-23</t>
+  </si>
+  <si>
+    <t>Resetear contraseña con nueva contraseña inválida</t>
+  </si>
+  <si>
+    <t>{"email":"ana@test.com","code":"XXXXXX","newPassword":"123"}</t>
+  </si>
+  <si>
+    <t>400 Bad Request</t>
+  </si>
+  <si>
+    <t>Menos de 8 caracteres, debe fallar validación</t>
+  </si>
+  <si>
     <t>Pruebas — Users</t>
   </si>
   <si>
@@ -654,9 +792,6 @@
   </si>
   <si>
     <t>Obtener perfil sin ser voluntario (User C)</t>
-  </si>
-  <si>
-    <t>404 Not Found</t>
   </si>
   <si>
     <t>Resource not found</t>
@@ -1618,7 +1753,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="7">
     <border/>
     <border>
       <left style="thin">
@@ -1640,11 +1775,6 @@
       <bottom/>
     </border>
     <border>
-      <top/>
-      <bottom/>
-    </border>
-    <border>
-      <right/>
       <top/>
       <bottom/>
     </border>
@@ -1682,7 +1812,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="57">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1701,7 +1831,7 @@
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="4" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="5" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
@@ -1713,10 +1843,7 @@
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="6" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="6" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="1" fillId="7" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
@@ -1724,11 +1851,8 @@
     <xf borderId="1" fillId="7" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="7" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
-    </xf>
     <xf borderId="1" fillId="7" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="7" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="0"/>
@@ -1739,29 +1863,14 @@
     <xf borderId="1" fillId="8" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="8" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
-    </xf>
     <xf borderId="1" fillId="8" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="8" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="1" fillId="8" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="8" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
     <xf borderId="1" fillId="8" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="7" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="7" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="7" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
@@ -1771,9 +1880,6 @@
     </xf>
     <xf borderId="1" fillId="7" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="7" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="9" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
@@ -1786,17 +1892,16 @@
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="3" fillId="0" fontId="10" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="4" fillId="0" fontId="10" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="5" fillId="5" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="4" fillId="5" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
+    <xf borderId="5" fillId="0" fontId="10" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="6" fillId="0" fontId="10" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="7" fillId="0" fontId="10" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="1" fillId="7" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="4" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="8" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
@@ -1807,6 +1912,24 @@
     <xf borderId="1" fillId="8" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
+    <xf borderId="4" fillId="5" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="8" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="8" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="4" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="7" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="7" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
     <xf borderId="1" fillId="7" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
@@ -1815,9 +1938,6 @@
     </xf>
     <xf borderId="1" fillId="7" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="7" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="7" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
@@ -1832,28 +1952,13 @@
       <alignment vertical="center"/>
     </xf>
     <xf borderId="1" fillId="10" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="10" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="10" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="10" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="8" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="7" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="8" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="8" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
@@ -2177,7 +2282,7 @@
   <cols>
     <col customWidth="1" min="1" max="1" width="4.0"/>
     <col customWidth="1" min="2" max="2" width="80.0"/>
-    <col customWidth="1" min="3" max="26" width="8.71"/>
+    <col customWidth="1" min="3" max="6" width="8.71"/>
   </cols>
   <sheetData>
     <row r="2" ht="27.75" customHeight="1">
@@ -3289,359 +3394,358 @@
     <col customWidth="1" min="8" max="8" width="16.0"/>
     <col customWidth="1" min="9" max="9" width="40.0"/>
     <col customWidth="1" min="10" max="10" width="14.0"/>
-    <col customWidth="1" min="11" max="26" width="8.71"/>
   </cols>
   <sheetData>
     <row r="1" ht="24.0" customHeight="1">
-      <c r="A1" s="35" t="s">
-        <v>382</v>
-      </c>
-      <c r="B1" s="36"/>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36"/>
-      <c r="E1" s="36"/>
-      <c r="F1" s="36"/>
-      <c r="G1" s="36"/>
-      <c r="H1" s="36"/>
-      <c r="I1" s="36"/>
-      <c r="J1" s="37"/>
+      <c r="A1" s="27" t="s">
+        <v>427</v>
+      </c>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+      <c r="H1" s="28"/>
+      <c r="I1" s="28"/>
+      <c r="J1" s="28"/>
     </row>
     <row r="2" ht="21.75" customHeight="1">
-      <c r="A2" s="29" t="s">
+      <c r="A2" s="22" t="s">
         <v>85</v>
       </c>
-      <c r="B2" s="29" t="s">
+      <c r="B2" s="22" t="s">
         <v>86</v>
       </c>
-      <c r="C2" s="29" t="s">
+      <c r="C2" s="22" t="s">
         <v>87</v>
       </c>
-      <c r="D2" s="29" t="s">
+      <c r="D2" s="22" t="s">
         <v>88</v>
       </c>
-      <c r="E2" s="29" t="s">
+      <c r="E2" s="22" t="s">
         <v>89</v>
       </c>
-      <c r="F2" s="29" t="s">
+      <c r="F2" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="G2" s="29" t="s">
+      <c r="G2" s="22" t="s">
         <v>90</v>
       </c>
-      <c r="H2" s="29" t="s">
+      <c r="H2" s="22" t="s">
         <v>91</v>
       </c>
-      <c r="I2" s="29" t="s">
+      <c r="I2" s="22" t="s">
         <v>92</v>
       </c>
-      <c r="J2" s="29" t="s">
+      <c r="J2" s="22" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="3" ht="18.0" customHeight="1">
-      <c r="A3" s="38" t="s">
-        <v>383</v>
-      </c>
-      <c r="B3" s="39"/>
-      <c r="C3" s="39"/>
-      <c r="D3" s="39"/>
-      <c r="E3" s="39"/>
-      <c r="F3" s="39"/>
-      <c r="G3" s="39"/>
-      <c r="H3" s="39"/>
-      <c r="I3" s="39"/>
-      <c r="J3" s="40"/>
+      <c r="A3" s="29" t="s">
+        <v>428</v>
+      </c>
+      <c r="B3" s="30"/>
+      <c r="C3" s="30"/>
+      <c r="D3" s="30"/>
+      <c r="E3" s="30"/>
+      <c r="F3" s="30"/>
+      <c r="G3" s="30"/>
+      <c r="H3" s="30"/>
+      <c r="I3" s="30"/>
+      <c r="J3" s="31"/>
     </row>
     <row r="4" ht="42.0" customHeight="1">
-      <c r="A4" s="30" t="s">
-        <v>384</v>
-      </c>
-      <c r="B4" s="28" t="s">
-        <v>385</v>
-      </c>
-      <c r="C4" s="41" t="s">
+      <c r="A4" s="23" t="s">
+        <v>429</v>
+      </c>
+      <c r="B4" s="21" t="s">
+        <v>430</v>
+      </c>
+      <c r="C4" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="D4" s="28" t="s">
-        <v>386</v>
-      </c>
-      <c r="E4" s="27" t="s">
-        <v>147</v>
-      </c>
-      <c r="F4" s="28" t="str">
+      <c r="D4" s="21" t="s">
+        <v>431</v>
+      </c>
+      <c r="E4" s="21" t="s">
+        <v>193</v>
+      </c>
+      <c r="F4" s="21" t="str">
         <f>Variables!C8 &amp; ", HELP_REQUEST" </f>
         <v>c7cf918d-7e04-4104-9790-fa5bb9d3756d, HELP_REQUEST</v>
       </c>
-      <c r="G4" s="28" t="s">
-        <v>387</v>
-      </c>
-      <c r="H4" s="42" t="s">
+      <c r="G4" s="21" t="s">
+        <v>432</v>
+      </c>
+      <c r="H4" s="33" t="s">
         <v>70</v>
       </c>
-      <c r="I4" s="28" t="s">
-        <v>388</v>
-      </c>
-      <c r="J4" s="30"/>
+      <c r="I4" s="21" t="s">
+        <v>433</v>
+      </c>
+      <c r="J4" s="23"/>
     </row>
     <row r="5" ht="42.0" customHeight="1">
-      <c r="A5" s="43" t="s">
-        <v>389</v>
-      </c>
-      <c r="B5" s="25" t="s">
-        <v>390</v>
-      </c>
-      <c r="C5" s="45" t="s">
+      <c r="A5" s="34" t="s">
+        <v>434</v>
+      </c>
+      <c r="B5" s="20" t="s">
+        <v>435</v>
+      </c>
+      <c r="C5" s="36" t="s">
         <v>139</v>
       </c>
-      <c r="D5" s="25" t="s">
-        <v>391</v>
-      </c>
-      <c r="E5" s="24" t="s">
-        <v>147</v>
-      </c>
-      <c r="F5" s="25" t="s">
+      <c r="D5" s="20" t="s">
+        <v>436</v>
+      </c>
+      <c r="E5" s="20" t="s">
+        <v>193</v>
+      </c>
+      <c r="F5" s="20" t="s">
         <v>141</v>
       </c>
-      <c r="G5" s="25" t="s">
-        <v>392</v>
-      </c>
-      <c r="H5" s="42" t="s">
+      <c r="G5" s="20" t="s">
+        <v>437</v>
+      </c>
+      <c r="H5" s="33" t="s">
         <v>70</v>
       </c>
-      <c r="I5" s="24" t="s">
-        <v>393</v>
-      </c>
-      <c r="J5" s="43"/>
+      <c r="I5" s="20" t="s">
+        <v>438</v>
+      </c>
+      <c r="J5" s="34"/>
     </row>
     <row r="6" ht="42.0" customHeight="1">
-      <c r="A6" s="30" t="s">
-        <v>394</v>
-      </c>
-      <c r="B6" s="28" t="s">
-        <v>395</v>
-      </c>
-      <c r="C6" s="41" t="s">
+      <c r="A6" s="23" t="s">
+        <v>439</v>
+      </c>
+      <c r="B6" s="21" t="s">
+        <v>440</v>
+      </c>
+      <c r="C6" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="D6" s="28" t="s">
-        <v>396</v>
-      </c>
-      <c r="E6" s="27" t="s">
-        <v>147</v>
-      </c>
-      <c r="F6" s="28" t="str">
+      <c r="D6" s="21" t="s">
+        <v>441</v>
+      </c>
+      <c r="E6" s="21" t="s">
+        <v>193</v>
+      </c>
+      <c r="F6" s="21" t="str">
         <f>Variables!C15 &amp; ", {""content"":""Hola, ¿a qué hora te va bien para la compra?""}"</f>
         <v>66cce1b2-c3f3-4c17-a0c2-1ab7c4292c37, {"content":"Hola, ¿a qué hora te va bien para la compra?"}</v>
       </c>
-      <c r="G6" s="28" t="s">
-        <v>397</v>
-      </c>
-      <c r="H6" s="42" t="s">
+      <c r="G6" s="21" t="s">
+        <v>442</v>
+      </c>
+      <c r="H6" s="33" t="s">
         <v>70</v>
       </c>
-      <c r="I6" s="27" t="s">
-        <v>398</v>
-      </c>
-      <c r="J6" s="30"/>
+      <c r="I6" s="21" t="s">
+        <v>443</v>
+      </c>
+      <c r="J6" s="23"/>
     </row>
     <row r="7" ht="42.0" customHeight="1">
-      <c r="A7" s="43" t="s">
-        <v>399</v>
-      </c>
-      <c r="B7" s="25" t="s">
-        <v>400</v>
-      </c>
-      <c r="C7" s="44" t="s">
+      <c r="A7" s="34" t="s">
+        <v>444</v>
+      </c>
+      <c r="B7" s="20" t="s">
+        <v>445</v>
+      </c>
+      <c r="C7" s="35" t="s">
         <v>97</v>
       </c>
-      <c r="D7" s="25" t="s">
-        <v>396</v>
-      </c>
-      <c r="E7" s="24" t="s">
-        <v>147</v>
-      </c>
-      <c r="F7" s="28" t="str">
+      <c r="D7" s="20" t="s">
+        <v>441</v>
+      </c>
+      <c r="E7" s="20" t="s">
+        <v>193</v>
+      </c>
+      <c r="F7" s="21" t="str">
         <f>Variables!C15 &amp; ", {""content"":""Perfecto, me viene bien a las 10h""}"</f>
         <v>66cce1b2-c3f3-4c17-a0c2-1ab7c4292c37, {"content":"Perfecto, me viene bien a las 10h"}</v>
       </c>
-      <c r="G7" s="25" t="s">
-        <v>401</v>
-      </c>
-      <c r="H7" s="42" t="s">
+      <c r="G7" s="20" t="s">
+        <v>446</v>
+      </c>
+      <c r="H7" s="33" t="s">
         <v>70</v>
       </c>
-      <c r="I7" s="27" t="s">
-        <v>402</v>
-      </c>
-      <c r="J7" s="43"/>
+      <c r="I7" s="21" t="s">
+        <v>447</v>
+      </c>
+      <c r="J7" s="34"/>
     </row>
     <row r="8" ht="42.0" customHeight="1">
-      <c r="A8" s="30" t="s">
-        <v>403</v>
-      </c>
-      <c r="B8" s="28" t="s">
-        <v>404</v>
-      </c>
-      <c r="C8" s="46" t="s">
+      <c r="A8" s="23" t="s">
+        <v>448</v>
+      </c>
+      <c r="B8" s="21" t="s">
+        <v>449</v>
+      </c>
+      <c r="C8" s="43" t="s">
         <v>139</v>
       </c>
-      <c r="D8" s="28" t="s">
-        <v>396</v>
-      </c>
-      <c r="E8" s="27" t="s">
-        <v>147</v>
-      </c>
-      <c r="F8" s="28" t="str">
+      <c r="D8" s="21" t="s">
+        <v>441</v>
+      </c>
+      <c r="E8" s="21" t="s">
+        <v>193</v>
+      </c>
+      <c r="F8" s="21" t="str">
         <f>Variables!C15</f>
         <v>66cce1b2-c3f3-4c17-a0c2-1ab7c4292c37</v>
       </c>
-      <c r="G8" s="28" t="s">
-        <v>405</v>
-      </c>
-      <c r="H8" s="42" t="s">
+      <c r="G8" s="21" t="s">
+        <v>450</v>
+      </c>
+      <c r="H8" s="33" t="s">
         <v>70</v>
       </c>
-      <c r="I8" s="27" t="s">
-        <v>406</v>
-      </c>
-      <c r="J8" s="30"/>
+      <c r="I8" s="21" t="s">
+        <v>451</v>
+      </c>
+      <c r="J8" s="23"/>
     </row>
     <row r="9" ht="42.0" customHeight="1">
-      <c r="A9" s="43" t="s">
-        <v>407</v>
-      </c>
-      <c r="B9" s="25" t="s">
-        <v>408</v>
-      </c>
-      <c r="C9" s="47" t="s">
-        <v>160</v>
-      </c>
-      <c r="D9" s="25" t="s">
-        <v>409</v>
-      </c>
-      <c r="E9" s="24" t="s">
-        <v>147</v>
-      </c>
-      <c r="F9" s="25" t="str">
+      <c r="A9" s="34" t="s">
+        <v>452</v>
+      </c>
+      <c r="B9" s="20" t="s">
+        <v>453</v>
+      </c>
+      <c r="C9" s="44" t="s">
+        <v>206</v>
+      </c>
+      <c r="D9" s="20" t="s">
+        <v>454</v>
+      </c>
+      <c r="E9" s="20" t="s">
+        <v>193</v>
+      </c>
+      <c r="F9" s="20" t="str">
         <f>Variables!C15</f>
         <v>66cce1b2-c3f3-4c17-a0c2-1ab7c4292c37</v>
       </c>
-      <c r="G9" s="25" t="s">
-        <v>287</v>
-      </c>
-      <c r="H9" s="42" t="s">
+      <c r="G9" s="20" t="s">
+        <v>332</v>
+      </c>
+      <c r="H9" s="33" t="s">
         <v>70</v>
       </c>
-      <c r="I9" s="24" t="s">
-        <v>410</v>
-      </c>
-      <c r="J9" s="43"/>
+      <c r="I9" s="20" t="s">
+        <v>455</v>
+      </c>
+      <c r="J9" s="34"/>
     </row>
     <row r="10" ht="42.0" customHeight="1">
-      <c r="A10" s="30" t="s">
-        <v>411</v>
-      </c>
-      <c r="B10" s="28" t="s">
-        <v>412</v>
-      </c>
-      <c r="C10" s="65" t="s">
-        <v>285</v>
-      </c>
-      <c r="D10" s="28" t="s">
-        <v>413</v>
-      </c>
-      <c r="E10" s="27" t="s">
-        <v>147</v>
-      </c>
-      <c r="F10" s="28" t="str">
+      <c r="A10" s="23" t="s">
+        <v>456</v>
+      </c>
+      <c r="B10" s="21" t="s">
+        <v>457</v>
+      </c>
+      <c r="C10" s="56" t="s">
+        <v>330</v>
+      </c>
+      <c r="D10" s="21" t="s">
+        <v>458</v>
+      </c>
+      <c r="E10" s="21" t="s">
+        <v>193</v>
+      </c>
+      <c r="F10" s="21" t="str">
         <f>Variables!C15</f>
         <v>66cce1b2-c3f3-4c17-a0c2-1ab7c4292c37</v>
       </c>
-      <c r="G10" s="28" t="s">
-        <v>287</v>
-      </c>
-      <c r="H10" s="42" t="s">
+      <c r="G10" s="21" t="s">
+        <v>332</v>
+      </c>
+      <c r="H10" s="33" t="s">
         <v>70</v>
       </c>
-      <c r="I10" s="27" t="s">
-        <v>414</v>
-      </c>
-      <c r="J10" s="30"/>
+      <c r="I10" s="21" t="s">
+        <v>459</v>
+      </c>
+      <c r="J10" s="23"/>
     </row>
     <row r="11" ht="42.0" customHeight="1">
-      <c r="A11" s="43" t="s">
-        <v>415</v>
-      </c>
-      <c r="B11" s="24" t="s">
-        <v>416</v>
-      </c>
-      <c r="C11" s="64" t="s">
-        <v>285</v>
-      </c>
-      <c r="D11" s="25" t="s">
-        <v>413</v>
-      </c>
-      <c r="E11" s="24" t="s">
-        <v>147</v>
-      </c>
-      <c r="F11" s="25" t="str">
+      <c r="A11" s="34" t="s">
+        <v>460</v>
+      </c>
+      <c r="B11" s="20" t="s">
+        <v>461</v>
+      </c>
+      <c r="C11" s="55" t="s">
+        <v>330</v>
+      </c>
+      <c r="D11" s="20" t="s">
+        <v>458</v>
+      </c>
+      <c r="E11" s="20" t="s">
+        <v>193</v>
+      </c>
+      <c r="F11" s="20" t="str">
         <f>Variables!C15</f>
         <v>66cce1b2-c3f3-4c17-a0c2-1ab7c4292c37</v>
       </c>
-      <c r="G11" s="25" t="s">
-        <v>172</v>
-      </c>
-      <c r="H11" s="42" t="s">
+      <c r="G11" s="20" t="s">
+        <v>218</v>
+      </c>
+      <c r="H11" s="33" t="s">
         <v>70</v>
       </c>
-      <c r="I11" s="24" t="s">
-        <v>417</v>
-      </c>
-      <c r="J11" s="43"/>
+      <c r="I11" s="20" t="s">
+        <v>462</v>
+      </c>
+      <c r="J11" s="34"/>
     </row>
     <row r="12" ht="18.0" customHeight="1">
-      <c r="A12" s="38" t="s">
-        <v>418</v>
-      </c>
-      <c r="B12" s="39"/>
-      <c r="C12" s="39"/>
-      <c r="D12" s="39"/>
-      <c r="E12" s="39"/>
-      <c r="F12" s="39"/>
-      <c r="G12" s="39"/>
-      <c r="H12" s="39"/>
-      <c r="I12" s="39"/>
-      <c r="J12" s="40"/>
+      <c r="A12" s="29" t="s">
+        <v>463</v>
+      </c>
+      <c r="B12" s="30"/>
+      <c r="C12" s="30"/>
+      <c r="D12" s="30"/>
+      <c r="E12" s="30"/>
+      <c r="F12" s="30"/>
+      <c r="G12" s="30"/>
+      <c r="H12" s="30"/>
+      <c r="I12" s="30"/>
+      <c r="J12" s="31"/>
     </row>
     <row r="13" ht="42.0" customHeight="1">
-      <c r="A13" s="43" t="s">
-        <v>419</v>
-      </c>
-      <c r="B13" s="24" t="s">
-        <v>420</v>
-      </c>
-      <c r="C13" s="45" t="s">
+      <c r="A13" s="34" t="s">
+        <v>464</v>
+      </c>
+      <c r="B13" s="20" t="s">
+        <v>465</v>
+      </c>
+      <c r="C13" s="36" t="s">
         <v>139</v>
       </c>
-      <c r="D13" s="25" t="s">
-        <v>421</v>
-      </c>
-      <c r="E13" s="24" t="s">
-        <v>147</v>
-      </c>
-      <c r="F13" s="25" t="s">
+      <c r="D13" s="20" t="s">
+        <v>466</v>
+      </c>
+      <c r="E13" s="20" t="s">
+        <v>193</v>
+      </c>
+      <c r="F13" s="20" t="s">
         <v>141</v>
       </c>
-      <c r="G13" s="25" t="s">
-        <v>422</v>
-      </c>
-      <c r="H13" s="42" t="s">
+      <c r="G13" s="20" t="s">
+        <v>467</v>
+      </c>
+      <c r="H13" s="33" t="s">
         <v>70</v>
       </c>
-      <c r="I13" s="24" t="s">
-        <v>423</v>
-      </c>
-      <c r="J13" s="43"/>
+      <c r="I13" s="20" t="s">
+        <v>468</v>
+      </c>
+      <c r="J13" s="34"/>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>
     <row r="22" ht="15.75" customHeight="1"/>
@@ -4673,448 +4777,447 @@
     <col customWidth="1" min="8" max="8" width="16.0"/>
     <col customWidth="1" min="9" max="9" width="40.0"/>
     <col customWidth="1" min="10" max="10" width="14.0"/>
-    <col customWidth="1" min="11" max="26" width="8.71"/>
   </cols>
   <sheetData>
     <row r="1" ht="24.0" customHeight="1">
-      <c r="A1" s="35" t="s">
-        <v>424</v>
-      </c>
-      <c r="B1" s="36"/>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36"/>
-      <c r="E1" s="36"/>
-      <c r="F1" s="36"/>
-      <c r="G1" s="36"/>
-      <c r="H1" s="36"/>
-      <c r="I1" s="36"/>
-      <c r="J1" s="37"/>
+      <c r="A1" s="27" t="s">
+        <v>469</v>
+      </c>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+      <c r="H1" s="28"/>
+      <c r="I1" s="28"/>
+      <c r="J1" s="28"/>
     </row>
     <row r="2" ht="21.75" customHeight="1">
-      <c r="A2" s="29" t="s">
+      <c r="A2" s="22" t="s">
         <v>85</v>
       </c>
-      <c r="B2" s="29" t="s">
+      <c r="B2" s="22" t="s">
         <v>86</v>
       </c>
-      <c r="C2" s="29" t="s">
+      <c r="C2" s="22" t="s">
         <v>87</v>
       </c>
-      <c r="D2" s="29" t="s">
+      <c r="D2" s="22" t="s">
         <v>88</v>
       </c>
-      <c r="E2" s="29" t="s">
+      <c r="E2" s="22" t="s">
         <v>89</v>
       </c>
-      <c r="F2" s="29" t="s">
+      <c r="F2" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="G2" s="29" t="s">
+      <c r="G2" s="22" t="s">
         <v>90</v>
       </c>
-      <c r="H2" s="29" t="s">
+      <c r="H2" s="22" t="s">
         <v>91</v>
       </c>
-      <c r="I2" s="29" t="s">
+      <c r="I2" s="22" t="s">
         <v>92</v>
       </c>
-      <c r="J2" s="29" t="s">
+      <c r="J2" s="22" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="3" ht="18.0" customHeight="1">
-      <c r="A3" s="38" t="s">
-        <v>425</v>
-      </c>
-      <c r="B3" s="39"/>
-      <c r="C3" s="39"/>
-      <c r="D3" s="39"/>
-      <c r="E3" s="39"/>
-      <c r="F3" s="39"/>
-      <c r="G3" s="39"/>
-      <c r="H3" s="39"/>
-      <c r="I3" s="39"/>
-      <c r="J3" s="40"/>
+      <c r="A3" s="29" t="s">
+        <v>470</v>
+      </c>
+      <c r="B3" s="30"/>
+      <c r="C3" s="30"/>
+      <c r="D3" s="30"/>
+      <c r="E3" s="30"/>
+      <c r="F3" s="30"/>
+      <c r="G3" s="30"/>
+      <c r="H3" s="30"/>
+      <c r="I3" s="30"/>
+      <c r="J3" s="31"/>
     </row>
     <row r="4" ht="42.0" customHeight="1">
-      <c r="A4" s="30" t="s">
-        <v>426</v>
-      </c>
-      <c r="B4" s="28" t="s">
-        <v>427</v>
-      </c>
-      <c r="C4" s="41" t="s">
+      <c r="A4" s="23" t="s">
+        <v>471</v>
+      </c>
+      <c r="B4" s="21" t="s">
+        <v>472</v>
+      </c>
+      <c r="C4" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="D4" s="28" t="s">
-        <v>428</v>
-      </c>
-      <c r="E4" s="27" t="s">
-        <v>147</v>
-      </c>
-      <c r="F4" s="28" t="str">
+      <c r="D4" s="21" t="s">
+        <v>473</v>
+      </c>
+      <c r="E4" s="21" t="s">
+        <v>193</v>
+      </c>
+      <c r="F4" s="21" t="str">
         <f>Variables!C8</f>
         <v>c7cf918d-7e04-4104-9790-fa5bb9d3756d</v>
       </c>
-      <c r="G4" s="28" t="s">
-        <v>429</v>
-      </c>
-      <c r="H4" s="42" t="s">
+      <c r="G4" s="21" t="s">
+        <v>474</v>
+      </c>
+      <c r="H4" s="33" t="s">
         <v>70</v>
       </c>
-      <c r="I4" s="28" t="s">
-        <v>430</v>
-      </c>
-      <c r="J4" s="30"/>
+      <c r="I4" s="21" t="s">
+        <v>475</v>
+      </c>
+      <c r="J4" s="23"/>
     </row>
     <row r="5" ht="18.0" customHeight="1">
-      <c r="A5" s="38" t="s">
-        <v>431</v>
-      </c>
-      <c r="B5" s="39"/>
-      <c r="C5" s="39"/>
-      <c r="D5" s="39"/>
-      <c r="E5" s="39"/>
-      <c r="F5" s="39"/>
-      <c r="G5" s="39"/>
-      <c r="H5" s="39"/>
-      <c r="I5" s="39"/>
-      <c r="J5" s="40"/>
+      <c r="A5" s="29" t="s">
+        <v>476</v>
+      </c>
+      <c r="B5" s="30"/>
+      <c r="C5" s="30"/>
+      <c r="D5" s="30"/>
+      <c r="E5" s="30"/>
+      <c r="F5" s="30"/>
+      <c r="G5" s="30"/>
+      <c r="H5" s="30"/>
+      <c r="I5" s="30"/>
+      <c r="J5" s="31"/>
     </row>
     <row r="6" ht="42.0" customHeight="1">
-      <c r="A6" s="30" t="s">
-        <v>432</v>
-      </c>
-      <c r="B6" s="28" t="s">
-        <v>433</v>
-      </c>
-      <c r="C6" s="41" t="s">
+      <c r="A6" s="23" t="s">
+        <v>477</v>
+      </c>
+      <c r="B6" s="21" t="s">
+        <v>478</v>
+      </c>
+      <c r="C6" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="D6" s="28" t="s">
-        <v>434</v>
-      </c>
-      <c r="E6" s="27" t="s">
-        <v>147</v>
-      </c>
-      <c r="F6" s="28" t="str">
+      <c r="D6" s="21" t="s">
+        <v>479</v>
+      </c>
+      <c r="E6" s="21" t="s">
+        <v>193</v>
+      </c>
+      <c r="F6" s="21" t="str">
         <f>"{""targetId"":""" &amp; Variables!C5 &amp; """,""helpRequestId"":""" &amp; Variables!C8 &amp; """,""rating"":5,""comment"":""Excelente voluntario, muy puntual y atento""}"</f>
         <v>{"targetId":"69ad88c5-bd50-46e1-824a-0625dabf99ea","helpRequestId":"c7cf918d-7e04-4104-9790-fa5bb9d3756d","rating":5,"comment":"Excelente voluntario, muy puntual y atento"}</v>
       </c>
-      <c r="G6" s="28" t="s">
-        <v>435</v>
-      </c>
-      <c r="H6" s="42" t="s">
+      <c r="G6" s="21" t="s">
+        <v>480</v>
+      </c>
+      <c r="H6" s="33" t="s">
         <v>70</v>
       </c>
-      <c r="I6" s="28" t="s">
-        <v>436</v>
-      </c>
-      <c r="J6" s="30"/>
+      <c r="I6" s="21" t="s">
+        <v>481</v>
+      </c>
+      <c r="J6" s="23"/>
     </row>
     <row r="7" ht="42.0" customHeight="1">
-      <c r="A7" s="43" t="s">
-        <v>437</v>
-      </c>
-      <c r="B7" s="25" t="s">
-        <v>438</v>
-      </c>
-      <c r="C7" s="44" t="s">
+      <c r="A7" s="34" t="s">
+        <v>482</v>
+      </c>
+      <c r="B7" s="20" t="s">
+        <v>483</v>
+      </c>
+      <c r="C7" s="35" t="s">
         <v>97</v>
       </c>
-      <c r="D7" s="25" t="s">
-        <v>434</v>
-      </c>
-      <c r="E7" s="24" t="s">
-        <v>147</v>
-      </c>
-      <c r="F7" s="25" t="str">
+      <c r="D7" s="20" t="s">
+        <v>479</v>
+      </c>
+      <c r="E7" s="20" t="s">
+        <v>193</v>
+      </c>
+      <c r="F7" s="20" t="str">
         <f>"{""targetId"":""" &amp; Variables!C7 &amp; """,""helpRequestId"":""" &amp; Variables!C8 &amp; """,""rating"":4,""comment"":""Todo muy claro y organizado""}"</f>
         <v>{"targetId":"f08371a0-756b-47d7-b714-533edd782035","helpRequestId":"c7cf918d-7e04-4104-9790-fa5bb9d3756d","rating":4,"comment":"Todo muy claro y organizado"}</v>
       </c>
-      <c r="G7" s="25" t="s">
-        <v>439</v>
-      </c>
-      <c r="H7" s="42" t="s">
+      <c r="G7" s="20" t="s">
+        <v>484</v>
+      </c>
+      <c r="H7" s="33" t="s">
         <v>70</v>
       </c>
-      <c r="I7" s="24" t="s">
-        <v>440</v>
-      </c>
-      <c r="J7" s="43"/>
+      <c r="I7" s="20" t="s">
+        <v>485</v>
+      </c>
+      <c r="J7" s="34"/>
     </row>
     <row r="8" ht="42.0" customHeight="1">
-      <c r="A8" s="30" t="s">
-        <v>441</v>
-      </c>
-      <c r="B8" s="28" t="s">
-        <v>442</v>
-      </c>
-      <c r="C8" s="41" t="s">
+      <c r="A8" s="23" t="s">
+        <v>486</v>
+      </c>
+      <c r="B8" s="21" t="s">
+        <v>487</v>
+      </c>
+      <c r="C8" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="D8" s="28" t="s">
-        <v>434</v>
-      </c>
-      <c r="E8" s="27" t="s">
-        <v>147</v>
-      </c>
-      <c r="F8" s="28" t="str">
+      <c r="D8" s="21" t="s">
+        <v>479</v>
+      </c>
+      <c r="E8" s="21" t="s">
+        <v>193</v>
+      </c>
+      <c r="F8" s="21" t="str">
         <f>"{""targetId"":""" &amp; Variables!C5 &amp; """,""donationId"":""" &amp; Variables!C11 &amp; """,""rating"":5,""comment"":""Recogió la donación perfectamente""}"</f>
         <v>{"targetId":"69ad88c5-bd50-46e1-824a-0625dabf99ea","donationId":"8396e74a-7bc5-4793-b7c4-bd79b3b7932b","rating":5,"comment":"Recogió la donación perfectamente"}</v>
       </c>
-      <c r="G8" s="28" t="s">
-        <v>443</v>
-      </c>
-      <c r="H8" s="42" t="s">
+      <c r="G8" s="21" t="s">
+        <v>488</v>
+      </c>
+      <c r="H8" s="33" t="s">
         <v>70</v>
       </c>
-      <c r="I8" s="27" t="s">
-        <v>440</v>
-      </c>
-      <c r="J8" s="30"/>
+      <c r="I8" s="21" t="s">
+        <v>485</v>
+      </c>
+      <c r="J8" s="23"/>
     </row>
     <row r="9" ht="18.0" customHeight="1">
-      <c r="A9" s="38" t="s">
-        <v>444</v>
-      </c>
-      <c r="B9" s="39"/>
-      <c r="C9" s="39"/>
-      <c r="D9" s="39"/>
-      <c r="E9" s="39"/>
-      <c r="F9" s="39"/>
-      <c r="G9" s="39"/>
-      <c r="H9" s="39"/>
-      <c r="I9" s="39"/>
-      <c r="J9" s="40"/>
+      <c r="A9" s="29" t="s">
+        <v>489</v>
+      </c>
+      <c r="B9" s="30"/>
+      <c r="C9" s="30"/>
+      <c r="D9" s="30"/>
+      <c r="E9" s="30"/>
+      <c r="F9" s="30"/>
+      <c r="G9" s="30"/>
+      <c r="H9" s="30"/>
+      <c r="I9" s="30"/>
+      <c r="J9" s="31"/>
     </row>
     <row r="10" ht="42.0" customHeight="1">
-      <c r="A10" s="30" t="s">
-        <v>445</v>
-      </c>
-      <c r="B10" s="27" t="s">
-        <v>446</v>
-      </c>
-      <c r="C10" s="41" t="s">
+      <c r="A10" s="23" t="s">
+        <v>490</v>
+      </c>
+      <c r="B10" s="21" t="s">
+        <v>491</v>
+      </c>
+      <c r="C10" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="D10" s="28" t="s">
-        <v>434</v>
-      </c>
-      <c r="E10" s="27" t="s">
-        <v>147</v>
-      </c>
-      <c r="F10" s="28" t="str">
+      <c r="D10" s="21" t="s">
+        <v>479</v>
+      </c>
+      <c r="E10" s="21" t="s">
+        <v>193</v>
+      </c>
+      <c r="F10" s="21" t="str">
         <f>"{""targetId"":""" &amp; Variables!C5 &amp; """,""helpRequestId"":""" &amp; Variables!C8 &amp; """,""rating"":3,""comment"":""Segunda review""}"</f>
         <v>{"targetId":"69ad88c5-bd50-46e1-824a-0625dabf99ea","helpRequestId":"c7cf918d-7e04-4104-9790-fa5bb9d3756d","rating":3,"comment":"Segunda review"}</v>
       </c>
-      <c r="G10" s="28" t="s">
-        <v>447</v>
-      </c>
-      <c r="H10" s="42" t="s">
+      <c r="G10" s="21" t="s">
+        <v>492</v>
+      </c>
+      <c r="H10" s="33" t="s">
         <v>70</v>
       </c>
-      <c r="I10" s="27" t="s">
-        <v>448</v>
-      </c>
-      <c r="J10" s="30"/>
+      <c r="I10" s="21" t="s">
+        <v>493</v>
+      </c>
+      <c r="J10" s="23"/>
     </row>
     <row r="11" ht="42.0" customHeight="1">
-      <c r="A11" s="43" t="s">
-        <v>449</v>
-      </c>
-      <c r="B11" s="24" t="s">
-        <v>450</v>
-      </c>
-      <c r="C11" s="44" t="s">
+      <c r="A11" s="34" t="s">
+        <v>494</v>
+      </c>
+      <c r="B11" s="20" t="s">
+        <v>495</v>
+      </c>
+      <c r="C11" s="35" t="s">
         <v>97</v>
       </c>
-      <c r="D11" s="25" t="s">
-        <v>434</v>
-      </c>
-      <c r="E11" s="24" t="s">
-        <v>147</v>
-      </c>
-      <c r="F11" s="25" t="str">
+      <c r="D11" s="20" t="s">
+        <v>479</v>
+      </c>
+      <c r="E11" s="20" t="s">
+        <v>193</v>
+      </c>
+      <c r="F11" s="20" t="str">
         <f>"{""targetId"":""" &amp; Variables!C6 &amp; """,""donationId"":""" &amp; Variables!C10 &amp; """,""rating"":3,""comment"":""Test""}"</f>
         <v>{"targetId":"beeaa200-52c6-44fa-9333-b4f6f375e314","donationId":"4a2c7d53-9a34-4c40-9e8f-c8972db67211","rating":3,"comment":"Test"}</v>
       </c>
-      <c r="G11" s="25" t="s">
-        <v>451</v>
-      </c>
-      <c r="H11" s="42" t="s">
+      <c r="G11" s="20" t="s">
+        <v>496</v>
+      </c>
+      <c r="H11" s="33" t="s">
         <v>70</v>
       </c>
-      <c r="I11" s="25" t="s">
-        <v>452</v>
-      </c>
-      <c r="J11" s="43"/>
+      <c r="I11" s="20" t="s">
+        <v>497</v>
+      </c>
+      <c r="J11" s="34"/>
     </row>
     <row r="12" ht="42.0" customHeight="1">
-      <c r="A12" s="30" t="s">
-        <v>453</v>
-      </c>
-      <c r="B12" s="27" t="s">
-        <v>454</v>
-      </c>
-      <c r="C12" s="41" t="s">
+      <c r="A12" s="23" t="s">
+        <v>498</v>
+      </c>
+      <c r="B12" s="21" t="s">
+        <v>499</v>
+      </c>
+      <c r="C12" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="D12" s="28" t="s">
-        <v>434</v>
-      </c>
-      <c r="E12" s="27" t="s">
-        <v>147</v>
-      </c>
-      <c r="F12" s="28" t="str">
+      <c r="D12" s="21" t="s">
+        <v>479</v>
+      </c>
+      <c r="E12" s="21" t="s">
+        <v>193</v>
+      </c>
+      <c r="F12" s="21" t="str">
         <f>"{""targetId"":""" &amp; Variables!C5 &amp; """,""helpRequestId"":""" &amp; Variables!C8 &amp; """,""rating"":4,""comment"":""Test""}"</f>
         <v>{"targetId":"69ad88c5-bd50-46e1-824a-0625dabf99ea","helpRequestId":"c7cf918d-7e04-4104-9790-fa5bb9d3756d","rating":4,"comment":"Test"}</v>
       </c>
-      <c r="G12" s="28" t="s">
-        <v>455</v>
-      </c>
-      <c r="H12" s="42" t="s">
+      <c r="G12" s="21" t="s">
+        <v>500</v>
+      </c>
+      <c r="H12" s="33" t="s">
         <v>70</v>
       </c>
-      <c r="I12" s="28" t="s">
-        <v>456</v>
-      </c>
-      <c r="J12" s="30"/>
+      <c r="I12" s="21" t="s">
+        <v>501</v>
+      </c>
+      <c r="J12" s="23"/>
     </row>
     <row r="13" ht="18.0" customHeight="1">
-      <c r="A13" s="38" t="s">
-        <v>190</v>
-      </c>
-      <c r="B13" s="39"/>
-      <c r="C13" s="39"/>
-      <c r="D13" s="39"/>
-      <c r="E13" s="39"/>
-      <c r="F13" s="39"/>
-      <c r="G13" s="39"/>
-      <c r="H13" s="39"/>
-      <c r="I13" s="39"/>
-      <c r="J13" s="40"/>
+      <c r="A13" s="29" t="s">
+        <v>236</v>
+      </c>
+      <c r="B13" s="30"/>
+      <c r="C13" s="30"/>
+      <c r="D13" s="30"/>
+      <c r="E13" s="30"/>
+      <c r="F13" s="30"/>
+      <c r="G13" s="30"/>
+      <c r="H13" s="30"/>
+      <c r="I13" s="30"/>
+      <c r="J13" s="31"/>
     </row>
     <row r="14" ht="42.0" customHeight="1">
-      <c r="A14" s="30" t="s">
-        <v>457</v>
-      </c>
-      <c r="B14" s="28" t="s">
-        <v>458</v>
-      </c>
-      <c r="C14" s="46" t="s">
+      <c r="A14" s="23" t="s">
+        <v>502</v>
+      </c>
+      <c r="B14" s="21" t="s">
+        <v>503</v>
+      </c>
+      <c r="C14" s="43" t="s">
         <v>139</v>
       </c>
-      <c r="D14" s="28" t="s">
-        <v>459</v>
-      </c>
-      <c r="E14" s="27" t="s">
-        <v>147</v>
-      </c>
-      <c r="F14" s="28" t="str">
+      <c r="D14" s="21" t="s">
+        <v>504</v>
+      </c>
+      <c r="E14" s="21" t="s">
+        <v>193</v>
+      </c>
+      <c r="F14" s="21" t="str">
         <f>Variables!C5</f>
         <v>69ad88c5-bd50-46e1-824a-0625dabf99ea</v>
       </c>
-      <c r="G14" s="28" t="s">
-        <v>460</v>
-      </c>
-      <c r="H14" s="42" t="s">
+      <c r="G14" s="21" t="s">
+        <v>505</v>
+      </c>
+      <c r="H14" s="33" t="s">
         <v>70</v>
       </c>
-      <c r="I14" s="28" t="s">
-        <v>461</v>
-      </c>
-      <c r="J14" s="30"/>
+      <c r="I14" s="21" t="s">
+        <v>506</v>
+      </c>
+      <c r="J14" s="23"/>
     </row>
     <row r="15" ht="42.0" customHeight="1">
-      <c r="A15" s="43" t="s">
-        <v>462</v>
-      </c>
-      <c r="B15" s="25" t="s">
-        <v>463</v>
-      </c>
-      <c r="C15" s="47" t="s">
-        <v>160</v>
-      </c>
-      <c r="D15" s="25" t="s">
-        <v>464</v>
-      </c>
-      <c r="E15" s="24" t="s">
-        <v>147</v>
-      </c>
-      <c r="F15" s="25" t="s">
-        <v>465</v>
-      </c>
-      <c r="G15" s="25" t="s">
-        <v>466</v>
-      </c>
-      <c r="H15" s="42" t="s">
+      <c r="A15" s="34" t="s">
+        <v>507</v>
+      </c>
+      <c r="B15" s="20" t="s">
+        <v>508</v>
+      </c>
+      <c r="C15" s="44" t="s">
+        <v>206</v>
+      </c>
+      <c r="D15" s="20" t="s">
+        <v>509</v>
+      </c>
+      <c r="E15" s="20" t="s">
+        <v>193</v>
+      </c>
+      <c r="F15" s="20" t="s">
+        <v>510</v>
+      </c>
+      <c r="G15" s="20" t="s">
+        <v>511</v>
+      </c>
+      <c r="H15" s="33" t="s">
         <v>70</v>
       </c>
-      <c r="I15" s="25" t="s">
-        <v>461</v>
-      </c>
-      <c r="J15" s="43"/>
+      <c r="I15" s="20" t="s">
+        <v>506</v>
+      </c>
+      <c r="J15" s="34"/>
     </row>
     <row r="16" ht="42.0" customHeight="1">
-      <c r="A16" s="30" t="s">
-        <v>467</v>
-      </c>
-      <c r="B16" s="27" t="s">
-        <v>468</v>
-      </c>
-      <c r="C16" s="48" t="s">
-        <v>160</v>
-      </c>
-      <c r="D16" s="28" t="s">
-        <v>464</v>
-      </c>
-      <c r="E16" s="27" t="s">
-        <v>147</v>
-      </c>
-      <c r="F16" s="28" t="s">
-        <v>469</v>
-      </c>
-      <c r="G16" s="27" t="s">
+      <c r="A16" s="23" t="s">
+        <v>512</v>
+      </c>
+      <c r="B16" s="21" t="s">
+        <v>513</v>
+      </c>
+      <c r="C16" s="45" t="s">
+        <v>206</v>
+      </c>
+      <c r="D16" s="21" t="s">
+        <v>509</v>
+      </c>
+      <c r="E16" s="21" t="s">
+        <v>193</v>
+      </c>
+      <c r="F16" s="21" t="s">
+        <v>514</v>
+      </c>
+      <c r="G16" s="21" t="s">
         <v>112</v>
       </c>
-      <c r="H16" s="42" t="s">
+      <c r="H16" s="33" t="s">
         <v>70</v>
       </c>
-      <c r="I16" s="28" t="s">
-        <v>470</v>
-      </c>
-      <c r="J16" s="30"/>
+      <c r="I16" s="21" t="s">
+        <v>515</v>
+      </c>
+      <c r="J16" s="23"/>
     </row>
     <row r="17" ht="42.0" customHeight="1">
-      <c r="A17" s="43" t="s">
-        <v>471</v>
-      </c>
-      <c r="B17" s="25" t="s">
-        <v>472</v>
-      </c>
-      <c r="C17" s="64" t="s">
-        <v>285</v>
-      </c>
-      <c r="D17" s="25" t="s">
-        <v>464</v>
-      </c>
-      <c r="E17" s="24" t="s">
-        <v>147</v>
-      </c>
-      <c r="F17" s="25" t="s">
+      <c r="A17" s="34" t="s">
+        <v>516</v>
+      </c>
+      <c r="B17" s="20" t="s">
+        <v>517</v>
+      </c>
+      <c r="C17" s="55" t="s">
+        <v>330</v>
+      </c>
+      <c r="D17" s="20" t="s">
+        <v>509</v>
+      </c>
+      <c r="E17" s="20" t="s">
+        <v>193</v>
+      </c>
+      <c r="F17" s="20" t="s">
         <v>141</v>
       </c>
-      <c r="G17" s="25" t="s">
-        <v>473</v>
-      </c>
-      <c r="H17" s="42" t="s">
+      <c r="G17" s="20" t="s">
+        <v>518</v>
+      </c>
+      <c r="H17" s="33" t="s">
         <v>70</v>
       </c>
-      <c r="I17" s="25" t="s">
-        <v>474</v>
-      </c>
-      <c r="J17" s="43"/>
+      <c r="I17" s="20" t="s">
+        <v>519</v>
+      </c>
+      <c r="J17" s="34"/>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>
     <row r="22" ht="15.75" customHeight="1"/>
@@ -6144,7 +6247,6 @@
     <col customWidth="1" min="4" max="4" width="40.0"/>
     <col customWidth="1" min="5" max="6" width="8.71"/>
     <col customWidth="1" min="7" max="7" width="41.43"/>
-    <col customWidth="1" min="8" max="25" width="8.71"/>
   </cols>
   <sheetData>
     <row r="2" ht="24.0" customHeight="1">
@@ -6162,167 +6264,167 @@
       <c r="D4" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="F4" s="11" t="s">
+      <c r="F4" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="G4" s="12" t="s">
+      <c r="G4" s="11" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="5" ht="18.0" customHeight="1">
-      <c r="B5" s="13" t="s">
+      <c r="B5" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="C5" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="D5" s="15" t="s">
+      <c r="D5" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="F5" s="16" t="s">
+      <c r="F5" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="G5" s="17" t="s">
+      <c r="G5" s="15" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="6" ht="18.0" customHeight="1">
-      <c r="B6" s="18" t="s">
+      <c r="B6" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="C6" s="19" t="s">
+      <c r="C6" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="D6" s="20" t="s">
+      <c r="D6" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="F6" s="21" t="s">
+      <c r="F6" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="G6" s="22" t="s">
+      <c r="G6" s="19" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="7" ht="18.0" customHeight="1">
-      <c r="B7" s="13" t="s">
+      <c r="B7" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="C7" s="14" t="s">
+      <c r="C7" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="D7" s="15" t="s">
+      <c r="D7" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="F7" s="16" t="s">
+      <c r="F7" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="G7" s="17" t="s">
+      <c r="G7" s="15" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="8" ht="18.0" customHeight="1">
-      <c r="B8" s="23" t="s">
+      <c r="B8" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="C8" s="24" t="s">
+      <c r="C8" s="20" t="s">
         <v>41</v>
       </c>
-      <c r="D8" s="25" t="s">
+      <c r="D8" s="20" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="9" ht="18.0" customHeight="1">
-      <c r="B9" s="26" t="s">
+      <c r="B9" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="C9" s="27" t="s">
+      <c r="C9" s="21" t="s">
         <v>44</v>
       </c>
-      <c r="D9" s="28" t="s">
+      <c r="D9" s="21" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="10" ht="18.0" customHeight="1">
-      <c r="B10" s="23" t="s">
+      <c r="B10" s="18" t="s">
         <v>46</v>
       </c>
-      <c r="C10" s="24" t="s">
+      <c r="C10" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="D10" s="25" t="s">
+      <c r="D10" s="20" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="11" ht="18.0" customHeight="1">
-      <c r="B11" s="26" t="s">
+      <c r="B11" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="C11" s="27" t="s">
+      <c r="C11" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="D11" s="28" t="s">
+      <c r="D11" s="21" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="12" ht="18.0" customHeight="1">
-      <c r="B12" s="21" t="s">
+      <c r="B12" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="C12" s="24" t="s">
+      <c r="C12" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="D12" s="25" t="s">
+      <c r="D12" s="20" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="13" ht="18.0" customHeight="1">
-      <c r="B13" s="21" t="s">
+      <c r="B13" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="C13" s="25" t="s">
+      <c r="C13" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="D13" s="25" t="s">
+      <c r="D13" s="20" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="14" ht="18.0" customHeight="1">
-      <c r="B14" s="26" t="s">
+      <c r="B14" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="C14" s="28"/>
-      <c r="D14" s="28" t="s">
+      <c r="C14" s="21"/>
+      <c r="D14" s="21" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="15" ht="18.0" customHeight="1">
-      <c r="B15" s="23" t="s">
+      <c r="B15" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="C15" s="24" t="s">
+      <c r="C15" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="D15" s="25" t="s">
+      <c r="D15" s="20" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="16" ht="18.0" customHeight="1">
-      <c r="B16" s="26" t="s">
+      <c r="B16" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="C16" s="28"/>
-      <c r="D16" s="28" t="s">
+      <c r="C16" s="21"/>
+      <c r="D16" s="21" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="17" ht="18.0" customHeight="1">
-      <c r="B17" s="23" t="s">
+      <c r="B17" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="C17" s="24" t="s">
+      <c r="C17" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="D17" s="25" t="s">
+      <c r="D17" s="20" t="s">
         <v>66</v>
       </c>
     </row>
@@ -7301,6 +7403,14 @@
     <row r="990" ht="15.75" customHeight="1"/>
     <row r="991" ht="15.75" customHeight="1"/>
     <row r="992" ht="15.75" customHeight="1"/>
+    <row r="993" ht="15.75" customHeight="1"/>
+    <row r="994" ht="15.75" customHeight="1"/>
+    <row r="995" ht="15.75" customHeight="1"/>
+    <row r="996" ht="15.75" customHeight="1"/>
+    <row r="997" ht="15.75" customHeight="1"/>
+    <row r="998" ht="15.75" customHeight="1"/>
+    <row r="999" ht="15.75" customHeight="1"/>
+    <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B2:D2"/>
@@ -7324,7 +7434,6 @@
     <col customWidth="1" min="3" max="5" width="14.0"/>
     <col customWidth="1" min="6" max="6" width="22.0"/>
     <col customWidth="1" min="7" max="7" width="11.71"/>
-    <col customWidth="1" min="8" max="26" width="8.71"/>
   </cols>
   <sheetData>
     <row r="2" ht="24.0" customHeight="1">
@@ -7333,252 +7442,252 @@
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="29" t="s">
+      <c r="B4" s="22" t="s">
         <v>68</v>
       </c>
-      <c r="C4" s="29" t="s">
+      <c r="C4" s="22" t="s">
         <v>69</v>
       </c>
-      <c r="D4" s="29" t="s">
+      <c r="D4" s="22" t="s">
         <v>70</v>
       </c>
-      <c r="E4" s="29" t="s">
+      <c r="E4" s="22" t="s">
         <v>71</v>
       </c>
-      <c r="F4" s="29" t="s">
+      <c r="F4" s="22" t="s">
         <v>72</v>
       </c>
-      <c r="G4" s="29" t="s">
+      <c r="G4" s="22" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="5" ht="18.0" customHeight="1">
-      <c r="B5" s="26" t="s">
+      <c r="B5" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="C5" s="30">
+      <c r="C5" s="23">
         <f>COUNTIF(Auth!A:A,"A-*")</f>
-        <v>11</v>
-      </c>
-      <c r="D5" s="31">
+        <v>21</v>
+      </c>
+      <c r="D5" s="23">
         <f>COUNTIF(Auth!H:H,D4)</f>
-        <v>11</v>
-      </c>
-      <c r="E5" s="30">
+        <v>21</v>
+      </c>
+      <c r="E5" s="23">
         <f>COUNTIF(Auth!H:H,E4)</f>
         <v>0</v>
       </c>
-      <c r="F5" s="30">
+      <c r="F5" s="23">
         <f>COUNTIF(Auth!H:H,F4)</f>
         <v>0</v>
       </c>
-      <c r="G5" s="30">
+      <c r="G5" s="23">
         <f t="shared" ref="G5:G13" si="1">(D5/C5) * 100</f>
         <v>100</v>
       </c>
     </row>
     <row r="6" ht="18.0" customHeight="1">
-      <c r="B6" s="23" t="s">
+      <c r="B6" s="18" t="s">
         <v>75</v>
       </c>
-      <c r="C6" s="30">
+      <c r="C6" s="23">
         <f>COUNTIF(Users!A:A,"U-*")</f>
         <v>6</v>
       </c>
-      <c r="D6" s="31">
+      <c r="D6" s="23">
         <f>COUNTIF(Users!H:H,D4)</f>
         <v>6</v>
       </c>
-      <c r="E6" s="31">
+      <c r="E6" s="23">
         <f>COUNTIF(Users!H:H,E4)</f>
         <v>0</v>
       </c>
-      <c r="F6" s="31">
+      <c r="F6" s="23">
         <f>COUNTIF(Users!H:H,F4)</f>
         <v>0</v>
       </c>
-      <c r="G6" s="30">
+      <c r="G6" s="23">
         <f t="shared" si="1"/>
         <v>100</v>
       </c>
     </row>
     <row r="7" ht="18.0" customHeight="1">
-      <c r="B7" s="26" t="s">
+      <c r="B7" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="C7" s="30">
+      <c r="C7" s="23">
         <f>COUNTIF(Volunteers!A:A,"V-*")</f>
         <v>8</v>
       </c>
-      <c r="D7" s="31">
+      <c r="D7" s="23">
         <f>COUNTIF(Volunteers!H:H,D4)</f>
         <v>8</v>
       </c>
-      <c r="E7" s="30">
+      <c r="E7" s="23">
         <f>COUNTIF(Volunteers!H:H,E4)</f>
         <v>0</v>
       </c>
-      <c r="F7" s="30">
+      <c r="F7" s="23">
         <f>COUNTIF(Volunteers!H:H,F4)</f>
         <v>0</v>
       </c>
-      <c r="G7" s="30">
+      <c r="G7" s="23">
         <f t="shared" si="1"/>
         <v>100</v>
       </c>
     </row>
     <row r="8" ht="18.0" customHeight="1">
-      <c r="B8" s="23" t="s">
+      <c r="B8" s="18" t="s">
         <v>77</v>
       </c>
-      <c r="C8" s="30">
+      <c r="C8" s="23">
         <f>COUNTIF('Help Requests'!A:A,"Hr-*")</f>
         <v>15</v>
       </c>
-      <c r="D8" s="31">
+      <c r="D8" s="23">
         <f>COUNTIF('Help Requests'!H:H,D4)</f>
         <v>15</v>
       </c>
-      <c r="E8" s="31">
+      <c r="E8" s="23">
         <f>COUNTIF('Help Requests'!H:H,E4)</f>
         <v>0</v>
       </c>
-      <c r="F8" s="31">
+      <c r="F8" s="23">
         <f>COUNTIF('Help Requests'!H:H,F4)</f>
         <v>0</v>
       </c>
-      <c r="G8" s="30">
+      <c r="G8" s="23">
         <f t="shared" si="1"/>
         <v>100</v>
       </c>
     </row>
     <row r="9" ht="18.0" customHeight="1">
-      <c r="B9" s="26" t="s">
+      <c r="B9" s="14" t="s">
         <v>78</v>
       </c>
-      <c r="C9" s="30">
+      <c r="C9" s="23">
         <f>COUNTIF(Donations!A:A,"D-*")</f>
         <v>10</v>
       </c>
-      <c r="D9" s="31">
+      <c r="D9" s="23">
         <f>COUNTIF(Donations!H:H,D4)</f>
         <v>10</v>
       </c>
-      <c r="E9" s="30">
+      <c r="E9" s="23">
         <f>COUNTIF(Donations!H:H,E4)</f>
         <v>0</v>
       </c>
-      <c r="F9" s="30">
+      <c r="F9" s="23">
         <f>COUNTIF(Donations!H:H,F4)</f>
         <v>0</v>
       </c>
-      <c r="G9" s="30">
+      <c r="G9" s="23">
         <f t="shared" si="1"/>
         <v>100</v>
       </c>
     </row>
     <row r="10" ht="18.0" customHeight="1">
-      <c r="B10" s="23" t="s">
+      <c r="B10" s="18" t="s">
         <v>79</v>
       </c>
-      <c r="C10" s="30">
+      <c r="C10" s="23">
         <f>COUNTIF(Proposals!A:A,"P-*")</f>
         <v>9</v>
       </c>
-      <c r="D10" s="31">
+      <c r="D10" s="23">
         <f>COUNTIF(Proposals!H:H,D4)</f>
         <v>9</v>
       </c>
-      <c r="E10" s="30">
+      <c r="E10" s="23">
         <f>COUNTIF(Proposals!H:H,E4)</f>
         <v>0</v>
       </c>
-      <c r="F10" s="30">
+      <c r="F10" s="23">
         <f>COUNTIF(Proposals!H:H,F4)</f>
         <v>0</v>
       </c>
-      <c r="G10" s="30">
+      <c r="G10" s="23">
         <f t="shared" si="1"/>
         <v>100</v>
       </c>
     </row>
     <row r="11" ht="18.0" customHeight="1">
-      <c r="B11" s="26" t="s">
+      <c r="B11" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="C11" s="30">
+      <c r="C11" s="23">
         <f>COUNTIF(Chat!A:A,"C-*")</f>
         <v>9</v>
       </c>
-      <c r="D11" s="31">
+      <c r="D11" s="23">
         <f>COUNTIF(Chat!H:H,D4)</f>
         <v>9</v>
       </c>
-      <c r="E11" s="30">
+      <c r="E11" s="23">
         <f>COUNTIF(Chat!H:H,E4)</f>
         <v>0</v>
       </c>
-      <c r="F11" s="30">
+      <c r="F11" s="23">
         <f>COUNTIF(Chat!H:H,F4)</f>
         <v>0</v>
       </c>
-      <c r="G11" s="30">
+      <c r="G11" s="23">
         <f t="shared" si="1"/>
         <v>100</v>
       </c>
     </row>
     <row r="12" ht="18.0" customHeight="1">
-      <c r="B12" s="23" t="s">
+      <c r="B12" s="18" t="s">
         <v>81</v>
       </c>
-      <c r="C12" s="30">
+      <c r="C12" s="23">
         <f>COUNTIF(Reviews!A:A,"R-*")</f>
         <v>11</v>
       </c>
-      <c r="D12" s="31">
+      <c r="D12" s="23">
         <f>COUNTIF(Reviews!H:H,D4)</f>
         <v>11</v>
       </c>
-      <c r="E12" s="30">
+      <c r="E12" s="23">
         <f>COUNTIF(Reviews!H:H,E4)</f>
         <v>0</v>
       </c>
-      <c r="F12" s="30">
+      <c r="F12" s="23">
         <f>COUNTIF(Reviews!H:H,F4)</f>
         <v>0</v>
       </c>
-      <c r="G12" s="30">
+      <c r="G12" s="23">
         <f t="shared" si="1"/>
         <v>100</v>
       </c>
     </row>
     <row r="13" ht="19.5" customHeight="1">
-      <c r="B13" s="32" t="s">
+      <c r="B13" s="24" t="s">
         <v>82</v>
       </c>
-      <c r="C13" s="33">
+      <c r="C13" s="25">
         <f t="shared" ref="C13:F13" si="2">SUM(C5:C12)</f>
-        <v>79</v>
-      </c>
-      <c r="D13" s="33">
+        <v>89</v>
+      </c>
+      <c r="D13" s="25">
         <f t="shared" si="2"/>
-        <v>79</v>
-      </c>
-      <c r="E13" s="33">
+        <v>89</v>
+      </c>
+      <c r="E13" s="25">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="F13" s="33">
+      <c r="F13" s="25">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="G13" s="33">
+      <c r="G13" s="25">
         <f t="shared" si="1"/>
         <v>100</v>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="34" t="s">
+      <c r="B15" s="26" t="s">
         <v>83</v>
       </c>
     </row>
@@ -8605,421 +8714,740 @@
     <col customWidth="1" min="8" max="8" width="16.0"/>
     <col customWidth="1" min="9" max="9" width="40.0"/>
     <col customWidth="1" min="10" max="10" width="14.0"/>
-    <col customWidth="1" min="11" max="26" width="8.71"/>
   </cols>
   <sheetData>
     <row r="1" ht="24.0" customHeight="1">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="27" t="s">
         <v>84</v>
       </c>
-      <c r="B1" s="36"/>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36"/>
-      <c r="E1" s="36"/>
-      <c r="F1" s="36"/>
-      <c r="G1" s="36"/>
-      <c r="H1" s="36"/>
-      <c r="I1" s="36"/>
-      <c r="J1" s="37"/>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+      <c r="H1" s="28"/>
+      <c r="I1" s="28"/>
+      <c r="J1" s="28"/>
     </row>
     <row r="2" ht="21.75" customHeight="1">
-      <c r="A2" s="29" t="s">
+      <c r="A2" s="22" t="s">
         <v>85</v>
       </c>
-      <c r="B2" s="29" t="s">
+      <c r="B2" s="22" t="s">
         <v>86</v>
       </c>
-      <c r="C2" s="29" t="s">
+      <c r="C2" s="22" t="s">
         <v>87</v>
       </c>
-      <c r="D2" s="29" t="s">
+      <c r="D2" s="22" t="s">
         <v>88</v>
       </c>
-      <c r="E2" s="29" t="s">
+      <c r="E2" s="22" t="s">
         <v>89</v>
       </c>
-      <c r="F2" s="29" t="s">
+      <c r="F2" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="G2" s="29" t="s">
+      <c r="G2" s="22" t="s">
         <v>90</v>
       </c>
-      <c r="H2" s="29" t="s">
+      <c r="H2" s="22" t="s">
         <v>91</v>
       </c>
-      <c r="I2" s="29" t="s">
+      <c r="I2" s="22" t="s">
         <v>92</v>
       </c>
-      <c r="J2" s="29" t="s">
+      <c r="J2" s="22" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="3" ht="18.0" customHeight="1">
-      <c r="A3" s="38" t="s">
+      <c r="A3" s="29" t="s">
         <v>94</v>
       </c>
-      <c r="B3" s="39"/>
-      <c r="C3" s="39"/>
-      <c r="D3" s="39"/>
-      <c r="E3" s="39"/>
-      <c r="F3" s="39"/>
-      <c r="G3" s="39"/>
-      <c r="H3" s="39"/>
-      <c r="I3" s="39"/>
-      <c r="J3" s="40"/>
+      <c r="B3" s="30"/>
+      <c r="C3" s="30"/>
+      <c r="D3" s="30"/>
+      <c r="E3" s="30"/>
+      <c r="F3" s="30"/>
+      <c r="G3" s="30"/>
+      <c r="H3" s="30"/>
+      <c r="I3" s="30"/>
+      <c r="J3" s="31"/>
     </row>
     <row r="4" ht="42.0" customHeight="1">
-      <c r="A4" s="30" t="s">
+      <c r="A4" s="23" t="s">
         <v>95</v>
       </c>
-      <c r="B4" s="28" t="s">
+      <c r="B4" s="21" t="s">
         <v>96</v>
       </c>
-      <c r="C4" s="41" t="s">
+      <c r="C4" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="D4" s="28" t="s">
+      <c r="D4" s="21" t="s">
         <v>98</v>
       </c>
-      <c r="E4" s="28" t="s">
+      <c r="E4" s="21" t="s">
         <v>99</v>
       </c>
-      <c r="F4" s="28" t="s">
+      <c r="F4" s="21" t="s">
         <v>100</v>
       </c>
-      <c r="G4" s="28" t="s">
+      <c r="G4" s="21" t="s">
         <v>101</v>
       </c>
-      <c r="H4" s="42" t="s">
+      <c r="H4" s="33" t="s">
         <v>70</v>
       </c>
-      <c r="I4" s="27" t="s">
+      <c r="I4" s="21" t="s">
         <v>102</v>
       </c>
-      <c r="J4" s="30"/>
+      <c r="J4" s="23"/>
     </row>
     <row r="5" ht="42.0" customHeight="1">
-      <c r="A5" s="43" t="s">
+      <c r="A5" s="34" t="s">
         <v>103</v>
       </c>
-      <c r="B5" s="25" t="s">
+      <c r="B5" s="20" t="s">
         <v>104</v>
       </c>
-      <c r="C5" s="44" t="s">
+      <c r="C5" s="35" t="s">
         <v>97</v>
       </c>
-      <c r="D5" s="25" t="s">
+      <c r="D5" s="20" t="s">
         <v>98</v>
       </c>
-      <c r="E5" s="25" t="s">
+      <c r="E5" s="20" t="s">
         <v>99</v>
       </c>
-      <c r="F5" s="25" t="s">
+      <c r="F5" s="20" t="s">
         <v>105</v>
       </c>
-      <c r="G5" s="25" t="s">
+      <c r="G5" s="20" t="s">
         <v>101</v>
       </c>
-      <c r="H5" s="42" t="s">
+      <c r="H5" s="33" t="s">
         <v>70</v>
       </c>
-      <c r="I5" s="24" t="s">
+      <c r="I5" s="20" t="s">
         <v>102</v>
       </c>
-      <c r="J5" s="43"/>
+      <c r="J5" s="34"/>
     </row>
     <row r="6" ht="42.0" customHeight="1">
-      <c r="A6" s="30" t="s">
+      <c r="A6" s="23" t="s">
         <v>106</v>
       </c>
-      <c r="B6" s="28" t="s">
+      <c r="B6" s="21" t="s">
         <v>107</v>
       </c>
-      <c r="C6" s="41" t="s">
+      <c r="C6" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="D6" s="28" t="s">
+      <c r="D6" s="21" t="s">
         <v>98</v>
       </c>
-      <c r="E6" s="28" t="s">
+      <c r="E6" s="21" t="s">
         <v>99</v>
       </c>
-      <c r="F6" s="28" t="s">
+      <c r="F6" s="21" t="s">
         <v>108</v>
       </c>
-      <c r="G6" s="28" t="s">
+      <c r="G6" s="21" t="s">
         <v>101</v>
       </c>
-      <c r="H6" s="42" t="s">
+      <c r="H6" s="33" t="s">
         <v>70</v>
       </c>
-      <c r="I6" s="27" t="s">
+      <c r="I6" s="21" t="s">
         <v>102</v>
       </c>
-      <c r="J6" s="30"/>
+      <c r="J6" s="23"/>
     </row>
     <row r="7" ht="42.0" customHeight="1">
-      <c r="A7" s="43" t="s">
+      <c r="A7" s="34" t="s">
         <v>109</v>
       </c>
-      <c r="B7" s="25" t="s">
+      <c r="B7" s="20" t="s">
         <v>110</v>
       </c>
-      <c r="C7" s="44" t="s">
+      <c r="C7" s="35" t="s">
         <v>97</v>
       </c>
-      <c r="D7" s="25" t="s">
+      <c r="D7" s="20" t="s">
         <v>98</v>
       </c>
-      <c r="E7" s="25" t="s">
+      <c r="E7" s="20" t="s">
         <v>99</v>
       </c>
-      <c r="F7" s="25" t="s">
+      <c r="F7" s="20" t="s">
         <v>111</v>
       </c>
-      <c r="G7" s="25" t="s">
+      <c r="G7" s="20" t="s">
         <v>112</v>
       </c>
-      <c r="H7" s="42" t="s">
+      <c r="H7" s="33" t="s">
         <v>70</v>
       </c>
-      <c r="I7" s="25" t="s">
+      <c r="I7" s="20" t="s">
         <v>113</v>
       </c>
-      <c r="J7" s="43"/>
+      <c r="J7" s="34"/>
     </row>
     <row r="8" ht="42.0" customHeight="1">
-      <c r="A8" s="30" t="s">
+      <c r="A8" s="23" t="s">
         <v>114</v>
       </c>
-      <c r="B8" s="28" t="s">
+      <c r="B8" s="21" t="s">
         <v>115</v>
       </c>
-      <c r="C8" s="41" t="s">
+      <c r="C8" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="D8" s="28" t="s">
+      <c r="D8" s="21" t="s">
         <v>98</v>
       </c>
-      <c r="E8" s="28" t="s">
+      <c r="E8" s="21" t="s">
         <v>99</v>
       </c>
-      <c r="F8" s="28" t="s">
+      <c r="F8" s="21" t="s">
         <v>116</v>
       </c>
-      <c r="G8" s="28" t="s">
+      <c r="G8" s="21" t="s">
         <v>117</v>
       </c>
-      <c r="H8" s="42" t="s">
+      <c r="H8" s="33" t="s">
         <v>70</v>
       </c>
-      <c r="I8" s="27" t="s">
+      <c r="I8" s="21" t="s">
         <v>118</v>
       </c>
-      <c r="J8" s="30"/>
+      <c r="J8" s="23"/>
     </row>
     <row r="9" ht="18.0" customHeight="1">
-      <c r="A9" s="38" t="s">
+      <c r="A9" s="29" t="s">
         <v>119</v>
       </c>
-      <c r="B9" s="39"/>
-      <c r="C9" s="39"/>
-      <c r="D9" s="39"/>
-      <c r="E9" s="39"/>
-      <c r="F9" s="39"/>
-      <c r="G9" s="39"/>
-      <c r="H9" s="39"/>
-      <c r="I9" s="39"/>
-      <c r="J9" s="40"/>
+      <c r="B9" s="30"/>
+      <c r="C9" s="30"/>
+      <c r="D9" s="30"/>
+      <c r="E9" s="30"/>
+      <c r="F9" s="30"/>
+      <c r="G9" s="30"/>
+      <c r="H9" s="30"/>
+      <c r="I9" s="30"/>
+      <c r="J9" s="31"/>
     </row>
     <row r="10" ht="42.0" customHeight="1">
-      <c r="A10" s="30" t="s">
+      <c r="A10" s="23" t="s">
         <v>120</v>
       </c>
-      <c r="B10" s="28" t="s">
+      <c r="B10" s="21" t="s">
         <v>121</v>
       </c>
-      <c r="C10" s="41" t="s">
+      <c r="C10" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="D10" s="28" t="s">
+      <c r="D10" s="21" t="s">
         <v>122</v>
       </c>
-      <c r="E10" s="28" t="s">
+      <c r="E10" s="21" t="s">
         <v>99</v>
       </c>
-      <c r="F10" s="28" t="s">
+      <c r="F10" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="G10" s="28" t="s">
+      <c r="G10" s="21" t="s">
         <v>123</v>
       </c>
-      <c r="H10" s="42" t="s">
+      <c r="H10" s="33" t="s">
         <v>70</v>
       </c>
-      <c r="I10" s="27" t="s">
+      <c r="I10" s="21" t="s">
         <v>124</v>
       </c>
-      <c r="J10" s="30"/>
+      <c r="J10" s="23"/>
     </row>
     <row r="11" ht="42.0" customHeight="1">
-      <c r="A11" s="43" t="s">
+      <c r="A11" s="34" t="s">
         <v>125</v>
       </c>
-      <c r="B11" s="25" t="s">
+      <c r="B11" s="20" t="s">
         <v>126</v>
       </c>
-      <c r="C11" s="44" t="s">
+      <c r="C11" s="35" t="s">
         <v>97</v>
       </c>
-      <c r="D11" s="25" t="s">
+      <c r="D11" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="E11" s="25" t="s">
+      <c r="E11" s="20" t="s">
         <v>99</v>
       </c>
-      <c r="F11" s="25" t="s">
+      <c r="F11" s="20" t="s">
         <v>35</v>
       </c>
-      <c r="G11" s="25" t="s">
+      <c r="G11" s="20" t="s">
         <v>123</v>
       </c>
-      <c r="H11" s="42" t="s">
+      <c r="H11" s="33" t="s">
         <v>70</v>
       </c>
-      <c r="I11" s="24" t="s">
+      <c r="I11" s="20" t="s">
         <v>124</v>
       </c>
-      <c r="J11" s="43"/>
+      <c r="J11" s="34"/>
     </row>
     <row r="12" ht="42.0" customHeight="1">
-      <c r="A12" s="30" t="s">
+      <c r="A12" s="23" t="s">
         <v>127</v>
       </c>
-      <c r="B12" s="28" t="s">
+      <c r="B12" s="21" t="s">
         <v>128</v>
       </c>
-      <c r="C12" s="41" t="s">
+      <c r="C12" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="D12" s="28" t="s">
+      <c r="D12" s="21" t="s">
         <v>122</v>
       </c>
-      <c r="E12" s="28" t="s">
+      <c r="E12" s="21" t="s">
         <v>99</v>
       </c>
-      <c r="F12" s="28" t="s">
+      <c r="F12" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="G12" s="28" t="s">
+      <c r="G12" s="21" t="s">
         <v>123</v>
       </c>
-      <c r="H12" s="42" t="s">
+      <c r="H12" s="33" t="s">
         <v>70</v>
       </c>
-      <c r="I12" s="27" t="s">
+      <c r="I12" s="21" t="s">
         <v>124</v>
       </c>
-      <c r="J12" s="30"/>
+      <c r="J12" s="23"/>
     </row>
     <row r="13" ht="42.0" customHeight="1">
-      <c r="A13" s="43" t="s">
+      <c r="A13" s="34" t="s">
         <v>129</v>
       </c>
-      <c r="B13" s="25" t="s">
+      <c r="B13" s="20" t="s">
         <v>130</v>
       </c>
-      <c r="C13" s="44" t="s">
+      <c r="C13" s="35" t="s">
         <v>97</v>
       </c>
-      <c r="D13" s="25" t="s">
+      <c r="D13" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="E13" s="25" t="s">
+      <c r="E13" s="20" t="s">
         <v>99</v>
       </c>
-      <c r="F13" s="25" t="s">
+      <c r="F13" s="20" t="s">
         <v>131</v>
       </c>
-      <c r="G13" s="25" t="s">
+      <c r="G13" s="20" t="s">
         <v>132</v>
       </c>
-      <c r="H13" s="42" t="s">
+      <c r="H13" s="33" t="s">
         <v>70</v>
       </c>
-      <c r="I13" s="24" t="s">
+      <c r="I13" s="20" t="s">
         <v>124</v>
       </c>
-      <c r="J13" s="43"/>
+      <c r="J13" s="34"/>
     </row>
     <row r="14" ht="42.0" customHeight="1">
-      <c r="A14" s="30" t="s">
+      <c r="A14" s="23" t="s">
         <v>133</v>
       </c>
-      <c r="B14" s="28" t="s">
+      <c r="B14" s="21" t="s">
         <v>134</v>
       </c>
-      <c r="C14" s="41" t="s">
+      <c r="C14" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="D14" s="28" t="s">
+      <c r="D14" s="21" t="s">
         <v>122</v>
       </c>
-      <c r="E14" s="28" t="s">
+      <c r="E14" s="21" t="s">
         <v>99</v>
       </c>
-      <c r="F14" s="28" t="s">
+      <c r="F14" s="21" t="s">
         <v>135</v>
       </c>
-      <c r="G14" s="28" t="s">
+      <c r="G14" s="21" t="s">
         <v>136</v>
       </c>
-      <c r="H14" s="42" t="s">
+      <c r="H14" s="33" t="s">
         <v>70</v>
       </c>
-      <c r="I14" s="28" t="s">
+      <c r="I14" s="21" t="s">
         <v>118</v>
       </c>
-      <c r="J14" s="30"/>
+      <c r="J14" s="23"/>
     </row>
     <row r="15" ht="42.0" customHeight="1">
-      <c r="A15" s="43" t="s">
+      <c r="A15" s="34" t="s">
         <v>137</v>
       </c>
-      <c r="B15" s="25" t="s">
+      <c r="B15" s="20" t="s">
         <v>138</v>
       </c>
-      <c r="C15" s="45" t="s">
+      <c r="C15" s="36" t="s">
         <v>139</v>
       </c>
-      <c r="D15" s="25" t="s">
+      <c r="D15" s="20" t="s">
         <v>140</v>
       </c>
-      <c r="E15" s="25" t="s">
+      <c r="E15" s="20" t="s">
         <v>99</v>
       </c>
-      <c r="F15" s="25" t="s">
+      <c r="F15" s="20" t="s">
         <v>141</v>
       </c>
-      <c r="G15" s="25" t="s">
+      <c r="G15" s="20" t="s">
         <v>136</v>
       </c>
-      <c r="H15" s="42" t="s">
+      <c r="H15" s="33" t="s">
         <v>70</v>
       </c>
-      <c r="I15" s="25" t="s">
+      <c r="I15" s="20" t="s">
         <v>142</v>
       </c>
-      <c r="J15" s="43"/>
-    </row>
-    <row r="20" ht="15.75" customHeight="1"/>
-    <row r="21" ht="15.75" customHeight="1"/>
-    <row r="22" ht="15.75" customHeight="1"/>
-    <row r="23" ht="15.75" customHeight="1"/>
-    <row r="24" ht="15.75" customHeight="1"/>
-    <row r="25" ht="15.75" customHeight="1"/>
-    <row r="26" ht="15.75" customHeight="1"/>
-    <row r="27" ht="15.75" customHeight="1"/>
+      <c r="J15" s="34"/>
+    </row>
+    <row r="16" ht="18.0" customHeight="1">
+      <c r="A16" s="37" t="s">
+        <v>143</v>
+      </c>
+      <c r="B16" s="30"/>
+      <c r="C16" s="30"/>
+      <c r="D16" s="30"/>
+      <c r="E16" s="30"/>
+      <c r="F16" s="30"/>
+      <c r="G16" s="30"/>
+      <c r="H16" s="30"/>
+      <c r="I16" s="30"/>
+      <c r="J16" s="31"/>
+    </row>
+    <row r="17" ht="42.0" customHeight="1">
+      <c r="A17" s="38" t="s">
+        <v>144</v>
+      </c>
+      <c r="B17" s="39" t="s">
+        <v>145</v>
+      </c>
+      <c r="C17" s="35" t="s">
+        <v>97</v>
+      </c>
+      <c r="D17" s="39" t="s">
+        <v>146</v>
+      </c>
+      <c r="E17" s="39" t="s">
+        <v>99</v>
+      </c>
+      <c r="F17" s="39" t="s">
+        <v>147</v>
+      </c>
+      <c r="G17" s="39" t="s">
+        <v>148</v>
+      </c>
+      <c r="H17" s="40" t="s">
+        <v>70</v>
+      </c>
+      <c r="I17" s="39" t="s">
+        <v>149</v>
+      </c>
+      <c r="J17" s="34"/>
+    </row>
+    <row r="18" ht="42.0" customHeight="1">
+      <c r="A18" s="41" t="s">
+        <v>150</v>
+      </c>
+      <c r="B18" s="42" t="s">
+        <v>151</v>
+      </c>
+      <c r="C18" s="32" t="s">
+        <v>97</v>
+      </c>
+      <c r="D18" s="42" t="s">
+        <v>146</v>
+      </c>
+      <c r="E18" s="42" t="s">
+        <v>99</v>
+      </c>
+      <c r="F18" s="42" t="s">
+        <v>147</v>
+      </c>
+      <c r="G18" s="42" t="s">
+        <v>136</v>
+      </c>
+      <c r="H18" s="40" t="s">
+        <v>70</v>
+      </c>
+      <c r="I18" s="42" t="s">
+        <v>152</v>
+      </c>
+      <c r="J18" s="23"/>
+    </row>
+    <row r="19" ht="42.0" customHeight="1">
+      <c r="A19" s="38" t="s">
+        <v>153</v>
+      </c>
+      <c r="B19" s="39" t="s">
+        <v>154</v>
+      </c>
+      <c r="C19" s="35" t="s">
+        <v>97</v>
+      </c>
+      <c r="D19" s="39" t="s">
+        <v>146</v>
+      </c>
+      <c r="E19" s="39" t="s">
+        <v>99</v>
+      </c>
+      <c r="F19" s="39" t="s">
+        <v>155</v>
+      </c>
+      <c r="G19" s="39" t="s">
+        <v>136</v>
+      </c>
+      <c r="H19" s="40" t="s">
+        <v>70</v>
+      </c>
+      <c r="I19" s="39" t="s">
+        <v>156</v>
+      </c>
+      <c r="J19" s="34"/>
+    </row>
+    <row r="20" ht="18.0" customHeight="1">
+      <c r="A20" s="37" t="s">
+        <v>157</v>
+      </c>
+      <c r="B20" s="30"/>
+      <c r="C20" s="30"/>
+      <c r="D20" s="30"/>
+      <c r="E20" s="30"/>
+      <c r="F20" s="30"/>
+      <c r="G20" s="30"/>
+      <c r="H20" s="30"/>
+      <c r="I20" s="30"/>
+      <c r="J20" s="31"/>
+    </row>
+    <row r="21" ht="42.0" customHeight="1">
+      <c r="A21" s="38" t="s">
+        <v>158</v>
+      </c>
+      <c r="B21" s="39" t="s">
+        <v>159</v>
+      </c>
+      <c r="C21" s="35" t="s">
+        <v>97</v>
+      </c>
+      <c r="D21" s="39" t="s">
+        <v>160</v>
+      </c>
+      <c r="E21" s="39" t="s">
+        <v>99</v>
+      </c>
+      <c r="F21" s="39" t="s">
+        <v>161</v>
+      </c>
+      <c r="G21" s="39" t="s">
+        <v>148</v>
+      </c>
+      <c r="H21" s="40" t="s">
+        <v>70</v>
+      </c>
+      <c r="I21" s="39" t="s">
+        <v>162</v>
+      </c>
+      <c r="J21" s="34"/>
+    </row>
+    <row r="22" ht="42.0" customHeight="1">
+      <c r="A22" s="41" t="s">
+        <v>163</v>
+      </c>
+      <c r="B22" s="42" t="s">
+        <v>164</v>
+      </c>
+      <c r="C22" s="32" t="s">
+        <v>97</v>
+      </c>
+      <c r="D22" s="42" t="s">
+        <v>160</v>
+      </c>
+      <c r="E22" s="42" t="s">
+        <v>99</v>
+      </c>
+      <c r="F22" s="42" t="s">
+        <v>165</v>
+      </c>
+      <c r="G22" s="42" t="s">
+        <v>166</v>
+      </c>
+      <c r="H22" s="40" t="s">
+        <v>70</v>
+      </c>
+      <c r="I22" s="42" t="s">
+        <v>167</v>
+      </c>
+      <c r="J22" s="23"/>
+    </row>
+    <row r="23" ht="42.0" customHeight="1">
+      <c r="A23" s="38" t="s">
+        <v>168</v>
+      </c>
+      <c r="B23" s="39" t="s">
+        <v>169</v>
+      </c>
+      <c r="C23" s="35" t="s">
+        <v>97</v>
+      </c>
+      <c r="D23" s="39" t="s">
+        <v>170</v>
+      </c>
+      <c r="E23" s="39" t="s">
+        <v>99</v>
+      </c>
+      <c r="F23" s="39" t="s">
+        <v>171</v>
+      </c>
+      <c r="G23" s="39" t="s">
+        <v>148</v>
+      </c>
+      <c r="H23" s="40" t="s">
+        <v>70</v>
+      </c>
+      <c r="I23" s="39" t="s">
+        <v>172</v>
+      </c>
+      <c r="J23" s="34"/>
+    </row>
+    <row r="24" ht="42.0" customHeight="1">
+      <c r="A24" s="41" t="s">
+        <v>173</v>
+      </c>
+      <c r="B24" s="42" t="s">
+        <v>174</v>
+      </c>
+      <c r="C24" s="32" t="s">
+        <v>97</v>
+      </c>
+      <c r="D24" s="42" t="s">
+        <v>122</v>
+      </c>
+      <c r="E24" s="42" t="s">
+        <v>99</v>
+      </c>
+      <c r="F24" s="42" t="s">
+        <v>175</v>
+      </c>
+      <c r="G24" s="42" t="s">
+        <v>123</v>
+      </c>
+      <c r="H24" s="40" t="s">
+        <v>70</v>
+      </c>
+      <c r="I24" s="42" t="s">
+        <v>176</v>
+      </c>
+      <c r="J24" s="23"/>
+    </row>
+    <row r="25" ht="42.0" customHeight="1">
+      <c r="A25" s="38" t="s">
+        <v>177</v>
+      </c>
+      <c r="B25" s="39" t="s">
+        <v>178</v>
+      </c>
+      <c r="C25" s="35" t="s">
+        <v>97</v>
+      </c>
+      <c r="D25" s="39" t="s">
+        <v>122</v>
+      </c>
+      <c r="E25" s="39" t="s">
+        <v>99</v>
+      </c>
+      <c r="F25" s="39" t="s">
+        <v>31</v>
+      </c>
+      <c r="G25" s="39" t="s">
+        <v>136</v>
+      </c>
+      <c r="H25" s="40" t="s">
+        <v>70</v>
+      </c>
+      <c r="I25" s="39" t="s">
+        <v>179</v>
+      </c>
+      <c r="J25" s="34"/>
+    </row>
+    <row r="26" ht="42.0" customHeight="1">
+      <c r="A26" s="41" t="s">
+        <v>180</v>
+      </c>
+      <c r="B26" s="42" t="s">
+        <v>181</v>
+      </c>
+      <c r="C26" s="32" t="s">
+        <v>97</v>
+      </c>
+      <c r="D26" s="42" t="s">
+        <v>170</v>
+      </c>
+      <c r="E26" s="42" t="s">
+        <v>99</v>
+      </c>
+      <c r="F26" s="42" t="s">
+        <v>182</v>
+      </c>
+      <c r="G26" s="42" t="s">
+        <v>136</v>
+      </c>
+      <c r="H26" s="40" t="s">
+        <v>70</v>
+      </c>
+      <c r="I26" s="42" t="s">
+        <v>183</v>
+      </c>
+      <c r="J26" s="23"/>
+    </row>
+    <row r="27" ht="42.0" customHeight="1">
+      <c r="A27" s="38" t="s">
+        <v>184</v>
+      </c>
+      <c r="B27" s="39" t="s">
+        <v>185</v>
+      </c>
+      <c r="C27" s="35" t="s">
+        <v>97</v>
+      </c>
+      <c r="D27" s="39" t="s">
+        <v>170</v>
+      </c>
+      <c r="E27" s="39" t="s">
+        <v>99</v>
+      </c>
+      <c r="F27" s="39" t="s">
+        <v>186</v>
+      </c>
+      <c r="G27" s="39" t="s">
+        <v>187</v>
+      </c>
+      <c r="H27" s="40" t="s">
+        <v>70</v>
+      </c>
+      <c r="I27" s="39" t="s">
+        <v>188</v>
+      </c>
+      <c r="J27" s="34"/>
+    </row>
     <row r="28" ht="15.75" customHeight="1"/>
     <row r="29" ht="15.75" customHeight="1"/>
     <row r="30" ht="15.75" customHeight="1"/>
@@ -9990,31 +10418,31 @@
     <row r="995" ht="15.75" customHeight="1"/>
     <row r="996" ht="15.75" customHeight="1"/>
     <row r="997" ht="15.75" customHeight="1"/>
-    <row r="998" ht="15.75" customHeight="1"/>
-    <row r="999" ht="15.75" customHeight="1"/>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="5">
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A3:J3"/>
     <mergeCell ref="A9:J9"/>
+    <mergeCell ref="A16:J16"/>
+    <mergeCell ref="A20:J20"/>
   </mergeCells>
-  <conditionalFormatting sqref="H4:H8 H10:H15">
+  <conditionalFormatting sqref="H4:H8 H10:H15 H17:H19 H21:H27">
     <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="✅ PASS">
       <formula>NOT(ISERROR(SEARCH(("✅ PASS"),(H4))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H4:H8 H10:H15">
+  <conditionalFormatting sqref="H4:H8 H10:H15 H17:H19 H21:H27">
     <cfRule type="containsText" dxfId="4" priority="2" operator="containsText" text="❌ FAIL">
       <formula>NOT(ISERROR(SEARCH(("❌ FAIL"),(H4))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H4:H8 H10:H15">
+  <conditionalFormatting sqref="H4:H8 H10:H15 H17:H19 H21:H27">
     <cfRule type="containsText" dxfId="2" priority="3" operator="containsText" text="⏳ PENDING">
       <formula>NOT(ISERROR(SEARCH(("⏳ PENDING"),(H4))))</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="H4:H8 H10:H15">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="H4:H8 H10:H15 H17:H19 H21:H27">
       <formula1>"⏳ PENDIENTE,✅ PASS,❌ FAIL"</formula1>
     </dataValidation>
   </dataValidations>
@@ -10042,262 +10470,261 @@
     <col customWidth="1" min="8" max="8" width="16.0"/>
     <col customWidth="1" min="9" max="9" width="40.0"/>
     <col customWidth="1" min="10" max="10" width="14.0"/>
-    <col customWidth="1" min="11" max="26" width="8.71"/>
   </cols>
   <sheetData>
     <row r="1" ht="24.0" customHeight="1">
-      <c r="A1" s="35" t="s">
-        <v>143</v>
-      </c>
-      <c r="B1" s="36"/>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36"/>
-      <c r="E1" s="36"/>
-      <c r="F1" s="36"/>
-      <c r="G1" s="36"/>
-      <c r="H1" s="36"/>
-      <c r="I1" s="36"/>
-      <c r="J1" s="37"/>
+      <c r="A1" s="27" t="s">
+        <v>189</v>
+      </c>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+      <c r="H1" s="28"/>
+      <c r="I1" s="28"/>
+      <c r="J1" s="28"/>
     </row>
     <row r="2" ht="21.75" customHeight="1">
-      <c r="A2" s="29" t="s">
+      <c r="A2" s="22" t="s">
         <v>85</v>
       </c>
-      <c r="B2" s="29" t="s">
+      <c r="B2" s="22" t="s">
         <v>86</v>
       </c>
-      <c r="C2" s="29" t="s">
+      <c r="C2" s="22" t="s">
         <v>87</v>
       </c>
-      <c r="D2" s="29" t="s">
+      <c r="D2" s="22" t="s">
         <v>88</v>
       </c>
-      <c r="E2" s="29" t="s">
+      <c r="E2" s="22" t="s">
         <v>89</v>
       </c>
-      <c r="F2" s="29" t="s">
+      <c r="F2" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="G2" s="29" t="s">
+      <c r="G2" s="22" t="s">
         <v>90</v>
       </c>
-      <c r="H2" s="29" t="s">
+      <c r="H2" s="22" t="s">
         <v>91</v>
       </c>
-      <c r="I2" s="29" t="s">
+      <c r="I2" s="22" t="s">
         <v>92</v>
       </c>
-      <c r="J2" s="29" t="s">
+      <c r="J2" s="22" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="3" ht="18.0" customHeight="1">
-      <c r="A3" s="38" t="s">
-        <v>144</v>
-      </c>
-      <c r="B3" s="39"/>
-      <c r="C3" s="39"/>
-      <c r="D3" s="39"/>
-      <c r="E3" s="39"/>
-      <c r="F3" s="39"/>
-      <c r="G3" s="39"/>
-      <c r="H3" s="39"/>
-      <c r="I3" s="39"/>
-      <c r="J3" s="40"/>
+      <c r="A3" s="29" t="s">
+        <v>190</v>
+      </c>
+      <c r="B3" s="30"/>
+      <c r="C3" s="30"/>
+      <c r="D3" s="30"/>
+      <c r="E3" s="30"/>
+      <c r="F3" s="30"/>
+      <c r="G3" s="30"/>
+      <c r="H3" s="30"/>
+      <c r="I3" s="30"/>
+      <c r="J3" s="31"/>
     </row>
     <row r="4" ht="42.0" customHeight="1">
-      <c r="A4" s="30" t="s">
-        <v>145</v>
-      </c>
-      <c r="B4" s="28" t="s">
-        <v>146</v>
-      </c>
-      <c r="C4" s="46" t="s">
+      <c r="A4" s="23" t="s">
+        <v>191</v>
+      </c>
+      <c r="B4" s="21" t="s">
+        <v>192</v>
+      </c>
+      <c r="C4" s="43" t="s">
         <v>139</v>
       </c>
-      <c r="D4" s="28" t="s">
+      <c r="D4" s="21" t="s">
         <v>140</v>
       </c>
-      <c r="E4" s="27" t="s">
-        <v>147</v>
-      </c>
-      <c r="F4" s="28" t="s">
+      <c r="E4" s="21" t="s">
+        <v>193</v>
+      </c>
+      <c r="F4" s="21" t="s">
         <v>141</v>
       </c>
-      <c r="G4" s="28" t="s">
-        <v>148</v>
-      </c>
-      <c r="H4" s="42" t="s">
+      <c r="G4" s="21" t="s">
+        <v>194</v>
+      </c>
+      <c r="H4" s="33" t="s">
         <v>70</v>
       </c>
-      <c r="I4" s="28" t="s">
-        <v>149</v>
-      </c>
-      <c r="J4" s="30"/>
+      <c r="I4" s="21" t="s">
+        <v>195</v>
+      </c>
+      <c r="J4" s="23"/>
     </row>
     <row r="5" ht="42.0" customHeight="1">
-      <c r="A5" s="43" t="s">
-        <v>150</v>
-      </c>
-      <c r="B5" s="25" t="s">
-        <v>151</v>
-      </c>
-      <c r="C5" s="45" t="s">
+      <c r="A5" s="34" t="s">
+        <v>196</v>
+      </c>
+      <c r="B5" s="20" t="s">
+        <v>197</v>
+      </c>
+      <c r="C5" s="36" t="s">
         <v>139</v>
       </c>
-      <c r="D5" s="25" t="s">
+      <c r="D5" s="20" t="s">
         <v>140</v>
       </c>
-      <c r="E5" s="24" t="s">
-        <v>147</v>
-      </c>
-      <c r="F5" s="25" t="s">
+      <c r="E5" s="20" t="s">
+        <v>193</v>
+      </c>
+      <c r="F5" s="20" t="s">
         <v>141</v>
       </c>
-      <c r="G5" s="25" t="s">
-        <v>152</v>
-      </c>
-      <c r="H5" s="42" t="s">
+      <c r="G5" s="20" t="s">
+        <v>198</v>
+      </c>
+      <c r="H5" s="33" t="s">
         <v>70</v>
       </c>
-      <c r="I5" s="25" t="s">
-        <v>153</v>
-      </c>
-      <c r="J5" s="43"/>
+      <c r="I5" s="20" t="s">
+        <v>199</v>
+      </c>
+      <c r="J5" s="34"/>
     </row>
     <row r="6" ht="42.0" customHeight="1">
-      <c r="A6" s="30" t="s">
-        <v>154</v>
-      </c>
-      <c r="B6" s="28" t="s">
-        <v>155</v>
-      </c>
-      <c r="C6" s="46" t="s">
+      <c r="A6" s="23" t="s">
+        <v>200</v>
+      </c>
+      <c r="B6" s="21" t="s">
+        <v>201</v>
+      </c>
+      <c r="C6" s="43" t="s">
         <v>139</v>
       </c>
-      <c r="D6" s="28" t="s">
+      <c r="D6" s="21" t="s">
         <v>140</v>
       </c>
-      <c r="E6" s="27" t="s">
-        <v>147</v>
-      </c>
-      <c r="F6" s="28" t="s">
+      <c r="E6" s="21" t="s">
+        <v>193</v>
+      </c>
+      <c r="F6" s="21" t="s">
         <v>141</v>
       </c>
-      <c r="G6" s="28" t="s">
-        <v>156</v>
-      </c>
-      <c r="H6" s="42" t="s">
+      <c r="G6" s="21" t="s">
+        <v>202</v>
+      </c>
+      <c r="H6" s="33" t="s">
         <v>70</v>
       </c>
-      <c r="I6" s="28" t="s">
-        <v>157</v>
-      </c>
-      <c r="J6" s="30"/>
+      <c r="I6" s="21" t="s">
+        <v>203</v>
+      </c>
+      <c r="J6" s="23"/>
     </row>
     <row r="7" ht="42.0" customHeight="1">
-      <c r="A7" s="43" t="s">
-        <v>158</v>
-      </c>
-      <c r="B7" s="24" t="s">
-        <v>159</v>
-      </c>
-      <c r="C7" s="47" t="s">
-        <v>160</v>
-      </c>
-      <c r="D7" s="25" t="s">
+      <c r="A7" s="34" t="s">
+        <v>204</v>
+      </c>
+      <c r="B7" s="20" t="s">
+        <v>205</v>
+      </c>
+      <c r="C7" s="44" t="s">
+        <v>206</v>
+      </c>
+      <c r="D7" s="20" t="s">
         <v>140</v>
       </c>
-      <c r="E7" s="24" t="s">
-        <v>147</v>
-      </c>
-      <c r="F7" s="24" t="s">
-        <v>161</v>
-      </c>
-      <c r="G7" s="25" t="s">
-        <v>162</v>
-      </c>
-      <c r="H7" s="42" t="s">
+      <c r="E7" s="20" t="s">
+        <v>193</v>
+      </c>
+      <c r="F7" s="20" t="s">
+        <v>207</v>
+      </c>
+      <c r="G7" s="20" t="s">
+        <v>208</v>
+      </c>
+      <c r="H7" s="33" t="s">
         <v>70</v>
       </c>
-      <c r="I7" s="25" t="s">
-        <v>163</v>
-      </c>
-      <c r="J7" s="43"/>
+      <c r="I7" s="20" t="s">
+        <v>209</v>
+      </c>
+      <c r="J7" s="34"/>
     </row>
     <row r="8" ht="18.0" customHeight="1">
-      <c r="A8" s="38" t="s">
-        <v>164</v>
-      </c>
-      <c r="B8" s="39"/>
-      <c r="C8" s="39"/>
-      <c r="D8" s="39"/>
-      <c r="E8" s="39"/>
-      <c r="F8" s="39"/>
-      <c r="G8" s="39"/>
-      <c r="H8" s="39"/>
-      <c r="I8" s="39"/>
-      <c r="J8" s="40"/>
+      <c r="A8" s="29" t="s">
+        <v>210</v>
+      </c>
+      <c r="B8" s="30"/>
+      <c r="C8" s="30"/>
+      <c r="D8" s="30"/>
+      <c r="E8" s="30"/>
+      <c r="F8" s="30"/>
+      <c r="G8" s="30"/>
+      <c r="H8" s="30"/>
+      <c r="I8" s="30"/>
+      <c r="J8" s="31"/>
     </row>
     <row r="9" ht="42.0" customHeight="1">
-      <c r="A9" s="43" t="s">
-        <v>165</v>
-      </c>
-      <c r="B9" s="24" t="s">
-        <v>166</v>
-      </c>
-      <c r="C9" s="45" t="s">
+      <c r="A9" s="34" t="s">
+        <v>211</v>
+      </c>
+      <c r="B9" s="20" t="s">
+        <v>212</v>
+      </c>
+      <c r="C9" s="36" t="s">
         <v>139</v>
       </c>
-      <c r="D9" s="25" t="s">
-        <v>167</v>
-      </c>
-      <c r="E9" s="24" t="s">
-        <v>147</v>
-      </c>
-      <c r="F9" s="25" t="s">
+      <c r="D9" s="20" t="s">
+        <v>213</v>
+      </c>
+      <c r="E9" s="20" t="s">
+        <v>193</v>
+      </c>
+      <c r="F9" s="20" t="s">
         <v>141</v>
       </c>
-      <c r="G9" s="25" t="s">
-        <v>168</v>
-      </c>
-      <c r="H9" s="42" t="s">
+      <c r="G9" s="20" t="s">
+        <v>214</v>
+      </c>
+      <c r="H9" s="33" t="s">
         <v>70</v>
       </c>
-      <c r="I9" s="25" t="s">
-        <v>169</v>
-      </c>
-      <c r="J9" s="43"/>
+      <c r="I9" s="20" t="s">
+        <v>215</v>
+      </c>
+      <c r="J9" s="34"/>
     </row>
     <row r="10" ht="42.0" customHeight="1">
-      <c r="A10" s="30" t="s">
-        <v>170</v>
-      </c>
-      <c r="B10" s="27" t="s">
-        <v>171</v>
-      </c>
-      <c r="C10" s="46" t="s">
+      <c r="A10" s="23" t="s">
+        <v>216</v>
+      </c>
+      <c r="B10" s="21" t="s">
+        <v>217</v>
+      </c>
+      <c r="C10" s="43" t="s">
         <v>139</v>
       </c>
-      <c r="D10" s="28" t="s">
-        <v>167</v>
-      </c>
-      <c r="E10" s="27" t="s">
-        <v>147</v>
-      </c>
-      <c r="F10" s="28" t="s">
+      <c r="D10" s="21" t="s">
+        <v>213</v>
+      </c>
+      <c r="E10" s="21" t="s">
+        <v>193</v>
+      </c>
+      <c r="F10" s="21" t="s">
         <v>141</v>
       </c>
-      <c r="G10" s="28" t="s">
-        <v>172</v>
-      </c>
-      <c r="H10" s="42" t="s">
+      <c r="G10" s="21" t="s">
+        <v>218</v>
+      </c>
+      <c r="H10" s="33" t="s">
         <v>70</v>
       </c>
-      <c r="I10" s="27" t="s">
-        <v>173</v>
-      </c>
-      <c r="J10" s="30"/>
+      <c r="I10" s="21" t="s">
+        <v>219</v>
+      </c>
+      <c r="J10" s="23"/>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>
     <row r="22" ht="15.75" customHeight="1"/>
@@ -11329,322 +11756,321 @@
     <col customWidth="1" min="8" max="8" width="16.0"/>
     <col customWidth="1" min="9" max="9" width="40.0"/>
     <col customWidth="1" min="10" max="10" width="14.0"/>
-    <col customWidth="1" min="11" max="26" width="8.71"/>
   </cols>
   <sheetData>
     <row r="1" ht="24.0" customHeight="1">
-      <c r="A1" s="35" t="s">
-        <v>174</v>
-      </c>
-      <c r="B1" s="36"/>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36"/>
-      <c r="E1" s="36"/>
-      <c r="F1" s="36"/>
-      <c r="G1" s="36"/>
-      <c r="H1" s="36"/>
-      <c r="I1" s="36"/>
-      <c r="J1" s="37"/>
+      <c r="A1" s="27" t="s">
+        <v>220</v>
+      </c>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+      <c r="H1" s="28"/>
+      <c r="I1" s="28"/>
+      <c r="J1" s="28"/>
     </row>
     <row r="2" ht="21.75" customHeight="1">
-      <c r="A2" s="29" t="s">
+      <c r="A2" s="22" t="s">
         <v>85</v>
       </c>
-      <c r="B2" s="29" t="s">
+      <c r="B2" s="22" t="s">
         <v>86</v>
       </c>
-      <c r="C2" s="29" t="s">
+      <c r="C2" s="22" t="s">
         <v>87</v>
       </c>
-      <c r="D2" s="29" t="s">
+      <c r="D2" s="22" t="s">
         <v>88</v>
       </c>
-      <c r="E2" s="29" t="s">
+      <c r="E2" s="22" t="s">
         <v>89</v>
       </c>
-      <c r="F2" s="29" t="s">
+      <c r="F2" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="G2" s="29" t="s">
+      <c r="G2" s="22" t="s">
         <v>90</v>
       </c>
-      <c r="H2" s="29" t="s">
+      <c r="H2" s="22" t="s">
         <v>91</v>
       </c>
-      <c r="I2" s="29" t="s">
+      <c r="I2" s="22" t="s">
         <v>92</v>
       </c>
-      <c r="J2" s="29" t="s">
+      <c r="J2" s="22" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="3" ht="18.0" customHeight="1">
-      <c r="A3" s="38" t="s">
-        <v>175</v>
-      </c>
-      <c r="B3" s="39"/>
-      <c r="C3" s="39"/>
-      <c r="D3" s="39"/>
-      <c r="E3" s="39"/>
-      <c r="F3" s="39"/>
-      <c r="G3" s="39"/>
-      <c r="H3" s="39"/>
-      <c r="I3" s="39"/>
-      <c r="J3" s="40"/>
+      <c r="A3" s="29" t="s">
+        <v>221</v>
+      </c>
+      <c r="B3" s="30"/>
+      <c r="C3" s="30"/>
+      <c r="D3" s="30"/>
+      <c r="E3" s="30"/>
+      <c r="F3" s="30"/>
+      <c r="G3" s="30"/>
+      <c r="H3" s="30"/>
+      <c r="I3" s="30"/>
+      <c r="J3" s="31"/>
     </row>
     <row r="4" ht="42.0" customHeight="1">
-      <c r="A4" s="30" t="s">
-        <v>176</v>
-      </c>
-      <c r="B4" s="28" t="s">
-        <v>177</v>
-      </c>
-      <c r="C4" s="41" t="s">
+      <c r="A4" s="23" t="s">
+        <v>222</v>
+      </c>
+      <c r="B4" s="21" t="s">
+        <v>223</v>
+      </c>
+      <c r="C4" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="D4" s="28" t="s">
-        <v>178</v>
-      </c>
-      <c r="E4" s="27" t="s">
-        <v>147</v>
-      </c>
-      <c r="F4" s="28" t="s">
-        <v>179</v>
-      </c>
-      <c r="G4" s="28" t="s">
-        <v>180</v>
-      </c>
-      <c r="H4" s="42" t="s">
+      <c r="D4" s="21" t="s">
+        <v>224</v>
+      </c>
+      <c r="E4" s="21" t="s">
+        <v>193</v>
+      </c>
+      <c r="F4" s="21" t="s">
+        <v>225</v>
+      </c>
+      <c r="G4" s="21" t="s">
+        <v>226</v>
+      </c>
+      <c r="H4" s="33" t="s">
         <v>70</v>
       </c>
-      <c r="I4" s="27" t="s">
-        <v>181</v>
-      </c>
-      <c r="J4" s="30"/>
+      <c r="I4" s="21" t="s">
+        <v>227</v>
+      </c>
+      <c r="J4" s="23"/>
     </row>
     <row r="5" ht="42.0" customHeight="1">
-      <c r="A5" s="43" t="s">
-        <v>182</v>
-      </c>
-      <c r="B5" s="25" t="s">
-        <v>183</v>
-      </c>
-      <c r="C5" s="44" t="s">
+      <c r="A5" s="34" t="s">
+        <v>228</v>
+      </c>
+      <c r="B5" s="20" t="s">
+        <v>229</v>
+      </c>
+      <c r="C5" s="35" t="s">
         <v>97</v>
       </c>
-      <c r="D5" s="25" t="s">
-        <v>178</v>
-      </c>
-      <c r="E5" s="24" t="s">
-        <v>147</v>
-      </c>
-      <c r="F5" s="24" t="s">
-        <v>184</v>
-      </c>
-      <c r="G5" s="25" t="s">
-        <v>180</v>
-      </c>
-      <c r="H5" s="42" t="s">
+      <c r="D5" s="20" t="s">
+        <v>224</v>
+      </c>
+      <c r="E5" s="20" t="s">
+        <v>193</v>
+      </c>
+      <c r="F5" s="20" t="s">
+        <v>230</v>
+      </c>
+      <c r="G5" s="20" t="s">
+        <v>226</v>
+      </c>
+      <c r="H5" s="33" t="s">
         <v>70</v>
       </c>
-      <c r="I5" s="24" t="s">
-        <v>185</v>
-      </c>
-      <c r="J5" s="43"/>
+      <c r="I5" s="20" t="s">
+        <v>231</v>
+      </c>
+      <c r="J5" s="34"/>
     </row>
     <row r="6" ht="42.0" customHeight="1">
-      <c r="A6" s="30" t="s">
-        <v>186</v>
-      </c>
-      <c r="B6" s="28" t="s">
-        <v>187</v>
-      </c>
-      <c r="C6" s="41" t="s">
+      <c r="A6" s="23" t="s">
+        <v>232</v>
+      </c>
+      <c r="B6" s="21" t="s">
+        <v>233</v>
+      </c>
+      <c r="C6" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="D6" s="28" t="s">
-        <v>178</v>
-      </c>
-      <c r="E6" s="27" t="s">
-        <v>147</v>
-      </c>
-      <c r="F6" s="28" t="s">
-        <v>188</v>
-      </c>
-      <c r="G6" s="28" t="s">
+      <c r="D6" s="21" t="s">
+        <v>224</v>
+      </c>
+      <c r="E6" s="21" t="s">
+        <v>193</v>
+      </c>
+      <c r="F6" s="21" t="s">
+        <v>234</v>
+      </c>
+      <c r="G6" s="21" t="s">
         <v>112</v>
       </c>
-      <c r="H6" s="42" t="s">
+      <c r="H6" s="33" t="s">
         <v>70</v>
       </c>
-      <c r="I6" s="27" t="s">
-        <v>189</v>
-      </c>
-      <c r="J6" s="30"/>
+      <c r="I6" s="21" t="s">
+        <v>235</v>
+      </c>
+      <c r="J6" s="23"/>
     </row>
     <row r="7" ht="18.0" customHeight="1">
-      <c r="A7" s="38" t="s">
-        <v>190</v>
-      </c>
-      <c r="B7" s="39"/>
-      <c r="C7" s="39"/>
-      <c r="D7" s="39"/>
-      <c r="E7" s="39"/>
-      <c r="F7" s="39"/>
-      <c r="G7" s="39"/>
-      <c r="H7" s="39"/>
-      <c r="I7" s="39"/>
-      <c r="J7" s="40"/>
+      <c r="A7" s="29" t="s">
+        <v>236</v>
+      </c>
+      <c r="B7" s="30"/>
+      <c r="C7" s="30"/>
+      <c r="D7" s="30"/>
+      <c r="E7" s="30"/>
+      <c r="F7" s="30"/>
+      <c r="G7" s="30"/>
+      <c r="H7" s="30"/>
+      <c r="I7" s="30"/>
+      <c r="J7" s="31"/>
     </row>
     <row r="8" ht="42.0" customHeight="1">
-      <c r="A8" s="30" t="s">
-        <v>191</v>
-      </c>
-      <c r="B8" s="28" t="s">
-        <v>192</v>
-      </c>
-      <c r="C8" s="46" t="s">
+      <c r="A8" s="23" t="s">
+        <v>237</v>
+      </c>
+      <c r="B8" s="21" t="s">
+        <v>238</v>
+      </c>
+      <c r="C8" s="43" t="s">
         <v>139</v>
       </c>
-      <c r="D8" s="28" t="s">
-        <v>178</v>
-      </c>
-      <c r="E8" s="27" t="s">
-        <v>147</v>
-      </c>
-      <c r="F8" s="28" t="s">
+      <c r="D8" s="21" t="s">
+        <v>224</v>
+      </c>
+      <c r="E8" s="21" t="s">
+        <v>193</v>
+      </c>
+      <c r="F8" s="21" t="s">
         <v>141</v>
       </c>
-      <c r="G8" s="27" t="s">
+      <c r="G8" s="21" t="s">
+        <v>239</v>
+      </c>
+      <c r="H8" s="33" t="s">
+        <v>70</v>
+      </c>
+      <c r="I8" s="21" t="s">
+        <v>240</v>
+      </c>
+      <c r="J8" s="23"/>
+    </row>
+    <row r="9" ht="42.0" customHeight="1">
+      <c r="A9" s="34" t="s">
+        <v>241</v>
+      </c>
+      <c r="B9" s="20" t="s">
+        <v>242</v>
+      </c>
+      <c r="C9" s="44" t="s">
+        <v>206</v>
+      </c>
+      <c r="D9" s="20" t="s">
+        <v>224</v>
+      </c>
+      <c r="E9" s="20" t="s">
         <v>193</v>
       </c>
-      <c r="H8" s="42" t="s">
+      <c r="F9" s="20" t="s">
+        <v>243</v>
+      </c>
+      <c r="G9" s="20" t="s">
+        <v>244</v>
+      </c>
+      <c r="H9" s="33" t="s">
         <v>70</v>
       </c>
-      <c r="I8" s="28" t="s">
-        <v>194</v>
-      </c>
-      <c r="J8" s="30"/>
-    </row>
-    <row r="9" ht="42.0" customHeight="1">
-      <c r="A9" s="43" t="s">
-        <v>195</v>
-      </c>
-      <c r="B9" s="25" t="s">
-        <v>196</v>
-      </c>
-      <c r="C9" s="47" t="s">
-        <v>160</v>
-      </c>
-      <c r="D9" s="25" t="s">
-        <v>178</v>
-      </c>
-      <c r="E9" s="24" t="s">
-        <v>147</v>
-      </c>
-      <c r="F9" s="25" t="s">
-        <v>197</v>
-      </c>
-      <c r="G9" s="25" t="s">
-        <v>198</v>
-      </c>
-      <c r="H9" s="42" t="s">
+      <c r="I9" s="20" t="s">
+        <v>245</v>
+      </c>
+      <c r="J9" s="34"/>
+    </row>
+    <row r="10" ht="42.0" customHeight="1">
+      <c r="A10" s="23" t="s">
+        <v>246</v>
+      </c>
+      <c r="B10" s="21" t="s">
+        <v>247</v>
+      </c>
+      <c r="C10" s="45" t="s">
+        <v>206</v>
+      </c>
+      <c r="D10" s="21" t="s">
+        <v>224</v>
+      </c>
+      <c r="E10" s="21" t="s">
+        <v>193</v>
+      </c>
+      <c r="F10" s="21" t="s">
+        <v>248</v>
+      </c>
+      <c r="G10" s="21" t="s">
+        <v>239</v>
+      </c>
+      <c r="H10" s="33" t="s">
         <v>70</v>
       </c>
-      <c r="I9" s="24" t="s">
-        <v>199</v>
-      </c>
-      <c r="J9" s="43"/>
-    </row>
-    <row r="10" ht="42.0" customHeight="1">
-      <c r="A10" s="30" t="s">
-        <v>200</v>
-      </c>
-      <c r="B10" s="28" t="s">
-        <v>201</v>
-      </c>
-      <c r="C10" s="48" t="s">
-        <v>160</v>
-      </c>
-      <c r="D10" s="28" t="s">
-        <v>178</v>
-      </c>
-      <c r="E10" s="27" t="s">
-        <v>147</v>
-      </c>
-      <c r="F10" s="28" t="s">
-        <v>202</v>
-      </c>
-      <c r="G10" s="28" t="s">
+      <c r="I10" s="21" t="s">
+        <v>249</v>
+      </c>
+      <c r="J10" s="23"/>
+    </row>
+    <row r="11" ht="42.0" customHeight="1">
+      <c r="A11" s="34" t="s">
+        <v>250</v>
+      </c>
+      <c r="B11" s="20" t="s">
+        <v>251</v>
+      </c>
+      <c r="C11" s="44" t="s">
+        <v>206</v>
+      </c>
+      <c r="D11" s="20" t="s">
+        <v>224</v>
+      </c>
+      <c r="E11" s="20" t="s">
         <v>193</v>
       </c>
-      <c r="H10" s="42" t="s">
+      <c r="F11" s="20" t="s">
+        <v>252</v>
+      </c>
+      <c r="G11" s="20" t="s">
+        <v>253</v>
+      </c>
+      <c r="H11" s="33" t="s">
         <v>70</v>
       </c>
-      <c r="I10" s="27" t="s">
-        <v>203</v>
-      </c>
-      <c r="J10" s="30"/>
-    </row>
-    <row r="11" ht="42.0" customHeight="1">
-      <c r="A11" s="43" t="s">
-        <v>204</v>
-      </c>
-      <c r="B11" s="25" t="s">
-        <v>205</v>
-      </c>
-      <c r="C11" s="47" t="s">
-        <v>160</v>
-      </c>
-      <c r="D11" s="25" t="s">
-        <v>178</v>
-      </c>
-      <c r="E11" s="24" t="s">
-        <v>147</v>
-      </c>
-      <c r="F11" s="25" t="s">
-        <v>206</v>
-      </c>
-      <c r="G11" s="25" t="s">
-        <v>207</v>
-      </c>
-      <c r="H11" s="42" t="s">
+      <c r="I11" s="20" t="s">
+        <v>254</v>
+      </c>
+      <c r="J11" s="34"/>
+    </row>
+    <row r="12" ht="42.0" customHeight="1">
+      <c r="A12" s="23" t="s">
+        <v>255</v>
+      </c>
+      <c r="B12" s="21" t="s">
+        <v>256</v>
+      </c>
+      <c r="C12" s="43" t="s">
+        <v>139</v>
+      </c>
+      <c r="D12" s="21" t="s">
+        <v>224</v>
+      </c>
+      <c r="E12" s="21" t="s">
+        <v>193</v>
+      </c>
+      <c r="F12" s="21" t="s">
+        <v>141</v>
+      </c>
+      <c r="G12" s="21" t="s">
+        <v>166</v>
+      </c>
+      <c r="H12" s="33" t="s">
         <v>70</v>
       </c>
-      <c r="I11" s="24" t="s">
-        <v>208</v>
-      </c>
-      <c r="J11" s="43"/>
-    </row>
-    <row r="12" ht="42.0" customHeight="1">
-      <c r="A12" s="30" t="s">
-        <v>209</v>
-      </c>
-      <c r="B12" s="28" t="s">
-        <v>210</v>
-      </c>
-      <c r="C12" s="46" t="s">
-        <v>139</v>
-      </c>
-      <c r="D12" s="28" t="s">
-        <v>178</v>
-      </c>
-      <c r="E12" s="27" t="s">
-        <v>147</v>
-      </c>
-      <c r="F12" s="28" t="s">
-        <v>141</v>
-      </c>
-      <c r="G12" s="28" t="s">
-        <v>211</v>
-      </c>
-      <c r="H12" s="42" t="s">
-        <v>70</v>
-      </c>
-      <c r="I12" s="27" t="s">
-        <v>212</v>
-      </c>
-      <c r="J12" s="30"/>
+      <c r="I12" s="21" t="s">
+        <v>257</v>
+      </c>
+      <c r="J12" s="23"/>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>
     <row r="22" ht="15.75" customHeight="1"/>
@@ -12680,641 +13106,644 @@
   </cols>
   <sheetData>
     <row r="1" ht="24.0" customHeight="1">
-      <c r="A1" s="35" t="s">
-        <v>213</v>
-      </c>
-      <c r="B1" s="36"/>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36"/>
-      <c r="E1" s="36"/>
-      <c r="F1" s="36"/>
-      <c r="G1" s="36"/>
-      <c r="H1" s="36"/>
-      <c r="I1" s="36"/>
-      <c r="J1" s="37"/>
+      <c r="A1" s="27" t="s">
+        <v>258</v>
+      </c>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+      <c r="H1" s="28"/>
+      <c r="I1" s="28"/>
+      <c r="J1" s="28"/>
     </row>
     <row r="2" ht="21.75" customHeight="1">
-      <c r="A2" s="29" t="s">
+      <c r="A2" s="22" t="s">
         <v>85</v>
       </c>
-      <c r="B2" s="29" t="s">
+      <c r="B2" s="22" t="s">
         <v>86</v>
       </c>
-      <c r="C2" s="29" t="s">
+      <c r="C2" s="22" t="s">
         <v>87</v>
       </c>
-      <c r="D2" s="29" t="s">
+      <c r="D2" s="22" t="s">
         <v>88</v>
       </c>
-      <c r="E2" s="29" t="s">
+      <c r="E2" s="22" t="s">
         <v>89</v>
       </c>
-      <c r="F2" s="29" t="s">
+      <c r="F2" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="G2" s="29" t="s">
+      <c r="G2" s="22" t="s">
         <v>90</v>
       </c>
-      <c r="H2" s="29" t="s">
+      <c r="H2" s="22" t="s">
         <v>91</v>
       </c>
-      <c r="I2" s="29" t="s">
+      <c r="I2" s="22" t="s">
         <v>92</v>
       </c>
-      <c r="J2" s="29" t="s">
+      <c r="J2" s="22" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="3" ht="18.0" customHeight="1">
-      <c r="A3" s="38" t="s">
-        <v>214</v>
-      </c>
-      <c r="B3" s="39"/>
-      <c r="C3" s="39"/>
-      <c r="D3" s="39"/>
-      <c r="E3" s="39"/>
-      <c r="F3" s="39"/>
-      <c r="G3" s="39"/>
-      <c r="H3" s="39"/>
-      <c r="I3" s="39"/>
-      <c r="J3" s="40"/>
+      <c r="A3" s="29" t="s">
+        <v>259</v>
+      </c>
+      <c r="B3" s="30"/>
+      <c r="C3" s="30"/>
+      <c r="D3" s="30"/>
+      <c r="E3" s="30"/>
+      <c r="F3" s="30"/>
+      <c r="G3" s="30"/>
+      <c r="H3" s="30"/>
+      <c r="I3" s="30"/>
+      <c r="J3" s="31"/>
     </row>
     <row r="4" ht="42.0" customHeight="1">
-      <c r="A4" s="30" t="s">
-        <v>215</v>
-      </c>
-      <c r="B4" s="28" t="s">
-        <v>216</v>
-      </c>
-      <c r="C4" s="41" t="s">
+      <c r="A4" s="23" t="s">
+        <v>260</v>
+      </c>
+      <c r="B4" s="21" t="s">
+        <v>261</v>
+      </c>
+      <c r="C4" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="D4" s="28" t="s">
-        <v>217</v>
-      </c>
-      <c r="E4" s="27" t="s">
-        <v>147</v>
-      </c>
-      <c r="F4" s="28" t="s">
-        <v>218</v>
-      </c>
-      <c r="G4" s="28" t="s">
-        <v>219</v>
-      </c>
-      <c r="H4" s="42" t="s">
+      <c r="D4" s="21" t="s">
+        <v>262</v>
+      </c>
+      <c r="E4" s="21" t="s">
+        <v>193</v>
+      </c>
+      <c r="F4" s="21" t="s">
+        <v>263</v>
+      </c>
+      <c r="G4" s="21" t="s">
+        <v>264</v>
+      </c>
+      <c r="H4" s="33" t="s">
         <v>70</v>
       </c>
-      <c r="I4" s="28" t="s">
-        <v>220</v>
-      </c>
-      <c r="J4" s="30"/>
+      <c r="I4" s="21" t="s">
+        <v>265</v>
+      </c>
+      <c r="J4" s="23"/>
     </row>
     <row r="5" ht="42.0" customHeight="1">
-      <c r="A5" s="43" t="s">
-        <v>221</v>
-      </c>
-      <c r="B5" s="25" t="s">
-        <v>222</v>
-      </c>
-      <c r="C5" s="44" t="s">
+      <c r="A5" s="34" t="s">
+        <v>266</v>
+      </c>
+      <c r="B5" s="20" t="s">
+        <v>267</v>
+      </c>
+      <c r="C5" s="35" t="s">
         <v>97</v>
       </c>
-      <c r="D5" s="25" t="s">
-        <v>217</v>
-      </c>
-      <c r="E5" s="24" t="s">
-        <v>147</v>
-      </c>
-      <c r="F5" s="24" t="s">
-        <v>223</v>
-      </c>
-      <c r="G5" s="25" t="s">
-        <v>224</v>
-      </c>
-      <c r="H5" s="42" t="s">
+      <c r="D5" s="20" t="s">
+        <v>262</v>
+      </c>
+      <c r="E5" s="20" t="s">
+        <v>193</v>
+      </c>
+      <c r="F5" s="20" t="s">
+        <v>268</v>
+      </c>
+      <c r="G5" s="20" t="s">
+        <v>269</v>
+      </c>
+      <c r="H5" s="33" t="s">
         <v>70</v>
       </c>
-      <c r="I5" s="25" t="s">
-        <v>225</v>
-      </c>
-      <c r="J5" s="43"/>
+      <c r="I5" s="20" t="s">
+        <v>270</v>
+      </c>
+      <c r="J5" s="34"/>
     </row>
     <row r="6" ht="42.0" customHeight="1">
-      <c r="A6" s="30" t="s">
-        <v>226</v>
-      </c>
-      <c r="B6" s="28" t="s">
-        <v>227</v>
-      </c>
-      <c r="C6" s="41" t="s">
+      <c r="A6" s="23" t="s">
+        <v>271</v>
+      </c>
+      <c r="B6" s="21" t="s">
+        <v>272</v>
+      </c>
+      <c r="C6" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="D6" s="28" t="s">
-        <v>217</v>
-      </c>
-      <c r="E6" s="27" t="s">
-        <v>147</v>
-      </c>
-      <c r="F6" s="28" t="s">
-        <v>228</v>
-      </c>
-      <c r="G6" s="28" t="s">
+      <c r="D6" s="21" t="s">
+        <v>262</v>
+      </c>
+      <c r="E6" s="21" t="s">
+        <v>193</v>
+      </c>
+      <c r="F6" s="21" t="s">
+        <v>273</v>
+      </c>
+      <c r="G6" s="21" t="s">
         <v>117</v>
       </c>
-      <c r="H6" s="42" t="s">
+      <c r="H6" s="33" t="s">
         <v>70</v>
       </c>
-      <c r="I6" s="27" t="s">
-        <v>229</v>
-      </c>
-      <c r="J6" s="30"/>
+      <c r="I6" s="21" t="s">
+        <v>274</v>
+      </c>
+      <c r="J6" s="23"/>
     </row>
     <row r="7" ht="18.0" customHeight="1">
-      <c r="A7" s="38" t="s">
-        <v>230</v>
-      </c>
-      <c r="B7" s="39"/>
-      <c r="C7" s="39"/>
-      <c r="D7" s="39"/>
-      <c r="E7" s="39"/>
-      <c r="F7" s="39"/>
-      <c r="G7" s="39"/>
-      <c r="H7" s="39"/>
-      <c r="I7" s="39"/>
-      <c r="J7" s="40"/>
+      <c r="A7" s="29" t="s">
+        <v>275</v>
+      </c>
+      <c r="B7" s="30"/>
+      <c r="C7" s="30"/>
+      <c r="D7" s="30"/>
+      <c r="E7" s="30"/>
+      <c r="F7" s="30"/>
+      <c r="G7" s="30"/>
+      <c r="H7" s="30"/>
+      <c r="I7" s="30"/>
+      <c r="J7" s="31"/>
     </row>
     <row r="8" ht="42.0" customHeight="1">
-      <c r="A8" s="31" t="s">
-        <v>231</v>
-      </c>
-      <c r="B8" s="49" t="s">
-        <v>232</v>
-      </c>
-      <c r="C8" s="46" t="s">
+      <c r="A8" s="23" t="s">
+        <v>276</v>
+      </c>
+      <c r="B8" s="46" t="s">
+        <v>277</v>
+      </c>
+      <c r="C8" s="43" t="s">
         <v>139</v>
       </c>
-      <c r="D8" s="49" t="s">
-        <v>217</v>
-      </c>
-      <c r="E8" s="50" t="s">
-        <v>147</v>
-      </c>
-      <c r="F8" s="49" t="s">
+      <c r="D8" s="46" t="s">
+        <v>262</v>
+      </c>
+      <c r="E8" s="46" t="s">
+        <v>193</v>
+      </c>
+      <c r="F8" s="46" t="s">
         <v>141</v>
       </c>
-      <c r="G8" s="49" t="s">
-        <v>233</v>
-      </c>
-      <c r="H8" s="51" t="s">
+      <c r="G8" s="46" t="s">
+        <v>278</v>
+      </c>
+      <c r="H8" s="47" t="s">
         <v>70</v>
       </c>
-      <c r="I8" s="50" t="s">
-        <v>234</v>
-      </c>
-      <c r="J8" s="52"/>
-      <c r="K8" s="53"/>
-      <c r="L8" s="53"/>
-      <c r="M8" s="53"/>
-      <c r="N8" s="53"/>
-      <c r="O8" s="53"/>
-      <c r="P8" s="53"/>
-      <c r="Q8" s="53"/>
-      <c r="R8" s="53"/>
-      <c r="S8" s="53"/>
-      <c r="T8" s="53"/>
-      <c r="U8" s="53"/>
-      <c r="V8" s="53"/>
-      <c r="W8" s="53"/>
-      <c r="X8" s="53"/>
-      <c r="Y8" s="53"/>
-      <c r="Z8" s="53"/>
+      <c r="I8" s="46" t="s">
+        <v>279</v>
+      </c>
+      <c r="J8" s="48"/>
+      <c r="K8" s="49"/>
+      <c r="L8" s="49"/>
+      <c r="M8" s="49"/>
+      <c r="N8" s="49"/>
+      <c r="O8" s="49"/>
+      <c r="P8" s="49"/>
+      <c r="Q8" s="49"/>
+      <c r="R8" s="49"/>
+      <c r="S8" s="49"/>
+      <c r="T8" s="49"/>
+      <c r="U8" s="49"/>
+      <c r="V8" s="49"/>
+      <c r="W8" s="49"/>
+      <c r="X8" s="49"/>
+      <c r="Y8" s="49"/>
+      <c r="Z8" s="49"/>
     </row>
     <row r="9" ht="42.0" customHeight="1">
-      <c r="A9" s="54" t="s">
-        <v>235</v>
-      </c>
-      <c r="B9" s="55" t="s">
-        <v>236</v>
-      </c>
-      <c r="C9" s="56" t="s">
+      <c r="A9" s="50" t="s">
+        <v>280</v>
+      </c>
+      <c r="B9" s="51" t="s">
+        <v>281</v>
+      </c>
+      <c r="C9" s="52" t="s">
         <v>139</v>
       </c>
-      <c r="D9" s="55" t="s">
-        <v>237</v>
-      </c>
-      <c r="E9" s="57" t="s">
-        <v>147</v>
-      </c>
-      <c r="F9" s="55" t="s">
+      <c r="D9" s="51" t="s">
+        <v>282</v>
+      </c>
+      <c r="E9" s="51" t="s">
+        <v>193</v>
+      </c>
+      <c r="F9" s="51" t="s">
         <v>141</v>
       </c>
-      <c r="G9" s="55" t="s">
-        <v>238</v>
-      </c>
-      <c r="H9" s="42" t="s">
+      <c r="G9" s="51" t="s">
+        <v>283</v>
+      </c>
+      <c r="H9" s="33" t="s">
         <v>70</v>
       </c>
-      <c r="I9" s="57" t="s">
-        <v>239</v>
-      </c>
-      <c r="J9" s="30"/>
+      <c r="I9" s="51" t="s">
+        <v>284</v>
+      </c>
+      <c r="J9" s="23"/>
     </row>
     <row r="10" ht="42.0" customHeight="1">
-      <c r="A10" s="31" t="s">
-        <v>240</v>
-      </c>
-      <c r="B10" s="28" t="s">
-        <v>241</v>
-      </c>
-      <c r="C10" s="46" t="s">
+      <c r="A10" s="23" t="s">
+        <v>285</v>
+      </c>
+      <c r="B10" s="21" t="s">
+        <v>286</v>
+      </c>
+      <c r="C10" s="43" t="s">
         <v>139</v>
       </c>
-      <c r="D10" s="27" t="s">
-        <v>242</v>
-      </c>
-      <c r="E10" s="27" t="s">
-        <v>147</v>
-      </c>
-      <c r="F10" s="28" t="str">
+      <c r="D10" s="21" t="s">
+        <v>287</v>
+      </c>
+      <c r="E10" s="21" t="s">
+        <v>193</v>
+      </c>
+      <c r="F10" s="21" t="str">
         <f>Variables!C8</f>
         <v>c7cf918d-7e04-4104-9790-fa5bb9d3756d</v>
       </c>
-      <c r="G10" s="28" t="s">
-        <v>243</v>
-      </c>
-      <c r="H10" s="42" t="s">
+      <c r="G10" s="21" t="s">
+        <v>288</v>
+      </c>
+      <c r="H10" s="33" t="s">
         <v>70</v>
       </c>
-      <c r="I10" s="27" t="s">
-        <v>244</v>
-      </c>
-      <c r="J10" s="43"/>
+      <c r="I10" s="21" t="s">
+        <v>289</v>
+      </c>
+      <c r="J10" s="34"/>
     </row>
     <row r="11" ht="42.0" customHeight="1">
-      <c r="A11" s="58" t="s">
-        <v>245</v>
-      </c>
-      <c r="B11" s="25" t="s">
-        <v>246</v>
-      </c>
-      <c r="C11" s="45" t="s">
+      <c r="A11" s="34" t="s">
+        <v>290</v>
+      </c>
+      <c r="B11" s="20" t="s">
+        <v>291</v>
+      </c>
+      <c r="C11" s="36" t="s">
         <v>139</v>
       </c>
-      <c r="D11" s="25" t="s">
-        <v>247</v>
-      </c>
-      <c r="E11" s="24" t="s">
-        <v>147</v>
-      </c>
-      <c r="F11" s="25" t="s">
+      <c r="D11" s="20" t="s">
+        <v>292</v>
+      </c>
+      <c r="E11" s="20" t="s">
+        <v>193</v>
+      </c>
+      <c r="F11" s="20" t="s">
         <v>141</v>
       </c>
-      <c r="G11" s="25" t="s">
-        <v>248</v>
-      </c>
-      <c r="H11" s="42" t="s">
+      <c r="G11" s="20" t="s">
+        <v>293</v>
+      </c>
+      <c r="H11" s="33" t="s">
         <v>70</v>
       </c>
-      <c r="I11" s="24" t="s">
-        <v>249</v>
-      </c>
-      <c r="J11" s="43"/>
+      <c r="I11" s="20" t="s">
+        <v>294</v>
+      </c>
+      <c r="J11" s="34"/>
     </row>
     <row r="12" ht="42.0" customHeight="1">
-      <c r="A12" s="31" t="s">
-        <v>250</v>
-      </c>
-      <c r="B12" s="59" t="s">
-        <v>251</v>
-      </c>
-      <c r="C12" s="46" t="s">
+      <c r="A12" s="23" t="s">
+        <v>295</v>
+      </c>
+      <c r="B12" s="46" t="s">
+        <v>296</v>
+      </c>
+      <c r="C12" s="43" t="s">
         <v>139</v>
       </c>
-      <c r="D12" s="59" t="s">
-        <v>252</v>
-      </c>
-      <c r="E12" s="50" t="s">
-        <v>147</v>
-      </c>
-      <c r="F12" s="28" t="str">
+      <c r="D12" s="46" t="s">
+        <v>297</v>
+      </c>
+      <c r="E12" s="46" t="s">
+        <v>193</v>
+      </c>
+      <c r="F12" s="21" t="str">
         <f>Variables!C8</f>
         <v>c7cf918d-7e04-4104-9790-fa5bb9d3756d</v>
       </c>
-      <c r="G12" s="59" t="s">
-        <v>253</v>
-      </c>
-      <c r="H12" s="60" t="s">
+      <c r="G12" s="46" t="s">
+        <v>298</v>
+      </c>
+      <c r="H12" s="47" t="s">
         <v>70</v>
       </c>
-      <c r="I12" s="59" t="s">
-        <v>254</v>
-      </c>
-      <c r="J12" s="52"/>
-      <c r="K12" s="53"/>
-      <c r="L12" s="53"/>
-      <c r="M12" s="53"/>
-      <c r="N12" s="53"/>
-      <c r="O12" s="53"/>
-      <c r="P12" s="53"/>
-      <c r="Q12" s="53"/>
-      <c r="R12" s="53"/>
-      <c r="S12" s="53"/>
-      <c r="T12" s="53"/>
-      <c r="U12" s="53"/>
-      <c r="V12" s="53"/>
-      <c r="W12" s="53"/>
-      <c r="X12" s="53"/>
-      <c r="Y12" s="53"/>
-      <c r="Z12" s="53"/>
+      <c r="I12" s="46" t="s">
+        <v>299</v>
+      </c>
+      <c r="J12" s="48"/>
+      <c r="K12" s="49"/>
+      <c r="L12" s="49"/>
+      <c r="M12" s="49"/>
+      <c r="N12" s="49"/>
+      <c r="O12" s="49"/>
+      <c r="P12" s="49"/>
+      <c r="Q12" s="49"/>
+      <c r="R12" s="49"/>
+      <c r="S12" s="49"/>
+      <c r="T12" s="49"/>
+      <c r="U12" s="49"/>
+      <c r="V12" s="49"/>
+      <c r="W12" s="49"/>
+      <c r="X12" s="49"/>
+      <c r="Y12" s="49"/>
+      <c r="Z12" s="49"/>
     </row>
     <row r="13" ht="42.0" customHeight="1">
-      <c r="A13" s="58" t="s">
-        <v>255</v>
-      </c>
-      <c r="B13" s="61" t="s">
-        <v>256</v>
-      </c>
-      <c r="C13" s="45" t="s">
+      <c r="A13" s="34" t="s">
+        <v>300</v>
+      </c>
+      <c r="B13" s="53" t="s">
+        <v>301</v>
+      </c>
+      <c r="C13" s="36" t="s">
         <v>139</v>
       </c>
-      <c r="D13" s="61" t="s">
-        <v>257</v>
-      </c>
-      <c r="E13" s="62" t="s">
-        <v>147</v>
-      </c>
-      <c r="F13" s="61" t="s">
-        <v>258</v>
-      </c>
-      <c r="G13" s="61" t="s">
-        <v>259</v>
-      </c>
-      <c r="H13" s="60" t="s">
+      <c r="D13" s="53" t="s">
+        <v>302</v>
+      </c>
+      <c r="E13" s="53" t="s">
+        <v>193</v>
+      </c>
+      <c r="F13" s="53" t="s">
+        <v>303</v>
+      </c>
+      <c r="G13" s="53" t="s">
+        <v>304</v>
+      </c>
+      <c r="H13" s="47" t="s">
         <v>70</v>
       </c>
-      <c r="I13" s="61" t="s">
-        <v>260</v>
-      </c>
-      <c r="J13" s="52"/>
-      <c r="K13" s="53"/>
-      <c r="L13" s="53"/>
-      <c r="M13" s="53"/>
-      <c r="N13" s="53"/>
-      <c r="O13" s="53"/>
-      <c r="P13" s="53"/>
-      <c r="Q13" s="53"/>
-      <c r="R13" s="53"/>
-      <c r="S13" s="53"/>
-      <c r="T13" s="53"/>
-      <c r="U13" s="53"/>
-      <c r="V13" s="53"/>
-      <c r="W13" s="53"/>
-      <c r="X13" s="53"/>
-      <c r="Y13" s="53"/>
-      <c r="Z13" s="53"/>
+      <c r="I13" s="53" t="s">
+        <v>305</v>
+      </c>
+      <c r="J13" s="48"/>
+      <c r="K13" s="49"/>
+      <c r="L13" s="49"/>
+      <c r="M13" s="49"/>
+      <c r="N13" s="49"/>
+      <c r="O13" s="49"/>
+      <c r="P13" s="49"/>
+      <c r="Q13" s="49"/>
+      <c r="R13" s="49"/>
+      <c r="S13" s="49"/>
+      <c r="T13" s="49"/>
+      <c r="U13" s="49"/>
+      <c r="V13" s="49"/>
+      <c r="W13" s="49"/>
+      <c r="X13" s="49"/>
+      <c r="Y13" s="49"/>
+      <c r="Z13" s="49"/>
     </row>
     <row r="14" ht="42.0" customHeight="1">
-      <c r="A14" s="31" t="s">
-        <v>261</v>
-      </c>
-      <c r="B14" s="59" t="s">
-        <v>262</v>
-      </c>
-      <c r="C14" s="46" t="s">
+      <c r="A14" s="23" t="s">
+        <v>306</v>
+      </c>
+      <c r="B14" s="46" t="s">
+        <v>307</v>
+      </c>
+      <c r="C14" s="43" t="s">
         <v>139</v>
       </c>
-      <c r="D14" s="59" t="s">
-        <v>263</v>
-      </c>
-      <c r="E14" s="50" t="s">
-        <v>147</v>
-      </c>
-      <c r="F14" s="59" t="s">
+      <c r="D14" s="46" t="s">
+        <v>308</v>
+      </c>
+      <c r="E14" s="46" t="s">
+        <v>193</v>
+      </c>
+      <c r="F14" s="46" t="s">
         <v>141</v>
       </c>
-      <c r="G14" s="59" t="s">
-        <v>248</v>
-      </c>
-      <c r="H14" s="60" t="s">
+      <c r="G14" s="46" t="s">
+        <v>293</v>
+      </c>
+      <c r="H14" s="47" t="s">
         <v>70</v>
       </c>
-      <c r="I14" s="59" t="s">
-        <v>264</v>
-      </c>
-      <c r="J14" s="63"/>
-      <c r="K14" s="53"/>
-      <c r="L14" s="53"/>
-      <c r="M14" s="53"/>
-      <c r="N14" s="53"/>
-      <c r="O14" s="53"/>
-      <c r="P14" s="53"/>
-      <c r="Q14" s="53"/>
-      <c r="R14" s="53"/>
-      <c r="S14" s="53"/>
-      <c r="T14" s="53"/>
-      <c r="U14" s="53"/>
-      <c r="V14" s="53"/>
-      <c r="W14" s="53"/>
-      <c r="X14" s="53"/>
-      <c r="Y14" s="53"/>
-      <c r="Z14" s="53"/>
+      <c r="I14" s="46" t="s">
+        <v>309</v>
+      </c>
+      <c r="J14" s="54"/>
+      <c r="K14" s="49"/>
+      <c r="L14" s="49"/>
+      <c r="M14" s="49"/>
+      <c r="N14" s="49"/>
+      <c r="O14" s="49"/>
+      <c r="P14" s="49"/>
+      <c r="Q14" s="49"/>
+      <c r="R14" s="49"/>
+      <c r="S14" s="49"/>
+      <c r="T14" s="49"/>
+      <c r="U14" s="49"/>
+      <c r="V14" s="49"/>
+      <c r="W14" s="49"/>
+      <c r="X14" s="49"/>
+      <c r="Y14" s="49"/>
+      <c r="Z14" s="49"/>
     </row>
     <row r="15" ht="42.0" customHeight="1">
-      <c r="A15" s="58" t="s">
-        <v>265</v>
-      </c>
-      <c r="B15" s="61" t="s">
-        <v>266</v>
-      </c>
-      <c r="C15" s="45" t="s">
+      <c r="A15" s="34" t="s">
+        <v>310</v>
+      </c>
+      <c r="B15" s="53" t="s">
+        <v>311</v>
+      </c>
+      <c r="C15" s="36" t="s">
         <v>139</v>
       </c>
-      <c r="D15" s="61" t="s">
-        <v>242</v>
-      </c>
-      <c r="E15" s="62" t="s">
-        <v>147</v>
-      </c>
-      <c r="F15" s="61" t="str">
+      <c r="D15" s="53" t="s">
+        <v>287</v>
+      </c>
+      <c r="E15" s="53" t="s">
+        <v>193</v>
+      </c>
+      <c r="F15" s="53" t="str">
         <f>Variables!C8</f>
         <v>c7cf918d-7e04-4104-9790-fa5bb9d3756d</v>
       </c>
-      <c r="G15" s="61" t="s">
-        <v>267</v>
-      </c>
-      <c r="H15" s="60" t="s">
+      <c r="G15" s="53" t="s">
+        <v>312</v>
+      </c>
+      <c r="H15" s="47" t="s">
         <v>70</v>
       </c>
-      <c r="I15" s="61" t="s">
-        <v>173</v>
-      </c>
-      <c r="J15" s="52"/>
-      <c r="K15" s="53"/>
-      <c r="L15" s="53"/>
-      <c r="M15" s="53"/>
-      <c r="N15" s="53"/>
-      <c r="O15" s="53"/>
-      <c r="P15" s="53"/>
-      <c r="Q15" s="53"/>
-      <c r="R15" s="53"/>
-      <c r="S15" s="53"/>
-      <c r="T15" s="53"/>
-      <c r="U15" s="53"/>
-      <c r="V15" s="53"/>
-      <c r="W15" s="53"/>
-      <c r="X15" s="53"/>
-      <c r="Y15" s="53"/>
-      <c r="Z15" s="53"/>
+      <c r="I15" s="53" t="s">
+        <v>219</v>
+      </c>
+      <c r="J15" s="48"/>
+      <c r="K15" s="49"/>
+      <c r="L15" s="49"/>
+      <c r="M15" s="49"/>
+      <c r="N15" s="49"/>
+      <c r="O15" s="49"/>
+      <c r="P15" s="49"/>
+      <c r="Q15" s="49"/>
+      <c r="R15" s="49"/>
+      <c r="S15" s="49"/>
+      <c r="T15" s="49"/>
+      <c r="U15" s="49"/>
+      <c r="V15" s="49"/>
+      <c r="W15" s="49"/>
+      <c r="X15" s="49"/>
+      <c r="Y15" s="49"/>
+      <c r="Z15" s="49"/>
     </row>
     <row r="16" ht="18.0" customHeight="1">
-      <c r="A16" s="38" t="s">
-        <v>268</v>
-      </c>
-      <c r="B16" s="39"/>
-      <c r="C16" s="39"/>
-      <c r="D16" s="39"/>
-      <c r="E16" s="39"/>
-      <c r="F16" s="39"/>
-      <c r="G16" s="39"/>
-      <c r="H16" s="39"/>
-      <c r="I16" s="39"/>
-      <c r="J16" s="40"/>
+      <c r="A16" s="29" t="s">
+        <v>313</v>
+      </c>
+      <c r="B16" s="30"/>
+      <c r="C16" s="30"/>
+      <c r="D16" s="30"/>
+      <c r="E16" s="30"/>
+      <c r="F16" s="30"/>
+      <c r="G16" s="30"/>
+      <c r="H16" s="30"/>
+      <c r="I16" s="30"/>
+      <c r="J16" s="31"/>
     </row>
     <row r="17" ht="42.0" customHeight="1">
-      <c r="A17" s="58" t="s">
-        <v>269</v>
-      </c>
-      <c r="B17" s="25" t="s">
-        <v>270</v>
-      </c>
-      <c r="C17" s="47" t="s">
-        <v>160</v>
-      </c>
-      <c r="D17" s="25" t="s">
-        <v>271</v>
-      </c>
-      <c r="E17" s="24" t="s">
-        <v>147</v>
-      </c>
-      <c r="F17" s="25" t="str">
+      <c r="A17" s="34" t="s">
+        <v>314</v>
+      </c>
+      <c r="B17" s="20" t="s">
+        <v>315</v>
+      </c>
+      <c r="C17" s="44" t="s">
+        <v>206</v>
+      </c>
+      <c r="D17" s="20" t="s">
+        <v>316</v>
+      </c>
+      <c r="E17" s="20" t="s">
+        <v>193</v>
+      </c>
+      <c r="F17" s="20" t="str">
         <f>Variables!C8 &amp; ", {""title"":""Compra en supermercado — URGENTE""}"</f>
         <v>c7cf918d-7e04-4104-9790-fa5bb9d3756d, {"title":"Compra en supermercado — URGENTE"}</v>
       </c>
-      <c r="G17" s="25" t="s">
-        <v>272</v>
-      </c>
-      <c r="H17" s="42" t="s">
+      <c r="G17" s="20" t="s">
+        <v>317</v>
+      </c>
+      <c r="H17" s="33" t="s">
         <v>70</v>
       </c>
-      <c r="I17" s="24" t="s">
-        <v>273</v>
-      </c>
-      <c r="J17" s="43"/>
+      <c r="I17" s="20" t="s">
+        <v>318</v>
+      </c>
+      <c r="J17" s="34"/>
     </row>
     <row r="18" ht="42.0" customHeight="1">
-      <c r="A18" s="31" t="s">
-        <v>274</v>
-      </c>
-      <c r="B18" s="27" t="s">
-        <v>275</v>
-      </c>
-      <c r="C18" s="48" t="s">
-        <v>160</v>
-      </c>
-      <c r="D18" s="28" t="s">
-        <v>271</v>
-      </c>
-      <c r="E18" s="27" t="s">
-        <v>147</v>
-      </c>
-      <c r="F18" s="28" t="s">
-        <v>276</v>
-      </c>
-      <c r="G18" s="27" t="s">
-        <v>172</v>
-      </c>
-      <c r="H18" s="42" t="s">
+      <c r="A18" s="23" t="s">
+        <v>319</v>
+      </c>
+      <c r="B18" s="21" t="s">
+        <v>320</v>
+      </c>
+      <c r="C18" s="45" t="s">
+        <v>206</v>
+      </c>
+      <c r="D18" s="21" t="s">
+        <v>316</v>
+      </c>
+      <c r="E18" s="21" t="s">
+        <v>193</v>
+      </c>
+      <c r="F18" s="21" t="s">
+        <v>321</v>
+      </c>
+      <c r="G18" s="21" t="s">
+        <v>218</v>
+      </c>
+      <c r="H18" s="33" t="s">
         <v>70</v>
       </c>
-      <c r="I18" s="61" t="s">
-        <v>173</v>
-      </c>
-      <c r="J18" s="30"/>
+      <c r="I18" s="53" t="s">
+        <v>219</v>
+      </c>
+      <c r="J18" s="23"/>
     </row>
     <row r="19" ht="18.0" customHeight="1">
-      <c r="A19" s="38" t="s">
-        <v>277</v>
-      </c>
-      <c r="B19" s="39"/>
-      <c r="C19" s="39"/>
-      <c r="D19" s="39"/>
-      <c r="E19" s="39"/>
-      <c r="F19" s="39"/>
-      <c r="G19" s="39"/>
-      <c r="H19" s="39"/>
-      <c r="I19" s="39"/>
-      <c r="J19" s="40"/>
+      <c r="A19" s="29" t="s">
+        <v>322</v>
+      </c>
+      <c r="B19" s="30"/>
+      <c r="C19" s="30"/>
+      <c r="D19" s="30"/>
+      <c r="E19" s="30"/>
+      <c r="F19" s="30"/>
+      <c r="G19" s="30"/>
+      <c r="H19" s="30"/>
+      <c r="I19" s="30"/>
+      <c r="J19" s="31"/>
     </row>
     <row r="20" ht="42.0" customHeight="1">
-      <c r="A20" s="31" t="s">
-        <v>278</v>
-      </c>
-      <c r="B20" s="28" t="s">
-        <v>279</v>
-      </c>
-      <c r="C20" s="41" t="s">
+      <c r="A20" s="23" t="s">
+        <v>323</v>
+      </c>
+      <c r="B20" s="21" t="s">
+        <v>324</v>
+      </c>
+      <c r="C20" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="D20" s="28" t="s">
-        <v>280</v>
-      </c>
-      <c r="E20" s="27" t="s">
-        <v>147</v>
-      </c>
-      <c r="F20" s="28" t="s">
+      <c r="D20" s="21" t="s">
+        <v>325</v>
+      </c>
+      <c r="E20" s="21" t="s">
+        <v>193</v>
+      </c>
+      <c r="F20" s="21" t="s">
         <v>141</v>
       </c>
-      <c r="G20" s="28" t="s">
-        <v>281</v>
-      </c>
-      <c r="H20" s="42" t="s">
+      <c r="G20" s="21" t="s">
+        <v>326</v>
+      </c>
+      <c r="H20" s="33" t="s">
         <v>70</v>
       </c>
-      <c r="I20" s="28" t="s">
-        <v>282</v>
-      </c>
-      <c r="J20" s="30"/>
+      <c r="I20" s="21" t="s">
+        <v>327</v>
+      </c>
+      <c r="J20" s="23"/>
     </row>
     <row r="21" ht="42.0" customHeight="1">
-      <c r="A21" s="58" t="s">
-        <v>283</v>
-      </c>
-      <c r="B21" s="25" t="s">
-        <v>284</v>
-      </c>
-      <c r="C21" s="64" t="s">
-        <v>285</v>
-      </c>
-      <c r="D21" s="25" t="s">
-        <v>286</v>
-      </c>
-      <c r="E21" s="24" t="s">
-        <v>147</v>
-      </c>
-      <c r="F21" s="25" t="s">
+      <c r="A21" s="34" t="s">
+        <v>328</v>
+      </c>
+      <c r="B21" s="20" t="s">
+        <v>329</v>
+      </c>
+      <c r="C21" s="55" t="s">
+        <v>330</v>
+      </c>
+      <c r="D21" s="20" t="s">
+        <v>331</v>
+      </c>
+      <c r="E21" s="20" t="s">
+        <v>193</v>
+      </c>
+      <c r="F21" s="20" t="s">
         <v>141</v>
       </c>
-      <c r="G21" s="25" t="s">
-        <v>287</v>
-      </c>
-      <c r="H21" s="42" t="s">
+      <c r="G21" s="20" t="s">
+        <v>332</v>
+      </c>
+      <c r="H21" s="33" t="s">
         <v>70</v>
       </c>
-      <c r="I21" s="24" t="s">
-        <v>288</v>
-      </c>
-      <c r="J21" s="43"/>
-    </row>
+      <c r="I21" s="20" t="s">
+        <v>333</v>
+      </c>
+      <c r="J21" s="34"/>
+    </row>
+    <row r="22" ht="15.75" customHeight="1"/>
+    <row r="23" ht="15.75" customHeight="1"/>
+    <row r="24" ht="15.75" customHeight="1"/>
     <row r="25" ht="15.75" customHeight="1"/>
     <row r="26" ht="15.75" customHeight="1"/>
     <row r="27" ht="15.75" customHeight="1"/>
@@ -14291,10 +14720,6 @@
     <row r="998" ht="15.75" customHeight="1"/>
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
-    <row r="1001" ht="15.75" customHeight="1"/>
-    <row r="1002" ht="15.75" customHeight="1"/>
-    <row r="1003" ht="15.75" customHeight="1"/>
-    <row r="1004" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="A1:J1"/>
@@ -14347,402 +14772,401 @@
     <col customWidth="1" min="8" max="8" width="16.0"/>
     <col customWidth="1" min="9" max="9" width="40.0"/>
     <col customWidth="1" min="10" max="10" width="14.0"/>
-    <col customWidth="1" min="11" max="26" width="8.71"/>
   </cols>
   <sheetData>
     <row r="1" ht="24.0" customHeight="1">
-      <c r="A1" s="35" t="s">
-        <v>289</v>
-      </c>
-      <c r="B1" s="36"/>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36"/>
-      <c r="E1" s="36"/>
-      <c r="F1" s="36"/>
-      <c r="G1" s="36"/>
-      <c r="H1" s="36"/>
-      <c r="I1" s="36"/>
-      <c r="J1" s="37"/>
+      <c r="A1" s="27" t="s">
+        <v>334</v>
+      </c>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+      <c r="H1" s="28"/>
+      <c r="I1" s="28"/>
+      <c r="J1" s="28"/>
     </row>
     <row r="2" ht="21.75" customHeight="1">
-      <c r="A2" s="29" t="s">
+      <c r="A2" s="22" t="s">
         <v>85</v>
       </c>
-      <c r="B2" s="29" t="s">
+      <c r="B2" s="22" t="s">
         <v>86</v>
       </c>
-      <c r="C2" s="29" t="s">
+      <c r="C2" s="22" t="s">
         <v>87</v>
       </c>
-      <c r="D2" s="29" t="s">
+      <c r="D2" s="22" t="s">
         <v>88</v>
       </c>
-      <c r="E2" s="29" t="s">
+      <c r="E2" s="22" t="s">
         <v>89</v>
       </c>
-      <c r="F2" s="29" t="s">
+      <c r="F2" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="G2" s="29" t="s">
+      <c r="G2" s="22" t="s">
         <v>90</v>
       </c>
-      <c r="H2" s="29" t="s">
+      <c r="H2" s="22" t="s">
         <v>91</v>
       </c>
-      <c r="I2" s="29" t="s">
+      <c r="I2" s="22" t="s">
         <v>92</v>
       </c>
-      <c r="J2" s="29" t="s">
+      <c r="J2" s="22" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="3" ht="18.0" customHeight="1">
-      <c r="A3" s="38" t="s">
-        <v>214</v>
-      </c>
-      <c r="B3" s="39"/>
-      <c r="C3" s="39"/>
-      <c r="D3" s="39"/>
-      <c r="E3" s="39"/>
-      <c r="F3" s="39"/>
-      <c r="G3" s="39"/>
-      <c r="H3" s="39"/>
-      <c r="I3" s="39"/>
-      <c r="J3" s="40"/>
+      <c r="A3" s="29" t="s">
+        <v>259</v>
+      </c>
+      <c r="B3" s="30"/>
+      <c r="C3" s="30"/>
+      <c r="D3" s="30"/>
+      <c r="E3" s="30"/>
+      <c r="F3" s="30"/>
+      <c r="G3" s="30"/>
+      <c r="H3" s="30"/>
+      <c r="I3" s="30"/>
+      <c r="J3" s="31"/>
     </row>
     <row r="4" ht="42.0" customHeight="1">
-      <c r="A4" s="30" t="s">
-        <v>290</v>
-      </c>
-      <c r="B4" s="28" t="s">
-        <v>291</v>
-      </c>
-      <c r="C4" s="41" t="s">
+      <c r="A4" s="23" t="s">
+        <v>335</v>
+      </c>
+      <c r="B4" s="21" t="s">
+        <v>336</v>
+      </c>
+      <c r="C4" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="D4" s="28" t="s">
-        <v>292</v>
-      </c>
-      <c r="E4" s="27" t="s">
-        <v>147</v>
-      </c>
-      <c r="F4" s="27" t="s">
-        <v>293</v>
-      </c>
-      <c r="G4" s="28" t="s">
-        <v>294</v>
-      </c>
-      <c r="H4" s="42" t="s">
+      <c r="D4" s="21" t="s">
+        <v>337</v>
+      </c>
+      <c r="E4" s="21" t="s">
+        <v>193</v>
+      </c>
+      <c r="F4" s="21" t="s">
+        <v>338</v>
+      </c>
+      <c r="G4" s="21" t="s">
+        <v>339</v>
+      </c>
+      <c r="H4" s="33" t="s">
         <v>70</v>
       </c>
-      <c r="I4" s="28" t="s">
-        <v>295</v>
-      </c>
-      <c r="J4" s="30"/>
+      <c r="I4" s="21" t="s">
+        <v>340</v>
+      </c>
+      <c r="J4" s="23"/>
     </row>
     <row r="5" ht="42.0" customHeight="1">
-      <c r="A5" s="43" t="s">
-        <v>296</v>
-      </c>
-      <c r="B5" s="25" t="s">
-        <v>297</v>
-      </c>
-      <c r="C5" s="44" t="s">
+      <c r="A5" s="34" t="s">
+        <v>341</v>
+      </c>
+      <c r="B5" s="20" t="s">
+        <v>342</v>
+      </c>
+      <c r="C5" s="35" t="s">
         <v>97</v>
       </c>
-      <c r="D5" s="25" t="s">
-        <v>292</v>
-      </c>
-      <c r="E5" s="24" t="s">
-        <v>147</v>
-      </c>
-      <c r="F5" s="25" t="s">
-        <v>298</v>
-      </c>
-      <c r="G5" s="25" t="s">
-        <v>299</v>
-      </c>
-      <c r="H5" s="42" t="s">
+      <c r="D5" s="20" t="s">
+        <v>337</v>
+      </c>
+      <c r="E5" s="20" t="s">
+        <v>193</v>
+      </c>
+      <c r="F5" s="20" t="s">
+        <v>343</v>
+      </c>
+      <c r="G5" s="20" t="s">
+        <v>344</v>
+      </c>
+      <c r="H5" s="33" t="s">
         <v>70</v>
       </c>
-      <c r="I5" s="25" t="s">
-        <v>300</v>
-      </c>
-      <c r="J5" s="43"/>
+      <c r="I5" s="20" t="s">
+        <v>345</v>
+      </c>
+      <c r="J5" s="34"/>
     </row>
     <row r="6" ht="18.0" customHeight="1">
-      <c r="A6" s="38" t="s">
-        <v>230</v>
-      </c>
-      <c r="B6" s="39"/>
-      <c r="C6" s="39"/>
-      <c r="D6" s="39"/>
-      <c r="E6" s="39"/>
-      <c r="F6" s="39"/>
-      <c r="G6" s="39"/>
-      <c r="H6" s="39"/>
-      <c r="I6" s="39"/>
-      <c r="J6" s="40"/>
+      <c r="A6" s="29" t="s">
+        <v>275</v>
+      </c>
+      <c r="B6" s="30"/>
+      <c r="C6" s="30"/>
+      <c r="D6" s="30"/>
+      <c r="E6" s="30"/>
+      <c r="F6" s="30"/>
+      <c r="G6" s="30"/>
+      <c r="H6" s="30"/>
+      <c r="I6" s="30"/>
+      <c r="J6" s="31"/>
     </row>
     <row r="7" ht="42.0" customHeight="1">
-      <c r="A7" s="43" t="s">
-        <v>301</v>
-      </c>
-      <c r="B7" s="25" t="s">
-        <v>302</v>
-      </c>
-      <c r="C7" s="45" t="s">
+      <c r="A7" s="34" t="s">
+        <v>346</v>
+      </c>
+      <c r="B7" s="20" t="s">
+        <v>347</v>
+      </c>
+      <c r="C7" s="36" t="s">
         <v>139</v>
       </c>
-      <c r="D7" s="25" t="s">
-        <v>303</v>
-      </c>
-      <c r="E7" s="24" t="s">
-        <v>147</v>
-      </c>
-      <c r="F7" s="25" t="s">
+      <c r="D7" s="20" t="s">
+        <v>348</v>
+      </c>
+      <c r="E7" s="20" t="s">
+        <v>193</v>
+      </c>
+      <c r="F7" s="20" t="s">
         <v>141</v>
       </c>
-      <c r="G7" s="25" t="s">
-        <v>304</v>
-      </c>
-      <c r="H7" s="42" t="s">
+      <c r="G7" s="20" t="s">
+        <v>349</v>
+      </c>
+      <c r="H7" s="33" t="s">
         <v>70</v>
       </c>
-      <c r="I7" s="24" t="s">
-        <v>305</v>
-      </c>
-      <c r="J7" s="43"/>
+      <c r="I7" s="20" t="s">
+        <v>350</v>
+      </c>
+      <c r="J7" s="34"/>
     </row>
     <row r="8" ht="42.0" customHeight="1">
-      <c r="A8" s="30" t="s">
-        <v>306</v>
-      </c>
-      <c r="B8" s="28" t="s">
-        <v>307</v>
-      </c>
-      <c r="C8" s="46" t="s">
+      <c r="A8" s="23" t="s">
+        <v>351</v>
+      </c>
+      <c r="B8" s="21" t="s">
+        <v>352</v>
+      </c>
+      <c r="C8" s="43" t="s">
         <v>139</v>
       </c>
-      <c r="D8" s="28" t="s">
-        <v>308</v>
-      </c>
-      <c r="E8" s="27" t="s">
-        <v>147</v>
-      </c>
-      <c r="F8" s="28" t="str">
+      <c r="D8" s="21" t="s">
+        <v>353</v>
+      </c>
+      <c r="E8" s="21" t="s">
+        <v>193</v>
+      </c>
+      <c r="F8" s="21" t="str">
         <f>Variables!C10</f>
         <v>4a2c7d53-9a34-4c40-9e8f-c8972db67211</v>
       </c>
-      <c r="G8" s="28" t="s">
-        <v>309</v>
-      </c>
-      <c r="H8" s="42" t="s">
+      <c r="G8" s="21" t="s">
+        <v>354</v>
+      </c>
+      <c r="H8" s="33" t="s">
         <v>70</v>
       </c>
-      <c r="I8" s="27" t="s">
-        <v>310</v>
-      </c>
-      <c r="J8" s="30"/>
+      <c r="I8" s="21" t="s">
+        <v>355</v>
+      </c>
+      <c r="J8" s="23"/>
     </row>
     <row r="9" ht="42.0" customHeight="1">
-      <c r="A9" s="43" t="s">
-        <v>311</v>
-      </c>
-      <c r="B9" s="25" t="s">
-        <v>312</v>
-      </c>
-      <c r="C9" s="45" t="s">
+      <c r="A9" s="34" t="s">
+        <v>356</v>
+      </c>
+      <c r="B9" s="20" t="s">
+        <v>357</v>
+      </c>
+      <c r="C9" s="36" t="s">
         <v>139</v>
       </c>
-      <c r="D9" s="25" t="s">
-        <v>313</v>
-      </c>
-      <c r="E9" s="24" t="s">
-        <v>147</v>
-      </c>
-      <c r="F9" s="25" t="s">
+      <c r="D9" s="20" t="s">
+        <v>358</v>
+      </c>
+      <c r="E9" s="20" t="s">
+        <v>193</v>
+      </c>
+      <c r="F9" s="20" t="s">
         <v>141</v>
       </c>
-      <c r="G9" s="25" t="s">
-        <v>314</v>
-      </c>
-      <c r="H9" s="42" t="s">
+      <c r="G9" s="20" t="s">
+        <v>359</v>
+      </c>
+      <c r="H9" s="33" t="s">
         <v>70</v>
       </c>
-      <c r="I9" s="24" t="s">
-        <v>315</v>
-      </c>
-      <c r="J9" s="43"/>
+      <c r="I9" s="20" t="s">
+        <v>360</v>
+      </c>
+      <c r="J9" s="34"/>
     </row>
     <row r="10" ht="18.0" customHeight="1">
-      <c r="A10" s="38" t="s">
-        <v>316</v>
-      </c>
-      <c r="B10" s="39"/>
-      <c r="C10" s="39"/>
-      <c r="D10" s="39"/>
-      <c r="E10" s="39"/>
-      <c r="F10" s="39"/>
-      <c r="G10" s="39"/>
-      <c r="H10" s="39"/>
-      <c r="I10" s="39"/>
-      <c r="J10" s="40"/>
+      <c r="A10" s="29" t="s">
+        <v>361</v>
+      </c>
+      <c r="B10" s="30"/>
+      <c r="C10" s="30"/>
+      <c r="D10" s="30"/>
+      <c r="E10" s="30"/>
+      <c r="F10" s="30"/>
+      <c r="G10" s="30"/>
+      <c r="H10" s="30"/>
+      <c r="I10" s="30"/>
+      <c r="J10" s="31"/>
     </row>
     <row r="11" ht="42.0" customHeight="1">
-      <c r="A11" s="43" t="s">
-        <v>317</v>
-      </c>
-      <c r="B11" s="25" t="s">
-        <v>318</v>
-      </c>
-      <c r="C11" s="44" t="s">
+      <c r="A11" s="34" t="s">
+        <v>362</v>
+      </c>
+      <c r="B11" s="20" t="s">
+        <v>363</v>
+      </c>
+      <c r="C11" s="35" t="s">
         <v>97</v>
       </c>
-      <c r="D11" s="25" t="s">
-        <v>319</v>
-      </c>
-      <c r="E11" s="24" t="s">
-        <v>147</v>
-      </c>
-      <c r="F11" s="25" t="str">
+      <c r="D11" s="20" t="s">
+        <v>364</v>
+      </c>
+      <c r="E11" s="20" t="s">
+        <v>193</v>
+      </c>
+      <c r="F11" s="20" t="str">
         <f>Variables!C11</f>
         <v>8396e74a-7bc5-4793-b7c4-bd79b3b7932b</v>
       </c>
-      <c r="G11" s="24" t="s">
-        <v>320</v>
-      </c>
-      <c r="H11" s="42" t="s">
+      <c r="G11" s="20" t="s">
+        <v>365</v>
+      </c>
+      <c r="H11" s="33" t="s">
         <v>70</v>
       </c>
-      <c r="I11" s="24" t="s">
-        <v>321</v>
-      </c>
-      <c r="J11" s="43"/>
+      <c r="I11" s="20" t="s">
+        <v>366</v>
+      </c>
+      <c r="J11" s="34"/>
     </row>
     <row r="12" ht="42.0" customHeight="1">
-      <c r="A12" s="30" t="s">
-        <v>322</v>
-      </c>
-      <c r="B12" s="28" t="s">
-        <v>323</v>
-      </c>
-      <c r="C12" s="41" t="s">
+      <c r="A12" s="23" t="s">
+        <v>367</v>
+      </c>
+      <c r="B12" s="21" t="s">
+        <v>368</v>
+      </c>
+      <c r="C12" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="D12" s="28" t="s">
-        <v>324</v>
-      </c>
-      <c r="E12" s="27" t="s">
-        <v>147</v>
-      </c>
-      <c r="F12" s="28" t="str">
+      <c r="D12" s="21" t="s">
+        <v>369</v>
+      </c>
+      <c r="E12" s="21" t="s">
+        <v>193</v>
+      </c>
+      <c r="F12" s="21" t="str">
         <f>Variables!C11</f>
         <v>8396e74a-7bc5-4793-b7c4-bd79b3b7932b</v>
       </c>
-      <c r="G12" s="27" t="s">
-        <v>325</v>
-      </c>
-      <c r="H12" s="42" t="s">
+      <c r="G12" s="21" t="s">
+        <v>370</v>
+      </c>
+      <c r="H12" s="33" t="s">
         <v>70</v>
       </c>
-      <c r="I12" s="27" t="s">
-        <v>326</v>
-      </c>
-      <c r="J12" s="30"/>
+      <c r="I12" s="21" t="s">
+        <v>371</v>
+      </c>
+      <c r="J12" s="23"/>
     </row>
     <row r="13" ht="42.0" customHeight="1">
-      <c r="A13" s="43" t="s">
-        <v>327</v>
-      </c>
-      <c r="B13" s="25" t="s">
-        <v>328</v>
-      </c>
-      <c r="C13" s="44" t="s">
+      <c r="A13" s="34" t="s">
+        <v>372</v>
+      </c>
+      <c r="B13" s="20" t="s">
+        <v>373</v>
+      </c>
+      <c r="C13" s="35" t="s">
         <v>97</v>
       </c>
-      <c r="D13" s="25" t="s">
-        <v>329</v>
-      </c>
-      <c r="E13" s="24" t="s">
-        <v>147</v>
-      </c>
-      <c r="F13" s="25" t="str">
+      <c r="D13" s="20" t="s">
+        <v>374</v>
+      </c>
+      <c r="E13" s="20" t="s">
+        <v>193</v>
+      </c>
+      <c r="F13" s="20" t="str">
         <f>Variables!C11</f>
         <v>8396e74a-7bc5-4793-b7c4-bd79b3b7932b</v>
       </c>
-      <c r="G13" s="24" t="s">
-        <v>330</v>
-      </c>
-      <c r="H13" s="42" t="s">
+      <c r="G13" s="20" t="s">
+        <v>375</v>
+      </c>
+      <c r="H13" s="33" t="s">
         <v>70</v>
       </c>
-      <c r="I13" s="24" t="s">
-        <v>331</v>
-      </c>
-      <c r="J13" s="43"/>
+      <c r="I13" s="20" t="s">
+        <v>376</v>
+      </c>
+      <c r="J13" s="34"/>
     </row>
     <row r="14" ht="42.0" customHeight="1">
-      <c r="A14" s="30" t="s">
-        <v>332</v>
-      </c>
-      <c r="B14" s="28" t="s">
-        <v>333</v>
-      </c>
-      <c r="C14" s="41" t="s">
+      <c r="A14" s="23" t="s">
+        <v>377</v>
+      </c>
+      <c r="B14" s="21" t="s">
+        <v>378</v>
+      </c>
+      <c r="C14" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="D14" s="28" t="s">
-        <v>334</v>
-      </c>
-      <c r="E14" s="27" t="s">
-        <v>147</v>
-      </c>
-      <c r="F14" s="28" t="str">
+      <c r="D14" s="21" t="s">
+        <v>379</v>
+      </c>
+      <c r="E14" s="21" t="s">
+        <v>193</v>
+      </c>
+      <c r="F14" s="21" t="str">
         <f>Variables!C11</f>
         <v>8396e74a-7bc5-4793-b7c4-bd79b3b7932b</v>
       </c>
-      <c r="G14" s="28" t="s">
-        <v>335</v>
-      </c>
-      <c r="H14" s="42" t="s">
+      <c r="G14" s="21" t="s">
+        <v>380</v>
+      </c>
+      <c r="H14" s="33" t="s">
         <v>70</v>
       </c>
-      <c r="I14" s="27" t="s">
-        <v>336</v>
-      </c>
-      <c r="J14" s="30"/>
+      <c r="I14" s="21" t="s">
+        <v>381</v>
+      </c>
+      <c r="J14" s="23"/>
     </row>
     <row r="15" ht="42.0" customHeight="1">
-      <c r="A15" s="43" t="s">
-        <v>337</v>
-      </c>
-      <c r="B15" s="25" t="s">
-        <v>338</v>
-      </c>
-      <c r="C15" s="44" t="s">
+      <c r="A15" s="34" t="s">
+        <v>382</v>
+      </c>
+      <c r="B15" s="20" t="s">
+        <v>383</v>
+      </c>
+      <c r="C15" s="35" t="s">
         <v>97</v>
       </c>
-      <c r="D15" s="25" t="s">
-        <v>339</v>
-      </c>
-      <c r="E15" s="24" t="s">
-        <v>147</v>
-      </c>
-      <c r="F15" s="25" t="str">
+      <c r="D15" s="20" t="s">
+        <v>384</v>
+      </c>
+      <c r="E15" s="20" t="s">
+        <v>193</v>
+      </c>
+      <c r="F15" s="20" t="str">
         <f>Variables!C10</f>
         <v>4a2c7d53-9a34-4c40-9e8f-c8972db67211</v>
       </c>
-      <c r="G15" s="24" t="s">
-        <v>281</v>
-      </c>
-      <c r="H15" s="42" t="s">
+      <c r="G15" s="20" t="s">
+        <v>326</v>
+      </c>
+      <c r="H15" s="33" t="s">
         <v>70</v>
       </c>
-      <c r="I15" s="25" t="s">
-        <v>340</v>
-      </c>
-      <c r="J15" s="43"/>
+      <c r="I15" s="20" t="s">
+        <v>385</v>
+      </c>
+      <c r="J15" s="34"/>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>
     <row r="22" ht="15.75" customHeight="1"/>
@@ -15775,364 +16199,363 @@
     <col customWidth="1" min="8" max="8" width="16.0"/>
     <col customWidth="1" min="9" max="9" width="40.0"/>
     <col customWidth="1" min="10" max="10" width="14.0"/>
-    <col customWidth="1" min="11" max="26" width="8.71"/>
   </cols>
   <sheetData>
     <row r="1" ht="24.0" customHeight="1">
-      <c r="A1" s="35" t="s">
-        <v>341</v>
-      </c>
-      <c r="B1" s="36"/>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36"/>
-      <c r="E1" s="36"/>
-      <c r="F1" s="36"/>
-      <c r="G1" s="36"/>
-      <c r="H1" s="36"/>
-      <c r="I1" s="36"/>
-      <c r="J1" s="37"/>
+      <c r="A1" s="27" t="s">
+        <v>386</v>
+      </c>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+      <c r="H1" s="28"/>
+      <c r="I1" s="28"/>
+      <c r="J1" s="28"/>
     </row>
     <row r="2" ht="21.75" customHeight="1">
-      <c r="A2" s="29" t="s">
+      <c r="A2" s="22" t="s">
         <v>85</v>
       </c>
-      <c r="B2" s="29" t="s">
+      <c r="B2" s="22" t="s">
         <v>86</v>
       </c>
-      <c r="C2" s="29" t="s">
+      <c r="C2" s="22" t="s">
         <v>87</v>
       </c>
-      <c r="D2" s="29" t="s">
+      <c r="D2" s="22" t="s">
         <v>88</v>
       </c>
-      <c r="E2" s="29" t="s">
+      <c r="E2" s="22" t="s">
         <v>89</v>
       </c>
-      <c r="F2" s="29" t="s">
+      <c r="F2" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="G2" s="29" t="s">
+      <c r="G2" s="22" t="s">
         <v>90</v>
       </c>
-      <c r="H2" s="29" t="s">
+      <c r="H2" s="22" t="s">
         <v>91</v>
       </c>
-      <c r="I2" s="29" t="s">
+      <c r="I2" s="22" t="s">
         <v>92</v>
       </c>
-      <c r="J2" s="29" t="s">
+      <c r="J2" s="22" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="3" ht="18.0" customHeight="1">
-      <c r="A3" s="38" t="s">
-        <v>342</v>
-      </c>
-      <c r="B3" s="39"/>
-      <c r="C3" s="39"/>
-      <c r="D3" s="39"/>
-      <c r="E3" s="39"/>
-      <c r="F3" s="39"/>
-      <c r="G3" s="39"/>
-      <c r="H3" s="39"/>
-      <c r="I3" s="39"/>
-      <c r="J3" s="40"/>
+      <c r="A3" s="29" t="s">
+        <v>387</v>
+      </c>
+      <c r="B3" s="30"/>
+      <c r="C3" s="30"/>
+      <c r="D3" s="30"/>
+      <c r="E3" s="30"/>
+      <c r="F3" s="30"/>
+      <c r="G3" s="30"/>
+      <c r="H3" s="30"/>
+      <c r="I3" s="30"/>
+      <c r="J3" s="31"/>
     </row>
     <row r="4" ht="42.0" customHeight="1">
-      <c r="A4" s="30" t="s">
-        <v>343</v>
-      </c>
-      <c r="B4" s="27" t="s">
-        <v>344</v>
-      </c>
-      <c r="C4" s="46" t="s">
+      <c r="A4" s="23" t="s">
+        <v>388</v>
+      </c>
+      <c r="B4" s="21" t="s">
+        <v>389</v>
+      </c>
+      <c r="C4" s="43" t="s">
         <v>139</v>
       </c>
-      <c r="D4" s="28" t="s">
-        <v>345</v>
-      </c>
-      <c r="E4" s="27" t="s">
-        <v>147</v>
-      </c>
-      <c r="F4" s="28" t="s">
+      <c r="D4" s="21" t="s">
+        <v>390</v>
+      </c>
+      <c r="E4" s="21" t="s">
+        <v>193</v>
+      </c>
+      <c r="F4" s="21" t="s">
         <v>141</v>
       </c>
-      <c r="G4" s="28" t="s">
-        <v>346</v>
-      </c>
-      <c r="H4" s="42" t="s">
+      <c r="G4" s="21" t="s">
+        <v>391</v>
+      </c>
+      <c r="H4" s="33" t="s">
         <v>70</v>
       </c>
-      <c r="I4" s="27" t="s">
-        <v>347</v>
-      </c>
-      <c r="J4" s="30"/>
+      <c r="I4" s="21" t="s">
+        <v>392</v>
+      </c>
+      <c r="J4" s="23"/>
     </row>
     <row r="5" ht="42.0" customHeight="1">
-      <c r="A5" s="43" t="s">
-        <v>348</v>
-      </c>
-      <c r="B5" s="25" t="s">
-        <v>349</v>
-      </c>
-      <c r="C5" s="45" t="s">
+      <c r="A5" s="34" t="s">
+        <v>393</v>
+      </c>
+      <c r="B5" s="20" t="s">
+        <v>394</v>
+      </c>
+      <c r="C5" s="36" t="s">
         <v>139</v>
       </c>
-      <c r="D5" s="25" t="s">
-        <v>345</v>
-      </c>
-      <c r="E5" s="24" t="s">
-        <v>147</v>
-      </c>
-      <c r="F5" s="25" t="s">
+      <c r="D5" s="20" t="s">
+        <v>390</v>
+      </c>
+      <c r="E5" s="20" t="s">
+        <v>193</v>
+      </c>
+      <c r="F5" s="20" t="s">
         <v>141</v>
       </c>
-      <c r="G5" s="25" t="s">
-        <v>350</v>
-      </c>
-      <c r="H5" s="42" t="s">
+      <c r="G5" s="20" t="s">
+        <v>395</v>
+      </c>
+      <c r="H5" s="33" t="s">
         <v>70</v>
       </c>
-      <c r="I5" s="24" t="s">
-        <v>351</v>
-      </c>
-      <c r="J5" s="43"/>
+      <c r="I5" s="20" t="s">
+        <v>396</v>
+      </c>
+      <c r="J5" s="34"/>
     </row>
     <row r="6" ht="18.0" customHeight="1">
-      <c r="A6" s="38" t="s">
-        <v>352</v>
-      </c>
-      <c r="B6" s="39"/>
-      <c r="C6" s="39"/>
-      <c r="D6" s="39"/>
-      <c r="E6" s="39"/>
-      <c r="F6" s="39"/>
-      <c r="G6" s="39"/>
-      <c r="H6" s="39"/>
-      <c r="I6" s="39"/>
-      <c r="J6" s="40"/>
+      <c r="A6" s="29" t="s">
+        <v>397</v>
+      </c>
+      <c r="B6" s="30"/>
+      <c r="C6" s="30"/>
+      <c r="D6" s="30"/>
+      <c r="E6" s="30"/>
+      <c r="F6" s="30"/>
+      <c r="G6" s="30"/>
+      <c r="H6" s="30"/>
+      <c r="I6" s="30"/>
+      <c r="J6" s="31"/>
     </row>
     <row r="7" ht="42.0" customHeight="1">
-      <c r="A7" s="31" t="s">
-        <v>353</v>
-      </c>
-      <c r="B7" s="28" t="s">
-        <v>354</v>
-      </c>
-      <c r="C7" s="41" t="s">
+      <c r="A7" s="23" t="s">
+        <v>398</v>
+      </c>
+      <c r="B7" s="21" t="s">
+        <v>399</v>
+      </c>
+      <c r="C7" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="D7" s="27" t="s">
-        <v>355</v>
-      </c>
-      <c r="E7" s="27" t="s">
-        <v>147</v>
-      </c>
-      <c r="F7" s="28" t="str">
+      <c r="D7" s="21" t="s">
+        <v>400</v>
+      </c>
+      <c r="E7" s="21" t="s">
+        <v>193</v>
+      </c>
+      <c r="F7" s="21" t="str">
         <f>Variables!C12</f>
         <v>967092f8-fb6a-4db2-af08-d77fa4540610</v>
       </c>
-      <c r="G7" s="28" t="s">
-        <v>356</v>
-      </c>
-      <c r="H7" s="42" t="s">
+      <c r="G7" s="21" t="s">
+        <v>401</v>
+      </c>
+      <c r="H7" s="33" t="s">
         <v>70</v>
       </c>
-      <c r="I7" s="28" t="s">
-        <v>357</v>
-      </c>
-      <c r="J7" s="30"/>
+      <c r="I7" s="21" t="s">
+        <v>402</v>
+      </c>
+      <c r="J7" s="23"/>
     </row>
     <row r="8" ht="42.0" customHeight="1">
-      <c r="A8" s="58" t="s">
-        <v>358</v>
-      </c>
-      <c r="B8" s="25" t="s">
-        <v>359</v>
-      </c>
-      <c r="C8" s="44" t="s">
+      <c r="A8" s="34" t="s">
+        <v>403</v>
+      </c>
+      <c r="B8" s="20" t="s">
+        <v>404</v>
+      </c>
+      <c r="C8" s="35" t="s">
         <v>97</v>
       </c>
-      <c r="D8" s="24" t="s">
-        <v>360</v>
-      </c>
-      <c r="E8" s="24" t="s">
-        <v>147</v>
-      </c>
-      <c r="F8" s="25" t="str">
+      <c r="D8" s="20" t="s">
+        <v>405</v>
+      </c>
+      <c r="E8" s="20" t="s">
+        <v>193</v>
+      </c>
+      <c r="F8" s="20" t="str">
         <f>Variables!C13</f>
         <v>5df1bedc-a8b4-4cb2-9a9a-7b3d60252582</v>
       </c>
-      <c r="G8" s="25" t="s">
-        <v>361</v>
-      </c>
-      <c r="H8" s="42" t="s">
+      <c r="G8" s="20" t="s">
+        <v>406</v>
+      </c>
+      <c r="H8" s="33" t="s">
         <v>70</v>
       </c>
-      <c r="I8" s="24" t="s">
-        <v>362</v>
-      </c>
-      <c r="J8" s="43"/>
+      <c r="I8" s="20" t="s">
+        <v>407</v>
+      </c>
+      <c r="J8" s="34"/>
     </row>
     <row r="9" ht="42.0" customHeight="1">
-      <c r="A9" s="31" t="s">
-        <v>363</v>
-      </c>
-      <c r="B9" s="27" t="s">
-        <v>364</v>
-      </c>
-      <c r="C9" s="41" t="s">
+      <c r="A9" s="23" t="s">
+        <v>408</v>
+      </c>
+      <c r="B9" s="21" t="s">
+        <v>409</v>
+      </c>
+      <c r="C9" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="D9" s="27" t="s">
-        <v>360</v>
-      </c>
-      <c r="E9" s="27" t="s">
-        <v>147</v>
-      </c>
-      <c r="F9" s="28" t="str">
+      <c r="D9" s="21" t="s">
+        <v>405</v>
+      </c>
+      <c r="E9" s="21" t="s">
+        <v>193</v>
+      </c>
+      <c r="F9" s="21" t="str">
         <f>Variables!C13</f>
         <v>5df1bedc-a8b4-4cb2-9a9a-7b3d60252582</v>
       </c>
-      <c r="G9" s="28" t="s">
-        <v>365</v>
-      </c>
-      <c r="H9" s="42" t="s">
+      <c r="G9" s="21" t="s">
+        <v>410</v>
+      </c>
+      <c r="H9" s="33" t="s">
         <v>70</v>
       </c>
-      <c r="I9" s="28"/>
-      <c r="J9" s="30"/>
+      <c r="I9" s="21"/>
+      <c r="J9" s="23"/>
     </row>
     <row r="10" ht="42.0" customHeight="1">
-      <c r="A10" s="58" t="s">
-        <v>366</v>
-      </c>
-      <c r="B10" s="24" t="s">
-        <v>367</v>
-      </c>
-      <c r="C10" s="44" t="s">
+      <c r="A10" s="34" t="s">
+        <v>411</v>
+      </c>
+      <c r="B10" s="20" t="s">
+        <v>412</v>
+      </c>
+      <c r="C10" s="35" t="s">
         <v>97</v>
       </c>
-      <c r="D10" s="24" t="s">
-        <v>360</v>
-      </c>
-      <c r="E10" s="24" t="s">
-        <v>147</v>
-      </c>
-      <c r="F10" s="25" t="str">
+      <c r="D10" s="20" t="s">
+        <v>405</v>
+      </c>
+      <c r="E10" s="20" t="s">
+        <v>193</v>
+      </c>
+      <c r="F10" s="20" t="str">
         <f>Variables!C12</f>
         <v>967092f8-fb6a-4db2-af08-d77fa4540610</v>
       </c>
-      <c r="G10" s="25" t="s">
-        <v>365</v>
-      </c>
-      <c r="H10" s="42" t="s">
+      <c r="G10" s="20" t="s">
+        <v>410</v>
+      </c>
+      <c r="H10" s="33" t="s">
         <v>70</v>
       </c>
-      <c r="I10" s="25"/>
-      <c r="J10" s="43"/>
+      <c r="I10" s="20"/>
+      <c r="J10" s="34"/>
     </row>
     <row r="11" ht="18.0" customHeight="1">
-      <c r="A11" s="38" t="s">
-        <v>368</v>
-      </c>
-      <c r="B11" s="39"/>
-      <c r="C11" s="39"/>
-      <c r="D11" s="39"/>
-      <c r="E11" s="39"/>
-      <c r="F11" s="39"/>
-      <c r="G11" s="39"/>
-      <c r="H11" s="39"/>
-      <c r="I11" s="39"/>
-      <c r="J11" s="40"/>
+      <c r="A11" s="29" t="s">
+        <v>413</v>
+      </c>
+      <c r="B11" s="30"/>
+      <c r="C11" s="30"/>
+      <c r="D11" s="30"/>
+      <c r="E11" s="30"/>
+      <c r="F11" s="30"/>
+      <c r="G11" s="30"/>
+      <c r="H11" s="30"/>
+      <c r="I11" s="30"/>
+      <c r="J11" s="31"/>
     </row>
     <row r="12" ht="42.0" customHeight="1">
-      <c r="A12" s="31" t="s">
-        <v>369</v>
-      </c>
-      <c r="B12" s="27" t="s">
-        <v>370</v>
-      </c>
-      <c r="C12" s="46" t="s">
+      <c r="A12" s="23" t="s">
+        <v>414</v>
+      </c>
+      <c r="B12" s="21" t="s">
+        <v>415</v>
+      </c>
+      <c r="C12" s="43" t="s">
         <v>139</v>
       </c>
-      <c r="D12" s="27" t="s">
-        <v>371</v>
-      </c>
-      <c r="E12" s="27" t="s">
-        <v>147</v>
-      </c>
-      <c r="F12" s="28" t="str">
+      <c r="D12" s="21" t="s">
+        <v>416</v>
+      </c>
+      <c r="E12" s="21" t="s">
+        <v>193</v>
+      </c>
+      <c r="F12" s="21" t="str">
         <f>Variables!C8</f>
         <v>c7cf918d-7e04-4104-9790-fa5bb9d3756d</v>
       </c>
-      <c r="G12" s="28" t="s">
-        <v>372</v>
-      </c>
-      <c r="H12" s="42" t="s">
+      <c r="G12" s="21" t="s">
+        <v>417</v>
+      </c>
+      <c r="H12" s="33" t="s">
         <v>70</v>
       </c>
-      <c r="I12" s="27"/>
-      <c r="J12" s="30"/>
+      <c r="I12" s="21"/>
+      <c r="J12" s="23"/>
     </row>
     <row r="13" ht="42.0" customHeight="1">
-      <c r="A13" s="43" t="s">
-        <v>373</v>
-      </c>
-      <c r="B13" s="25" t="s">
-        <v>374</v>
-      </c>
-      <c r="C13" s="45" t="s">
+      <c r="A13" s="34" t="s">
+        <v>418</v>
+      </c>
+      <c r="B13" s="20" t="s">
+        <v>419</v>
+      </c>
+      <c r="C13" s="36" t="s">
         <v>139</v>
       </c>
-      <c r="D13" s="25" t="s">
-        <v>375</v>
-      </c>
-      <c r="E13" s="24" t="s">
-        <v>147</v>
-      </c>
-      <c r="F13" s="25" t="s">
+      <c r="D13" s="20" t="s">
+        <v>420</v>
+      </c>
+      <c r="E13" s="20" t="s">
+        <v>193</v>
+      </c>
+      <c r="F13" s="20" t="s">
         <v>141</v>
       </c>
-      <c r="G13" s="25" t="s">
-        <v>376</v>
-      </c>
-      <c r="H13" s="42" t="s">
+      <c r="G13" s="20" t="s">
+        <v>421</v>
+      </c>
+      <c r="H13" s="33" t="s">
         <v>70</v>
       </c>
-      <c r="I13" s="25"/>
-      <c r="J13" s="43"/>
+      <c r="I13" s="20"/>
+      <c r="J13" s="34"/>
     </row>
     <row r="14" ht="42.0" customHeight="1">
-      <c r="A14" s="30" t="s">
-        <v>377</v>
-      </c>
-      <c r="B14" s="28" t="s">
-        <v>378</v>
-      </c>
-      <c r="C14" s="41" t="s">
+      <c r="A14" s="23" t="s">
+        <v>422</v>
+      </c>
+      <c r="B14" s="21" t="s">
+        <v>423</v>
+      </c>
+      <c r="C14" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="D14" s="28" t="s">
-        <v>379</v>
-      </c>
-      <c r="E14" s="27" t="s">
-        <v>147</v>
-      </c>
-      <c r="F14" s="28" t="str">
+      <c r="D14" s="21" t="s">
+        <v>424</v>
+      </c>
+      <c r="E14" s="21" t="s">
+        <v>193</v>
+      </c>
+      <c r="F14" s="21" t="str">
         <f>Variables!C8</f>
         <v>c7cf918d-7e04-4104-9790-fa5bb9d3756d</v>
       </c>
-      <c r="G14" s="28" t="s">
-        <v>380</v>
-      </c>
-      <c r="H14" s="42" t="s">
+      <c r="G14" s="21" t="s">
+        <v>425</v>
+      </c>
+      <c r="H14" s="33" t="s">
         <v>70</v>
       </c>
-      <c r="I14" s="28" t="s">
-        <v>381</v>
-      </c>
-      <c r="J14" s="30"/>
+      <c r="I14" s="21" t="s">
+        <v>426</v>
+      </c>
+      <c r="J14" s="23"/>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>
     <row r="22" ht="15.75" customHeight="1"/>

--- a/community-help-api/docs/api/community-help-api-test.xlsx
+++ b/community-help-api/docs/api/community-help-api-test.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="965" uniqueCount="520">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="992" uniqueCount="534">
   <si>
     <t>Community Help API — Plan de Pruebas Swagger</t>
   </si>
@@ -590,6 +590,21 @@
     <t>Menos de 8 caracteres, debe fallar validación</t>
   </si>
   <si>
+    <t>A-24</t>
+  </si>
+  <si>
+    <t>Lanzar error de límite excedido</t>
+  </si>
+  <si>
+    <t>{ "email": "ana@test.com"}, Ejecutarlo más de 3 veces hasta que salte el error</t>
+  </si>
+  <si>
+    <t>429 Rate Limit Exceeded</t>
+  </si>
+  <si>
+    <t>RATE_LIMIT_EXCEEDED</t>
+  </si>
+  <si>
     <t>Pruebas — Users</t>
   </si>
   <si>
@@ -962,10 +977,26 @@
     <t>403 Forbiden</t>
   </si>
   <si>
+    <t>HR-12</t>
+  </si>
+  <si>
+    <t>Obtener Help Request cercanas abierta dentro de un radio</t>
+  </si>
+  <si>
+    <t>/api/v1/help-requests/nearby</t>
+  </si>
+  <si>
+    <t>lat=43.5350,
+lon=-5,6650</t>
+  </si>
+  <si>
+    <t>Verificar donaciones cercanas, si las hay</t>
+  </si>
+  <si>
     <t>Actualización</t>
   </si>
   <si>
-    <t>HR-12</t>
+    <t>HR-13</t>
   </si>
   <si>
     <t>Actualizar título (User C, propietario)</t>
@@ -980,7 +1011,7 @@
     <t>Verificar cambio y que updated_at fue modificado de fecha</t>
   </si>
   <si>
-    <t>HR-13</t>
+    <t>HR-14</t>
   </si>
   <si>
     <t>Actualizar Help Request de otro usuario (User A)</t>
@@ -992,7 +1023,7 @@
     <t>Acciones de negocio</t>
   </si>
   <si>
-    <t>HR-14</t>
+    <t>HR-15</t>
   </si>
   <si>
     <t>Cancelar Help Request 2 (User C)</t>
@@ -1007,7 +1038,7 @@
     <t>Verificar que las proposals pendientes también se cancelan</t>
   </si>
   <si>
-    <t>HR-15</t>
+    <t>HR-16</t>
   </si>
   <si>
     <t>Admin — Borrar Help Request</t>
@@ -1106,10 +1137,23 @@
     <t>Verificar que devuelve las donaciones creadas disponibles</t>
   </si>
   <si>
+    <t>D-06</t>
+  </si>
+  <si>
+    <t>Obtener donaciones disponibles dentro de un radio</t>
+  </si>
+  <si>
+    <t>/api/v1/donations/nearby</t>
+  </si>
+  <si>
+    <t>lat=43.5350,
+lon=-5.6650</t>
+  </si>
+  <si>
     <t>Ciclo de vida completo (Donation 2)</t>
   </si>
   <si>
-    <t>D-06</t>
+    <t>D-07</t>
   </si>
   <si>
     <t>Reservar Donation 2 (User A como voluntario)</t>
@@ -1124,7 +1168,7 @@
     <t>Verificar que la Donation pasa a estar reservada</t>
   </si>
   <si>
-    <t>D-07</t>
+    <t>D-08</t>
   </si>
   <si>
     <t>Confirmar reserva (User C como donante)</t>
@@ -1139,7 +1183,7 @@
     <t>Verificar que la Donation pasa a estar confirmada</t>
   </si>
   <si>
-    <t>D-08</t>
+    <t>D-09</t>
   </si>
   <si>
     <t>Marcar como recogida (User A)</t>
@@ -1154,7 +1198,7 @@
     <t>Verificar que la Donation pasa a estar recogida</t>
   </si>
   <si>
-    <t>D-09</t>
+    <t>D-10</t>
   </si>
   <si>
     <t>Completar donación (User A)</t>
@@ -1169,7 +1213,7 @@
     <t>Verificar que la Donation pasa a estar completa</t>
   </si>
   <si>
-    <t>D-10</t>
+    <t>D-11</t>
   </si>
   <si>
     <t>Cancelar Donation 1 (User C)</t>
@@ -1812,7 +1856,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="58">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1965,6 +2009,9 @@
     </xf>
     <xf borderId="1" fillId="8" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf borderId="1" fillId="7" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="8" fontId="17" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
@@ -3398,7 +3445,7 @@
   <sheetData>
     <row r="1" ht="24.0" customHeight="1">
       <c r="A1" s="27" t="s">
-        <v>427</v>
+        <v>441</v>
       </c>
       <c r="B1" s="28"/>
       <c r="C1" s="28"/>
@@ -3444,7 +3491,7 @@
     </row>
     <row r="3" ht="18.0" customHeight="1">
       <c r="A3" s="29" t="s">
-        <v>428</v>
+        <v>442</v>
       </c>
       <c r="B3" s="30"/>
       <c r="C3" s="30"/>
@@ -3458,254 +3505,254 @@
     </row>
     <row r="4" ht="42.0" customHeight="1">
       <c r="A4" s="23" t="s">
-        <v>429</v>
+        <v>443</v>
       </c>
       <c r="B4" s="21" t="s">
-        <v>430</v>
+        <v>444</v>
       </c>
       <c r="C4" s="32" t="s">
         <v>97</v>
       </c>
       <c r="D4" s="21" t="s">
-        <v>431</v>
+        <v>445</v>
       </c>
       <c r="E4" s="21" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="F4" s="21" t="str">
         <f>Variables!C8 &amp; ", HELP_REQUEST" </f>
         <v>c7cf918d-7e04-4104-9790-fa5bb9d3756d, HELP_REQUEST</v>
       </c>
       <c r="G4" s="21" t="s">
-        <v>432</v>
+        <v>446</v>
       </c>
       <c r="H4" s="33" t="s">
         <v>70</v>
       </c>
       <c r="I4" s="21" t="s">
-        <v>433</v>
+        <v>447</v>
       </c>
       <c r="J4" s="23"/>
     </row>
     <row r="5" ht="42.0" customHeight="1">
       <c r="A5" s="34" t="s">
-        <v>434</v>
+        <v>448</v>
       </c>
       <c r="B5" s="20" t="s">
-        <v>435</v>
+        <v>449</v>
       </c>
       <c r="C5" s="36" t="s">
         <v>139</v>
       </c>
       <c r="D5" s="20" t="s">
-        <v>436</v>
+        <v>450</v>
       </c>
       <c r="E5" s="20" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="F5" s="20" t="s">
         <v>141</v>
       </c>
       <c r="G5" s="20" t="s">
-        <v>437</v>
+        <v>451</v>
       </c>
       <c r="H5" s="33" t="s">
         <v>70</v>
       </c>
       <c r="I5" s="20" t="s">
-        <v>438</v>
+        <v>452</v>
       </c>
       <c r="J5" s="34"/>
     </row>
     <row r="6" ht="42.0" customHeight="1">
       <c r="A6" s="23" t="s">
-        <v>439</v>
+        <v>453</v>
       </c>
       <c r="B6" s="21" t="s">
-        <v>440</v>
+        <v>454</v>
       </c>
       <c r="C6" s="32" t="s">
         <v>97</v>
       </c>
       <c r="D6" s="21" t="s">
-        <v>441</v>
+        <v>455</v>
       </c>
       <c r="E6" s="21" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="F6" s="21" t="str">
         <f>Variables!C15 &amp; ", {""content"":""Hola, ¿a qué hora te va bien para la compra?""}"</f>
         <v>66cce1b2-c3f3-4c17-a0c2-1ab7c4292c37, {"content":"Hola, ¿a qué hora te va bien para la compra?"}</v>
       </c>
       <c r="G6" s="21" t="s">
-        <v>442</v>
+        <v>456</v>
       </c>
       <c r="H6" s="33" t="s">
         <v>70</v>
       </c>
       <c r="I6" s="21" t="s">
-        <v>443</v>
+        <v>457</v>
       </c>
       <c r="J6" s="23"/>
     </row>
     <row r="7" ht="42.0" customHeight="1">
       <c r="A7" s="34" t="s">
-        <v>444</v>
+        <v>458</v>
       </c>
       <c r="B7" s="20" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="C7" s="35" t="s">
         <v>97</v>
       </c>
       <c r="D7" s="20" t="s">
-        <v>441</v>
+        <v>455</v>
       </c>
       <c r="E7" s="20" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="F7" s="21" t="str">
         <f>Variables!C15 &amp; ", {""content"":""Perfecto, me viene bien a las 10h""}"</f>
         <v>66cce1b2-c3f3-4c17-a0c2-1ab7c4292c37, {"content":"Perfecto, me viene bien a las 10h"}</v>
       </c>
       <c r="G7" s="20" t="s">
-        <v>446</v>
+        <v>460</v>
       </c>
       <c r="H7" s="33" t="s">
         <v>70</v>
       </c>
       <c r="I7" s="21" t="s">
-        <v>447</v>
+        <v>461</v>
       </c>
       <c r="J7" s="34"/>
     </row>
     <row r="8" ht="42.0" customHeight="1">
       <c r="A8" s="23" t="s">
-        <v>448</v>
+        <v>462</v>
       </c>
       <c r="B8" s="21" t="s">
-        <v>449</v>
+        <v>463</v>
       </c>
       <c r="C8" s="43" t="s">
         <v>139</v>
       </c>
       <c r="D8" s="21" t="s">
-        <v>441</v>
+        <v>455</v>
       </c>
       <c r="E8" s="21" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="F8" s="21" t="str">
         <f>Variables!C15</f>
         <v>66cce1b2-c3f3-4c17-a0c2-1ab7c4292c37</v>
       </c>
       <c r="G8" s="21" t="s">
-        <v>450</v>
+        <v>464</v>
       </c>
       <c r="H8" s="33" t="s">
         <v>70</v>
       </c>
       <c r="I8" s="21" t="s">
-        <v>451</v>
+        <v>465</v>
       </c>
       <c r="J8" s="23"/>
     </row>
     <row r="9" ht="42.0" customHeight="1">
       <c r="A9" s="34" t="s">
-        <v>452</v>
+        <v>466</v>
       </c>
       <c r="B9" s="20" t="s">
-        <v>453</v>
+        <v>467</v>
       </c>
       <c r="C9" s="44" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="D9" s="20" t="s">
-        <v>454</v>
+        <v>468</v>
       </c>
       <c r="E9" s="20" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="F9" s="20" t="str">
         <f>Variables!C15</f>
         <v>66cce1b2-c3f3-4c17-a0c2-1ab7c4292c37</v>
       </c>
       <c r="G9" s="20" t="s">
-        <v>332</v>
+        <v>342</v>
       </c>
       <c r="H9" s="33" t="s">
         <v>70</v>
       </c>
       <c r="I9" s="20" t="s">
-        <v>455</v>
+        <v>469</v>
       </c>
       <c r="J9" s="34"/>
     </row>
     <row r="10" ht="42.0" customHeight="1">
       <c r="A10" s="23" t="s">
-        <v>456</v>
+        <v>470</v>
       </c>
       <c r="B10" s="21" t="s">
-        <v>457</v>
-      </c>
-      <c r="C10" s="56" t="s">
-        <v>330</v>
+        <v>471</v>
+      </c>
+      <c r="C10" s="57" t="s">
+        <v>340</v>
       </c>
       <c r="D10" s="21" t="s">
-        <v>458</v>
+        <v>472</v>
       </c>
       <c r="E10" s="21" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="F10" s="21" t="str">
         <f>Variables!C15</f>
         <v>66cce1b2-c3f3-4c17-a0c2-1ab7c4292c37</v>
       </c>
       <c r="G10" s="21" t="s">
-        <v>332</v>
+        <v>342</v>
       </c>
       <c r="H10" s="33" t="s">
         <v>70</v>
       </c>
       <c r="I10" s="21" t="s">
-        <v>459</v>
+        <v>473</v>
       </c>
       <c r="J10" s="23"/>
     </row>
     <row r="11" ht="42.0" customHeight="1">
       <c r="A11" s="34" t="s">
-        <v>460</v>
+        <v>474</v>
       </c>
       <c r="B11" s="20" t="s">
-        <v>461</v>
-      </c>
-      <c r="C11" s="55" t="s">
-        <v>330</v>
+        <v>475</v>
+      </c>
+      <c r="C11" s="56" t="s">
+        <v>340</v>
       </c>
       <c r="D11" s="20" t="s">
-        <v>458</v>
+        <v>472</v>
       </c>
       <c r="E11" s="20" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="F11" s="20" t="str">
         <f>Variables!C15</f>
         <v>66cce1b2-c3f3-4c17-a0c2-1ab7c4292c37</v>
       </c>
       <c r="G11" s="20" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="H11" s="33" t="s">
         <v>70</v>
       </c>
       <c r="I11" s="20" t="s">
-        <v>462</v>
+        <v>476</v>
       </c>
       <c r="J11" s="34"/>
     </row>
     <row r="12" ht="18.0" customHeight="1">
       <c r="A12" s="29" t="s">
-        <v>463</v>
+        <v>477</v>
       </c>
       <c r="B12" s="30"/>
       <c r="C12" s="30"/>
@@ -3719,31 +3766,31 @@
     </row>
     <row r="13" ht="42.0" customHeight="1">
       <c r="A13" s="34" t="s">
-        <v>464</v>
+        <v>478</v>
       </c>
       <c r="B13" s="20" t="s">
-        <v>465</v>
+        <v>479</v>
       </c>
       <c r="C13" s="36" t="s">
         <v>139</v>
       </c>
       <c r="D13" s="20" t="s">
-        <v>466</v>
+        <v>480</v>
       </c>
       <c r="E13" s="20" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="F13" s="20" t="s">
         <v>141</v>
       </c>
       <c r="G13" s="20" t="s">
-        <v>467</v>
+        <v>481</v>
       </c>
       <c r="H13" s="33" t="s">
         <v>70</v>
       </c>
       <c r="I13" s="20" t="s">
-        <v>468</v>
+        <v>482</v>
       </c>
       <c r="J13" s="34"/>
     </row>
@@ -4781,7 +4828,7 @@
   <sheetData>
     <row r="1" ht="24.0" customHeight="1">
       <c r="A1" s="27" t="s">
-        <v>469</v>
+        <v>483</v>
       </c>
       <c r="B1" s="28"/>
       <c r="C1" s="28"/>
@@ -4827,7 +4874,7 @@
     </row>
     <row r="3" ht="18.0" customHeight="1">
       <c r="A3" s="29" t="s">
-        <v>470</v>
+        <v>484</v>
       </c>
       <c r="B3" s="30"/>
       <c r="C3" s="30"/>
@@ -4841,38 +4888,38 @@
     </row>
     <row r="4" ht="42.0" customHeight="1">
       <c r="A4" s="23" t="s">
-        <v>471</v>
+        <v>485</v>
       </c>
       <c r="B4" s="21" t="s">
-        <v>472</v>
+        <v>486</v>
       </c>
       <c r="C4" s="32" t="s">
         <v>97</v>
       </c>
       <c r="D4" s="21" t="s">
-        <v>473</v>
+        <v>487</v>
       </c>
       <c r="E4" s="21" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="F4" s="21" t="str">
         <f>Variables!C8</f>
         <v>c7cf918d-7e04-4104-9790-fa5bb9d3756d</v>
       </c>
       <c r="G4" s="21" t="s">
-        <v>474</v>
+        <v>488</v>
       </c>
       <c r="H4" s="33" t="s">
         <v>70</v>
       </c>
       <c r="I4" s="21" t="s">
-        <v>475</v>
+        <v>489</v>
       </c>
       <c r="J4" s="23"/>
     </row>
     <row r="5" ht="18.0" customHeight="1">
       <c r="A5" s="29" t="s">
-        <v>476</v>
+        <v>490</v>
       </c>
       <c r="B5" s="30"/>
       <c r="C5" s="30"/>
@@ -4886,100 +4933,100 @@
     </row>
     <row r="6" ht="42.0" customHeight="1">
       <c r="A6" s="23" t="s">
-        <v>477</v>
+        <v>491</v>
       </c>
       <c r="B6" s="21" t="s">
-        <v>478</v>
+        <v>492</v>
       </c>
       <c r="C6" s="32" t="s">
         <v>97</v>
       </c>
       <c r="D6" s="21" t="s">
-        <v>479</v>
+        <v>493</v>
       </c>
       <c r="E6" s="21" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="F6" s="21" t="str">
         <f>"{""targetId"":""" &amp; Variables!C5 &amp; """,""helpRequestId"":""" &amp; Variables!C8 &amp; """,""rating"":5,""comment"":""Excelente voluntario, muy puntual y atento""}"</f>
         <v>{"targetId":"69ad88c5-bd50-46e1-824a-0625dabf99ea","helpRequestId":"c7cf918d-7e04-4104-9790-fa5bb9d3756d","rating":5,"comment":"Excelente voluntario, muy puntual y atento"}</v>
       </c>
       <c r="G6" s="21" t="s">
-        <v>480</v>
+        <v>494</v>
       </c>
       <c r="H6" s="33" t="s">
         <v>70</v>
       </c>
       <c r="I6" s="21" t="s">
-        <v>481</v>
+        <v>495</v>
       </c>
       <c r="J6" s="23"/>
     </row>
     <row r="7" ht="42.0" customHeight="1">
       <c r="A7" s="34" t="s">
-        <v>482</v>
+        <v>496</v>
       </c>
       <c r="B7" s="20" t="s">
-        <v>483</v>
+        <v>497</v>
       </c>
       <c r="C7" s="35" t="s">
         <v>97</v>
       </c>
       <c r="D7" s="20" t="s">
-        <v>479</v>
+        <v>493</v>
       </c>
       <c r="E7" s="20" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="F7" s="20" t="str">
         <f>"{""targetId"":""" &amp; Variables!C7 &amp; """,""helpRequestId"":""" &amp; Variables!C8 &amp; """,""rating"":4,""comment"":""Todo muy claro y organizado""}"</f>
         <v>{"targetId":"f08371a0-756b-47d7-b714-533edd782035","helpRequestId":"c7cf918d-7e04-4104-9790-fa5bb9d3756d","rating":4,"comment":"Todo muy claro y organizado"}</v>
       </c>
       <c r="G7" s="20" t="s">
-        <v>484</v>
+        <v>498</v>
       </c>
       <c r="H7" s="33" t="s">
         <v>70</v>
       </c>
       <c r="I7" s="20" t="s">
-        <v>485</v>
+        <v>499</v>
       </c>
       <c r="J7" s="34"/>
     </row>
     <row r="8" ht="42.0" customHeight="1">
       <c r="A8" s="23" t="s">
-        <v>486</v>
+        <v>500</v>
       </c>
       <c r="B8" s="21" t="s">
-        <v>487</v>
+        <v>501</v>
       </c>
       <c r="C8" s="32" t="s">
         <v>97</v>
       </c>
       <c r="D8" s="21" t="s">
-        <v>479</v>
+        <v>493</v>
       </c>
       <c r="E8" s="21" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="F8" s="21" t="str">
         <f>"{""targetId"":""" &amp; Variables!C5 &amp; """,""donationId"":""" &amp; Variables!C11 &amp; """,""rating"":5,""comment"":""Recogió la donación perfectamente""}"</f>
         <v>{"targetId":"69ad88c5-bd50-46e1-824a-0625dabf99ea","donationId":"8396e74a-7bc5-4793-b7c4-bd79b3b7932b","rating":5,"comment":"Recogió la donación perfectamente"}</v>
       </c>
       <c r="G8" s="21" t="s">
-        <v>488</v>
+        <v>502</v>
       </c>
       <c r="H8" s="33" t="s">
         <v>70</v>
       </c>
       <c r="I8" s="21" t="s">
-        <v>485</v>
+        <v>499</v>
       </c>
       <c r="J8" s="23"/>
     </row>
     <row r="9" ht="18.0" customHeight="1">
       <c r="A9" s="29" t="s">
-        <v>489</v>
+        <v>503</v>
       </c>
       <c r="B9" s="30"/>
       <c r="C9" s="30"/>
@@ -4993,100 +5040,100 @@
     </row>
     <row r="10" ht="42.0" customHeight="1">
       <c r="A10" s="23" t="s">
-        <v>490</v>
+        <v>504</v>
       </c>
       <c r="B10" s="21" t="s">
-        <v>491</v>
+        <v>505</v>
       </c>
       <c r="C10" s="32" t="s">
         <v>97</v>
       </c>
       <c r="D10" s="21" t="s">
-        <v>479</v>
+        <v>493</v>
       </c>
       <c r="E10" s="21" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="F10" s="21" t="str">
         <f>"{""targetId"":""" &amp; Variables!C5 &amp; """,""helpRequestId"":""" &amp; Variables!C8 &amp; """,""rating"":3,""comment"":""Segunda review""}"</f>
         <v>{"targetId":"69ad88c5-bd50-46e1-824a-0625dabf99ea","helpRequestId":"c7cf918d-7e04-4104-9790-fa5bb9d3756d","rating":3,"comment":"Segunda review"}</v>
       </c>
       <c r="G10" s="21" t="s">
-        <v>492</v>
+        <v>506</v>
       </c>
       <c r="H10" s="33" t="s">
         <v>70</v>
       </c>
       <c r="I10" s="21" t="s">
-        <v>493</v>
+        <v>507</v>
       </c>
       <c r="J10" s="23"/>
     </row>
     <row r="11" ht="42.0" customHeight="1">
       <c r="A11" s="34" t="s">
-        <v>494</v>
+        <v>508</v>
       </c>
       <c r="B11" s="20" t="s">
-        <v>495</v>
+        <v>509</v>
       </c>
       <c r="C11" s="35" t="s">
         <v>97</v>
       </c>
       <c r="D11" s="20" t="s">
-        <v>479</v>
+        <v>493</v>
       </c>
       <c r="E11" s="20" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="F11" s="20" t="str">
         <f>"{""targetId"":""" &amp; Variables!C6 &amp; """,""donationId"":""" &amp; Variables!C10 &amp; """,""rating"":3,""comment"":""Test""}"</f>
         <v>{"targetId":"beeaa200-52c6-44fa-9333-b4f6f375e314","donationId":"4a2c7d53-9a34-4c40-9e8f-c8972db67211","rating":3,"comment":"Test"}</v>
       </c>
       <c r="G11" s="20" t="s">
-        <v>496</v>
+        <v>510</v>
       </c>
       <c r="H11" s="33" t="s">
         <v>70</v>
       </c>
       <c r="I11" s="20" t="s">
-        <v>497</v>
+        <v>511</v>
       </c>
       <c r="J11" s="34"/>
     </row>
     <row r="12" ht="42.0" customHeight="1">
       <c r="A12" s="23" t="s">
-        <v>498</v>
+        <v>512</v>
       </c>
       <c r="B12" s="21" t="s">
-        <v>499</v>
+        <v>513</v>
       </c>
       <c r="C12" s="32" t="s">
         <v>97</v>
       </c>
       <c r="D12" s="21" t="s">
-        <v>479</v>
+        <v>493</v>
       </c>
       <c r="E12" s="21" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="F12" s="21" t="str">
         <f>"{""targetId"":""" &amp; Variables!C5 &amp; """,""helpRequestId"":""" &amp; Variables!C8 &amp; """,""rating"":4,""comment"":""Test""}"</f>
         <v>{"targetId":"69ad88c5-bd50-46e1-824a-0625dabf99ea","helpRequestId":"c7cf918d-7e04-4104-9790-fa5bb9d3756d","rating":4,"comment":"Test"}</v>
       </c>
       <c r="G12" s="21" t="s">
-        <v>500</v>
+        <v>514</v>
       </c>
       <c r="H12" s="33" t="s">
         <v>70</v>
       </c>
       <c r="I12" s="21" t="s">
-        <v>501</v>
+        <v>515</v>
       </c>
       <c r="J12" s="23"/>
     </row>
     <row r="13" ht="18.0" customHeight="1">
       <c r="A13" s="29" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="B13" s="30"/>
       <c r="C13" s="30"/>
@@ -5100,83 +5147,83 @@
     </row>
     <row r="14" ht="42.0" customHeight="1">
       <c r="A14" s="23" t="s">
-        <v>502</v>
+        <v>516</v>
       </c>
       <c r="B14" s="21" t="s">
-        <v>503</v>
+        <v>517</v>
       </c>
       <c r="C14" s="43" t="s">
         <v>139</v>
       </c>
       <c r="D14" s="21" t="s">
-        <v>504</v>
+        <v>518</v>
       </c>
       <c r="E14" s="21" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="F14" s="21" t="str">
         <f>Variables!C5</f>
         <v>69ad88c5-bd50-46e1-824a-0625dabf99ea</v>
       </c>
       <c r="G14" s="21" t="s">
-        <v>505</v>
+        <v>519</v>
       </c>
       <c r="H14" s="33" t="s">
         <v>70</v>
       </c>
       <c r="I14" s="21" t="s">
-        <v>506</v>
+        <v>520</v>
       </c>
       <c r="J14" s="23"/>
     </row>
     <row r="15" ht="42.0" customHeight="1">
       <c r="A15" s="34" t="s">
-        <v>507</v>
+        <v>521</v>
       </c>
       <c r="B15" s="20" t="s">
-        <v>508</v>
+        <v>522</v>
       </c>
       <c r="C15" s="44" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="D15" s="20" t="s">
-        <v>509</v>
+        <v>523</v>
       </c>
       <c r="E15" s="20" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="F15" s="20" t="s">
-        <v>510</v>
+        <v>524</v>
       </c>
       <c r="G15" s="20" t="s">
-        <v>511</v>
+        <v>525</v>
       </c>
       <c r="H15" s="33" t="s">
         <v>70</v>
       </c>
       <c r="I15" s="20" t="s">
-        <v>506</v>
+        <v>520</v>
       </c>
       <c r="J15" s="34"/>
     </row>
     <row r="16" ht="42.0" customHeight="1">
       <c r="A16" s="23" t="s">
-        <v>512</v>
+        <v>526</v>
       </c>
       <c r="B16" s="21" t="s">
-        <v>513</v>
+        <v>527</v>
       </c>
       <c r="C16" s="45" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="D16" s="21" t="s">
-        <v>509</v>
+        <v>523</v>
       </c>
       <c r="E16" s="21" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="F16" s="21" t="s">
-        <v>514</v>
+        <v>528</v>
       </c>
       <c r="G16" s="21" t="s">
         <v>112</v>
@@ -5185,37 +5232,37 @@
         <v>70</v>
       </c>
       <c r="I16" s="21" t="s">
-        <v>515</v>
+        <v>529</v>
       </c>
       <c r="J16" s="23"/>
     </row>
     <row r="17" ht="42.0" customHeight="1">
       <c r="A17" s="34" t="s">
-        <v>516</v>
+        <v>530</v>
       </c>
       <c r="B17" s="20" t="s">
-        <v>517</v>
-      </c>
-      <c r="C17" s="55" t="s">
-        <v>330</v>
+        <v>531</v>
+      </c>
+      <c r="C17" s="56" t="s">
+        <v>340</v>
       </c>
       <c r="D17" s="20" t="s">
-        <v>509</v>
+        <v>523</v>
       </c>
       <c r="E17" s="20" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="F17" s="20" t="s">
         <v>141</v>
       </c>
       <c r="G17" s="20" t="s">
-        <v>518</v>
+        <v>532</v>
       </c>
       <c r="H17" s="33" t="s">
         <v>70</v>
       </c>
       <c r="I17" s="20" t="s">
-        <v>519</v>
+        <v>533</v>
       </c>
       <c r="J17" s="34"/>
     </row>
@@ -7467,11 +7514,11 @@
       </c>
       <c r="C5" s="23">
         <f>COUNTIF(Auth!A:A,"A-*")</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D5" s="23">
         <f>COUNTIF(Auth!H:H,D4)</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E5" s="23">
         <f>COUNTIF(Auth!H:H,E4)</f>
@@ -7542,11 +7589,11 @@
       </c>
       <c r="C8" s="23">
         <f>COUNTIF('Help Requests'!A:A,"Hr-*")</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D8" s="23">
         <f>COUNTIF('Help Requests'!H:H,D4)</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E8" s="23">
         <f>COUNTIF('Help Requests'!H:H,E4)</f>
@@ -7567,11 +7614,11 @@
       </c>
       <c r="C9" s="23">
         <f>COUNTIF(Donations!A:A,"D-*")</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D9" s="23">
         <f>COUNTIF(Donations!H:H,D4)</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E9" s="23">
         <f>COUNTIF(Donations!H:H,E4)</f>
@@ -7667,11 +7714,11 @@
       </c>
       <c r="C13" s="25">
         <f t="shared" ref="C13:F13" si="2">SUM(C5:C12)</f>
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D13" s="25">
         <f t="shared" si="2"/>
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E13" s="25">
         <f t="shared" si="2"/>
@@ -9448,7 +9495,36 @@
       </c>
       <c r="J27" s="34"/>
     </row>
-    <row r="28" ht="15.75" customHeight="1"/>
+    <row r="28" ht="42.0" customHeight="1">
+      <c r="A28" s="41" t="s">
+        <v>189</v>
+      </c>
+      <c r="B28" s="42" t="s">
+        <v>190</v>
+      </c>
+      <c r="C28" s="32" t="s">
+        <v>97</v>
+      </c>
+      <c r="D28" s="42" t="s">
+        <v>160</v>
+      </c>
+      <c r="E28" s="42" t="s">
+        <v>99</v>
+      </c>
+      <c r="F28" s="42" t="s">
+        <v>191</v>
+      </c>
+      <c r="G28" s="42" t="s">
+        <v>192</v>
+      </c>
+      <c r="H28" s="40" t="s">
+        <v>70</v>
+      </c>
+      <c r="I28" s="42" t="s">
+        <v>193</v>
+      </c>
+      <c r="J28" s="23"/>
+    </row>
     <row r="29" ht="15.75" customHeight="1"/>
     <row r="30" ht="15.75" customHeight="1"/>
     <row r="31" ht="15.75" customHeight="1"/>
@@ -10418,6 +10494,7 @@
     <row r="995" ht="15.75" customHeight="1"/>
     <row r="996" ht="15.75" customHeight="1"/>
     <row r="997" ht="15.75" customHeight="1"/>
+    <row r="998" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="A1:J1"/>
@@ -10426,23 +10503,23 @@
     <mergeCell ref="A16:J16"/>
     <mergeCell ref="A20:J20"/>
   </mergeCells>
-  <conditionalFormatting sqref="H4:H8 H10:H15 H17:H19 H21:H27">
+  <conditionalFormatting sqref="H4:H8 H10:H15 H17:H19 H21:H28">
     <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="✅ PASS">
       <formula>NOT(ISERROR(SEARCH(("✅ PASS"),(H4))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H4:H8 H10:H15 H17:H19 H21:H27">
+  <conditionalFormatting sqref="H4:H8 H10:H15 H17:H19 H21:H28">
     <cfRule type="containsText" dxfId="4" priority="2" operator="containsText" text="❌ FAIL">
       <formula>NOT(ISERROR(SEARCH(("❌ FAIL"),(H4))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H4:H8 H10:H15 H17:H19 H21:H27">
+  <conditionalFormatting sqref="H4:H8 H10:H15 H17:H19 H21:H28">
     <cfRule type="containsText" dxfId="2" priority="3" operator="containsText" text="⏳ PENDING">
       <formula>NOT(ISERROR(SEARCH(("⏳ PENDING"),(H4))))</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="H4:H8 H10:H15 H17:H19 H21:H27">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="H4:H8 H10:H15 H17:H19 H21:H28">
       <formula1>"⏳ PENDIENTE,✅ PASS,❌ FAIL"</formula1>
     </dataValidation>
   </dataValidations>
@@ -10474,7 +10551,7 @@
   <sheetData>
     <row r="1" ht="24.0" customHeight="1">
       <c r="A1" s="27" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="B1" s="28"/>
       <c r="C1" s="28"/>
@@ -10520,7 +10597,7 @@
     </row>
     <row r="3" ht="18.0" customHeight="1">
       <c r="A3" s="29" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="B3" s="30"/>
       <c r="C3" s="30"/>
@@ -10534,10 +10611,10 @@
     </row>
     <row r="4" ht="42.0" customHeight="1">
       <c r="A4" s="23" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="B4" s="21" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="C4" s="43" t="s">
         <v>139</v>
@@ -10546,28 +10623,28 @@
         <v>140</v>
       </c>
       <c r="E4" s="21" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="F4" s="21" t="s">
         <v>141</v>
       </c>
       <c r="G4" s="21" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="H4" s="33" t="s">
         <v>70</v>
       </c>
       <c r="I4" s="21" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="J4" s="23"/>
     </row>
     <row r="5" ht="42.0" customHeight="1">
       <c r="A5" s="34" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="B5" s="20" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="C5" s="36" t="s">
         <v>139</v>
@@ -10576,28 +10653,28 @@
         <v>140</v>
       </c>
       <c r="E5" s="20" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="F5" s="20" t="s">
         <v>141</v>
       </c>
       <c r="G5" s="20" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="H5" s="33" t="s">
         <v>70</v>
       </c>
       <c r="I5" s="20" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="J5" s="34"/>
     </row>
     <row r="6" ht="42.0" customHeight="1">
       <c r="A6" s="23" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="B6" s="21" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="C6" s="43" t="s">
         <v>139</v>
@@ -10606,55 +10683,55 @@
         <v>140</v>
       </c>
       <c r="E6" s="21" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="F6" s="21" t="s">
         <v>141</v>
       </c>
       <c r="G6" s="21" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="H6" s="33" t="s">
         <v>70</v>
       </c>
       <c r="I6" s="21" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="J6" s="23"/>
     </row>
     <row r="7" ht="42.0" customHeight="1">
       <c r="A7" s="34" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="B7" s="20" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="C7" s="44" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="D7" s="20" t="s">
         <v>140</v>
       </c>
       <c r="E7" s="20" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="F7" s="20" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="G7" s="20" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="H7" s="33" t="s">
         <v>70</v>
       </c>
       <c r="I7" s="20" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="J7" s="34"/>
     </row>
     <row r="8" ht="18.0" customHeight="1">
       <c r="A8" s="29" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="B8" s="30"/>
       <c r="C8" s="30"/>
@@ -10668,61 +10745,61 @@
     </row>
     <row r="9" ht="42.0" customHeight="1">
       <c r="A9" s="34" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="B9" s="20" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="C9" s="36" t="s">
         <v>139</v>
       </c>
       <c r="D9" s="20" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="E9" s="20" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="F9" s="20" t="s">
         <v>141</v>
       </c>
       <c r="G9" s="20" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="H9" s="33" t="s">
         <v>70</v>
       </c>
       <c r="I9" s="20" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="J9" s="34"/>
     </row>
     <row r="10" ht="42.0" customHeight="1">
       <c r="A10" s="23" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="B10" s="21" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="C10" s="43" t="s">
         <v>139</v>
       </c>
       <c r="D10" s="21" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="E10" s="21" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="F10" s="21" t="s">
         <v>141</v>
       </c>
       <c r="G10" s="21" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="H10" s="33" t="s">
         <v>70</v>
       </c>
       <c r="I10" s="21" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="J10" s="23"/>
     </row>
@@ -11760,7 +11837,7 @@
   <sheetData>
     <row r="1" ht="24.0" customHeight="1">
       <c r="A1" s="27" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="B1" s="28"/>
       <c r="C1" s="28"/>
@@ -11806,7 +11883,7 @@
     </row>
     <row r="3" ht="18.0" customHeight="1">
       <c r="A3" s="29" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="B3" s="30"/>
       <c r="C3" s="30"/>
@@ -11820,82 +11897,82 @@
     </row>
     <row r="4" ht="42.0" customHeight="1">
       <c r="A4" s="23" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="B4" s="21" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="C4" s="32" t="s">
         <v>97</v>
       </c>
       <c r="D4" s="21" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="E4" s="21" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="F4" s="21" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="G4" s="21" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="H4" s="33" t="s">
         <v>70</v>
       </c>
       <c r="I4" s="21" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="J4" s="23"/>
     </row>
     <row r="5" ht="42.0" customHeight="1">
       <c r="A5" s="34" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="B5" s="20" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="C5" s="35" t="s">
         <v>97</v>
       </c>
       <c r="D5" s="20" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="E5" s="20" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="F5" s="20" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="G5" s="20" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="H5" s="33" t="s">
         <v>70</v>
       </c>
       <c r="I5" s="20" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="J5" s="34"/>
     </row>
     <row r="6" ht="42.0" customHeight="1">
       <c r="A6" s="23" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="B6" s="21" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="C6" s="32" t="s">
         <v>97</v>
       </c>
       <c r="D6" s="21" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="E6" s="21" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="F6" s="21" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="G6" s="21" t="s">
         <v>112</v>
@@ -11904,13 +11981,13 @@
         <v>70</v>
       </c>
       <c r="I6" s="21" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="J6" s="23"/>
     </row>
     <row r="7" ht="18.0" customHeight="1">
       <c r="A7" s="29" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="B7" s="30"/>
       <c r="C7" s="30"/>
@@ -11924,139 +12001,139 @@
     </row>
     <row r="8" ht="42.0" customHeight="1">
       <c r="A8" s="23" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="B8" s="21" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="C8" s="43" t="s">
         <v>139</v>
       </c>
       <c r="D8" s="21" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="E8" s="21" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="F8" s="21" t="s">
         <v>141</v>
       </c>
       <c r="G8" s="21" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="H8" s="33" t="s">
         <v>70</v>
       </c>
       <c r="I8" s="21" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="J8" s="23"/>
     </row>
     <row r="9" ht="42.0" customHeight="1">
       <c r="A9" s="34" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="B9" s="20" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="C9" s="44" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="D9" s="20" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="E9" s="20" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="F9" s="20" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="G9" s="20" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="H9" s="33" t="s">
         <v>70</v>
       </c>
       <c r="I9" s="20" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="J9" s="34"/>
     </row>
     <row r="10" ht="42.0" customHeight="1">
       <c r="A10" s="23" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="B10" s="21" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="C10" s="45" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="D10" s="21" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="E10" s="21" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="F10" s="21" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="G10" s="21" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="H10" s="33" t="s">
         <v>70</v>
       </c>
       <c r="I10" s="21" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="J10" s="23"/>
     </row>
     <row r="11" ht="42.0" customHeight="1">
       <c r="A11" s="34" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="B11" s="20" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="C11" s="44" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="D11" s="20" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="E11" s="20" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="F11" s="20" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="G11" s="20" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="H11" s="33" t="s">
         <v>70</v>
       </c>
       <c r="I11" s="20" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="J11" s="34"/>
     </row>
     <row r="12" ht="42.0" customHeight="1">
       <c r="A12" s="23" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="B12" s="21" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="C12" s="43" t="s">
         <v>139</v>
       </c>
       <c r="D12" s="21" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="E12" s="21" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="F12" s="21" t="s">
         <v>141</v>
@@ -12068,7 +12145,7 @@
         <v>70</v>
       </c>
       <c r="I12" s="21" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="J12" s="23"/>
     </row>
@@ -13107,7 +13184,7 @@
   <sheetData>
     <row r="1" ht="24.0" customHeight="1">
       <c r="A1" s="27" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="B1" s="28"/>
       <c r="C1" s="28"/>
@@ -13153,7 +13230,7 @@
     </row>
     <row r="3" ht="18.0" customHeight="1">
       <c r="A3" s="29" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="B3" s="30"/>
       <c r="C3" s="30"/>
@@ -13167,82 +13244,82 @@
     </row>
     <row r="4" ht="42.0" customHeight="1">
       <c r="A4" s="23" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="B4" s="21" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="C4" s="32" t="s">
         <v>97</v>
       </c>
       <c r="D4" s="21" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="E4" s="21" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="F4" s="21" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="G4" s="21" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="H4" s="33" t="s">
         <v>70</v>
       </c>
       <c r="I4" s="21" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="J4" s="23"/>
     </row>
     <row r="5" ht="42.0" customHeight="1">
       <c r="A5" s="34" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="B5" s="20" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="C5" s="35" t="s">
         <v>97</v>
       </c>
       <c r="D5" s="20" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="E5" s="20" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="F5" s="20" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="G5" s="20" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="H5" s="33" t="s">
         <v>70</v>
       </c>
       <c r="I5" s="20" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="J5" s="34"/>
     </row>
     <row r="6" ht="42.0" customHeight="1">
       <c r="A6" s="23" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="B6" s="21" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="C6" s="32" t="s">
         <v>97</v>
       </c>
       <c r="D6" s="21" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="E6" s="21" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="F6" s="21" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="G6" s="21" t="s">
         <v>117</v>
@@ -13251,13 +13328,13 @@
         <v>70</v>
       </c>
       <c r="I6" s="21" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="J6" s="23"/>
     </row>
     <row r="7" ht="18.0" customHeight="1">
       <c r="A7" s="29" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="B7" s="30"/>
       <c r="C7" s="30"/>
@@ -13271,31 +13348,31 @@
     </row>
     <row r="8" ht="42.0" customHeight="1">
       <c r="A8" s="23" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="B8" s="46" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="C8" s="43" t="s">
         <v>139</v>
       </c>
       <c r="D8" s="46" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="E8" s="46" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="F8" s="46" t="s">
         <v>141</v>
       </c>
       <c r="G8" s="46" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="H8" s="47" t="s">
         <v>70</v>
       </c>
       <c r="I8" s="46" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="J8" s="48"/>
       <c r="K8" s="49"/>
@@ -13317,123 +13394,123 @@
     </row>
     <row r="9" ht="42.0" customHeight="1">
       <c r="A9" s="50" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="B9" s="51" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="C9" s="52" t="s">
         <v>139</v>
       </c>
       <c r="D9" s="51" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="E9" s="51" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="F9" s="51" t="s">
         <v>141</v>
       </c>
       <c r="G9" s="51" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="H9" s="33" t="s">
         <v>70</v>
       </c>
       <c r="I9" s="51" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="J9" s="23"/>
     </row>
     <row r="10" ht="42.0" customHeight="1">
       <c r="A10" s="23" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="B10" s="21" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="C10" s="43" t="s">
         <v>139</v>
       </c>
       <c r="D10" s="21" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="E10" s="21" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="F10" s="21" t="str">
         <f>Variables!C8</f>
         <v>c7cf918d-7e04-4104-9790-fa5bb9d3756d</v>
       </c>
       <c r="G10" s="21" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="H10" s="33" t="s">
         <v>70</v>
       </c>
       <c r="I10" s="21" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="J10" s="34"/>
     </row>
     <row r="11" ht="42.0" customHeight="1">
       <c r="A11" s="34" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="B11" s="20" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="C11" s="36" t="s">
         <v>139</v>
       </c>
       <c r="D11" s="20" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="E11" s="20" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="F11" s="20" t="s">
         <v>141</v>
       </c>
       <c r="G11" s="20" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="H11" s="33" t="s">
         <v>70</v>
       </c>
       <c r="I11" s="20" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="J11" s="34"/>
     </row>
     <row r="12" ht="42.0" customHeight="1">
       <c r="A12" s="23" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="B12" s="46" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="C12" s="43" t="s">
         <v>139</v>
       </c>
       <c r="D12" s="46" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="E12" s="46" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="F12" s="21" t="str">
         <f>Variables!C8</f>
         <v>c7cf918d-7e04-4104-9790-fa5bb9d3756d</v>
       </c>
       <c r="G12" s="46" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="H12" s="47" t="s">
         <v>70</v>
       </c>
       <c r="I12" s="46" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="J12" s="48"/>
       <c r="K12" s="49"/>
@@ -13455,33 +13532,33 @@
     </row>
     <row r="13" ht="42.0" customHeight="1">
       <c r="A13" s="34" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="B13" s="53" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C13" s="36" t="s">
         <v>139</v>
       </c>
       <c r="D13" s="53" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="E13" s="53" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="F13" s="53" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="G13" s="53" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="H13" s="47" t="s">
         <v>70</v>
       </c>
       <c r="I13" s="53" t="s">
-        <v>305</v>
-      </c>
-      <c r="J13" s="48"/>
+        <v>310</v>
+      </c>
+      <c r="J13" s="54"/>
       <c r="K13" s="49"/>
       <c r="L13" s="49"/>
       <c r="M13" s="49"/>
@@ -13501,33 +13578,33 @@
     </row>
     <row r="14" ht="42.0" customHeight="1">
       <c r="A14" s="23" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="B14" s="46" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="C14" s="43" t="s">
         <v>139</v>
       </c>
       <c r="D14" s="46" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="E14" s="46" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="F14" s="46" t="s">
         <v>141</v>
       </c>
       <c r="G14" s="46" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="H14" s="47" t="s">
         <v>70</v>
       </c>
       <c r="I14" s="46" t="s">
-        <v>309</v>
-      </c>
-      <c r="J14" s="54"/>
+        <v>314</v>
+      </c>
+      <c r="J14" s="48"/>
       <c r="K14" s="49"/>
       <c r="L14" s="49"/>
       <c r="M14" s="49"/>
@@ -13547,34 +13624,34 @@
     </row>
     <row r="15" ht="42.0" customHeight="1">
       <c r="A15" s="34" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="B15" s="53" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="C15" s="36" t="s">
         <v>139</v>
       </c>
       <c r="D15" s="53" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="E15" s="53" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="F15" s="53" t="str">
         <f>Variables!C8</f>
         <v>c7cf918d-7e04-4104-9790-fa5bb9d3756d</v>
       </c>
       <c r="G15" s="53" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="H15" s="47" t="s">
         <v>70</v>
       </c>
       <c r="I15" s="53" t="s">
-        <v>219</v>
-      </c>
-      <c r="J15" s="48"/>
+        <v>224</v>
+      </c>
+      <c r="J15" s="54"/>
       <c r="K15" s="49"/>
       <c r="L15" s="49"/>
       <c r="M15" s="49"/>
@@ -13592,154 +13669,1657 @@
       <c r="Y15" s="49"/>
       <c r="Z15" s="49"/>
     </row>
-    <row r="16" ht="18.0" customHeight="1">
-      <c r="A16" s="29" t="s">
-        <v>313</v>
-      </c>
-      <c r="B16" s="30"/>
-      <c r="C16" s="30"/>
-      <c r="D16" s="30"/>
-      <c r="E16" s="30"/>
-      <c r="F16" s="30"/>
-      <c r="G16" s="30"/>
-      <c r="H16" s="30"/>
-      <c r="I16" s="30"/>
-      <c r="J16" s="31"/>
-    </row>
-    <row r="17" ht="42.0" customHeight="1">
-      <c r="A17" s="34" t="s">
-        <v>314</v>
-      </c>
-      <c r="B17" s="20" t="s">
-        <v>315</v>
-      </c>
-      <c r="C17" s="44" t="s">
-        <v>206</v>
-      </c>
-      <c r="D17" s="20" t="s">
-        <v>316</v>
-      </c>
-      <c r="E17" s="20" t="s">
-        <v>193</v>
-      </c>
-      <c r="F17" s="20" t="str">
+    <row r="16" ht="42.0" customHeight="1">
+      <c r="A16" s="41" t="s">
+        <v>318</v>
+      </c>
+      <c r="B16" s="55" t="s">
+        <v>319</v>
+      </c>
+      <c r="C16" s="43" t="s">
+        <v>139</v>
+      </c>
+      <c r="D16" s="55" t="s">
+        <v>320</v>
+      </c>
+      <c r="E16" s="46" t="s">
+        <v>198</v>
+      </c>
+      <c r="F16" s="55" t="s">
+        <v>321</v>
+      </c>
+      <c r="G16" s="55" t="s">
+        <v>148</v>
+      </c>
+      <c r="H16" s="47" t="s">
+        <v>70</v>
+      </c>
+      <c r="I16" s="55" t="s">
+        <v>322</v>
+      </c>
+      <c r="J16" s="48"/>
+      <c r="K16" s="49"/>
+      <c r="L16" s="49"/>
+      <c r="M16" s="49"/>
+      <c r="N16" s="49"/>
+      <c r="O16" s="49"/>
+      <c r="P16" s="49"/>
+      <c r="Q16" s="49"/>
+      <c r="R16" s="49"/>
+      <c r="S16" s="49"/>
+      <c r="T16" s="49"/>
+      <c r="U16" s="49"/>
+      <c r="V16" s="49"/>
+      <c r="W16" s="49"/>
+      <c r="X16" s="49"/>
+      <c r="Y16" s="49"/>
+      <c r="Z16" s="49"/>
+    </row>
+    <row r="17" ht="18.0" customHeight="1">
+      <c r="A17" s="29" t="s">
+        <v>323</v>
+      </c>
+      <c r="B17" s="30"/>
+      <c r="C17" s="30"/>
+      <c r="D17" s="30"/>
+      <c r="E17" s="30"/>
+      <c r="F17" s="30"/>
+      <c r="G17" s="30"/>
+      <c r="H17" s="30"/>
+      <c r="I17" s="30"/>
+      <c r="J17" s="31"/>
+    </row>
+    <row r="18" ht="42.0" customHeight="1">
+      <c r="A18" s="38" t="s">
+        <v>324</v>
+      </c>
+      <c r="B18" s="20" t="s">
+        <v>325</v>
+      </c>
+      <c r="C18" s="44" t="s">
+        <v>211</v>
+      </c>
+      <c r="D18" s="20" t="s">
+        <v>326</v>
+      </c>
+      <c r="E18" s="20" t="s">
+        <v>198</v>
+      </c>
+      <c r="F18" s="20" t="str">
         <f>Variables!C8 &amp; ", {""title"":""Compra en supermercado — URGENTE""}"</f>
         <v>c7cf918d-7e04-4104-9790-fa5bb9d3756d, {"title":"Compra en supermercado — URGENTE"}</v>
       </c>
-      <c r="G17" s="20" t="s">
-        <v>317</v>
-      </c>
-      <c r="H17" s="33" t="s">
-        <v>70</v>
-      </c>
-      <c r="I17" s="20" t="s">
-        <v>318</v>
-      </c>
-      <c r="J17" s="34"/>
-    </row>
-    <row r="18" ht="42.0" customHeight="1">
-      <c r="A18" s="23" t="s">
-        <v>319</v>
-      </c>
-      <c r="B18" s="21" t="s">
-        <v>320</v>
-      </c>
-      <c r="C18" s="45" t="s">
-        <v>206</v>
-      </c>
-      <c r="D18" s="21" t="s">
-        <v>316</v>
-      </c>
-      <c r="E18" s="21" t="s">
-        <v>193</v>
-      </c>
-      <c r="F18" s="21" t="s">
-        <v>321</v>
-      </c>
-      <c r="G18" s="21" t="s">
-        <v>218</v>
+      <c r="G18" s="20" t="s">
+        <v>327</v>
       </c>
       <c r="H18" s="33" t="s">
         <v>70</v>
       </c>
-      <c r="I18" s="53" t="s">
-        <v>219</v>
-      </c>
-      <c r="J18" s="23"/>
-    </row>
-    <row r="19" ht="18.0" customHeight="1">
-      <c r="A19" s="29" t="s">
-        <v>322</v>
-      </c>
-      <c r="B19" s="30"/>
-      <c r="C19" s="30"/>
-      <c r="D19" s="30"/>
-      <c r="E19" s="30"/>
-      <c r="F19" s="30"/>
-      <c r="G19" s="30"/>
-      <c r="H19" s="30"/>
-      <c r="I19" s="30"/>
-      <c r="J19" s="31"/>
-    </row>
-    <row r="20" ht="42.0" customHeight="1">
-      <c r="A20" s="23" t="s">
-        <v>323</v>
-      </c>
-      <c r="B20" s="21" t="s">
-        <v>324</v>
-      </c>
-      <c r="C20" s="32" t="s">
+      <c r="I18" s="20" t="s">
+        <v>328</v>
+      </c>
+      <c r="J18" s="34"/>
+    </row>
+    <row r="19" ht="42.0" customHeight="1">
+      <c r="A19" s="41" t="s">
+        <v>329</v>
+      </c>
+      <c r="B19" s="21" t="s">
+        <v>330</v>
+      </c>
+      <c r="C19" s="45" t="s">
+        <v>211</v>
+      </c>
+      <c r="D19" s="21" t="s">
+        <v>326</v>
+      </c>
+      <c r="E19" s="21" t="s">
+        <v>198</v>
+      </c>
+      <c r="F19" s="21" t="s">
+        <v>331</v>
+      </c>
+      <c r="G19" s="21" t="s">
+        <v>223</v>
+      </c>
+      <c r="H19" s="33" t="s">
+        <v>70</v>
+      </c>
+      <c r="I19" s="46" t="s">
+        <v>224</v>
+      </c>
+      <c r="J19" s="23"/>
+    </row>
+    <row r="20" ht="18.0" customHeight="1">
+      <c r="A20" s="29" t="s">
+        <v>332</v>
+      </c>
+      <c r="B20" s="30"/>
+      <c r="C20" s="30"/>
+      <c r="D20" s="30"/>
+      <c r="E20" s="30"/>
+      <c r="F20" s="30"/>
+      <c r="G20" s="30"/>
+      <c r="H20" s="30"/>
+      <c r="I20" s="30"/>
+      <c r="J20" s="31"/>
+    </row>
+    <row r="21" ht="42.0" customHeight="1">
+      <c r="A21" s="41" t="s">
+        <v>333</v>
+      </c>
+      <c r="B21" s="21" t="s">
+        <v>334</v>
+      </c>
+      <c r="C21" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="D20" s="21" t="s">
-        <v>325</v>
-      </c>
-      <c r="E20" s="21" t="s">
-        <v>193</v>
-      </c>
-      <c r="F20" s="21" t="s">
+      <c r="D21" s="21" t="s">
+        <v>335</v>
+      </c>
+      <c r="E21" s="21" t="s">
+        <v>198</v>
+      </c>
+      <c r="F21" s="21" t="s">
         <v>141</v>
       </c>
-      <c r="G20" s="21" t="s">
-        <v>326</v>
-      </c>
-      <c r="H20" s="33" t="s">
-        <v>70</v>
-      </c>
-      <c r="I20" s="21" t="s">
-        <v>327</v>
-      </c>
-      <c r="J20" s="23"/>
-    </row>
-    <row r="21" ht="42.0" customHeight="1">
-      <c r="A21" s="34" t="s">
-        <v>328</v>
-      </c>
-      <c r="B21" s="20" t="s">
-        <v>329</v>
-      </c>
-      <c r="C21" s="55" t="s">
-        <v>330</v>
-      </c>
-      <c r="D21" s="20" t="s">
-        <v>331</v>
-      </c>
-      <c r="E21" s="20" t="s">
-        <v>193</v>
-      </c>
-      <c r="F21" s="20" t="s">
-        <v>141</v>
-      </c>
-      <c r="G21" s="20" t="s">
-        <v>332</v>
+      <c r="G21" s="21" t="s">
+        <v>336</v>
       </c>
       <c r="H21" s="33" t="s">
         <v>70</v>
       </c>
-      <c r="I21" s="20" t="s">
-        <v>333</v>
-      </c>
-      <c r="J21" s="34"/>
+      <c r="I21" s="21" t="s">
+        <v>337</v>
+      </c>
+      <c r="J21" s="23"/>
+    </row>
+    <row r="22" ht="42.0" customHeight="1">
+      <c r="A22" s="38" t="s">
+        <v>338</v>
+      </c>
+      <c r="B22" s="20" t="s">
+        <v>339</v>
+      </c>
+      <c r="C22" s="56" t="s">
+        <v>340</v>
+      </c>
+      <c r="D22" s="20" t="s">
+        <v>341</v>
+      </c>
+      <c r="E22" s="20" t="s">
+        <v>198</v>
+      </c>
+      <c r="F22" s="20" t="s">
+        <v>141</v>
+      </c>
+      <c r="G22" s="20" t="s">
+        <v>342</v>
+      </c>
+      <c r="H22" s="33" t="s">
+        <v>70</v>
+      </c>
+      <c r="I22" s="20" t="s">
+        <v>343</v>
+      </c>
+      <c r="J22" s="34"/>
+    </row>
+    <row r="23" ht="15.75" customHeight="1"/>
+    <row r="24" ht="15.75" customHeight="1"/>
+    <row r="25" ht="15.75" customHeight="1"/>
+    <row r="26" ht="15.75" customHeight="1"/>
+    <row r="27" ht="15.75" customHeight="1"/>
+    <row r="28" ht="15.75" customHeight="1"/>
+    <row r="29" ht="15.75" customHeight="1"/>
+    <row r="30" ht="15.75" customHeight="1"/>
+    <row r="31" ht="15.75" customHeight="1"/>
+    <row r="32" ht="15.75" customHeight="1"/>
+    <row r="33" ht="15.75" customHeight="1"/>
+    <row r="34" ht="15.75" customHeight="1"/>
+    <row r="35" ht="15.75" customHeight="1"/>
+    <row r="36" ht="15.75" customHeight="1"/>
+    <row r="37" ht="15.75" customHeight="1"/>
+    <row r="38" ht="15.75" customHeight="1"/>
+    <row r="39" ht="15.75" customHeight="1"/>
+    <row r="40" ht="15.75" customHeight="1"/>
+    <row r="41" ht="15.75" customHeight="1"/>
+    <row r="42" ht="15.75" customHeight="1"/>
+    <row r="43" ht="15.75" customHeight="1"/>
+    <row r="44" ht="15.75" customHeight="1"/>
+    <row r="45" ht="15.75" customHeight="1"/>
+    <row r="46" ht="15.75" customHeight="1"/>
+    <row r="47" ht="15.75" customHeight="1"/>
+    <row r="48" ht="15.75" customHeight="1"/>
+    <row r="49" ht="15.75" customHeight="1"/>
+    <row r="50" ht="15.75" customHeight="1"/>
+    <row r="51" ht="15.75" customHeight="1"/>
+    <row r="52" ht="15.75" customHeight="1"/>
+    <row r="53" ht="15.75" customHeight="1"/>
+    <row r="54" ht="15.75" customHeight="1"/>
+    <row r="55" ht="15.75" customHeight="1"/>
+    <row r="56" ht="15.75" customHeight="1"/>
+    <row r="57" ht="15.75" customHeight="1"/>
+    <row r="58" ht="15.75" customHeight="1"/>
+    <row r="59" ht="15.75" customHeight="1"/>
+    <row r="60" ht="15.75" customHeight="1"/>
+    <row r="61" ht="15.75" customHeight="1"/>
+    <row r="62" ht="15.75" customHeight="1"/>
+    <row r="63" ht="15.75" customHeight="1"/>
+    <row r="64" ht="15.75" customHeight="1"/>
+    <row r="65" ht="15.75" customHeight="1"/>
+    <row r="66" ht="15.75" customHeight="1"/>
+    <row r="67" ht="15.75" customHeight="1"/>
+    <row r="68" ht="15.75" customHeight="1"/>
+    <row r="69" ht="15.75" customHeight="1"/>
+    <row r="70" ht="15.75" customHeight="1"/>
+    <row r="71" ht="15.75" customHeight="1"/>
+    <row r="72" ht="15.75" customHeight="1"/>
+    <row r="73" ht="15.75" customHeight="1"/>
+    <row r="74" ht="15.75" customHeight="1"/>
+    <row r="75" ht="15.75" customHeight="1"/>
+    <row r="76" ht="15.75" customHeight="1"/>
+    <row r="77" ht="15.75" customHeight="1"/>
+    <row r="78" ht="15.75" customHeight="1"/>
+    <row r="79" ht="15.75" customHeight="1"/>
+    <row r="80" ht="15.75" customHeight="1"/>
+    <row r="81" ht="15.75" customHeight="1"/>
+    <row r="82" ht="15.75" customHeight="1"/>
+    <row r="83" ht="15.75" customHeight="1"/>
+    <row r="84" ht="15.75" customHeight="1"/>
+    <row r="85" ht="15.75" customHeight="1"/>
+    <row r="86" ht="15.75" customHeight="1"/>
+    <row r="87" ht="15.75" customHeight="1"/>
+    <row r="88" ht="15.75" customHeight="1"/>
+    <row r="89" ht="15.75" customHeight="1"/>
+    <row r="90" ht="15.75" customHeight="1"/>
+    <row r="91" ht="15.75" customHeight="1"/>
+    <row r="92" ht="15.75" customHeight="1"/>
+    <row r="93" ht="15.75" customHeight="1"/>
+    <row r="94" ht="15.75" customHeight="1"/>
+    <row r="95" ht="15.75" customHeight="1"/>
+    <row r="96" ht="15.75" customHeight="1"/>
+    <row r="97" ht="15.75" customHeight="1"/>
+    <row r="98" ht="15.75" customHeight="1"/>
+    <row r="99" ht="15.75" customHeight="1"/>
+    <row r="100" ht="15.75" customHeight="1"/>
+    <row r="101" ht="15.75" customHeight="1"/>
+    <row r="102" ht="15.75" customHeight="1"/>
+    <row r="103" ht="15.75" customHeight="1"/>
+    <row r="104" ht="15.75" customHeight="1"/>
+    <row r="105" ht="15.75" customHeight="1"/>
+    <row r="106" ht="15.75" customHeight="1"/>
+    <row r="107" ht="15.75" customHeight="1"/>
+    <row r="108" ht="15.75" customHeight="1"/>
+    <row r="109" ht="15.75" customHeight="1"/>
+    <row r="110" ht="15.75" customHeight="1"/>
+    <row r="111" ht="15.75" customHeight="1"/>
+    <row r="112" ht="15.75" customHeight="1"/>
+    <row r="113" ht="15.75" customHeight="1"/>
+    <row r="114" ht="15.75" customHeight="1"/>
+    <row r="115" ht="15.75" customHeight="1"/>
+    <row r="116" ht="15.75" customHeight="1"/>
+    <row r="117" ht="15.75" customHeight="1"/>
+    <row r="118" ht="15.75" customHeight="1"/>
+    <row r="119" ht="15.75" customHeight="1"/>
+    <row r="120" ht="15.75" customHeight="1"/>
+    <row r="121" ht="15.75" customHeight="1"/>
+    <row r="122" ht="15.75" customHeight="1"/>
+    <row r="123" ht="15.75" customHeight="1"/>
+    <row r="124" ht="15.75" customHeight="1"/>
+    <row r="125" ht="15.75" customHeight="1"/>
+    <row r="126" ht="15.75" customHeight="1"/>
+    <row r="127" ht="15.75" customHeight="1"/>
+    <row r="128" ht="15.75" customHeight="1"/>
+    <row r="129" ht="15.75" customHeight="1"/>
+    <row r="130" ht="15.75" customHeight="1"/>
+    <row r="131" ht="15.75" customHeight="1"/>
+    <row r="132" ht="15.75" customHeight="1"/>
+    <row r="133" ht="15.75" customHeight="1"/>
+    <row r="134" ht="15.75" customHeight="1"/>
+    <row r="135" ht="15.75" customHeight="1"/>
+    <row r="136" ht="15.75" customHeight="1"/>
+    <row r="137" ht="15.75" customHeight="1"/>
+    <row r="138" ht="15.75" customHeight="1"/>
+    <row r="139" ht="15.75" customHeight="1"/>
+    <row r="140" ht="15.75" customHeight="1"/>
+    <row r="141" ht="15.75" customHeight="1"/>
+    <row r="142" ht="15.75" customHeight="1"/>
+    <row r="143" ht="15.75" customHeight="1"/>
+    <row r="144" ht="15.75" customHeight="1"/>
+    <row r="145" ht="15.75" customHeight="1"/>
+    <row r="146" ht="15.75" customHeight="1"/>
+    <row r="147" ht="15.75" customHeight="1"/>
+    <row r="148" ht="15.75" customHeight="1"/>
+    <row r="149" ht="15.75" customHeight="1"/>
+    <row r="150" ht="15.75" customHeight="1"/>
+    <row r="151" ht="15.75" customHeight="1"/>
+    <row r="152" ht="15.75" customHeight="1"/>
+    <row r="153" ht="15.75" customHeight="1"/>
+    <row r="154" ht="15.75" customHeight="1"/>
+    <row r="155" ht="15.75" customHeight="1"/>
+    <row r="156" ht="15.75" customHeight="1"/>
+    <row r="157" ht="15.75" customHeight="1"/>
+    <row r="158" ht="15.75" customHeight="1"/>
+    <row r="159" ht="15.75" customHeight="1"/>
+    <row r="160" ht="15.75" customHeight="1"/>
+    <row r="161" ht="15.75" customHeight="1"/>
+    <row r="162" ht="15.75" customHeight="1"/>
+    <row r="163" ht="15.75" customHeight="1"/>
+    <row r="164" ht="15.75" customHeight="1"/>
+    <row r="165" ht="15.75" customHeight="1"/>
+    <row r="166" ht="15.75" customHeight="1"/>
+    <row r="167" ht="15.75" customHeight="1"/>
+    <row r="168" ht="15.75" customHeight="1"/>
+    <row r="169" ht="15.75" customHeight="1"/>
+    <row r="170" ht="15.75" customHeight="1"/>
+    <row r="171" ht="15.75" customHeight="1"/>
+    <row r="172" ht="15.75" customHeight="1"/>
+    <row r="173" ht="15.75" customHeight="1"/>
+    <row r="174" ht="15.75" customHeight="1"/>
+    <row r="175" ht="15.75" customHeight="1"/>
+    <row r="176" ht="15.75" customHeight="1"/>
+    <row r="177" ht="15.75" customHeight="1"/>
+    <row r="178" ht="15.75" customHeight="1"/>
+    <row r="179" ht="15.75" customHeight="1"/>
+    <row r="180" ht="15.75" customHeight="1"/>
+    <row r="181" ht="15.75" customHeight="1"/>
+    <row r="182" ht="15.75" customHeight="1"/>
+    <row r="183" ht="15.75" customHeight="1"/>
+    <row r="184" ht="15.75" customHeight="1"/>
+    <row r="185" ht="15.75" customHeight="1"/>
+    <row r="186" ht="15.75" customHeight="1"/>
+    <row r="187" ht="15.75" customHeight="1"/>
+    <row r="188" ht="15.75" customHeight="1"/>
+    <row r="189" ht="15.75" customHeight="1"/>
+    <row r="190" ht="15.75" customHeight="1"/>
+    <row r="191" ht="15.75" customHeight="1"/>
+    <row r="192" ht="15.75" customHeight="1"/>
+    <row r="193" ht="15.75" customHeight="1"/>
+    <row r="194" ht="15.75" customHeight="1"/>
+    <row r="195" ht="15.75" customHeight="1"/>
+    <row r="196" ht="15.75" customHeight="1"/>
+    <row r="197" ht="15.75" customHeight="1"/>
+    <row r="198" ht="15.75" customHeight="1"/>
+    <row r="199" ht="15.75" customHeight="1"/>
+    <row r="200" ht="15.75" customHeight="1"/>
+    <row r="201" ht="15.75" customHeight="1"/>
+    <row r="202" ht="15.75" customHeight="1"/>
+    <row r="203" ht="15.75" customHeight="1"/>
+    <row r="204" ht="15.75" customHeight="1"/>
+    <row r="205" ht="15.75" customHeight="1"/>
+    <row r="206" ht="15.75" customHeight="1"/>
+    <row r="207" ht="15.75" customHeight="1"/>
+    <row r="208" ht="15.75" customHeight="1"/>
+    <row r="209" ht="15.75" customHeight="1"/>
+    <row r="210" ht="15.75" customHeight="1"/>
+    <row r="211" ht="15.75" customHeight="1"/>
+    <row r="212" ht="15.75" customHeight="1"/>
+    <row r="213" ht="15.75" customHeight="1"/>
+    <row r="214" ht="15.75" customHeight="1"/>
+    <row r="215" ht="15.75" customHeight="1"/>
+    <row r="216" ht="15.75" customHeight="1"/>
+    <row r="217" ht="15.75" customHeight="1"/>
+    <row r="218" ht="15.75" customHeight="1"/>
+    <row r="219" ht="15.75" customHeight="1"/>
+    <row r="220" ht="15.75" customHeight="1"/>
+    <row r="221" ht="15.75" customHeight="1"/>
+    <row r="222" ht="15.75" customHeight="1"/>
+    <row r="223" ht="15.75" customHeight="1"/>
+    <row r="224" ht="15.75" customHeight="1"/>
+    <row r="225" ht="15.75" customHeight="1"/>
+    <row r="226" ht="15.75" customHeight="1"/>
+    <row r="227" ht="15.75" customHeight="1"/>
+    <row r="228" ht="15.75" customHeight="1"/>
+    <row r="229" ht="15.75" customHeight="1"/>
+    <row r="230" ht="15.75" customHeight="1"/>
+    <row r="231" ht="15.75" customHeight="1"/>
+    <row r="232" ht="15.75" customHeight="1"/>
+    <row r="233" ht="15.75" customHeight="1"/>
+    <row r="234" ht="15.75" customHeight="1"/>
+    <row r="235" ht="15.75" customHeight="1"/>
+    <row r="236" ht="15.75" customHeight="1"/>
+    <row r="237" ht="15.75" customHeight="1"/>
+    <row r="238" ht="15.75" customHeight="1"/>
+    <row r="239" ht="15.75" customHeight="1"/>
+    <row r="240" ht="15.75" customHeight="1"/>
+    <row r="241" ht="15.75" customHeight="1"/>
+    <row r="242" ht="15.75" customHeight="1"/>
+    <row r="243" ht="15.75" customHeight="1"/>
+    <row r="244" ht="15.75" customHeight="1"/>
+    <row r="245" ht="15.75" customHeight="1"/>
+    <row r="246" ht="15.75" customHeight="1"/>
+    <row r="247" ht="15.75" customHeight="1"/>
+    <row r="248" ht="15.75" customHeight="1"/>
+    <row r="249" ht="15.75" customHeight="1"/>
+    <row r="250" ht="15.75" customHeight="1"/>
+    <row r="251" ht="15.75" customHeight="1"/>
+    <row r="252" ht="15.75" customHeight="1"/>
+    <row r="253" ht="15.75" customHeight="1"/>
+    <row r="254" ht="15.75" customHeight="1"/>
+    <row r="255" ht="15.75" customHeight="1"/>
+    <row r="256" ht="15.75" customHeight="1"/>
+    <row r="257" ht="15.75" customHeight="1"/>
+    <row r="258" ht="15.75" customHeight="1"/>
+    <row r="259" ht="15.75" customHeight="1"/>
+    <row r="260" ht="15.75" customHeight="1"/>
+    <row r="261" ht="15.75" customHeight="1"/>
+    <row r="262" ht="15.75" customHeight="1"/>
+    <row r="263" ht="15.75" customHeight="1"/>
+    <row r="264" ht="15.75" customHeight="1"/>
+    <row r="265" ht="15.75" customHeight="1"/>
+    <row r="266" ht="15.75" customHeight="1"/>
+    <row r="267" ht="15.75" customHeight="1"/>
+    <row r="268" ht="15.75" customHeight="1"/>
+    <row r="269" ht="15.75" customHeight="1"/>
+    <row r="270" ht="15.75" customHeight="1"/>
+    <row r="271" ht="15.75" customHeight="1"/>
+    <row r="272" ht="15.75" customHeight="1"/>
+    <row r="273" ht="15.75" customHeight="1"/>
+    <row r="274" ht="15.75" customHeight="1"/>
+    <row r="275" ht="15.75" customHeight="1"/>
+    <row r="276" ht="15.75" customHeight="1"/>
+    <row r="277" ht="15.75" customHeight="1"/>
+    <row r="278" ht="15.75" customHeight="1"/>
+    <row r="279" ht="15.75" customHeight="1"/>
+    <row r="280" ht="15.75" customHeight="1"/>
+    <row r="281" ht="15.75" customHeight="1"/>
+    <row r="282" ht="15.75" customHeight="1"/>
+    <row r="283" ht="15.75" customHeight="1"/>
+    <row r="284" ht="15.75" customHeight="1"/>
+    <row r="285" ht="15.75" customHeight="1"/>
+    <row r="286" ht="15.75" customHeight="1"/>
+    <row r="287" ht="15.75" customHeight="1"/>
+    <row r="288" ht="15.75" customHeight="1"/>
+    <row r="289" ht="15.75" customHeight="1"/>
+    <row r="290" ht="15.75" customHeight="1"/>
+    <row r="291" ht="15.75" customHeight="1"/>
+    <row r="292" ht="15.75" customHeight="1"/>
+    <row r="293" ht="15.75" customHeight="1"/>
+    <row r="294" ht="15.75" customHeight="1"/>
+    <row r="295" ht="15.75" customHeight="1"/>
+    <row r="296" ht="15.75" customHeight="1"/>
+    <row r="297" ht="15.75" customHeight="1"/>
+    <row r="298" ht="15.75" customHeight="1"/>
+    <row r="299" ht="15.75" customHeight="1"/>
+    <row r="300" ht="15.75" customHeight="1"/>
+    <row r="301" ht="15.75" customHeight="1"/>
+    <row r="302" ht="15.75" customHeight="1"/>
+    <row r="303" ht="15.75" customHeight="1"/>
+    <row r="304" ht="15.75" customHeight="1"/>
+    <row r="305" ht="15.75" customHeight="1"/>
+    <row r="306" ht="15.75" customHeight="1"/>
+    <row r="307" ht="15.75" customHeight="1"/>
+    <row r="308" ht="15.75" customHeight="1"/>
+    <row r="309" ht="15.75" customHeight="1"/>
+    <row r="310" ht="15.75" customHeight="1"/>
+    <row r="311" ht="15.75" customHeight="1"/>
+    <row r="312" ht="15.75" customHeight="1"/>
+    <row r="313" ht="15.75" customHeight="1"/>
+    <row r="314" ht="15.75" customHeight="1"/>
+    <row r="315" ht="15.75" customHeight="1"/>
+    <row r="316" ht="15.75" customHeight="1"/>
+    <row r="317" ht="15.75" customHeight="1"/>
+    <row r="318" ht="15.75" customHeight="1"/>
+    <row r="319" ht="15.75" customHeight="1"/>
+    <row r="320" ht="15.75" customHeight="1"/>
+    <row r="321" ht="15.75" customHeight="1"/>
+    <row r="322" ht="15.75" customHeight="1"/>
+    <row r="323" ht="15.75" customHeight="1"/>
+    <row r="324" ht="15.75" customHeight="1"/>
+    <row r="325" ht="15.75" customHeight="1"/>
+    <row r="326" ht="15.75" customHeight="1"/>
+    <row r="327" ht="15.75" customHeight="1"/>
+    <row r="328" ht="15.75" customHeight="1"/>
+    <row r="329" ht="15.75" customHeight="1"/>
+    <row r="330" ht="15.75" customHeight="1"/>
+    <row r="331" ht="15.75" customHeight="1"/>
+    <row r="332" ht="15.75" customHeight="1"/>
+    <row r="333" ht="15.75" customHeight="1"/>
+    <row r="334" ht="15.75" customHeight="1"/>
+    <row r="335" ht="15.75" customHeight="1"/>
+    <row r="336" ht="15.75" customHeight="1"/>
+    <row r="337" ht="15.75" customHeight="1"/>
+    <row r="338" ht="15.75" customHeight="1"/>
+    <row r="339" ht="15.75" customHeight="1"/>
+    <row r="340" ht="15.75" customHeight="1"/>
+    <row r="341" ht="15.75" customHeight="1"/>
+    <row r="342" ht="15.75" customHeight="1"/>
+    <row r="343" ht="15.75" customHeight="1"/>
+    <row r="344" ht="15.75" customHeight="1"/>
+    <row r="345" ht="15.75" customHeight="1"/>
+    <row r="346" ht="15.75" customHeight="1"/>
+    <row r="347" ht="15.75" customHeight="1"/>
+    <row r="348" ht="15.75" customHeight="1"/>
+    <row r="349" ht="15.75" customHeight="1"/>
+    <row r="350" ht="15.75" customHeight="1"/>
+    <row r="351" ht="15.75" customHeight="1"/>
+    <row r="352" ht="15.75" customHeight="1"/>
+    <row r="353" ht="15.75" customHeight="1"/>
+    <row r="354" ht="15.75" customHeight="1"/>
+    <row r="355" ht="15.75" customHeight="1"/>
+    <row r="356" ht="15.75" customHeight="1"/>
+    <row r="357" ht="15.75" customHeight="1"/>
+    <row r="358" ht="15.75" customHeight="1"/>
+    <row r="359" ht="15.75" customHeight="1"/>
+    <row r="360" ht="15.75" customHeight="1"/>
+    <row r="361" ht="15.75" customHeight="1"/>
+    <row r="362" ht="15.75" customHeight="1"/>
+    <row r="363" ht="15.75" customHeight="1"/>
+    <row r="364" ht="15.75" customHeight="1"/>
+    <row r="365" ht="15.75" customHeight="1"/>
+    <row r="366" ht="15.75" customHeight="1"/>
+    <row r="367" ht="15.75" customHeight="1"/>
+    <row r="368" ht="15.75" customHeight="1"/>
+    <row r="369" ht="15.75" customHeight="1"/>
+    <row r="370" ht="15.75" customHeight="1"/>
+    <row r="371" ht="15.75" customHeight="1"/>
+    <row r="372" ht="15.75" customHeight="1"/>
+    <row r="373" ht="15.75" customHeight="1"/>
+    <row r="374" ht="15.75" customHeight="1"/>
+    <row r="375" ht="15.75" customHeight="1"/>
+    <row r="376" ht="15.75" customHeight="1"/>
+    <row r="377" ht="15.75" customHeight="1"/>
+    <row r="378" ht="15.75" customHeight="1"/>
+    <row r="379" ht="15.75" customHeight="1"/>
+    <row r="380" ht="15.75" customHeight="1"/>
+    <row r="381" ht="15.75" customHeight="1"/>
+    <row r="382" ht="15.75" customHeight="1"/>
+    <row r="383" ht="15.75" customHeight="1"/>
+    <row r="384" ht="15.75" customHeight="1"/>
+    <row r="385" ht="15.75" customHeight="1"/>
+    <row r="386" ht="15.75" customHeight="1"/>
+    <row r="387" ht="15.75" customHeight="1"/>
+    <row r="388" ht="15.75" customHeight="1"/>
+    <row r="389" ht="15.75" customHeight="1"/>
+    <row r="390" ht="15.75" customHeight="1"/>
+    <row r="391" ht="15.75" customHeight="1"/>
+    <row r="392" ht="15.75" customHeight="1"/>
+    <row r="393" ht="15.75" customHeight="1"/>
+    <row r="394" ht="15.75" customHeight="1"/>
+    <row r="395" ht="15.75" customHeight="1"/>
+    <row r="396" ht="15.75" customHeight="1"/>
+    <row r="397" ht="15.75" customHeight="1"/>
+    <row r="398" ht="15.75" customHeight="1"/>
+    <row r="399" ht="15.75" customHeight="1"/>
+    <row r="400" ht="15.75" customHeight="1"/>
+    <row r="401" ht="15.75" customHeight="1"/>
+    <row r="402" ht="15.75" customHeight="1"/>
+    <row r="403" ht="15.75" customHeight="1"/>
+    <row r="404" ht="15.75" customHeight="1"/>
+    <row r="405" ht="15.75" customHeight="1"/>
+    <row r="406" ht="15.75" customHeight="1"/>
+    <row r="407" ht="15.75" customHeight="1"/>
+    <row r="408" ht="15.75" customHeight="1"/>
+    <row r="409" ht="15.75" customHeight="1"/>
+    <row r="410" ht="15.75" customHeight="1"/>
+    <row r="411" ht="15.75" customHeight="1"/>
+    <row r="412" ht="15.75" customHeight="1"/>
+    <row r="413" ht="15.75" customHeight="1"/>
+    <row r="414" ht="15.75" customHeight="1"/>
+    <row r="415" ht="15.75" customHeight="1"/>
+    <row r="416" ht="15.75" customHeight="1"/>
+    <row r="417" ht="15.75" customHeight="1"/>
+    <row r="418" ht="15.75" customHeight="1"/>
+    <row r="419" ht="15.75" customHeight="1"/>
+    <row r="420" ht="15.75" customHeight="1"/>
+    <row r="421" ht="15.75" customHeight="1"/>
+    <row r="422" ht="15.75" customHeight="1"/>
+    <row r="423" ht="15.75" customHeight="1"/>
+    <row r="424" ht="15.75" customHeight="1"/>
+    <row r="425" ht="15.75" customHeight="1"/>
+    <row r="426" ht="15.75" customHeight="1"/>
+    <row r="427" ht="15.75" customHeight="1"/>
+    <row r="428" ht="15.75" customHeight="1"/>
+    <row r="429" ht="15.75" customHeight="1"/>
+    <row r="430" ht="15.75" customHeight="1"/>
+    <row r="431" ht="15.75" customHeight="1"/>
+    <row r="432" ht="15.75" customHeight="1"/>
+    <row r="433" ht="15.75" customHeight="1"/>
+    <row r="434" ht="15.75" customHeight="1"/>
+    <row r="435" ht="15.75" customHeight="1"/>
+    <row r="436" ht="15.75" customHeight="1"/>
+    <row r="437" ht="15.75" customHeight="1"/>
+    <row r="438" ht="15.75" customHeight="1"/>
+    <row r="439" ht="15.75" customHeight="1"/>
+    <row r="440" ht="15.75" customHeight="1"/>
+    <row r="441" ht="15.75" customHeight="1"/>
+    <row r="442" ht="15.75" customHeight="1"/>
+    <row r="443" ht="15.75" customHeight="1"/>
+    <row r="444" ht="15.75" customHeight="1"/>
+    <row r="445" ht="15.75" customHeight="1"/>
+    <row r="446" ht="15.75" customHeight="1"/>
+    <row r="447" ht="15.75" customHeight="1"/>
+    <row r="448" ht="15.75" customHeight="1"/>
+    <row r="449" ht="15.75" customHeight="1"/>
+    <row r="450" ht="15.75" customHeight="1"/>
+    <row r="451" ht="15.75" customHeight="1"/>
+    <row r="452" ht="15.75" customHeight="1"/>
+    <row r="453" ht="15.75" customHeight="1"/>
+    <row r="454" ht="15.75" customHeight="1"/>
+    <row r="455" ht="15.75" customHeight="1"/>
+    <row r="456" ht="15.75" customHeight="1"/>
+    <row r="457" ht="15.75" customHeight="1"/>
+    <row r="458" ht="15.75" customHeight="1"/>
+    <row r="459" ht="15.75" customHeight="1"/>
+    <row r="460" ht="15.75" customHeight="1"/>
+    <row r="461" ht="15.75" customHeight="1"/>
+    <row r="462" ht="15.75" customHeight="1"/>
+    <row r="463" ht="15.75" customHeight="1"/>
+    <row r="464" ht="15.75" customHeight="1"/>
+    <row r="465" ht="15.75" customHeight="1"/>
+    <row r="466" ht="15.75" customHeight="1"/>
+    <row r="467" ht="15.75" customHeight="1"/>
+    <row r="468" ht="15.75" customHeight="1"/>
+    <row r="469" ht="15.75" customHeight="1"/>
+    <row r="470" ht="15.75" customHeight="1"/>
+    <row r="471" ht="15.75" customHeight="1"/>
+    <row r="472" ht="15.75" customHeight="1"/>
+    <row r="473" ht="15.75" customHeight="1"/>
+    <row r="474" ht="15.75" customHeight="1"/>
+    <row r="475" ht="15.75" customHeight="1"/>
+    <row r="476" ht="15.75" customHeight="1"/>
+    <row r="477" ht="15.75" customHeight="1"/>
+    <row r="478" ht="15.75" customHeight="1"/>
+    <row r="479" ht="15.75" customHeight="1"/>
+    <row r="480" ht="15.75" customHeight="1"/>
+    <row r="481" ht="15.75" customHeight="1"/>
+    <row r="482" ht="15.75" customHeight="1"/>
+    <row r="483" ht="15.75" customHeight="1"/>
+    <row r="484" ht="15.75" customHeight="1"/>
+    <row r="485" ht="15.75" customHeight="1"/>
+    <row r="486" ht="15.75" customHeight="1"/>
+    <row r="487" ht="15.75" customHeight="1"/>
+    <row r="488" ht="15.75" customHeight="1"/>
+    <row r="489" ht="15.75" customHeight="1"/>
+    <row r="490" ht="15.75" customHeight="1"/>
+    <row r="491" ht="15.75" customHeight="1"/>
+    <row r="492" ht="15.75" customHeight="1"/>
+    <row r="493" ht="15.75" customHeight="1"/>
+    <row r="494" ht="15.75" customHeight="1"/>
+    <row r="495" ht="15.75" customHeight="1"/>
+    <row r="496" ht="15.75" customHeight="1"/>
+    <row r="497" ht="15.75" customHeight="1"/>
+    <row r="498" ht="15.75" customHeight="1"/>
+    <row r="499" ht="15.75" customHeight="1"/>
+    <row r="500" ht="15.75" customHeight="1"/>
+    <row r="501" ht="15.75" customHeight="1"/>
+    <row r="502" ht="15.75" customHeight="1"/>
+    <row r="503" ht="15.75" customHeight="1"/>
+    <row r="504" ht="15.75" customHeight="1"/>
+    <row r="505" ht="15.75" customHeight="1"/>
+    <row r="506" ht="15.75" customHeight="1"/>
+    <row r="507" ht="15.75" customHeight="1"/>
+    <row r="508" ht="15.75" customHeight="1"/>
+    <row r="509" ht="15.75" customHeight="1"/>
+    <row r="510" ht="15.75" customHeight="1"/>
+    <row r="511" ht="15.75" customHeight="1"/>
+    <row r="512" ht="15.75" customHeight="1"/>
+    <row r="513" ht="15.75" customHeight="1"/>
+    <row r="514" ht="15.75" customHeight="1"/>
+    <row r="515" ht="15.75" customHeight="1"/>
+    <row r="516" ht="15.75" customHeight="1"/>
+    <row r="517" ht="15.75" customHeight="1"/>
+    <row r="518" ht="15.75" customHeight="1"/>
+    <row r="519" ht="15.75" customHeight="1"/>
+    <row r="520" ht="15.75" customHeight="1"/>
+    <row r="521" ht="15.75" customHeight="1"/>
+    <row r="522" ht="15.75" customHeight="1"/>
+    <row r="523" ht="15.75" customHeight="1"/>
+    <row r="524" ht="15.75" customHeight="1"/>
+    <row r="525" ht="15.75" customHeight="1"/>
+    <row r="526" ht="15.75" customHeight="1"/>
+    <row r="527" ht="15.75" customHeight="1"/>
+    <row r="528" ht="15.75" customHeight="1"/>
+    <row r="529" ht="15.75" customHeight="1"/>
+    <row r="530" ht="15.75" customHeight="1"/>
+    <row r="531" ht="15.75" customHeight="1"/>
+    <row r="532" ht="15.75" customHeight="1"/>
+    <row r="533" ht="15.75" customHeight="1"/>
+    <row r="534" ht="15.75" customHeight="1"/>
+    <row r="535" ht="15.75" customHeight="1"/>
+    <row r="536" ht="15.75" customHeight="1"/>
+    <row r="537" ht="15.75" customHeight="1"/>
+    <row r="538" ht="15.75" customHeight="1"/>
+    <row r="539" ht="15.75" customHeight="1"/>
+    <row r="540" ht="15.75" customHeight="1"/>
+    <row r="541" ht="15.75" customHeight="1"/>
+    <row r="542" ht="15.75" customHeight="1"/>
+    <row r="543" ht="15.75" customHeight="1"/>
+    <row r="544" ht="15.75" customHeight="1"/>
+    <row r="545" ht="15.75" customHeight="1"/>
+    <row r="546" ht="15.75" customHeight="1"/>
+    <row r="547" ht="15.75" customHeight="1"/>
+    <row r="548" ht="15.75" customHeight="1"/>
+    <row r="549" ht="15.75" customHeight="1"/>
+    <row r="550" ht="15.75" customHeight="1"/>
+    <row r="551" ht="15.75" customHeight="1"/>
+    <row r="552" ht="15.75" customHeight="1"/>
+    <row r="553" ht="15.75" customHeight="1"/>
+    <row r="554" ht="15.75" customHeight="1"/>
+    <row r="555" ht="15.75" customHeight="1"/>
+    <row r="556" ht="15.75" customHeight="1"/>
+    <row r="557" ht="15.75" customHeight="1"/>
+    <row r="558" ht="15.75" customHeight="1"/>
+    <row r="559" ht="15.75" customHeight="1"/>
+    <row r="560" ht="15.75" customHeight="1"/>
+    <row r="561" ht="15.75" customHeight="1"/>
+    <row r="562" ht="15.75" customHeight="1"/>
+    <row r="563" ht="15.75" customHeight="1"/>
+    <row r="564" ht="15.75" customHeight="1"/>
+    <row r="565" ht="15.75" customHeight="1"/>
+    <row r="566" ht="15.75" customHeight="1"/>
+    <row r="567" ht="15.75" customHeight="1"/>
+    <row r="568" ht="15.75" customHeight="1"/>
+    <row r="569" ht="15.75" customHeight="1"/>
+    <row r="570" ht="15.75" customHeight="1"/>
+    <row r="571" ht="15.75" customHeight="1"/>
+    <row r="572" ht="15.75" customHeight="1"/>
+    <row r="573" ht="15.75" customHeight="1"/>
+    <row r="574" ht="15.75" customHeight="1"/>
+    <row r="575" ht="15.75" customHeight="1"/>
+    <row r="576" ht="15.75" customHeight="1"/>
+    <row r="577" ht="15.75" customHeight="1"/>
+    <row r="578" ht="15.75" customHeight="1"/>
+    <row r="579" ht="15.75" customHeight="1"/>
+    <row r="580" ht="15.75" customHeight="1"/>
+    <row r="581" ht="15.75" customHeight="1"/>
+    <row r="582" ht="15.75" customHeight="1"/>
+    <row r="583" ht="15.75" customHeight="1"/>
+    <row r="584" ht="15.75" customHeight="1"/>
+    <row r="585" ht="15.75" customHeight="1"/>
+    <row r="586" ht="15.75" customHeight="1"/>
+    <row r="587" ht="15.75" customHeight="1"/>
+    <row r="588" ht="15.75" customHeight="1"/>
+    <row r="589" ht="15.75" customHeight="1"/>
+    <row r="590" ht="15.75" customHeight="1"/>
+    <row r="591" ht="15.75" customHeight="1"/>
+    <row r="592" ht="15.75" customHeight="1"/>
+    <row r="593" ht="15.75" customHeight="1"/>
+    <row r="594" ht="15.75" customHeight="1"/>
+    <row r="595" ht="15.75" customHeight="1"/>
+    <row r="596" ht="15.75" customHeight="1"/>
+    <row r="597" ht="15.75" customHeight="1"/>
+    <row r="598" ht="15.75" customHeight="1"/>
+    <row r="599" ht="15.75" customHeight="1"/>
+    <row r="600" ht="15.75" customHeight="1"/>
+    <row r="601" ht="15.75" customHeight="1"/>
+    <row r="602" ht="15.75" customHeight="1"/>
+    <row r="603" ht="15.75" customHeight="1"/>
+    <row r="604" ht="15.75" customHeight="1"/>
+    <row r="605" ht="15.75" customHeight="1"/>
+    <row r="606" ht="15.75" customHeight="1"/>
+    <row r="607" ht="15.75" customHeight="1"/>
+    <row r="608" ht="15.75" customHeight="1"/>
+    <row r="609" ht="15.75" customHeight="1"/>
+    <row r="610" ht="15.75" customHeight="1"/>
+    <row r="611" ht="15.75" customHeight="1"/>
+    <row r="612" ht="15.75" customHeight="1"/>
+    <row r="613" ht="15.75" customHeight="1"/>
+    <row r="614" ht="15.75" customHeight="1"/>
+    <row r="615" ht="15.75" customHeight="1"/>
+    <row r="616" ht="15.75" customHeight="1"/>
+    <row r="617" ht="15.75" customHeight="1"/>
+    <row r="618" ht="15.75" customHeight="1"/>
+    <row r="619" ht="15.75" customHeight="1"/>
+    <row r="620" ht="15.75" customHeight="1"/>
+    <row r="621" ht="15.75" customHeight="1"/>
+    <row r="622" ht="15.75" customHeight="1"/>
+    <row r="623" ht="15.75" customHeight="1"/>
+    <row r="624" ht="15.75" customHeight="1"/>
+    <row r="625" ht="15.75" customHeight="1"/>
+    <row r="626" ht="15.75" customHeight="1"/>
+    <row r="627" ht="15.75" customHeight="1"/>
+    <row r="628" ht="15.75" customHeight="1"/>
+    <row r="629" ht="15.75" customHeight="1"/>
+    <row r="630" ht="15.75" customHeight="1"/>
+    <row r="631" ht="15.75" customHeight="1"/>
+    <row r="632" ht="15.75" customHeight="1"/>
+    <row r="633" ht="15.75" customHeight="1"/>
+    <row r="634" ht="15.75" customHeight="1"/>
+    <row r="635" ht="15.75" customHeight="1"/>
+    <row r="636" ht="15.75" customHeight="1"/>
+    <row r="637" ht="15.75" customHeight="1"/>
+    <row r="638" ht="15.75" customHeight="1"/>
+    <row r="639" ht="15.75" customHeight="1"/>
+    <row r="640" ht="15.75" customHeight="1"/>
+    <row r="641" ht="15.75" customHeight="1"/>
+    <row r="642" ht="15.75" customHeight="1"/>
+    <row r="643" ht="15.75" customHeight="1"/>
+    <row r="644" ht="15.75" customHeight="1"/>
+    <row r="645" ht="15.75" customHeight="1"/>
+    <row r="646" ht="15.75" customHeight="1"/>
+    <row r="647" ht="15.75" customHeight="1"/>
+    <row r="648" ht="15.75" customHeight="1"/>
+    <row r="649" ht="15.75" customHeight="1"/>
+    <row r="650" ht="15.75" customHeight="1"/>
+    <row r="651" ht="15.75" customHeight="1"/>
+    <row r="652" ht="15.75" customHeight="1"/>
+    <row r="653" ht="15.75" customHeight="1"/>
+    <row r="654" ht="15.75" customHeight="1"/>
+    <row r="655" ht="15.75" customHeight="1"/>
+    <row r="656" ht="15.75" customHeight="1"/>
+    <row r="657" ht="15.75" customHeight="1"/>
+    <row r="658" ht="15.75" customHeight="1"/>
+    <row r="659" ht="15.75" customHeight="1"/>
+    <row r="660" ht="15.75" customHeight="1"/>
+    <row r="661" ht="15.75" customHeight="1"/>
+    <row r="662" ht="15.75" customHeight="1"/>
+    <row r="663" ht="15.75" customHeight="1"/>
+    <row r="664" ht="15.75" customHeight="1"/>
+    <row r="665" ht="15.75" customHeight="1"/>
+    <row r="666" ht="15.75" customHeight="1"/>
+    <row r="667" ht="15.75" customHeight="1"/>
+    <row r="668" ht="15.75" customHeight="1"/>
+    <row r="669" ht="15.75" customHeight="1"/>
+    <row r="670" ht="15.75" customHeight="1"/>
+    <row r="671" ht="15.75" customHeight="1"/>
+    <row r="672" ht="15.75" customHeight="1"/>
+    <row r="673" ht="15.75" customHeight="1"/>
+    <row r="674" ht="15.75" customHeight="1"/>
+    <row r="675" ht="15.75" customHeight="1"/>
+    <row r="676" ht="15.75" customHeight="1"/>
+    <row r="677" ht="15.75" customHeight="1"/>
+    <row r="678" ht="15.75" customHeight="1"/>
+    <row r="679" ht="15.75" customHeight="1"/>
+    <row r="680" ht="15.75" customHeight="1"/>
+    <row r="681" ht="15.75" customHeight="1"/>
+    <row r="682" ht="15.75" customHeight="1"/>
+    <row r="683" ht="15.75" customHeight="1"/>
+    <row r="684" ht="15.75" customHeight="1"/>
+    <row r="685" ht="15.75" customHeight="1"/>
+    <row r="686" ht="15.75" customHeight="1"/>
+    <row r="687" ht="15.75" customHeight="1"/>
+    <row r="688" ht="15.75" customHeight="1"/>
+    <row r="689" ht="15.75" customHeight="1"/>
+    <row r="690" ht="15.75" customHeight="1"/>
+    <row r="691" ht="15.75" customHeight="1"/>
+    <row r="692" ht="15.75" customHeight="1"/>
+    <row r="693" ht="15.75" customHeight="1"/>
+    <row r="694" ht="15.75" customHeight="1"/>
+    <row r="695" ht="15.75" customHeight="1"/>
+    <row r="696" ht="15.75" customHeight="1"/>
+    <row r="697" ht="15.75" customHeight="1"/>
+    <row r="698" ht="15.75" customHeight="1"/>
+    <row r="699" ht="15.75" customHeight="1"/>
+    <row r="700" ht="15.75" customHeight="1"/>
+    <row r="701" ht="15.75" customHeight="1"/>
+    <row r="702" ht="15.75" customHeight="1"/>
+    <row r="703" ht="15.75" customHeight="1"/>
+    <row r="704" ht="15.75" customHeight="1"/>
+    <row r="705" ht="15.75" customHeight="1"/>
+    <row r="706" ht="15.75" customHeight="1"/>
+    <row r="707" ht="15.75" customHeight="1"/>
+    <row r="708" ht="15.75" customHeight="1"/>
+    <row r="709" ht="15.75" customHeight="1"/>
+    <row r="710" ht="15.75" customHeight="1"/>
+    <row r="711" ht="15.75" customHeight="1"/>
+    <row r="712" ht="15.75" customHeight="1"/>
+    <row r="713" ht="15.75" customHeight="1"/>
+    <row r="714" ht="15.75" customHeight="1"/>
+    <row r="715" ht="15.75" customHeight="1"/>
+    <row r="716" ht="15.75" customHeight="1"/>
+    <row r="717" ht="15.75" customHeight="1"/>
+    <row r="718" ht="15.75" customHeight="1"/>
+    <row r="719" ht="15.75" customHeight="1"/>
+    <row r="720" ht="15.75" customHeight="1"/>
+    <row r="721" ht="15.75" customHeight="1"/>
+    <row r="722" ht="15.75" customHeight="1"/>
+    <row r="723" ht="15.75" customHeight="1"/>
+    <row r="724" ht="15.75" customHeight="1"/>
+    <row r="725" ht="15.75" customHeight="1"/>
+    <row r="726" ht="15.75" customHeight="1"/>
+    <row r="727" ht="15.75" customHeight="1"/>
+    <row r="728" ht="15.75" customHeight="1"/>
+    <row r="729" ht="15.75" customHeight="1"/>
+    <row r="730" ht="15.75" customHeight="1"/>
+    <row r="731" ht="15.75" customHeight="1"/>
+    <row r="732" ht="15.75" customHeight="1"/>
+    <row r="733" ht="15.75" customHeight="1"/>
+    <row r="734" ht="15.75" customHeight="1"/>
+    <row r="735" ht="15.75" customHeight="1"/>
+    <row r="736" ht="15.75" customHeight="1"/>
+    <row r="737" ht="15.75" customHeight="1"/>
+    <row r="738" ht="15.75" customHeight="1"/>
+    <row r="739" ht="15.75" customHeight="1"/>
+    <row r="740" ht="15.75" customHeight="1"/>
+    <row r="741" ht="15.75" customHeight="1"/>
+    <row r="742" ht="15.75" customHeight="1"/>
+    <row r="743" ht="15.75" customHeight="1"/>
+    <row r="744" ht="15.75" customHeight="1"/>
+    <row r="745" ht="15.75" customHeight="1"/>
+    <row r="746" ht="15.75" customHeight="1"/>
+    <row r="747" ht="15.75" customHeight="1"/>
+    <row r="748" ht="15.75" customHeight="1"/>
+    <row r="749" ht="15.75" customHeight="1"/>
+    <row r="750" ht="15.75" customHeight="1"/>
+    <row r="751" ht="15.75" customHeight="1"/>
+    <row r="752" ht="15.75" customHeight="1"/>
+    <row r="753" ht="15.75" customHeight="1"/>
+    <row r="754" ht="15.75" customHeight="1"/>
+    <row r="755" ht="15.75" customHeight="1"/>
+    <row r="756" ht="15.75" customHeight="1"/>
+    <row r="757" ht="15.75" customHeight="1"/>
+    <row r="758" ht="15.75" customHeight="1"/>
+    <row r="759" ht="15.75" customHeight="1"/>
+    <row r="760" ht="15.75" customHeight="1"/>
+    <row r="761" ht="15.75" customHeight="1"/>
+    <row r="762" ht="15.75" customHeight="1"/>
+    <row r="763" ht="15.75" customHeight="1"/>
+    <row r="764" ht="15.75" customHeight="1"/>
+    <row r="765" ht="15.75" customHeight="1"/>
+    <row r="766" ht="15.75" customHeight="1"/>
+    <row r="767" ht="15.75" customHeight="1"/>
+    <row r="768" ht="15.75" customHeight="1"/>
+    <row r="769" ht="15.75" customHeight="1"/>
+    <row r="770" ht="15.75" customHeight="1"/>
+    <row r="771" ht="15.75" customHeight="1"/>
+    <row r="772" ht="15.75" customHeight="1"/>
+    <row r="773" ht="15.75" customHeight="1"/>
+    <row r="774" ht="15.75" customHeight="1"/>
+    <row r="775" ht="15.75" customHeight="1"/>
+    <row r="776" ht="15.75" customHeight="1"/>
+    <row r="777" ht="15.75" customHeight="1"/>
+    <row r="778" ht="15.75" customHeight="1"/>
+    <row r="779" ht="15.75" customHeight="1"/>
+    <row r="780" ht="15.75" customHeight="1"/>
+    <row r="781" ht="15.75" customHeight="1"/>
+    <row r="782" ht="15.75" customHeight="1"/>
+    <row r="783" ht="15.75" customHeight="1"/>
+    <row r="784" ht="15.75" customHeight="1"/>
+    <row r="785" ht="15.75" customHeight="1"/>
+    <row r="786" ht="15.75" customHeight="1"/>
+    <row r="787" ht="15.75" customHeight="1"/>
+    <row r="788" ht="15.75" customHeight="1"/>
+    <row r="789" ht="15.75" customHeight="1"/>
+    <row r="790" ht="15.75" customHeight="1"/>
+    <row r="791" ht="15.75" customHeight="1"/>
+    <row r="792" ht="15.75" customHeight="1"/>
+    <row r="793" ht="15.75" customHeight="1"/>
+    <row r="794" ht="15.75" customHeight="1"/>
+    <row r="795" ht="15.75" customHeight="1"/>
+    <row r="796" ht="15.75" customHeight="1"/>
+    <row r="797" ht="15.75" customHeight="1"/>
+    <row r="798" ht="15.75" customHeight="1"/>
+    <row r="799" ht="15.75" customHeight="1"/>
+    <row r="800" ht="15.75" customHeight="1"/>
+    <row r="801" ht="15.75" customHeight="1"/>
+    <row r="802" ht="15.75" customHeight="1"/>
+    <row r="803" ht="15.75" customHeight="1"/>
+    <row r="804" ht="15.75" customHeight="1"/>
+    <row r="805" ht="15.75" customHeight="1"/>
+    <row r="806" ht="15.75" customHeight="1"/>
+    <row r="807" ht="15.75" customHeight="1"/>
+    <row r="808" ht="15.75" customHeight="1"/>
+    <row r="809" ht="15.75" customHeight="1"/>
+    <row r="810" ht="15.75" customHeight="1"/>
+    <row r="811" ht="15.75" customHeight="1"/>
+    <row r="812" ht="15.75" customHeight="1"/>
+    <row r="813" ht="15.75" customHeight="1"/>
+    <row r="814" ht="15.75" customHeight="1"/>
+    <row r="815" ht="15.75" customHeight="1"/>
+    <row r="816" ht="15.75" customHeight="1"/>
+    <row r="817" ht="15.75" customHeight="1"/>
+    <row r="818" ht="15.75" customHeight="1"/>
+    <row r="819" ht="15.75" customHeight="1"/>
+    <row r="820" ht="15.75" customHeight="1"/>
+    <row r="821" ht="15.75" customHeight="1"/>
+    <row r="822" ht="15.75" customHeight="1"/>
+    <row r="823" ht="15.75" customHeight="1"/>
+    <row r="824" ht="15.75" customHeight="1"/>
+    <row r="825" ht="15.75" customHeight="1"/>
+    <row r="826" ht="15.75" customHeight="1"/>
+    <row r="827" ht="15.75" customHeight="1"/>
+    <row r="828" ht="15.75" customHeight="1"/>
+    <row r="829" ht="15.75" customHeight="1"/>
+    <row r="830" ht="15.75" customHeight="1"/>
+    <row r="831" ht="15.75" customHeight="1"/>
+    <row r="832" ht="15.75" customHeight="1"/>
+    <row r="833" ht="15.75" customHeight="1"/>
+    <row r="834" ht="15.75" customHeight="1"/>
+    <row r="835" ht="15.75" customHeight="1"/>
+    <row r="836" ht="15.75" customHeight="1"/>
+    <row r="837" ht="15.75" customHeight="1"/>
+    <row r="838" ht="15.75" customHeight="1"/>
+    <row r="839" ht="15.75" customHeight="1"/>
+    <row r="840" ht="15.75" customHeight="1"/>
+    <row r="841" ht="15.75" customHeight="1"/>
+    <row r="842" ht="15.75" customHeight="1"/>
+    <row r="843" ht="15.75" customHeight="1"/>
+    <row r="844" ht="15.75" customHeight="1"/>
+    <row r="845" ht="15.75" customHeight="1"/>
+    <row r="846" ht="15.75" customHeight="1"/>
+    <row r="847" ht="15.75" customHeight="1"/>
+    <row r="848" ht="15.75" customHeight="1"/>
+    <row r="849" ht="15.75" customHeight="1"/>
+    <row r="850" ht="15.75" customHeight="1"/>
+    <row r="851" ht="15.75" customHeight="1"/>
+    <row r="852" ht="15.75" customHeight="1"/>
+    <row r="853" ht="15.75" customHeight="1"/>
+    <row r="854" ht="15.75" customHeight="1"/>
+    <row r="855" ht="15.75" customHeight="1"/>
+    <row r="856" ht="15.75" customHeight="1"/>
+    <row r="857" ht="15.75" customHeight="1"/>
+    <row r="858" ht="15.75" customHeight="1"/>
+    <row r="859" ht="15.75" customHeight="1"/>
+    <row r="860" ht="15.75" customHeight="1"/>
+    <row r="861" ht="15.75" customHeight="1"/>
+    <row r="862" ht="15.75" customHeight="1"/>
+    <row r="863" ht="15.75" customHeight="1"/>
+    <row r="864" ht="15.75" customHeight="1"/>
+    <row r="865" ht="15.75" customHeight="1"/>
+    <row r="866" ht="15.75" customHeight="1"/>
+    <row r="867" ht="15.75" customHeight="1"/>
+    <row r="868" ht="15.75" customHeight="1"/>
+    <row r="869" ht="15.75" customHeight="1"/>
+    <row r="870" ht="15.75" customHeight="1"/>
+    <row r="871" ht="15.75" customHeight="1"/>
+    <row r="872" ht="15.75" customHeight="1"/>
+    <row r="873" ht="15.75" customHeight="1"/>
+    <row r="874" ht="15.75" customHeight="1"/>
+    <row r="875" ht="15.75" customHeight="1"/>
+    <row r="876" ht="15.75" customHeight="1"/>
+    <row r="877" ht="15.75" customHeight="1"/>
+    <row r="878" ht="15.75" customHeight="1"/>
+    <row r="879" ht="15.75" customHeight="1"/>
+    <row r="880" ht="15.75" customHeight="1"/>
+    <row r="881" ht="15.75" customHeight="1"/>
+    <row r="882" ht="15.75" customHeight="1"/>
+    <row r="883" ht="15.75" customHeight="1"/>
+    <row r="884" ht="15.75" customHeight="1"/>
+    <row r="885" ht="15.75" customHeight="1"/>
+    <row r="886" ht="15.75" customHeight="1"/>
+    <row r="887" ht="15.75" customHeight="1"/>
+    <row r="888" ht="15.75" customHeight="1"/>
+    <row r="889" ht="15.75" customHeight="1"/>
+    <row r="890" ht="15.75" customHeight="1"/>
+    <row r="891" ht="15.75" customHeight="1"/>
+    <row r="892" ht="15.75" customHeight="1"/>
+    <row r="893" ht="15.75" customHeight="1"/>
+    <row r="894" ht="15.75" customHeight="1"/>
+    <row r="895" ht="15.75" customHeight="1"/>
+    <row r="896" ht="15.75" customHeight="1"/>
+    <row r="897" ht="15.75" customHeight="1"/>
+    <row r="898" ht="15.75" customHeight="1"/>
+    <row r="899" ht="15.75" customHeight="1"/>
+    <row r="900" ht="15.75" customHeight="1"/>
+    <row r="901" ht="15.75" customHeight="1"/>
+    <row r="902" ht="15.75" customHeight="1"/>
+    <row r="903" ht="15.75" customHeight="1"/>
+    <row r="904" ht="15.75" customHeight="1"/>
+    <row r="905" ht="15.75" customHeight="1"/>
+    <row r="906" ht="15.75" customHeight="1"/>
+    <row r="907" ht="15.75" customHeight="1"/>
+    <row r="908" ht="15.75" customHeight="1"/>
+    <row r="909" ht="15.75" customHeight="1"/>
+    <row r="910" ht="15.75" customHeight="1"/>
+    <row r="911" ht="15.75" customHeight="1"/>
+    <row r="912" ht="15.75" customHeight="1"/>
+    <row r="913" ht="15.75" customHeight="1"/>
+    <row r="914" ht="15.75" customHeight="1"/>
+    <row r="915" ht="15.75" customHeight="1"/>
+    <row r="916" ht="15.75" customHeight="1"/>
+    <row r="917" ht="15.75" customHeight="1"/>
+    <row r="918" ht="15.75" customHeight="1"/>
+    <row r="919" ht="15.75" customHeight="1"/>
+    <row r="920" ht="15.75" customHeight="1"/>
+    <row r="921" ht="15.75" customHeight="1"/>
+    <row r="922" ht="15.75" customHeight="1"/>
+    <row r="923" ht="15.75" customHeight="1"/>
+    <row r="924" ht="15.75" customHeight="1"/>
+    <row r="925" ht="15.75" customHeight="1"/>
+    <row r="926" ht="15.75" customHeight="1"/>
+    <row r="927" ht="15.75" customHeight="1"/>
+    <row r="928" ht="15.75" customHeight="1"/>
+    <row r="929" ht="15.75" customHeight="1"/>
+    <row r="930" ht="15.75" customHeight="1"/>
+    <row r="931" ht="15.75" customHeight="1"/>
+    <row r="932" ht="15.75" customHeight="1"/>
+    <row r="933" ht="15.75" customHeight="1"/>
+    <row r="934" ht="15.75" customHeight="1"/>
+    <row r="935" ht="15.75" customHeight="1"/>
+    <row r="936" ht="15.75" customHeight="1"/>
+    <row r="937" ht="15.75" customHeight="1"/>
+    <row r="938" ht="15.75" customHeight="1"/>
+    <row r="939" ht="15.75" customHeight="1"/>
+    <row r="940" ht="15.75" customHeight="1"/>
+    <row r="941" ht="15.75" customHeight="1"/>
+    <row r="942" ht="15.75" customHeight="1"/>
+    <row r="943" ht="15.75" customHeight="1"/>
+    <row r="944" ht="15.75" customHeight="1"/>
+    <row r="945" ht="15.75" customHeight="1"/>
+    <row r="946" ht="15.75" customHeight="1"/>
+    <row r="947" ht="15.75" customHeight="1"/>
+    <row r="948" ht="15.75" customHeight="1"/>
+    <row r="949" ht="15.75" customHeight="1"/>
+    <row r="950" ht="15.75" customHeight="1"/>
+    <row r="951" ht="15.75" customHeight="1"/>
+    <row r="952" ht="15.75" customHeight="1"/>
+    <row r="953" ht="15.75" customHeight="1"/>
+    <row r="954" ht="15.75" customHeight="1"/>
+    <row r="955" ht="15.75" customHeight="1"/>
+    <row r="956" ht="15.75" customHeight="1"/>
+    <row r="957" ht="15.75" customHeight="1"/>
+    <row r="958" ht="15.75" customHeight="1"/>
+    <row r="959" ht="15.75" customHeight="1"/>
+    <row r="960" ht="15.75" customHeight="1"/>
+    <row r="961" ht="15.75" customHeight="1"/>
+    <row r="962" ht="15.75" customHeight="1"/>
+    <row r="963" ht="15.75" customHeight="1"/>
+    <row r="964" ht="15.75" customHeight="1"/>
+    <row r="965" ht="15.75" customHeight="1"/>
+    <row r="966" ht="15.75" customHeight="1"/>
+    <row r="967" ht="15.75" customHeight="1"/>
+    <row r="968" ht="15.75" customHeight="1"/>
+    <row r="969" ht="15.75" customHeight="1"/>
+    <row r="970" ht="15.75" customHeight="1"/>
+    <row r="971" ht="15.75" customHeight="1"/>
+    <row r="972" ht="15.75" customHeight="1"/>
+    <row r="973" ht="15.75" customHeight="1"/>
+    <row r="974" ht="15.75" customHeight="1"/>
+    <row r="975" ht="15.75" customHeight="1"/>
+    <row r="976" ht="15.75" customHeight="1"/>
+    <row r="977" ht="15.75" customHeight="1"/>
+    <row r="978" ht="15.75" customHeight="1"/>
+    <row r="979" ht="15.75" customHeight="1"/>
+    <row r="980" ht="15.75" customHeight="1"/>
+    <row r="981" ht="15.75" customHeight="1"/>
+    <row r="982" ht="15.75" customHeight="1"/>
+    <row r="983" ht="15.75" customHeight="1"/>
+    <row r="984" ht="15.75" customHeight="1"/>
+    <row r="985" ht="15.75" customHeight="1"/>
+    <row r="986" ht="15.75" customHeight="1"/>
+    <row r="987" ht="15.75" customHeight="1"/>
+    <row r="988" ht="15.75" customHeight="1"/>
+    <row r="989" ht="15.75" customHeight="1"/>
+    <row r="990" ht="15.75" customHeight="1"/>
+    <row r="991" ht="15.75" customHeight="1"/>
+    <row r="992" ht="15.75" customHeight="1"/>
+    <row r="993" ht="15.75" customHeight="1"/>
+    <row r="994" ht="15.75" customHeight="1"/>
+    <row r="995" ht="15.75" customHeight="1"/>
+    <row r="996" ht="15.75" customHeight="1"/>
+    <row r="997" ht="15.75" customHeight="1"/>
+    <row r="998" ht="15.75" customHeight="1"/>
+    <row r="999" ht="15.75" customHeight="1"/>
+    <row r="1000" ht="15.75" customHeight="1"/>
+    <row r="1001" ht="15.75" customHeight="1"/>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A3:J3"/>
+    <mergeCell ref="A7:J7"/>
+    <mergeCell ref="A17:J17"/>
+    <mergeCell ref="A20:J20"/>
+  </mergeCells>
+  <conditionalFormatting sqref="H4:H6 H8:H16 H18:H19 H21:H22">
+    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="✅ PASS">
+      <formula>NOT(ISERROR(SEARCH(("✅ PASS"),(H4))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H4:H6 H8:H16 H18:H19 H21:H22">
+    <cfRule type="containsText" dxfId="4" priority="2" operator="containsText" text="❌ FAIL">
+      <formula>NOT(ISERROR(SEARCH(("❌ FAIL"),(H4))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H4:H6 H8:H16 H18:H19 H21:H22">
+    <cfRule type="containsText" dxfId="2" priority="3" operator="containsText" text="⏳ PENDING">
+      <formula>NOT(ISERROR(SEARCH(("⏳ PENDING"),(H4))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="H4:H6 H8:H16 H18:H19 H21:H22">
+      <formula1>"⏳ PENDIENTE,✅ PASS,❌ FAIL"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <printOptions/>
+  <pageMargins bottom="1.0" footer="0.0" header="0.0" left="0.75" right="0.75" top="1.0"/>
+  <pageSetup orientation="landscape"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <pageSetUpPr/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="6.0"/>
+    <col customWidth="1" min="2" max="2" width="38.0"/>
+    <col customWidth="1" min="3" max="3" width="9.0"/>
+    <col customWidth="1" min="4" max="4" width="42.0"/>
+    <col customWidth="1" min="5" max="5" width="18.0"/>
+    <col customWidth="1" min="6" max="6" width="55.0"/>
+    <col customWidth="1" min="7" max="7" width="45.0"/>
+    <col customWidth="1" min="8" max="8" width="16.0"/>
+    <col customWidth="1" min="9" max="9" width="40.0"/>
+    <col customWidth="1" min="10" max="10" width="14.0"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24.0" customHeight="1">
+      <c r="A1" s="27" t="s">
+        <v>344</v>
+      </c>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+      <c r="H1" s="28"/>
+      <c r="I1" s="28"/>
+      <c r="J1" s="28"/>
+    </row>
+    <row r="2" ht="21.75" customHeight="1">
+      <c r="A2" s="22" t="s">
+        <v>85</v>
+      </c>
+      <c r="B2" s="22" t="s">
+        <v>86</v>
+      </c>
+      <c r="C2" s="22" t="s">
+        <v>87</v>
+      </c>
+      <c r="D2" s="22" t="s">
+        <v>88</v>
+      </c>
+      <c r="E2" s="22" t="s">
+        <v>89</v>
+      </c>
+      <c r="F2" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="G2" s="22" t="s">
+        <v>90</v>
+      </c>
+      <c r="H2" s="22" t="s">
+        <v>91</v>
+      </c>
+      <c r="I2" s="22" t="s">
+        <v>92</v>
+      </c>
+      <c r="J2" s="22" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="3" ht="18.0" customHeight="1">
+      <c r="A3" s="29" t="s">
+        <v>264</v>
+      </c>
+      <c r="B3" s="30"/>
+      <c r="C3" s="30"/>
+      <c r="D3" s="30"/>
+      <c r="E3" s="30"/>
+      <c r="F3" s="30"/>
+      <c r="G3" s="30"/>
+      <c r="H3" s="30"/>
+      <c r="I3" s="30"/>
+      <c r="J3" s="31"/>
+    </row>
+    <row r="4" ht="42.0" customHeight="1">
+      <c r="A4" s="23" t="s">
+        <v>345</v>
+      </c>
+      <c r="B4" s="21" t="s">
+        <v>346</v>
+      </c>
+      <c r="C4" s="32" t="s">
+        <v>97</v>
+      </c>
+      <c r="D4" s="21" t="s">
+        <v>347</v>
+      </c>
+      <c r="E4" s="21" t="s">
+        <v>198</v>
+      </c>
+      <c r="F4" s="21" t="s">
+        <v>348</v>
+      </c>
+      <c r="G4" s="21" t="s">
+        <v>349</v>
+      </c>
+      <c r="H4" s="33" t="s">
+        <v>70</v>
+      </c>
+      <c r="I4" s="21" t="s">
+        <v>350</v>
+      </c>
+      <c r="J4" s="23"/>
+    </row>
+    <row r="5" ht="42.0" customHeight="1">
+      <c r="A5" s="34" t="s">
+        <v>351</v>
+      </c>
+      <c r="B5" s="20" t="s">
+        <v>352</v>
+      </c>
+      <c r="C5" s="35" t="s">
+        <v>97</v>
+      </c>
+      <c r="D5" s="20" t="s">
+        <v>347</v>
+      </c>
+      <c r="E5" s="20" t="s">
+        <v>198</v>
+      </c>
+      <c r="F5" s="20" t="s">
+        <v>353</v>
+      </c>
+      <c r="G5" s="20" t="s">
+        <v>354</v>
+      </c>
+      <c r="H5" s="33" t="s">
+        <v>70</v>
+      </c>
+      <c r="I5" s="20" t="s">
+        <v>355</v>
+      </c>
+      <c r="J5" s="34"/>
+    </row>
+    <row r="6" ht="18.0" customHeight="1">
+      <c r="A6" s="29" t="s">
+        <v>280</v>
+      </c>
+      <c r="B6" s="30"/>
+      <c r="C6" s="30"/>
+      <c r="D6" s="30"/>
+      <c r="E6" s="30"/>
+      <c r="F6" s="30"/>
+      <c r="G6" s="30"/>
+      <c r="H6" s="30"/>
+      <c r="I6" s="30"/>
+      <c r="J6" s="31"/>
+    </row>
+    <row r="7" ht="42.0" customHeight="1">
+      <c r="A7" s="34" t="s">
+        <v>356</v>
+      </c>
+      <c r="B7" s="20" t="s">
+        <v>357</v>
+      </c>
+      <c r="C7" s="36" t="s">
+        <v>139</v>
+      </c>
+      <c r="D7" s="20" t="s">
+        <v>358</v>
+      </c>
+      <c r="E7" s="20" t="s">
+        <v>198</v>
+      </c>
+      <c r="F7" s="20" t="s">
+        <v>141</v>
+      </c>
+      <c r="G7" s="20" t="s">
+        <v>359</v>
+      </c>
+      <c r="H7" s="33" t="s">
+        <v>70</v>
+      </c>
+      <c r="I7" s="20" t="s">
+        <v>360</v>
+      </c>
+      <c r="J7" s="34"/>
+    </row>
+    <row r="8" ht="42.0" customHeight="1">
+      <c r="A8" s="23" t="s">
+        <v>361</v>
+      </c>
+      <c r="B8" s="21" t="s">
+        <v>362</v>
+      </c>
+      <c r="C8" s="43" t="s">
+        <v>139</v>
+      </c>
+      <c r="D8" s="21" t="s">
+        <v>363</v>
+      </c>
+      <c r="E8" s="21" t="s">
+        <v>198</v>
+      </c>
+      <c r="F8" s="21" t="str">
+        <f>Variables!C10</f>
+        <v>4a2c7d53-9a34-4c40-9e8f-c8972db67211</v>
+      </c>
+      <c r="G8" s="21" t="s">
+        <v>364</v>
+      </c>
+      <c r="H8" s="33" t="s">
+        <v>70</v>
+      </c>
+      <c r="I8" s="21" t="s">
+        <v>365</v>
+      </c>
+      <c r="J8" s="23"/>
+    </row>
+    <row r="9" ht="42.0" customHeight="1">
+      <c r="A9" s="34" t="s">
+        <v>366</v>
+      </c>
+      <c r="B9" s="20" t="s">
+        <v>367</v>
+      </c>
+      <c r="C9" s="36" t="s">
+        <v>139</v>
+      </c>
+      <c r="D9" s="20" t="s">
+        <v>368</v>
+      </c>
+      <c r="E9" s="20" t="s">
+        <v>198</v>
+      </c>
+      <c r="F9" s="20" t="s">
+        <v>141</v>
+      </c>
+      <c r="G9" s="20" t="s">
+        <v>369</v>
+      </c>
+      <c r="H9" s="33" t="s">
+        <v>70</v>
+      </c>
+      <c r="I9" s="20" t="s">
+        <v>370</v>
+      </c>
+      <c r="J9" s="34"/>
+    </row>
+    <row r="10" ht="42.0" customHeight="1">
+      <c r="A10" s="41" t="s">
+        <v>371</v>
+      </c>
+      <c r="B10" s="42" t="s">
+        <v>372</v>
+      </c>
+      <c r="C10" s="43" t="s">
+        <v>139</v>
+      </c>
+      <c r="D10" s="42" t="s">
+        <v>373</v>
+      </c>
+      <c r="E10" s="21" t="s">
+        <v>198</v>
+      </c>
+      <c r="F10" s="42" t="s">
+        <v>374</v>
+      </c>
+      <c r="G10" s="42" t="s">
+        <v>148</v>
+      </c>
+      <c r="H10" s="33" t="s">
+        <v>70</v>
+      </c>
+      <c r="I10" s="42" t="s">
+        <v>322</v>
+      </c>
+      <c r="J10" s="23"/>
+    </row>
+    <row r="11" ht="18.0" customHeight="1">
+      <c r="A11" s="29" t="s">
+        <v>375</v>
+      </c>
+      <c r="B11" s="30"/>
+      <c r="C11" s="30"/>
+      <c r="D11" s="30"/>
+      <c r="E11" s="30"/>
+      <c r="F11" s="30"/>
+      <c r="G11" s="30"/>
+      <c r="H11" s="30"/>
+      <c r="I11" s="30"/>
+      <c r="J11" s="31"/>
+    </row>
+    <row r="12" ht="42.0" customHeight="1">
+      <c r="A12" s="38" t="s">
+        <v>376</v>
+      </c>
+      <c r="B12" s="20" t="s">
+        <v>377</v>
+      </c>
+      <c r="C12" s="35" t="s">
+        <v>97</v>
+      </c>
+      <c r="D12" s="20" t="s">
+        <v>378</v>
+      </c>
+      <c r="E12" s="20" t="s">
+        <v>198</v>
+      </c>
+      <c r="F12" s="20" t="str">
+        <f>Variables!C11</f>
+        <v>8396e74a-7bc5-4793-b7c4-bd79b3b7932b</v>
+      </c>
+      <c r="G12" s="20" t="s">
+        <v>379</v>
+      </c>
+      <c r="H12" s="33" t="s">
+        <v>70</v>
+      </c>
+      <c r="I12" s="20" t="s">
+        <v>380</v>
+      </c>
+      <c r="J12" s="34"/>
+    </row>
+    <row r="13" ht="42.0" customHeight="1">
+      <c r="A13" s="41" t="s">
+        <v>381</v>
+      </c>
+      <c r="B13" s="21" t="s">
+        <v>382</v>
+      </c>
+      <c r="C13" s="32" t="s">
+        <v>97</v>
+      </c>
+      <c r="D13" s="21" t="s">
+        <v>383</v>
+      </c>
+      <c r="E13" s="21" t="s">
+        <v>198</v>
+      </c>
+      <c r="F13" s="21" t="str">
+        <f>Variables!C11</f>
+        <v>8396e74a-7bc5-4793-b7c4-bd79b3b7932b</v>
+      </c>
+      <c r="G13" s="21" t="s">
+        <v>384</v>
+      </c>
+      <c r="H13" s="33" t="s">
+        <v>70</v>
+      </c>
+      <c r="I13" s="21" t="s">
+        <v>385</v>
+      </c>
+      <c r="J13" s="23"/>
+    </row>
+    <row r="14" ht="42.0" customHeight="1">
+      <c r="A14" s="38" t="s">
+        <v>386</v>
+      </c>
+      <c r="B14" s="20" t="s">
+        <v>387</v>
+      </c>
+      <c r="C14" s="35" t="s">
+        <v>97</v>
+      </c>
+      <c r="D14" s="20" t="s">
+        <v>388</v>
+      </c>
+      <c r="E14" s="20" t="s">
+        <v>198</v>
+      </c>
+      <c r="F14" s="20" t="str">
+        <f>Variables!C11</f>
+        <v>8396e74a-7bc5-4793-b7c4-bd79b3b7932b</v>
+      </c>
+      <c r="G14" s="20" t="s">
+        <v>389</v>
+      </c>
+      <c r="H14" s="33" t="s">
+        <v>70</v>
+      </c>
+      <c r="I14" s="20" t="s">
+        <v>390</v>
+      </c>
+      <c r="J14" s="34"/>
+    </row>
+    <row r="15" ht="42.0" customHeight="1">
+      <c r="A15" s="41" t="s">
+        <v>391</v>
+      </c>
+      <c r="B15" s="21" t="s">
+        <v>392</v>
+      </c>
+      <c r="C15" s="32" t="s">
+        <v>97</v>
+      </c>
+      <c r="D15" s="21" t="s">
+        <v>393</v>
+      </c>
+      <c r="E15" s="21" t="s">
+        <v>198</v>
+      </c>
+      <c r="F15" s="21" t="str">
+        <f>Variables!C11</f>
+        <v>8396e74a-7bc5-4793-b7c4-bd79b3b7932b</v>
+      </c>
+      <c r="G15" s="21" t="s">
+        <v>394</v>
+      </c>
+      <c r="H15" s="33" t="s">
+        <v>70</v>
+      </c>
+      <c r="I15" s="21" t="s">
+        <v>395</v>
+      </c>
+      <c r="J15" s="23"/>
+    </row>
+    <row r="16" ht="42.0" customHeight="1">
+      <c r="A16" s="38" t="s">
+        <v>396</v>
+      </c>
+      <c r="B16" s="20" t="s">
+        <v>397</v>
+      </c>
+      <c r="C16" s="35" t="s">
+        <v>97</v>
+      </c>
+      <c r="D16" s="20" t="s">
+        <v>398</v>
+      </c>
+      <c r="E16" s="20" t="s">
+        <v>198</v>
+      </c>
+      <c r="F16" s="20" t="str">
+        <f>Variables!C10</f>
+        <v>4a2c7d53-9a34-4c40-9e8f-c8972db67211</v>
+      </c>
+      <c r="G16" s="20" t="s">
+        <v>336</v>
+      </c>
+      <c r="H16" s="33" t="s">
+        <v>70</v>
+      </c>
+      <c r="I16" s="20" t="s">
+        <v>399</v>
+      </c>
+      <c r="J16" s="34"/>
     </row>
     <row r="22" ht="15.75" customHeight="1"/>
     <row r="23" ht="15.75" customHeight="1"/>
@@ -14720,1458 +16300,31 @@
     <row r="998" ht="15.75" customHeight="1"/>
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
+    <row r="1001" ht="15.75" customHeight="1"/>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="4">
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A3:J3"/>
-    <mergeCell ref="A7:J7"/>
-    <mergeCell ref="A16:J16"/>
-    <mergeCell ref="A19:J19"/>
+    <mergeCell ref="A6:J6"/>
+    <mergeCell ref="A11:J11"/>
   </mergeCells>
-  <conditionalFormatting sqref="H4:H6 H8:H15 H17:H18 H20:H21">
+  <conditionalFormatting sqref="H4:H5 H7:H10 H12:H16">
     <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="✅ PASS">
       <formula>NOT(ISERROR(SEARCH(("✅ PASS"),(H4))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H4:H6 H8:H15 H17:H18 H20:H21">
+  <conditionalFormatting sqref="H4:H5 H7:H10 H12:H16">
     <cfRule type="containsText" dxfId="4" priority="2" operator="containsText" text="❌ FAIL">
       <formula>NOT(ISERROR(SEARCH(("❌ FAIL"),(H4))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H4:H6 H8:H15 H17:H18 H20:H21">
+  <conditionalFormatting sqref="H4:H5 H7:H10 H12:H16">
     <cfRule type="containsText" dxfId="2" priority="3" operator="containsText" text="⏳ PENDING">
       <formula>NOT(ISERROR(SEARCH(("⏳ PENDING"),(H4))))</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="H4:H6 H8:H15 H17:H18 H20:H21">
-      <formula1>"⏳ PENDIENTE,✅ PASS,❌ FAIL"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <printOptions/>
-  <pageMargins bottom="1.0" footer="0.0" header="0.0" left="0.75" right="0.75" top="1.0"/>
-  <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
-  <cols>
-    <col customWidth="1" min="1" max="1" width="6.0"/>
-    <col customWidth="1" min="2" max="2" width="38.0"/>
-    <col customWidth="1" min="3" max="3" width="9.0"/>
-    <col customWidth="1" min="4" max="4" width="42.0"/>
-    <col customWidth="1" min="5" max="5" width="18.0"/>
-    <col customWidth="1" min="6" max="6" width="55.0"/>
-    <col customWidth="1" min="7" max="7" width="45.0"/>
-    <col customWidth="1" min="8" max="8" width="16.0"/>
-    <col customWidth="1" min="9" max="9" width="40.0"/>
-    <col customWidth="1" min="10" max="10" width="14.0"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="24.0" customHeight="1">
-      <c r="A1" s="27" t="s">
-        <v>334</v>
-      </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
-      <c r="H1" s="28"/>
-      <c r="I1" s="28"/>
-      <c r="J1" s="28"/>
-    </row>
-    <row r="2" ht="21.75" customHeight="1">
-      <c r="A2" s="22" t="s">
-        <v>85</v>
-      </c>
-      <c r="B2" s="22" t="s">
-        <v>86</v>
-      </c>
-      <c r="C2" s="22" t="s">
-        <v>87</v>
-      </c>
-      <c r="D2" s="22" t="s">
-        <v>88</v>
-      </c>
-      <c r="E2" s="22" t="s">
-        <v>89</v>
-      </c>
-      <c r="F2" s="22" t="s">
-        <v>26</v>
-      </c>
-      <c r="G2" s="22" t="s">
-        <v>90</v>
-      </c>
-      <c r="H2" s="22" t="s">
-        <v>91</v>
-      </c>
-      <c r="I2" s="22" t="s">
-        <v>92</v>
-      </c>
-      <c r="J2" s="22" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="3" ht="18.0" customHeight="1">
-      <c r="A3" s="29" t="s">
-        <v>259</v>
-      </c>
-      <c r="B3" s="30"/>
-      <c r="C3" s="30"/>
-      <c r="D3" s="30"/>
-      <c r="E3" s="30"/>
-      <c r="F3" s="30"/>
-      <c r="G3" s="30"/>
-      <c r="H3" s="30"/>
-      <c r="I3" s="30"/>
-      <c r="J3" s="31"/>
-    </row>
-    <row r="4" ht="42.0" customHeight="1">
-      <c r="A4" s="23" t="s">
-        <v>335</v>
-      </c>
-      <c r="B4" s="21" t="s">
-        <v>336</v>
-      </c>
-      <c r="C4" s="32" t="s">
-        <v>97</v>
-      </c>
-      <c r="D4" s="21" t="s">
-        <v>337</v>
-      </c>
-      <c r="E4" s="21" t="s">
-        <v>193</v>
-      </c>
-      <c r="F4" s="21" t="s">
-        <v>338</v>
-      </c>
-      <c r="G4" s="21" t="s">
-        <v>339</v>
-      </c>
-      <c r="H4" s="33" t="s">
-        <v>70</v>
-      </c>
-      <c r="I4" s="21" t="s">
-        <v>340</v>
-      </c>
-      <c r="J4" s="23"/>
-    </row>
-    <row r="5" ht="42.0" customHeight="1">
-      <c r="A5" s="34" t="s">
-        <v>341</v>
-      </c>
-      <c r="B5" s="20" t="s">
-        <v>342</v>
-      </c>
-      <c r="C5" s="35" t="s">
-        <v>97</v>
-      </c>
-      <c r="D5" s="20" t="s">
-        <v>337</v>
-      </c>
-      <c r="E5" s="20" t="s">
-        <v>193</v>
-      </c>
-      <c r="F5" s="20" t="s">
-        <v>343</v>
-      </c>
-      <c r="G5" s="20" t="s">
-        <v>344</v>
-      </c>
-      <c r="H5" s="33" t="s">
-        <v>70</v>
-      </c>
-      <c r="I5" s="20" t="s">
-        <v>345</v>
-      </c>
-      <c r="J5" s="34"/>
-    </row>
-    <row r="6" ht="18.0" customHeight="1">
-      <c r="A6" s="29" t="s">
-        <v>275</v>
-      </c>
-      <c r="B6" s="30"/>
-      <c r="C6" s="30"/>
-      <c r="D6" s="30"/>
-      <c r="E6" s="30"/>
-      <c r="F6" s="30"/>
-      <c r="G6" s="30"/>
-      <c r="H6" s="30"/>
-      <c r="I6" s="30"/>
-      <c r="J6" s="31"/>
-    </row>
-    <row r="7" ht="42.0" customHeight="1">
-      <c r="A7" s="34" t="s">
-        <v>346</v>
-      </c>
-      <c r="B7" s="20" t="s">
-        <v>347</v>
-      </c>
-      <c r="C7" s="36" t="s">
-        <v>139</v>
-      </c>
-      <c r="D7" s="20" t="s">
-        <v>348</v>
-      </c>
-      <c r="E7" s="20" t="s">
-        <v>193</v>
-      </c>
-      <c r="F7" s="20" t="s">
-        <v>141</v>
-      </c>
-      <c r="G7" s="20" t="s">
-        <v>349</v>
-      </c>
-      <c r="H7" s="33" t="s">
-        <v>70</v>
-      </c>
-      <c r="I7" s="20" t="s">
-        <v>350</v>
-      </c>
-      <c r="J7" s="34"/>
-    </row>
-    <row r="8" ht="42.0" customHeight="1">
-      <c r="A8" s="23" t="s">
-        <v>351</v>
-      </c>
-      <c r="B8" s="21" t="s">
-        <v>352</v>
-      </c>
-      <c r="C8" s="43" t="s">
-        <v>139</v>
-      </c>
-      <c r="D8" s="21" t="s">
-        <v>353</v>
-      </c>
-      <c r="E8" s="21" t="s">
-        <v>193</v>
-      </c>
-      <c r="F8" s="21" t="str">
-        <f>Variables!C10</f>
-        <v>4a2c7d53-9a34-4c40-9e8f-c8972db67211</v>
-      </c>
-      <c r="G8" s="21" t="s">
-        <v>354</v>
-      </c>
-      <c r="H8" s="33" t="s">
-        <v>70</v>
-      </c>
-      <c r="I8" s="21" t="s">
-        <v>355</v>
-      </c>
-      <c r="J8" s="23"/>
-    </row>
-    <row r="9" ht="42.0" customHeight="1">
-      <c r="A9" s="34" t="s">
-        <v>356</v>
-      </c>
-      <c r="B9" s="20" t="s">
-        <v>357</v>
-      </c>
-      <c r="C9" s="36" t="s">
-        <v>139</v>
-      </c>
-      <c r="D9" s="20" t="s">
-        <v>358</v>
-      </c>
-      <c r="E9" s="20" t="s">
-        <v>193</v>
-      </c>
-      <c r="F9" s="20" t="s">
-        <v>141</v>
-      </c>
-      <c r="G9" s="20" t="s">
-        <v>359</v>
-      </c>
-      <c r="H9" s="33" t="s">
-        <v>70</v>
-      </c>
-      <c r="I9" s="20" t="s">
-        <v>360</v>
-      </c>
-      <c r="J9" s="34"/>
-    </row>
-    <row r="10" ht="18.0" customHeight="1">
-      <c r="A10" s="29" t="s">
-        <v>361</v>
-      </c>
-      <c r="B10" s="30"/>
-      <c r="C10" s="30"/>
-      <c r="D10" s="30"/>
-      <c r="E10" s="30"/>
-      <c r="F10" s="30"/>
-      <c r="G10" s="30"/>
-      <c r="H10" s="30"/>
-      <c r="I10" s="30"/>
-      <c r="J10" s="31"/>
-    </row>
-    <row r="11" ht="42.0" customHeight="1">
-      <c r="A11" s="34" t="s">
-        <v>362</v>
-      </c>
-      <c r="B11" s="20" t="s">
-        <v>363</v>
-      </c>
-      <c r="C11" s="35" t="s">
-        <v>97</v>
-      </c>
-      <c r="D11" s="20" t="s">
-        <v>364</v>
-      </c>
-      <c r="E11" s="20" t="s">
-        <v>193</v>
-      </c>
-      <c r="F11" s="20" t="str">
-        <f>Variables!C11</f>
-        <v>8396e74a-7bc5-4793-b7c4-bd79b3b7932b</v>
-      </c>
-      <c r="G11" s="20" t="s">
-        <v>365</v>
-      </c>
-      <c r="H11" s="33" t="s">
-        <v>70</v>
-      </c>
-      <c r="I11" s="20" t="s">
-        <v>366</v>
-      </c>
-      <c r="J11" s="34"/>
-    </row>
-    <row r="12" ht="42.0" customHeight="1">
-      <c r="A12" s="23" t="s">
-        <v>367</v>
-      </c>
-      <c r="B12" s="21" t="s">
-        <v>368</v>
-      </c>
-      <c r="C12" s="32" t="s">
-        <v>97</v>
-      </c>
-      <c r="D12" s="21" t="s">
-        <v>369</v>
-      </c>
-      <c r="E12" s="21" t="s">
-        <v>193</v>
-      </c>
-      <c r="F12" s="21" t="str">
-        <f>Variables!C11</f>
-        <v>8396e74a-7bc5-4793-b7c4-bd79b3b7932b</v>
-      </c>
-      <c r="G12" s="21" t="s">
-        <v>370</v>
-      </c>
-      <c r="H12" s="33" t="s">
-        <v>70</v>
-      </c>
-      <c r="I12" s="21" t="s">
-        <v>371</v>
-      </c>
-      <c r="J12" s="23"/>
-    </row>
-    <row r="13" ht="42.0" customHeight="1">
-      <c r="A13" s="34" t="s">
-        <v>372</v>
-      </c>
-      <c r="B13" s="20" t="s">
-        <v>373</v>
-      </c>
-      <c r="C13" s="35" t="s">
-        <v>97</v>
-      </c>
-      <c r="D13" s="20" t="s">
-        <v>374</v>
-      </c>
-      <c r="E13" s="20" t="s">
-        <v>193</v>
-      </c>
-      <c r="F13" s="20" t="str">
-        <f>Variables!C11</f>
-        <v>8396e74a-7bc5-4793-b7c4-bd79b3b7932b</v>
-      </c>
-      <c r="G13" s="20" t="s">
-        <v>375</v>
-      </c>
-      <c r="H13" s="33" t="s">
-        <v>70</v>
-      </c>
-      <c r="I13" s="20" t="s">
-        <v>376</v>
-      </c>
-      <c r="J13" s="34"/>
-    </row>
-    <row r="14" ht="42.0" customHeight="1">
-      <c r="A14" s="23" t="s">
-        <v>377</v>
-      </c>
-      <c r="B14" s="21" t="s">
-        <v>378</v>
-      </c>
-      <c r="C14" s="32" t="s">
-        <v>97</v>
-      </c>
-      <c r="D14" s="21" t="s">
-        <v>379</v>
-      </c>
-      <c r="E14" s="21" t="s">
-        <v>193</v>
-      </c>
-      <c r="F14" s="21" t="str">
-        <f>Variables!C11</f>
-        <v>8396e74a-7bc5-4793-b7c4-bd79b3b7932b</v>
-      </c>
-      <c r="G14" s="21" t="s">
-        <v>380</v>
-      </c>
-      <c r="H14" s="33" t="s">
-        <v>70</v>
-      </c>
-      <c r="I14" s="21" t="s">
-        <v>381</v>
-      </c>
-      <c r="J14" s="23"/>
-    </row>
-    <row r="15" ht="42.0" customHeight="1">
-      <c r="A15" s="34" t="s">
-        <v>382</v>
-      </c>
-      <c r="B15" s="20" t="s">
-        <v>383</v>
-      </c>
-      <c r="C15" s="35" t="s">
-        <v>97</v>
-      </c>
-      <c r="D15" s="20" t="s">
-        <v>384</v>
-      </c>
-      <c r="E15" s="20" t="s">
-        <v>193</v>
-      </c>
-      <c r="F15" s="20" t="str">
-        <f>Variables!C10</f>
-        <v>4a2c7d53-9a34-4c40-9e8f-c8972db67211</v>
-      </c>
-      <c r="G15" s="20" t="s">
-        <v>326</v>
-      </c>
-      <c r="H15" s="33" t="s">
-        <v>70</v>
-      </c>
-      <c r="I15" s="20" t="s">
-        <v>385</v>
-      </c>
-      <c r="J15" s="34"/>
-    </row>
-    <row r="21" ht="15.75" customHeight="1"/>
-    <row r="22" ht="15.75" customHeight="1"/>
-    <row r="23" ht="15.75" customHeight="1"/>
-    <row r="24" ht="15.75" customHeight="1"/>
-    <row r="25" ht="15.75" customHeight="1"/>
-    <row r="26" ht="15.75" customHeight="1"/>
-    <row r="27" ht="15.75" customHeight="1"/>
-    <row r="28" ht="15.75" customHeight="1"/>
-    <row r="29" ht="15.75" customHeight="1"/>
-    <row r="30" ht="15.75" customHeight="1"/>
-    <row r="31" ht="15.75" customHeight="1"/>
-    <row r="32" ht="15.75" customHeight="1"/>
-    <row r="33" ht="15.75" customHeight="1"/>
-    <row r="34" ht="15.75" customHeight="1"/>
-    <row r="35" ht="15.75" customHeight="1"/>
-    <row r="36" ht="15.75" customHeight="1"/>
-    <row r="37" ht="15.75" customHeight="1"/>
-    <row r="38" ht="15.75" customHeight="1"/>
-    <row r="39" ht="15.75" customHeight="1"/>
-    <row r="40" ht="15.75" customHeight="1"/>
-    <row r="41" ht="15.75" customHeight="1"/>
-    <row r="42" ht="15.75" customHeight="1"/>
-    <row r="43" ht="15.75" customHeight="1"/>
-    <row r="44" ht="15.75" customHeight="1"/>
-    <row r="45" ht="15.75" customHeight="1"/>
-    <row r="46" ht="15.75" customHeight="1"/>
-    <row r="47" ht="15.75" customHeight="1"/>
-    <row r="48" ht="15.75" customHeight="1"/>
-    <row r="49" ht="15.75" customHeight="1"/>
-    <row r="50" ht="15.75" customHeight="1"/>
-    <row r="51" ht="15.75" customHeight="1"/>
-    <row r="52" ht="15.75" customHeight="1"/>
-    <row r="53" ht="15.75" customHeight="1"/>
-    <row r="54" ht="15.75" customHeight="1"/>
-    <row r="55" ht="15.75" customHeight="1"/>
-    <row r="56" ht="15.75" customHeight="1"/>
-    <row r="57" ht="15.75" customHeight="1"/>
-    <row r="58" ht="15.75" customHeight="1"/>
-    <row r="59" ht="15.75" customHeight="1"/>
-    <row r="60" ht="15.75" customHeight="1"/>
-    <row r="61" ht="15.75" customHeight="1"/>
-    <row r="62" ht="15.75" customHeight="1"/>
-    <row r="63" ht="15.75" customHeight="1"/>
-    <row r="64" ht="15.75" customHeight="1"/>
-    <row r="65" ht="15.75" customHeight="1"/>
-    <row r="66" ht="15.75" customHeight="1"/>
-    <row r="67" ht="15.75" customHeight="1"/>
-    <row r="68" ht="15.75" customHeight="1"/>
-    <row r="69" ht="15.75" customHeight="1"/>
-    <row r="70" ht="15.75" customHeight="1"/>
-    <row r="71" ht="15.75" customHeight="1"/>
-    <row r="72" ht="15.75" customHeight="1"/>
-    <row r="73" ht="15.75" customHeight="1"/>
-    <row r="74" ht="15.75" customHeight="1"/>
-    <row r="75" ht="15.75" customHeight="1"/>
-    <row r="76" ht="15.75" customHeight="1"/>
-    <row r="77" ht="15.75" customHeight="1"/>
-    <row r="78" ht="15.75" customHeight="1"/>
-    <row r="79" ht="15.75" customHeight="1"/>
-    <row r="80" ht="15.75" customHeight="1"/>
-    <row r="81" ht="15.75" customHeight="1"/>
-    <row r="82" ht="15.75" customHeight="1"/>
-    <row r="83" ht="15.75" customHeight="1"/>
-    <row r="84" ht="15.75" customHeight="1"/>
-    <row r="85" ht="15.75" customHeight="1"/>
-    <row r="86" ht="15.75" customHeight="1"/>
-    <row r="87" ht="15.75" customHeight="1"/>
-    <row r="88" ht="15.75" customHeight="1"/>
-    <row r="89" ht="15.75" customHeight="1"/>
-    <row r="90" ht="15.75" customHeight="1"/>
-    <row r="91" ht="15.75" customHeight="1"/>
-    <row r="92" ht="15.75" customHeight="1"/>
-    <row r="93" ht="15.75" customHeight="1"/>
-    <row r="94" ht="15.75" customHeight="1"/>
-    <row r="95" ht="15.75" customHeight="1"/>
-    <row r="96" ht="15.75" customHeight="1"/>
-    <row r="97" ht="15.75" customHeight="1"/>
-    <row r="98" ht="15.75" customHeight="1"/>
-    <row r="99" ht="15.75" customHeight="1"/>
-    <row r="100" ht="15.75" customHeight="1"/>
-    <row r="101" ht="15.75" customHeight="1"/>
-    <row r="102" ht="15.75" customHeight="1"/>
-    <row r="103" ht="15.75" customHeight="1"/>
-    <row r="104" ht="15.75" customHeight="1"/>
-    <row r="105" ht="15.75" customHeight="1"/>
-    <row r="106" ht="15.75" customHeight="1"/>
-    <row r="107" ht="15.75" customHeight="1"/>
-    <row r="108" ht="15.75" customHeight="1"/>
-    <row r="109" ht="15.75" customHeight="1"/>
-    <row r="110" ht="15.75" customHeight="1"/>
-    <row r="111" ht="15.75" customHeight="1"/>
-    <row r="112" ht="15.75" customHeight="1"/>
-    <row r="113" ht="15.75" customHeight="1"/>
-    <row r="114" ht="15.75" customHeight="1"/>
-    <row r="115" ht="15.75" customHeight="1"/>
-    <row r="116" ht="15.75" customHeight="1"/>
-    <row r="117" ht="15.75" customHeight="1"/>
-    <row r="118" ht="15.75" customHeight="1"/>
-    <row r="119" ht="15.75" customHeight="1"/>
-    <row r="120" ht="15.75" customHeight="1"/>
-    <row r="121" ht="15.75" customHeight="1"/>
-    <row r="122" ht="15.75" customHeight="1"/>
-    <row r="123" ht="15.75" customHeight="1"/>
-    <row r="124" ht="15.75" customHeight="1"/>
-    <row r="125" ht="15.75" customHeight="1"/>
-    <row r="126" ht="15.75" customHeight="1"/>
-    <row r="127" ht="15.75" customHeight="1"/>
-    <row r="128" ht="15.75" customHeight="1"/>
-    <row r="129" ht="15.75" customHeight="1"/>
-    <row r="130" ht="15.75" customHeight="1"/>
-    <row r="131" ht="15.75" customHeight="1"/>
-    <row r="132" ht="15.75" customHeight="1"/>
-    <row r="133" ht="15.75" customHeight="1"/>
-    <row r="134" ht="15.75" customHeight="1"/>
-    <row r="135" ht="15.75" customHeight="1"/>
-    <row r="136" ht="15.75" customHeight="1"/>
-    <row r="137" ht="15.75" customHeight="1"/>
-    <row r="138" ht="15.75" customHeight="1"/>
-    <row r="139" ht="15.75" customHeight="1"/>
-    <row r="140" ht="15.75" customHeight="1"/>
-    <row r="141" ht="15.75" customHeight="1"/>
-    <row r="142" ht="15.75" customHeight="1"/>
-    <row r="143" ht="15.75" customHeight="1"/>
-    <row r="144" ht="15.75" customHeight="1"/>
-    <row r="145" ht="15.75" customHeight="1"/>
-    <row r="146" ht="15.75" customHeight="1"/>
-    <row r="147" ht="15.75" customHeight="1"/>
-    <row r="148" ht="15.75" customHeight="1"/>
-    <row r="149" ht="15.75" customHeight="1"/>
-    <row r="150" ht="15.75" customHeight="1"/>
-    <row r="151" ht="15.75" customHeight="1"/>
-    <row r="152" ht="15.75" customHeight="1"/>
-    <row r="153" ht="15.75" customHeight="1"/>
-    <row r="154" ht="15.75" customHeight="1"/>
-    <row r="155" ht="15.75" customHeight="1"/>
-    <row r="156" ht="15.75" customHeight="1"/>
-    <row r="157" ht="15.75" customHeight="1"/>
-    <row r="158" ht="15.75" customHeight="1"/>
-    <row r="159" ht="15.75" customHeight="1"/>
-    <row r="160" ht="15.75" customHeight="1"/>
-    <row r="161" ht="15.75" customHeight="1"/>
-    <row r="162" ht="15.75" customHeight="1"/>
-    <row r="163" ht="15.75" customHeight="1"/>
-    <row r="164" ht="15.75" customHeight="1"/>
-    <row r="165" ht="15.75" customHeight="1"/>
-    <row r="166" ht="15.75" customHeight="1"/>
-    <row r="167" ht="15.75" customHeight="1"/>
-    <row r="168" ht="15.75" customHeight="1"/>
-    <row r="169" ht="15.75" customHeight="1"/>
-    <row r="170" ht="15.75" customHeight="1"/>
-    <row r="171" ht="15.75" customHeight="1"/>
-    <row r="172" ht="15.75" customHeight="1"/>
-    <row r="173" ht="15.75" customHeight="1"/>
-    <row r="174" ht="15.75" customHeight="1"/>
-    <row r="175" ht="15.75" customHeight="1"/>
-    <row r="176" ht="15.75" customHeight="1"/>
-    <row r="177" ht="15.75" customHeight="1"/>
-    <row r="178" ht="15.75" customHeight="1"/>
-    <row r="179" ht="15.75" customHeight="1"/>
-    <row r="180" ht="15.75" customHeight="1"/>
-    <row r="181" ht="15.75" customHeight="1"/>
-    <row r="182" ht="15.75" customHeight="1"/>
-    <row r="183" ht="15.75" customHeight="1"/>
-    <row r="184" ht="15.75" customHeight="1"/>
-    <row r="185" ht="15.75" customHeight="1"/>
-    <row r="186" ht="15.75" customHeight="1"/>
-    <row r="187" ht="15.75" customHeight="1"/>
-    <row r="188" ht="15.75" customHeight="1"/>
-    <row r="189" ht="15.75" customHeight="1"/>
-    <row r="190" ht="15.75" customHeight="1"/>
-    <row r="191" ht="15.75" customHeight="1"/>
-    <row r="192" ht="15.75" customHeight="1"/>
-    <row r="193" ht="15.75" customHeight="1"/>
-    <row r="194" ht="15.75" customHeight="1"/>
-    <row r="195" ht="15.75" customHeight="1"/>
-    <row r="196" ht="15.75" customHeight="1"/>
-    <row r="197" ht="15.75" customHeight="1"/>
-    <row r="198" ht="15.75" customHeight="1"/>
-    <row r="199" ht="15.75" customHeight="1"/>
-    <row r="200" ht="15.75" customHeight="1"/>
-    <row r="201" ht="15.75" customHeight="1"/>
-    <row r="202" ht="15.75" customHeight="1"/>
-    <row r="203" ht="15.75" customHeight="1"/>
-    <row r="204" ht="15.75" customHeight="1"/>
-    <row r="205" ht="15.75" customHeight="1"/>
-    <row r="206" ht="15.75" customHeight="1"/>
-    <row r="207" ht="15.75" customHeight="1"/>
-    <row r="208" ht="15.75" customHeight="1"/>
-    <row r="209" ht="15.75" customHeight="1"/>
-    <row r="210" ht="15.75" customHeight="1"/>
-    <row r="211" ht="15.75" customHeight="1"/>
-    <row r="212" ht="15.75" customHeight="1"/>
-    <row r="213" ht="15.75" customHeight="1"/>
-    <row r="214" ht="15.75" customHeight="1"/>
-    <row r="215" ht="15.75" customHeight="1"/>
-    <row r="216" ht="15.75" customHeight="1"/>
-    <row r="217" ht="15.75" customHeight="1"/>
-    <row r="218" ht="15.75" customHeight="1"/>
-    <row r="219" ht="15.75" customHeight="1"/>
-    <row r="220" ht="15.75" customHeight="1"/>
-    <row r="221" ht="15.75" customHeight="1"/>
-    <row r="222" ht="15.75" customHeight="1"/>
-    <row r="223" ht="15.75" customHeight="1"/>
-    <row r="224" ht="15.75" customHeight="1"/>
-    <row r="225" ht="15.75" customHeight="1"/>
-    <row r="226" ht="15.75" customHeight="1"/>
-    <row r="227" ht="15.75" customHeight="1"/>
-    <row r="228" ht="15.75" customHeight="1"/>
-    <row r="229" ht="15.75" customHeight="1"/>
-    <row r="230" ht="15.75" customHeight="1"/>
-    <row r="231" ht="15.75" customHeight="1"/>
-    <row r="232" ht="15.75" customHeight="1"/>
-    <row r="233" ht="15.75" customHeight="1"/>
-    <row r="234" ht="15.75" customHeight="1"/>
-    <row r="235" ht="15.75" customHeight="1"/>
-    <row r="236" ht="15.75" customHeight="1"/>
-    <row r="237" ht="15.75" customHeight="1"/>
-    <row r="238" ht="15.75" customHeight="1"/>
-    <row r="239" ht="15.75" customHeight="1"/>
-    <row r="240" ht="15.75" customHeight="1"/>
-    <row r="241" ht="15.75" customHeight="1"/>
-    <row r="242" ht="15.75" customHeight="1"/>
-    <row r="243" ht="15.75" customHeight="1"/>
-    <row r="244" ht="15.75" customHeight="1"/>
-    <row r="245" ht="15.75" customHeight="1"/>
-    <row r="246" ht="15.75" customHeight="1"/>
-    <row r="247" ht="15.75" customHeight="1"/>
-    <row r="248" ht="15.75" customHeight="1"/>
-    <row r="249" ht="15.75" customHeight="1"/>
-    <row r="250" ht="15.75" customHeight="1"/>
-    <row r="251" ht="15.75" customHeight="1"/>
-    <row r="252" ht="15.75" customHeight="1"/>
-    <row r="253" ht="15.75" customHeight="1"/>
-    <row r="254" ht="15.75" customHeight="1"/>
-    <row r="255" ht="15.75" customHeight="1"/>
-    <row r="256" ht="15.75" customHeight="1"/>
-    <row r="257" ht="15.75" customHeight="1"/>
-    <row r="258" ht="15.75" customHeight="1"/>
-    <row r="259" ht="15.75" customHeight="1"/>
-    <row r="260" ht="15.75" customHeight="1"/>
-    <row r="261" ht="15.75" customHeight="1"/>
-    <row r="262" ht="15.75" customHeight="1"/>
-    <row r="263" ht="15.75" customHeight="1"/>
-    <row r="264" ht="15.75" customHeight="1"/>
-    <row r="265" ht="15.75" customHeight="1"/>
-    <row r="266" ht="15.75" customHeight="1"/>
-    <row r="267" ht="15.75" customHeight="1"/>
-    <row r="268" ht="15.75" customHeight="1"/>
-    <row r="269" ht="15.75" customHeight="1"/>
-    <row r="270" ht="15.75" customHeight="1"/>
-    <row r="271" ht="15.75" customHeight="1"/>
-    <row r="272" ht="15.75" customHeight="1"/>
-    <row r="273" ht="15.75" customHeight="1"/>
-    <row r="274" ht="15.75" customHeight="1"/>
-    <row r="275" ht="15.75" customHeight="1"/>
-    <row r="276" ht="15.75" customHeight="1"/>
-    <row r="277" ht="15.75" customHeight="1"/>
-    <row r="278" ht="15.75" customHeight="1"/>
-    <row r="279" ht="15.75" customHeight="1"/>
-    <row r="280" ht="15.75" customHeight="1"/>
-    <row r="281" ht="15.75" customHeight="1"/>
-    <row r="282" ht="15.75" customHeight="1"/>
-    <row r="283" ht="15.75" customHeight="1"/>
-    <row r="284" ht="15.75" customHeight="1"/>
-    <row r="285" ht="15.75" customHeight="1"/>
-    <row r="286" ht="15.75" customHeight="1"/>
-    <row r="287" ht="15.75" customHeight="1"/>
-    <row r="288" ht="15.75" customHeight="1"/>
-    <row r="289" ht="15.75" customHeight="1"/>
-    <row r="290" ht="15.75" customHeight="1"/>
-    <row r="291" ht="15.75" customHeight="1"/>
-    <row r="292" ht="15.75" customHeight="1"/>
-    <row r="293" ht="15.75" customHeight="1"/>
-    <row r="294" ht="15.75" customHeight="1"/>
-    <row r="295" ht="15.75" customHeight="1"/>
-    <row r="296" ht="15.75" customHeight="1"/>
-    <row r="297" ht="15.75" customHeight="1"/>
-    <row r="298" ht="15.75" customHeight="1"/>
-    <row r="299" ht="15.75" customHeight="1"/>
-    <row r="300" ht="15.75" customHeight="1"/>
-    <row r="301" ht="15.75" customHeight="1"/>
-    <row r="302" ht="15.75" customHeight="1"/>
-    <row r="303" ht="15.75" customHeight="1"/>
-    <row r="304" ht="15.75" customHeight="1"/>
-    <row r="305" ht="15.75" customHeight="1"/>
-    <row r="306" ht="15.75" customHeight="1"/>
-    <row r="307" ht="15.75" customHeight="1"/>
-    <row r="308" ht="15.75" customHeight="1"/>
-    <row r="309" ht="15.75" customHeight="1"/>
-    <row r="310" ht="15.75" customHeight="1"/>
-    <row r="311" ht="15.75" customHeight="1"/>
-    <row r="312" ht="15.75" customHeight="1"/>
-    <row r="313" ht="15.75" customHeight="1"/>
-    <row r="314" ht="15.75" customHeight="1"/>
-    <row r="315" ht="15.75" customHeight="1"/>
-    <row r="316" ht="15.75" customHeight="1"/>
-    <row r="317" ht="15.75" customHeight="1"/>
-    <row r="318" ht="15.75" customHeight="1"/>
-    <row r="319" ht="15.75" customHeight="1"/>
-    <row r="320" ht="15.75" customHeight="1"/>
-    <row r="321" ht="15.75" customHeight="1"/>
-    <row r="322" ht="15.75" customHeight="1"/>
-    <row r="323" ht="15.75" customHeight="1"/>
-    <row r="324" ht="15.75" customHeight="1"/>
-    <row r="325" ht="15.75" customHeight="1"/>
-    <row r="326" ht="15.75" customHeight="1"/>
-    <row r="327" ht="15.75" customHeight="1"/>
-    <row r="328" ht="15.75" customHeight="1"/>
-    <row r="329" ht="15.75" customHeight="1"/>
-    <row r="330" ht="15.75" customHeight="1"/>
-    <row r="331" ht="15.75" customHeight="1"/>
-    <row r="332" ht="15.75" customHeight="1"/>
-    <row r="333" ht="15.75" customHeight="1"/>
-    <row r="334" ht="15.75" customHeight="1"/>
-    <row r="335" ht="15.75" customHeight="1"/>
-    <row r="336" ht="15.75" customHeight="1"/>
-    <row r="337" ht="15.75" customHeight="1"/>
-    <row r="338" ht="15.75" customHeight="1"/>
-    <row r="339" ht="15.75" customHeight="1"/>
-    <row r="340" ht="15.75" customHeight="1"/>
-    <row r="341" ht="15.75" customHeight="1"/>
-    <row r="342" ht="15.75" customHeight="1"/>
-    <row r="343" ht="15.75" customHeight="1"/>
-    <row r="344" ht="15.75" customHeight="1"/>
-    <row r="345" ht="15.75" customHeight="1"/>
-    <row r="346" ht="15.75" customHeight="1"/>
-    <row r="347" ht="15.75" customHeight="1"/>
-    <row r="348" ht="15.75" customHeight="1"/>
-    <row r="349" ht="15.75" customHeight="1"/>
-    <row r="350" ht="15.75" customHeight="1"/>
-    <row r="351" ht="15.75" customHeight="1"/>
-    <row r="352" ht="15.75" customHeight="1"/>
-    <row r="353" ht="15.75" customHeight="1"/>
-    <row r="354" ht="15.75" customHeight="1"/>
-    <row r="355" ht="15.75" customHeight="1"/>
-    <row r="356" ht="15.75" customHeight="1"/>
-    <row r="357" ht="15.75" customHeight="1"/>
-    <row r="358" ht="15.75" customHeight="1"/>
-    <row r="359" ht="15.75" customHeight="1"/>
-    <row r="360" ht="15.75" customHeight="1"/>
-    <row r="361" ht="15.75" customHeight="1"/>
-    <row r="362" ht="15.75" customHeight="1"/>
-    <row r="363" ht="15.75" customHeight="1"/>
-    <row r="364" ht="15.75" customHeight="1"/>
-    <row r="365" ht="15.75" customHeight="1"/>
-    <row r="366" ht="15.75" customHeight="1"/>
-    <row r="367" ht="15.75" customHeight="1"/>
-    <row r="368" ht="15.75" customHeight="1"/>
-    <row r="369" ht="15.75" customHeight="1"/>
-    <row r="370" ht="15.75" customHeight="1"/>
-    <row r="371" ht="15.75" customHeight="1"/>
-    <row r="372" ht="15.75" customHeight="1"/>
-    <row r="373" ht="15.75" customHeight="1"/>
-    <row r="374" ht="15.75" customHeight="1"/>
-    <row r="375" ht="15.75" customHeight="1"/>
-    <row r="376" ht="15.75" customHeight="1"/>
-    <row r="377" ht="15.75" customHeight="1"/>
-    <row r="378" ht="15.75" customHeight="1"/>
-    <row r="379" ht="15.75" customHeight="1"/>
-    <row r="380" ht="15.75" customHeight="1"/>
-    <row r="381" ht="15.75" customHeight="1"/>
-    <row r="382" ht="15.75" customHeight="1"/>
-    <row r="383" ht="15.75" customHeight="1"/>
-    <row r="384" ht="15.75" customHeight="1"/>
-    <row r="385" ht="15.75" customHeight="1"/>
-    <row r="386" ht="15.75" customHeight="1"/>
-    <row r="387" ht="15.75" customHeight="1"/>
-    <row r="388" ht="15.75" customHeight="1"/>
-    <row r="389" ht="15.75" customHeight="1"/>
-    <row r="390" ht="15.75" customHeight="1"/>
-    <row r="391" ht="15.75" customHeight="1"/>
-    <row r="392" ht="15.75" customHeight="1"/>
-    <row r="393" ht="15.75" customHeight="1"/>
-    <row r="394" ht="15.75" customHeight="1"/>
-    <row r="395" ht="15.75" customHeight="1"/>
-    <row r="396" ht="15.75" customHeight="1"/>
-    <row r="397" ht="15.75" customHeight="1"/>
-    <row r="398" ht="15.75" customHeight="1"/>
-    <row r="399" ht="15.75" customHeight="1"/>
-    <row r="400" ht="15.75" customHeight="1"/>
-    <row r="401" ht="15.75" customHeight="1"/>
-    <row r="402" ht="15.75" customHeight="1"/>
-    <row r="403" ht="15.75" customHeight="1"/>
-    <row r="404" ht="15.75" customHeight="1"/>
-    <row r="405" ht="15.75" customHeight="1"/>
-    <row r="406" ht="15.75" customHeight="1"/>
-    <row r="407" ht="15.75" customHeight="1"/>
-    <row r="408" ht="15.75" customHeight="1"/>
-    <row r="409" ht="15.75" customHeight="1"/>
-    <row r="410" ht="15.75" customHeight="1"/>
-    <row r="411" ht="15.75" customHeight="1"/>
-    <row r="412" ht="15.75" customHeight="1"/>
-    <row r="413" ht="15.75" customHeight="1"/>
-    <row r="414" ht="15.75" customHeight="1"/>
-    <row r="415" ht="15.75" customHeight="1"/>
-    <row r="416" ht="15.75" customHeight="1"/>
-    <row r="417" ht="15.75" customHeight="1"/>
-    <row r="418" ht="15.75" customHeight="1"/>
-    <row r="419" ht="15.75" customHeight="1"/>
-    <row r="420" ht="15.75" customHeight="1"/>
-    <row r="421" ht="15.75" customHeight="1"/>
-    <row r="422" ht="15.75" customHeight="1"/>
-    <row r="423" ht="15.75" customHeight="1"/>
-    <row r="424" ht="15.75" customHeight="1"/>
-    <row r="425" ht="15.75" customHeight="1"/>
-    <row r="426" ht="15.75" customHeight="1"/>
-    <row r="427" ht="15.75" customHeight="1"/>
-    <row r="428" ht="15.75" customHeight="1"/>
-    <row r="429" ht="15.75" customHeight="1"/>
-    <row r="430" ht="15.75" customHeight="1"/>
-    <row r="431" ht="15.75" customHeight="1"/>
-    <row r="432" ht="15.75" customHeight="1"/>
-    <row r="433" ht="15.75" customHeight="1"/>
-    <row r="434" ht="15.75" customHeight="1"/>
-    <row r="435" ht="15.75" customHeight="1"/>
-    <row r="436" ht="15.75" customHeight="1"/>
-    <row r="437" ht="15.75" customHeight="1"/>
-    <row r="438" ht="15.75" customHeight="1"/>
-    <row r="439" ht="15.75" customHeight="1"/>
-    <row r="440" ht="15.75" customHeight="1"/>
-    <row r="441" ht="15.75" customHeight="1"/>
-    <row r="442" ht="15.75" customHeight="1"/>
-    <row r="443" ht="15.75" customHeight="1"/>
-    <row r="444" ht="15.75" customHeight="1"/>
-    <row r="445" ht="15.75" customHeight="1"/>
-    <row r="446" ht="15.75" customHeight="1"/>
-    <row r="447" ht="15.75" customHeight="1"/>
-    <row r="448" ht="15.75" customHeight="1"/>
-    <row r="449" ht="15.75" customHeight="1"/>
-    <row r="450" ht="15.75" customHeight="1"/>
-    <row r="451" ht="15.75" customHeight="1"/>
-    <row r="452" ht="15.75" customHeight="1"/>
-    <row r="453" ht="15.75" customHeight="1"/>
-    <row r="454" ht="15.75" customHeight="1"/>
-    <row r="455" ht="15.75" customHeight="1"/>
-    <row r="456" ht="15.75" customHeight="1"/>
-    <row r="457" ht="15.75" customHeight="1"/>
-    <row r="458" ht="15.75" customHeight="1"/>
-    <row r="459" ht="15.75" customHeight="1"/>
-    <row r="460" ht="15.75" customHeight="1"/>
-    <row r="461" ht="15.75" customHeight="1"/>
-    <row r="462" ht="15.75" customHeight="1"/>
-    <row r="463" ht="15.75" customHeight="1"/>
-    <row r="464" ht="15.75" customHeight="1"/>
-    <row r="465" ht="15.75" customHeight="1"/>
-    <row r="466" ht="15.75" customHeight="1"/>
-    <row r="467" ht="15.75" customHeight="1"/>
-    <row r="468" ht="15.75" customHeight="1"/>
-    <row r="469" ht="15.75" customHeight="1"/>
-    <row r="470" ht="15.75" customHeight="1"/>
-    <row r="471" ht="15.75" customHeight="1"/>
-    <row r="472" ht="15.75" customHeight="1"/>
-    <row r="473" ht="15.75" customHeight="1"/>
-    <row r="474" ht="15.75" customHeight="1"/>
-    <row r="475" ht="15.75" customHeight="1"/>
-    <row r="476" ht="15.75" customHeight="1"/>
-    <row r="477" ht="15.75" customHeight="1"/>
-    <row r="478" ht="15.75" customHeight="1"/>
-    <row r="479" ht="15.75" customHeight="1"/>
-    <row r="480" ht="15.75" customHeight="1"/>
-    <row r="481" ht="15.75" customHeight="1"/>
-    <row r="482" ht="15.75" customHeight="1"/>
-    <row r="483" ht="15.75" customHeight="1"/>
-    <row r="484" ht="15.75" customHeight="1"/>
-    <row r="485" ht="15.75" customHeight="1"/>
-    <row r="486" ht="15.75" customHeight="1"/>
-    <row r="487" ht="15.75" customHeight="1"/>
-    <row r="488" ht="15.75" customHeight="1"/>
-    <row r="489" ht="15.75" customHeight="1"/>
-    <row r="490" ht="15.75" customHeight="1"/>
-    <row r="491" ht="15.75" customHeight="1"/>
-    <row r="492" ht="15.75" customHeight="1"/>
-    <row r="493" ht="15.75" customHeight="1"/>
-    <row r="494" ht="15.75" customHeight="1"/>
-    <row r="495" ht="15.75" customHeight="1"/>
-    <row r="496" ht="15.75" customHeight="1"/>
-    <row r="497" ht="15.75" customHeight="1"/>
-    <row r="498" ht="15.75" customHeight="1"/>
-    <row r="499" ht="15.75" customHeight="1"/>
-    <row r="500" ht="15.75" customHeight="1"/>
-    <row r="501" ht="15.75" customHeight="1"/>
-    <row r="502" ht="15.75" customHeight="1"/>
-    <row r="503" ht="15.75" customHeight="1"/>
-    <row r="504" ht="15.75" customHeight="1"/>
-    <row r="505" ht="15.75" customHeight="1"/>
-    <row r="506" ht="15.75" customHeight="1"/>
-    <row r="507" ht="15.75" customHeight="1"/>
-    <row r="508" ht="15.75" customHeight="1"/>
-    <row r="509" ht="15.75" customHeight="1"/>
-    <row r="510" ht="15.75" customHeight="1"/>
-    <row r="511" ht="15.75" customHeight="1"/>
-    <row r="512" ht="15.75" customHeight="1"/>
-    <row r="513" ht="15.75" customHeight="1"/>
-    <row r="514" ht="15.75" customHeight="1"/>
-    <row r="515" ht="15.75" customHeight="1"/>
-    <row r="516" ht="15.75" customHeight="1"/>
-    <row r="517" ht="15.75" customHeight="1"/>
-    <row r="518" ht="15.75" customHeight="1"/>
-    <row r="519" ht="15.75" customHeight="1"/>
-    <row r="520" ht="15.75" customHeight="1"/>
-    <row r="521" ht="15.75" customHeight="1"/>
-    <row r="522" ht="15.75" customHeight="1"/>
-    <row r="523" ht="15.75" customHeight="1"/>
-    <row r="524" ht="15.75" customHeight="1"/>
-    <row r="525" ht="15.75" customHeight="1"/>
-    <row r="526" ht="15.75" customHeight="1"/>
-    <row r="527" ht="15.75" customHeight="1"/>
-    <row r="528" ht="15.75" customHeight="1"/>
-    <row r="529" ht="15.75" customHeight="1"/>
-    <row r="530" ht="15.75" customHeight="1"/>
-    <row r="531" ht="15.75" customHeight="1"/>
-    <row r="532" ht="15.75" customHeight="1"/>
-    <row r="533" ht="15.75" customHeight="1"/>
-    <row r="534" ht="15.75" customHeight="1"/>
-    <row r="535" ht="15.75" customHeight="1"/>
-    <row r="536" ht="15.75" customHeight="1"/>
-    <row r="537" ht="15.75" customHeight="1"/>
-    <row r="538" ht="15.75" customHeight="1"/>
-    <row r="539" ht="15.75" customHeight="1"/>
-    <row r="540" ht="15.75" customHeight="1"/>
-    <row r="541" ht="15.75" customHeight="1"/>
-    <row r="542" ht="15.75" customHeight="1"/>
-    <row r="543" ht="15.75" customHeight="1"/>
-    <row r="544" ht="15.75" customHeight="1"/>
-    <row r="545" ht="15.75" customHeight="1"/>
-    <row r="546" ht="15.75" customHeight="1"/>
-    <row r="547" ht="15.75" customHeight="1"/>
-    <row r="548" ht="15.75" customHeight="1"/>
-    <row r="549" ht="15.75" customHeight="1"/>
-    <row r="550" ht="15.75" customHeight="1"/>
-    <row r="551" ht="15.75" customHeight="1"/>
-    <row r="552" ht="15.75" customHeight="1"/>
-    <row r="553" ht="15.75" customHeight="1"/>
-    <row r="554" ht="15.75" customHeight="1"/>
-    <row r="555" ht="15.75" customHeight="1"/>
-    <row r="556" ht="15.75" customHeight="1"/>
-    <row r="557" ht="15.75" customHeight="1"/>
-    <row r="558" ht="15.75" customHeight="1"/>
-    <row r="559" ht="15.75" customHeight="1"/>
-    <row r="560" ht="15.75" customHeight="1"/>
-    <row r="561" ht="15.75" customHeight="1"/>
-    <row r="562" ht="15.75" customHeight="1"/>
-    <row r="563" ht="15.75" customHeight="1"/>
-    <row r="564" ht="15.75" customHeight="1"/>
-    <row r="565" ht="15.75" customHeight="1"/>
-    <row r="566" ht="15.75" customHeight="1"/>
-    <row r="567" ht="15.75" customHeight="1"/>
-    <row r="568" ht="15.75" customHeight="1"/>
-    <row r="569" ht="15.75" customHeight="1"/>
-    <row r="570" ht="15.75" customHeight="1"/>
-    <row r="571" ht="15.75" customHeight="1"/>
-    <row r="572" ht="15.75" customHeight="1"/>
-    <row r="573" ht="15.75" customHeight="1"/>
-    <row r="574" ht="15.75" customHeight="1"/>
-    <row r="575" ht="15.75" customHeight="1"/>
-    <row r="576" ht="15.75" customHeight="1"/>
-    <row r="577" ht="15.75" customHeight="1"/>
-    <row r="578" ht="15.75" customHeight="1"/>
-    <row r="579" ht="15.75" customHeight="1"/>
-    <row r="580" ht="15.75" customHeight="1"/>
-    <row r="581" ht="15.75" customHeight="1"/>
-    <row r="582" ht="15.75" customHeight="1"/>
-    <row r="583" ht="15.75" customHeight="1"/>
-    <row r="584" ht="15.75" customHeight="1"/>
-    <row r="585" ht="15.75" customHeight="1"/>
-    <row r="586" ht="15.75" customHeight="1"/>
-    <row r="587" ht="15.75" customHeight="1"/>
-    <row r="588" ht="15.75" customHeight="1"/>
-    <row r="589" ht="15.75" customHeight="1"/>
-    <row r="590" ht="15.75" customHeight="1"/>
-    <row r="591" ht="15.75" customHeight="1"/>
-    <row r="592" ht="15.75" customHeight="1"/>
-    <row r="593" ht="15.75" customHeight="1"/>
-    <row r="594" ht="15.75" customHeight="1"/>
-    <row r="595" ht="15.75" customHeight="1"/>
-    <row r="596" ht="15.75" customHeight="1"/>
-    <row r="597" ht="15.75" customHeight="1"/>
-    <row r="598" ht="15.75" customHeight="1"/>
-    <row r="599" ht="15.75" customHeight="1"/>
-    <row r="600" ht="15.75" customHeight="1"/>
-    <row r="601" ht="15.75" customHeight="1"/>
-    <row r="602" ht="15.75" customHeight="1"/>
-    <row r="603" ht="15.75" customHeight="1"/>
-    <row r="604" ht="15.75" customHeight="1"/>
-    <row r="605" ht="15.75" customHeight="1"/>
-    <row r="606" ht="15.75" customHeight="1"/>
-    <row r="607" ht="15.75" customHeight="1"/>
-    <row r="608" ht="15.75" customHeight="1"/>
-    <row r="609" ht="15.75" customHeight="1"/>
-    <row r="610" ht="15.75" customHeight="1"/>
-    <row r="611" ht="15.75" customHeight="1"/>
-    <row r="612" ht="15.75" customHeight="1"/>
-    <row r="613" ht="15.75" customHeight="1"/>
-    <row r="614" ht="15.75" customHeight="1"/>
-    <row r="615" ht="15.75" customHeight="1"/>
-    <row r="616" ht="15.75" customHeight="1"/>
-    <row r="617" ht="15.75" customHeight="1"/>
-    <row r="618" ht="15.75" customHeight="1"/>
-    <row r="619" ht="15.75" customHeight="1"/>
-    <row r="620" ht="15.75" customHeight="1"/>
-    <row r="621" ht="15.75" customHeight="1"/>
-    <row r="622" ht="15.75" customHeight="1"/>
-    <row r="623" ht="15.75" customHeight="1"/>
-    <row r="624" ht="15.75" customHeight="1"/>
-    <row r="625" ht="15.75" customHeight="1"/>
-    <row r="626" ht="15.75" customHeight="1"/>
-    <row r="627" ht="15.75" customHeight="1"/>
-    <row r="628" ht="15.75" customHeight="1"/>
-    <row r="629" ht="15.75" customHeight="1"/>
-    <row r="630" ht="15.75" customHeight="1"/>
-    <row r="631" ht="15.75" customHeight="1"/>
-    <row r="632" ht="15.75" customHeight="1"/>
-    <row r="633" ht="15.75" customHeight="1"/>
-    <row r="634" ht="15.75" customHeight="1"/>
-    <row r="635" ht="15.75" customHeight="1"/>
-    <row r="636" ht="15.75" customHeight="1"/>
-    <row r="637" ht="15.75" customHeight="1"/>
-    <row r="638" ht="15.75" customHeight="1"/>
-    <row r="639" ht="15.75" customHeight="1"/>
-    <row r="640" ht="15.75" customHeight="1"/>
-    <row r="641" ht="15.75" customHeight="1"/>
-    <row r="642" ht="15.75" customHeight="1"/>
-    <row r="643" ht="15.75" customHeight="1"/>
-    <row r="644" ht="15.75" customHeight="1"/>
-    <row r="645" ht="15.75" customHeight="1"/>
-    <row r="646" ht="15.75" customHeight="1"/>
-    <row r="647" ht="15.75" customHeight="1"/>
-    <row r="648" ht="15.75" customHeight="1"/>
-    <row r="649" ht="15.75" customHeight="1"/>
-    <row r="650" ht="15.75" customHeight="1"/>
-    <row r="651" ht="15.75" customHeight="1"/>
-    <row r="652" ht="15.75" customHeight="1"/>
-    <row r="653" ht="15.75" customHeight="1"/>
-    <row r="654" ht="15.75" customHeight="1"/>
-    <row r="655" ht="15.75" customHeight="1"/>
-    <row r="656" ht="15.75" customHeight="1"/>
-    <row r="657" ht="15.75" customHeight="1"/>
-    <row r="658" ht="15.75" customHeight="1"/>
-    <row r="659" ht="15.75" customHeight="1"/>
-    <row r="660" ht="15.75" customHeight="1"/>
-    <row r="661" ht="15.75" customHeight="1"/>
-    <row r="662" ht="15.75" customHeight="1"/>
-    <row r="663" ht="15.75" customHeight="1"/>
-    <row r="664" ht="15.75" customHeight="1"/>
-    <row r="665" ht="15.75" customHeight="1"/>
-    <row r="666" ht="15.75" customHeight="1"/>
-    <row r="667" ht="15.75" customHeight="1"/>
-    <row r="668" ht="15.75" customHeight="1"/>
-    <row r="669" ht="15.75" customHeight="1"/>
-    <row r="670" ht="15.75" customHeight="1"/>
-    <row r="671" ht="15.75" customHeight="1"/>
-    <row r="672" ht="15.75" customHeight="1"/>
-    <row r="673" ht="15.75" customHeight="1"/>
-    <row r="674" ht="15.75" customHeight="1"/>
-    <row r="675" ht="15.75" customHeight="1"/>
-    <row r="676" ht="15.75" customHeight="1"/>
-    <row r="677" ht="15.75" customHeight="1"/>
-    <row r="678" ht="15.75" customHeight="1"/>
-    <row r="679" ht="15.75" customHeight="1"/>
-    <row r="680" ht="15.75" customHeight="1"/>
-    <row r="681" ht="15.75" customHeight="1"/>
-    <row r="682" ht="15.75" customHeight="1"/>
-    <row r="683" ht="15.75" customHeight="1"/>
-    <row r="684" ht="15.75" customHeight="1"/>
-    <row r="685" ht="15.75" customHeight="1"/>
-    <row r="686" ht="15.75" customHeight="1"/>
-    <row r="687" ht="15.75" customHeight="1"/>
-    <row r="688" ht="15.75" customHeight="1"/>
-    <row r="689" ht="15.75" customHeight="1"/>
-    <row r="690" ht="15.75" customHeight="1"/>
-    <row r="691" ht="15.75" customHeight="1"/>
-    <row r="692" ht="15.75" customHeight="1"/>
-    <row r="693" ht="15.75" customHeight="1"/>
-    <row r="694" ht="15.75" customHeight="1"/>
-    <row r="695" ht="15.75" customHeight="1"/>
-    <row r="696" ht="15.75" customHeight="1"/>
-    <row r="697" ht="15.75" customHeight="1"/>
-    <row r="698" ht="15.75" customHeight="1"/>
-    <row r="699" ht="15.75" customHeight="1"/>
-    <row r="700" ht="15.75" customHeight="1"/>
-    <row r="701" ht="15.75" customHeight="1"/>
-    <row r="702" ht="15.75" customHeight="1"/>
-    <row r="703" ht="15.75" customHeight="1"/>
-    <row r="704" ht="15.75" customHeight="1"/>
-    <row r="705" ht="15.75" customHeight="1"/>
-    <row r="706" ht="15.75" customHeight="1"/>
-    <row r="707" ht="15.75" customHeight="1"/>
-    <row r="708" ht="15.75" customHeight="1"/>
-    <row r="709" ht="15.75" customHeight="1"/>
-    <row r="710" ht="15.75" customHeight="1"/>
-    <row r="711" ht="15.75" customHeight="1"/>
-    <row r="712" ht="15.75" customHeight="1"/>
-    <row r="713" ht="15.75" customHeight="1"/>
-    <row r="714" ht="15.75" customHeight="1"/>
-    <row r="715" ht="15.75" customHeight="1"/>
-    <row r="716" ht="15.75" customHeight="1"/>
-    <row r="717" ht="15.75" customHeight="1"/>
-    <row r="718" ht="15.75" customHeight="1"/>
-    <row r="719" ht="15.75" customHeight="1"/>
-    <row r="720" ht="15.75" customHeight="1"/>
-    <row r="721" ht="15.75" customHeight="1"/>
-    <row r="722" ht="15.75" customHeight="1"/>
-    <row r="723" ht="15.75" customHeight="1"/>
-    <row r="724" ht="15.75" customHeight="1"/>
-    <row r="725" ht="15.75" customHeight="1"/>
-    <row r="726" ht="15.75" customHeight="1"/>
-    <row r="727" ht="15.75" customHeight="1"/>
-    <row r="728" ht="15.75" customHeight="1"/>
-    <row r="729" ht="15.75" customHeight="1"/>
-    <row r="730" ht="15.75" customHeight="1"/>
-    <row r="731" ht="15.75" customHeight="1"/>
-    <row r="732" ht="15.75" customHeight="1"/>
-    <row r="733" ht="15.75" customHeight="1"/>
-    <row r="734" ht="15.75" customHeight="1"/>
-    <row r="735" ht="15.75" customHeight="1"/>
-    <row r="736" ht="15.75" customHeight="1"/>
-    <row r="737" ht="15.75" customHeight="1"/>
-    <row r="738" ht="15.75" customHeight="1"/>
-    <row r="739" ht="15.75" customHeight="1"/>
-    <row r="740" ht="15.75" customHeight="1"/>
-    <row r="741" ht="15.75" customHeight="1"/>
-    <row r="742" ht="15.75" customHeight="1"/>
-    <row r="743" ht="15.75" customHeight="1"/>
-    <row r="744" ht="15.75" customHeight="1"/>
-    <row r="745" ht="15.75" customHeight="1"/>
-    <row r="746" ht="15.75" customHeight="1"/>
-    <row r="747" ht="15.75" customHeight="1"/>
-    <row r="748" ht="15.75" customHeight="1"/>
-    <row r="749" ht="15.75" customHeight="1"/>
-    <row r="750" ht="15.75" customHeight="1"/>
-    <row r="751" ht="15.75" customHeight="1"/>
-    <row r="752" ht="15.75" customHeight="1"/>
-    <row r="753" ht="15.75" customHeight="1"/>
-    <row r="754" ht="15.75" customHeight="1"/>
-    <row r="755" ht="15.75" customHeight="1"/>
-    <row r="756" ht="15.75" customHeight="1"/>
-    <row r="757" ht="15.75" customHeight="1"/>
-    <row r="758" ht="15.75" customHeight="1"/>
-    <row r="759" ht="15.75" customHeight="1"/>
-    <row r="760" ht="15.75" customHeight="1"/>
-    <row r="761" ht="15.75" customHeight="1"/>
-    <row r="762" ht="15.75" customHeight="1"/>
-    <row r="763" ht="15.75" customHeight="1"/>
-    <row r="764" ht="15.75" customHeight="1"/>
-    <row r="765" ht="15.75" customHeight="1"/>
-    <row r="766" ht="15.75" customHeight="1"/>
-    <row r="767" ht="15.75" customHeight="1"/>
-    <row r="768" ht="15.75" customHeight="1"/>
-    <row r="769" ht="15.75" customHeight="1"/>
-    <row r="770" ht="15.75" customHeight="1"/>
-    <row r="771" ht="15.75" customHeight="1"/>
-    <row r="772" ht="15.75" customHeight="1"/>
-    <row r="773" ht="15.75" customHeight="1"/>
-    <row r="774" ht="15.75" customHeight="1"/>
-    <row r="775" ht="15.75" customHeight="1"/>
-    <row r="776" ht="15.75" customHeight="1"/>
-    <row r="777" ht="15.75" customHeight="1"/>
-    <row r="778" ht="15.75" customHeight="1"/>
-    <row r="779" ht="15.75" customHeight="1"/>
-    <row r="780" ht="15.75" customHeight="1"/>
-    <row r="781" ht="15.75" customHeight="1"/>
-    <row r="782" ht="15.75" customHeight="1"/>
-    <row r="783" ht="15.75" customHeight="1"/>
-    <row r="784" ht="15.75" customHeight="1"/>
-    <row r="785" ht="15.75" customHeight="1"/>
-    <row r="786" ht="15.75" customHeight="1"/>
-    <row r="787" ht="15.75" customHeight="1"/>
-    <row r="788" ht="15.75" customHeight="1"/>
-    <row r="789" ht="15.75" customHeight="1"/>
-    <row r="790" ht="15.75" customHeight="1"/>
-    <row r="791" ht="15.75" customHeight="1"/>
-    <row r="792" ht="15.75" customHeight="1"/>
-    <row r="793" ht="15.75" customHeight="1"/>
-    <row r="794" ht="15.75" customHeight="1"/>
-    <row r="795" ht="15.75" customHeight="1"/>
-    <row r="796" ht="15.75" customHeight="1"/>
-    <row r="797" ht="15.75" customHeight="1"/>
-    <row r="798" ht="15.75" customHeight="1"/>
-    <row r="799" ht="15.75" customHeight="1"/>
-    <row r="800" ht="15.75" customHeight="1"/>
-    <row r="801" ht="15.75" customHeight="1"/>
-    <row r="802" ht="15.75" customHeight="1"/>
-    <row r="803" ht="15.75" customHeight="1"/>
-    <row r="804" ht="15.75" customHeight="1"/>
-    <row r="805" ht="15.75" customHeight="1"/>
-    <row r="806" ht="15.75" customHeight="1"/>
-    <row r="807" ht="15.75" customHeight="1"/>
-    <row r="808" ht="15.75" customHeight="1"/>
-    <row r="809" ht="15.75" customHeight="1"/>
-    <row r="810" ht="15.75" customHeight="1"/>
-    <row r="811" ht="15.75" customHeight="1"/>
-    <row r="812" ht="15.75" customHeight="1"/>
-    <row r="813" ht="15.75" customHeight="1"/>
-    <row r="814" ht="15.75" customHeight="1"/>
-    <row r="815" ht="15.75" customHeight="1"/>
-    <row r="816" ht="15.75" customHeight="1"/>
-    <row r="817" ht="15.75" customHeight="1"/>
-    <row r="818" ht="15.75" customHeight="1"/>
-    <row r="819" ht="15.75" customHeight="1"/>
-    <row r="820" ht="15.75" customHeight="1"/>
-    <row r="821" ht="15.75" customHeight="1"/>
-    <row r="822" ht="15.75" customHeight="1"/>
-    <row r="823" ht="15.75" customHeight="1"/>
-    <row r="824" ht="15.75" customHeight="1"/>
-    <row r="825" ht="15.75" customHeight="1"/>
-    <row r="826" ht="15.75" customHeight="1"/>
-    <row r="827" ht="15.75" customHeight="1"/>
-    <row r="828" ht="15.75" customHeight="1"/>
-    <row r="829" ht="15.75" customHeight="1"/>
-    <row r="830" ht="15.75" customHeight="1"/>
-    <row r="831" ht="15.75" customHeight="1"/>
-    <row r="832" ht="15.75" customHeight="1"/>
-    <row r="833" ht="15.75" customHeight="1"/>
-    <row r="834" ht="15.75" customHeight="1"/>
-    <row r="835" ht="15.75" customHeight="1"/>
-    <row r="836" ht="15.75" customHeight="1"/>
-    <row r="837" ht="15.75" customHeight="1"/>
-    <row r="838" ht="15.75" customHeight="1"/>
-    <row r="839" ht="15.75" customHeight="1"/>
-    <row r="840" ht="15.75" customHeight="1"/>
-    <row r="841" ht="15.75" customHeight="1"/>
-    <row r="842" ht="15.75" customHeight="1"/>
-    <row r="843" ht="15.75" customHeight="1"/>
-    <row r="844" ht="15.75" customHeight="1"/>
-    <row r="845" ht="15.75" customHeight="1"/>
-    <row r="846" ht="15.75" customHeight="1"/>
-    <row r="847" ht="15.75" customHeight="1"/>
-    <row r="848" ht="15.75" customHeight="1"/>
-    <row r="849" ht="15.75" customHeight="1"/>
-    <row r="850" ht="15.75" customHeight="1"/>
-    <row r="851" ht="15.75" customHeight="1"/>
-    <row r="852" ht="15.75" customHeight="1"/>
-    <row r="853" ht="15.75" customHeight="1"/>
-    <row r="854" ht="15.75" customHeight="1"/>
-    <row r="855" ht="15.75" customHeight="1"/>
-    <row r="856" ht="15.75" customHeight="1"/>
-    <row r="857" ht="15.75" customHeight="1"/>
-    <row r="858" ht="15.75" customHeight="1"/>
-    <row r="859" ht="15.75" customHeight="1"/>
-    <row r="860" ht="15.75" customHeight="1"/>
-    <row r="861" ht="15.75" customHeight="1"/>
-    <row r="862" ht="15.75" customHeight="1"/>
-    <row r="863" ht="15.75" customHeight="1"/>
-    <row r="864" ht="15.75" customHeight="1"/>
-    <row r="865" ht="15.75" customHeight="1"/>
-    <row r="866" ht="15.75" customHeight="1"/>
-    <row r="867" ht="15.75" customHeight="1"/>
-    <row r="868" ht="15.75" customHeight="1"/>
-    <row r="869" ht="15.75" customHeight="1"/>
-    <row r="870" ht="15.75" customHeight="1"/>
-    <row r="871" ht="15.75" customHeight="1"/>
-    <row r="872" ht="15.75" customHeight="1"/>
-    <row r="873" ht="15.75" customHeight="1"/>
-    <row r="874" ht="15.75" customHeight="1"/>
-    <row r="875" ht="15.75" customHeight="1"/>
-    <row r="876" ht="15.75" customHeight="1"/>
-    <row r="877" ht="15.75" customHeight="1"/>
-    <row r="878" ht="15.75" customHeight="1"/>
-    <row r="879" ht="15.75" customHeight="1"/>
-    <row r="880" ht="15.75" customHeight="1"/>
-    <row r="881" ht="15.75" customHeight="1"/>
-    <row r="882" ht="15.75" customHeight="1"/>
-    <row r="883" ht="15.75" customHeight="1"/>
-    <row r="884" ht="15.75" customHeight="1"/>
-    <row r="885" ht="15.75" customHeight="1"/>
-    <row r="886" ht="15.75" customHeight="1"/>
-    <row r="887" ht="15.75" customHeight="1"/>
-    <row r="888" ht="15.75" customHeight="1"/>
-    <row r="889" ht="15.75" customHeight="1"/>
-    <row r="890" ht="15.75" customHeight="1"/>
-    <row r="891" ht="15.75" customHeight="1"/>
-    <row r="892" ht="15.75" customHeight="1"/>
-    <row r="893" ht="15.75" customHeight="1"/>
-    <row r="894" ht="15.75" customHeight="1"/>
-    <row r="895" ht="15.75" customHeight="1"/>
-    <row r="896" ht="15.75" customHeight="1"/>
-    <row r="897" ht="15.75" customHeight="1"/>
-    <row r="898" ht="15.75" customHeight="1"/>
-    <row r="899" ht="15.75" customHeight="1"/>
-    <row r="900" ht="15.75" customHeight="1"/>
-    <row r="901" ht="15.75" customHeight="1"/>
-    <row r="902" ht="15.75" customHeight="1"/>
-    <row r="903" ht="15.75" customHeight="1"/>
-    <row r="904" ht="15.75" customHeight="1"/>
-    <row r="905" ht="15.75" customHeight="1"/>
-    <row r="906" ht="15.75" customHeight="1"/>
-    <row r="907" ht="15.75" customHeight="1"/>
-    <row r="908" ht="15.75" customHeight="1"/>
-    <row r="909" ht="15.75" customHeight="1"/>
-    <row r="910" ht="15.75" customHeight="1"/>
-    <row r="911" ht="15.75" customHeight="1"/>
-    <row r="912" ht="15.75" customHeight="1"/>
-    <row r="913" ht="15.75" customHeight="1"/>
-    <row r="914" ht="15.75" customHeight="1"/>
-    <row r="915" ht="15.75" customHeight="1"/>
-    <row r="916" ht="15.75" customHeight="1"/>
-    <row r="917" ht="15.75" customHeight="1"/>
-    <row r="918" ht="15.75" customHeight="1"/>
-    <row r="919" ht="15.75" customHeight="1"/>
-    <row r="920" ht="15.75" customHeight="1"/>
-    <row r="921" ht="15.75" customHeight="1"/>
-    <row r="922" ht="15.75" customHeight="1"/>
-    <row r="923" ht="15.75" customHeight="1"/>
-    <row r="924" ht="15.75" customHeight="1"/>
-    <row r="925" ht="15.75" customHeight="1"/>
-    <row r="926" ht="15.75" customHeight="1"/>
-    <row r="927" ht="15.75" customHeight="1"/>
-    <row r="928" ht="15.75" customHeight="1"/>
-    <row r="929" ht="15.75" customHeight="1"/>
-    <row r="930" ht="15.75" customHeight="1"/>
-    <row r="931" ht="15.75" customHeight="1"/>
-    <row r="932" ht="15.75" customHeight="1"/>
-    <row r="933" ht="15.75" customHeight="1"/>
-    <row r="934" ht="15.75" customHeight="1"/>
-    <row r="935" ht="15.75" customHeight="1"/>
-    <row r="936" ht="15.75" customHeight="1"/>
-    <row r="937" ht="15.75" customHeight="1"/>
-    <row r="938" ht="15.75" customHeight="1"/>
-    <row r="939" ht="15.75" customHeight="1"/>
-    <row r="940" ht="15.75" customHeight="1"/>
-    <row r="941" ht="15.75" customHeight="1"/>
-    <row r="942" ht="15.75" customHeight="1"/>
-    <row r="943" ht="15.75" customHeight="1"/>
-    <row r="944" ht="15.75" customHeight="1"/>
-    <row r="945" ht="15.75" customHeight="1"/>
-    <row r="946" ht="15.75" customHeight="1"/>
-    <row r="947" ht="15.75" customHeight="1"/>
-    <row r="948" ht="15.75" customHeight="1"/>
-    <row r="949" ht="15.75" customHeight="1"/>
-    <row r="950" ht="15.75" customHeight="1"/>
-    <row r="951" ht="15.75" customHeight="1"/>
-    <row r="952" ht="15.75" customHeight="1"/>
-    <row r="953" ht="15.75" customHeight="1"/>
-    <row r="954" ht="15.75" customHeight="1"/>
-    <row r="955" ht="15.75" customHeight="1"/>
-    <row r="956" ht="15.75" customHeight="1"/>
-    <row r="957" ht="15.75" customHeight="1"/>
-    <row r="958" ht="15.75" customHeight="1"/>
-    <row r="959" ht="15.75" customHeight="1"/>
-    <row r="960" ht="15.75" customHeight="1"/>
-    <row r="961" ht="15.75" customHeight="1"/>
-    <row r="962" ht="15.75" customHeight="1"/>
-    <row r="963" ht="15.75" customHeight="1"/>
-    <row r="964" ht="15.75" customHeight="1"/>
-    <row r="965" ht="15.75" customHeight="1"/>
-    <row r="966" ht="15.75" customHeight="1"/>
-    <row r="967" ht="15.75" customHeight="1"/>
-    <row r="968" ht="15.75" customHeight="1"/>
-    <row r="969" ht="15.75" customHeight="1"/>
-    <row r="970" ht="15.75" customHeight="1"/>
-    <row r="971" ht="15.75" customHeight="1"/>
-    <row r="972" ht="15.75" customHeight="1"/>
-    <row r="973" ht="15.75" customHeight="1"/>
-    <row r="974" ht="15.75" customHeight="1"/>
-    <row r="975" ht="15.75" customHeight="1"/>
-    <row r="976" ht="15.75" customHeight="1"/>
-    <row r="977" ht="15.75" customHeight="1"/>
-    <row r="978" ht="15.75" customHeight="1"/>
-    <row r="979" ht="15.75" customHeight="1"/>
-    <row r="980" ht="15.75" customHeight="1"/>
-    <row r="981" ht="15.75" customHeight="1"/>
-    <row r="982" ht="15.75" customHeight="1"/>
-    <row r="983" ht="15.75" customHeight="1"/>
-    <row r="984" ht="15.75" customHeight="1"/>
-    <row r="985" ht="15.75" customHeight="1"/>
-    <row r="986" ht="15.75" customHeight="1"/>
-    <row r="987" ht="15.75" customHeight="1"/>
-    <row r="988" ht="15.75" customHeight="1"/>
-    <row r="989" ht="15.75" customHeight="1"/>
-    <row r="990" ht="15.75" customHeight="1"/>
-    <row r="991" ht="15.75" customHeight="1"/>
-    <row r="992" ht="15.75" customHeight="1"/>
-    <row r="993" ht="15.75" customHeight="1"/>
-    <row r="994" ht="15.75" customHeight="1"/>
-    <row r="995" ht="15.75" customHeight="1"/>
-    <row r="996" ht="15.75" customHeight="1"/>
-    <row r="997" ht="15.75" customHeight="1"/>
-    <row r="998" ht="15.75" customHeight="1"/>
-    <row r="999" ht="15.75" customHeight="1"/>
-    <row r="1000" ht="15.75" customHeight="1"/>
-  </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A3:J3"/>
-    <mergeCell ref="A6:J6"/>
-    <mergeCell ref="A10:J10"/>
-  </mergeCells>
-  <conditionalFormatting sqref="H4:H5 H7:H9 H11:H15">
-    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="✅ PASS">
-      <formula>NOT(ISERROR(SEARCH(("✅ PASS"),(H4))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H4:H5 H7:H9 H11:H15">
-    <cfRule type="containsText" dxfId="4" priority="2" operator="containsText" text="❌ FAIL">
-      <formula>NOT(ISERROR(SEARCH(("❌ FAIL"),(H4))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H4:H5 H7:H9 H11:H15">
-    <cfRule type="containsText" dxfId="2" priority="3" operator="containsText" text="⏳ PENDING">
-      <formula>NOT(ISERROR(SEARCH(("⏳ PENDING"),(H4))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <dataValidations>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="H4:H5 H7:H9 H11:H15">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="H4:H5 H7:H10 H12:H16">
       <formula1>"⏳ PENDIENTE,✅ PASS,❌ FAIL"</formula1>
     </dataValidation>
   </dataValidations>
@@ -16203,7 +16356,7 @@
   <sheetData>
     <row r="1" ht="24.0" customHeight="1">
       <c r="A1" s="27" t="s">
-        <v>386</v>
+        <v>400</v>
       </c>
       <c r="B1" s="28"/>
       <c r="C1" s="28"/>
@@ -16249,7 +16402,7 @@
     </row>
     <row r="3" ht="18.0" customHeight="1">
       <c r="A3" s="29" t="s">
-        <v>387</v>
+        <v>401</v>
       </c>
       <c r="B3" s="30"/>
       <c r="C3" s="30"/>
@@ -16263,67 +16416,67 @@
     </row>
     <row r="4" ht="42.0" customHeight="1">
       <c r="A4" s="23" t="s">
-        <v>388</v>
+        <v>402</v>
       </c>
       <c r="B4" s="21" t="s">
-        <v>389</v>
+        <v>403</v>
       </c>
       <c r="C4" s="43" t="s">
         <v>139</v>
       </c>
       <c r="D4" s="21" t="s">
-        <v>390</v>
+        <v>404</v>
       </c>
       <c r="E4" s="21" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="F4" s="21" t="s">
         <v>141</v>
       </c>
       <c r="G4" s="21" t="s">
-        <v>391</v>
+        <v>405</v>
       </c>
       <c r="H4" s="33" t="s">
         <v>70</v>
       </c>
       <c r="I4" s="21" t="s">
-        <v>392</v>
+        <v>406</v>
       </c>
       <c r="J4" s="23"/>
     </row>
     <row r="5" ht="42.0" customHeight="1">
       <c r="A5" s="34" t="s">
-        <v>393</v>
+        <v>407</v>
       </c>
       <c r="B5" s="20" t="s">
-        <v>394</v>
+        <v>408</v>
       </c>
       <c r="C5" s="36" t="s">
         <v>139</v>
       </c>
       <c r="D5" s="20" t="s">
-        <v>390</v>
+        <v>404</v>
       </c>
       <c r="E5" s="20" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="F5" s="20" t="s">
         <v>141</v>
       </c>
       <c r="G5" s="20" t="s">
-        <v>395</v>
+        <v>409</v>
       </c>
       <c r="H5" s="33" t="s">
         <v>70</v>
       </c>
       <c r="I5" s="20" t="s">
-        <v>396</v>
+        <v>410</v>
       </c>
       <c r="J5" s="34"/>
     </row>
     <row r="6" ht="18.0" customHeight="1">
       <c r="A6" s="29" t="s">
-        <v>397</v>
+        <v>411</v>
       </c>
       <c r="B6" s="30"/>
       <c r="C6" s="30"/>
@@ -16337,88 +16490,88 @@
     </row>
     <row r="7" ht="42.0" customHeight="1">
       <c r="A7" s="23" t="s">
-        <v>398</v>
+        <v>412</v>
       </c>
       <c r="B7" s="21" t="s">
-        <v>399</v>
+        <v>413</v>
       </c>
       <c r="C7" s="32" t="s">
         <v>97</v>
       </c>
       <c r="D7" s="21" t="s">
-        <v>400</v>
+        <v>414</v>
       </c>
       <c r="E7" s="21" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="F7" s="21" t="str">
         <f>Variables!C12</f>
         <v>967092f8-fb6a-4db2-af08-d77fa4540610</v>
       </c>
       <c r="G7" s="21" t="s">
-        <v>401</v>
+        <v>415</v>
       </c>
       <c r="H7" s="33" t="s">
         <v>70</v>
       </c>
       <c r="I7" s="21" t="s">
-        <v>402</v>
+        <v>416</v>
       </c>
       <c r="J7" s="23"/>
     </row>
     <row r="8" ht="42.0" customHeight="1">
       <c r="A8" s="34" t="s">
-        <v>403</v>
+        <v>417</v>
       </c>
       <c r="B8" s="20" t="s">
-        <v>404</v>
+        <v>418</v>
       </c>
       <c r="C8" s="35" t="s">
         <v>97</v>
       </c>
       <c r="D8" s="20" t="s">
-        <v>405</v>
+        <v>419</v>
       </c>
       <c r="E8" s="20" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="F8" s="20" t="str">
         <f>Variables!C13</f>
         <v>5df1bedc-a8b4-4cb2-9a9a-7b3d60252582</v>
       </c>
       <c r="G8" s="20" t="s">
-        <v>406</v>
+        <v>420</v>
       </c>
       <c r="H8" s="33" t="s">
         <v>70</v>
       </c>
       <c r="I8" s="20" t="s">
-        <v>407</v>
+        <v>421</v>
       </c>
       <c r="J8" s="34"/>
     </row>
     <row r="9" ht="42.0" customHeight="1">
       <c r="A9" s="23" t="s">
-        <v>408</v>
+        <v>422</v>
       </c>
       <c r="B9" s="21" t="s">
-        <v>409</v>
+        <v>423</v>
       </c>
       <c r="C9" s="32" t="s">
         <v>97</v>
       </c>
       <c r="D9" s="21" t="s">
-        <v>405</v>
+        <v>419</v>
       </c>
       <c r="E9" s="21" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="F9" s="21" t="str">
         <f>Variables!C13</f>
         <v>5df1bedc-a8b4-4cb2-9a9a-7b3d60252582</v>
       </c>
       <c r="G9" s="21" t="s">
-        <v>410</v>
+        <v>424</v>
       </c>
       <c r="H9" s="33" t="s">
         <v>70</v>
@@ -16428,26 +16581,26 @@
     </row>
     <row r="10" ht="42.0" customHeight="1">
       <c r="A10" s="34" t="s">
-        <v>411</v>
+        <v>425</v>
       </c>
       <c r="B10" s="20" t="s">
-        <v>412</v>
+        <v>426</v>
       </c>
       <c r="C10" s="35" t="s">
         <v>97</v>
       </c>
       <c r="D10" s="20" t="s">
-        <v>405</v>
+        <v>419</v>
       </c>
       <c r="E10" s="20" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="F10" s="20" t="str">
         <f>Variables!C12</f>
         <v>967092f8-fb6a-4db2-af08-d77fa4540610</v>
       </c>
       <c r="G10" s="20" t="s">
-        <v>410</v>
+        <v>424</v>
       </c>
       <c r="H10" s="33" t="s">
         <v>70</v>
@@ -16457,7 +16610,7 @@
     </row>
     <row r="11" ht="18.0" customHeight="1">
       <c r="A11" s="29" t="s">
-        <v>413</v>
+        <v>427</v>
       </c>
       <c r="B11" s="30"/>
       <c r="C11" s="30"/>
@@ -16471,26 +16624,26 @@
     </row>
     <row r="12" ht="42.0" customHeight="1">
       <c r="A12" s="23" t="s">
-        <v>414</v>
+        <v>428</v>
       </c>
       <c r="B12" s="21" t="s">
-        <v>415</v>
+        <v>429</v>
       </c>
       <c r="C12" s="43" t="s">
         <v>139</v>
       </c>
       <c r="D12" s="21" t="s">
-        <v>416</v>
+        <v>430</v>
       </c>
       <c r="E12" s="21" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="F12" s="21" t="str">
         <f>Variables!C8</f>
         <v>c7cf918d-7e04-4104-9790-fa5bb9d3756d</v>
       </c>
       <c r="G12" s="21" t="s">
-        <v>417</v>
+        <v>431</v>
       </c>
       <c r="H12" s="33" t="s">
         <v>70</v>
@@ -16500,25 +16653,25 @@
     </row>
     <row r="13" ht="42.0" customHeight="1">
       <c r="A13" s="34" t="s">
-        <v>418</v>
+        <v>432</v>
       </c>
       <c r="B13" s="20" t="s">
-        <v>419</v>
+        <v>433</v>
       </c>
       <c r="C13" s="36" t="s">
         <v>139</v>
       </c>
       <c r="D13" s="20" t="s">
-        <v>420</v>
+        <v>434</v>
       </c>
       <c r="E13" s="20" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="F13" s="20" t="s">
         <v>141</v>
       </c>
       <c r="G13" s="20" t="s">
-        <v>421</v>
+        <v>435</v>
       </c>
       <c r="H13" s="33" t="s">
         <v>70</v>
@@ -16528,32 +16681,32 @@
     </row>
     <row r="14" ht="42.0" customHeight="1">
       <c r="A14" s="23" t="s">
-        <v>422</v>
+        <v>436</v>
       </c>
       <c r="B14" s="21" t="s">
-        <v>423</v>
+        <v>437</v>
       </c>
       <c r="C14" s="32" t="s">
         <v>97</v>
       </c>
       <c r="D14" s="21" t="s">
-        <v>424</v>
+        <v>438</v>
       </c>
       <c r="E14" s="21" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="F14" s="21" t="str">
         <f>Variables!C8</f>
         <v>c7cf918d-7e04-4104-9790-fa5bb9d3756d</v>
       </c>
       <c r="G14" s="21" t="s">
-        <v>425</v>
+        <v>439</v>
       </c>
       <c r="H14" s="33" t="s">
         <v>70</v>
       </c>
       <c r="I14" s="21" t="s">
-        <v>426</v>
+        <v>440</v>
       </c>
       <c r="J14" s="23"/>
     </row>

--- a/community-help-api/docs/api/community-help-api-test.xlsx
+++ b/community-help-api/docs/api/community-help-api-test.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="992" uniqueCount="534">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1010" uniqueCount="541">
   <si>
     <t>Community Help API — Plan de Pruebas Swagger</t>
   </si>
@@ -854,6 +854,18 @@
     <t>HR-03</t>
   </si>
   <si>
+    <t>Crear Help Request 2 Duplicado (User C)</t>
+  </si>
+  <si>
+    <t>409 DUPLICATE</t>
+  </si>
+  <si>
+    <t>You already have an active help request with this title.</t>
+  </si>
+  <si>
+    <t>HR-04</t>
+  </si>
+  <si>
     <t>Crear Help Request con datos inválidos</t>
   </si>
   <si>
@@ -866,7 +878,7 @@
     <t>Consulta</t>
   </si>
   <si>
-    <t>HR-04</t>
+    <t>HR-05</t>
   </si>
   <si>
     <t>Obtener Help Requests abiertas (marketplace)</t>
@@ -878,7 +890,7 @@
     <t>Cualquier usuario puede ver todas las Help Requests con status Open</t>
   </si>
   <si>
-    <t>HR-05</t>
+    <t>HR-06</t>
   </si>
   <si>
     <t>Obtener mis Help Requests (User C)</t>
@@ -893,7 +905,7 @@
     <t>Verificar que devuelve las Help Requests creadas</t>
   </si>
   <si>
-    <t>HR-06</t>
+    <t>HR-07</t>
   </si>
   <si>
     <t>Obtener Help Request por ID</t>
@@ -908,7 +920,7 @@
     <t>Visualizar a Help Request del User C</t>
   </si>
   <si>
-    <t>HR-07</t>
+    <t>HR-08</t>
   </si>
   <si>
     <t>Solicitudes asignadas a mí como voluntario (User A)</t>
@@ -923,7 +935,7 @@
     <t>Visualizar las Help Requests (si las hay) del User.</t>
   </si>
   <si>
-    <t>HR-08</t>
+    <t>HR-09</t>
   </si>
   <si>
     <t>Obtener Help Requests por ID (Admin)</t>
@@ -938,7 +950,7 @@
     <t>Visualizar la Help Request del User como Admin.</t>
   </si>
   <si>
-    <t>HR-09</t>
+    <t>HR-10</t>
   </si>
   <si>
     <t>Obtener Help Requests por estado (Admin)</t>
@@ -956,7 +968,7 @@
     <t>Verificar que devuelve las Help Requests existentes como Admin</t>
   </si>
   <si>
-    <t>HR-10</t>
+    <t>HR-11</t>
   </si>
   <si>
     <t>Obtener Help Request asignadas a un Voluntario (Admin)</t>
@@ -968,7 +980,7 @@
     <t>Visualizar a Help Request del User A (si las tuviera)</t>
   </si>
   <si>
-    <t>HR-11</t>
+    <t>HR-12</t>
   </si>
   <si>
     <t>Obtener Help Requests por ID de otro usuario (User A)</t>
@@ -977,7 +989,7 @@
     <t>403 Forbiden</t>
   </si>
   <si>
-    <t>HR-12</t>
+    <t>HR-13</t>
   </si>
   <si>
     <t>Obtener Help Request cercanas abierta dentro de un radio</t>
@@ -996,7 +1008,7 @@
     <t>Actualización</t>
   </si>
   <si>
-    <t>HR-13</t>
+    <t>HR-14</t>
   </si>
   <si>
     <t>Actualizar título (User C, propietario)</t>
@@ -1011,7 +1023,7 @@
     <t>Verificar cambio y que updated_at fue modificado de fecha</t>
   </si>
   <si>
-    <t>HR-14</t>
+    <t>HR-15</t>
   </si>
   <si>
     <t>Actualizar Help Request de otro usuario (User A)</t>
@@ -1023,7 +1035,7 @@
     <t>Acciones de negocio</t>
   </si>
   <si>
-    <t>HR-15</t>
+    <t>HR-16</t>
   </si>
   <si>
     <t>Cancelar Help Request 2 (User C)</t>
@@ -1038,7 +1050,7 @@
     <t>Verificar que las proposals pendientes también se cancelan</t>
   </si>
   <si>
-    <t>HR-16</t>
+    <t>HR-17</t>
   </si>
   <si>
     <t>Admin — Borrar Help Request</t>
@@ -1095,6 +1107,15 @@
     <t>D-03</t>
   </si>
   <si>
+    <t>Crear Donation 2 — Duplicado (User C)</t>
+  </si>
+  <si>
+    <t>You already have an active donation with this title.</t>
+  </si>
+  <si>
+    <t>D-04</t>
+  </si>
+  <si>
     <t>Obtener mis donaciones (User C)</t>
   </si>
   <si>
@@ -1107,7 +1128,7 @@
     <t>Verificar que devuelve las donaciones creadas</t>
   </si>
   <si>
-    <t>D-04</t>
+    <t>D-05</t>
   </si>
   <si>
     <t>Obtener donación por ID</t>
@@ -1122,7 +1143,7 @@
     <t>Verificar la donación</t>
   </si>
   <si>
-    <t>D-05</t>
+    <t>D-06</t>
   </si>
   <si>
     <t>Mis donaciones filtradas por estado</t>
@@ -1137,7 +1158,7 @@
     <t>Verificar que devuelve las donaciones creadas disponibles</t>
   </si>
   <si>
-    <t>D-06</t>
+    <t>D-07</t>
   </si>
   <si>
     <t>Obtener donaciones disponibles dentro de un radio</t>
@@ -1153,7 +1174,7 @@
     <t>Ciclo de vida completo (Donation 2)</t>
   </si>
   <si>
-    <t>D-07</t>
+    <t>D-08</t>
   </si>
   <si>
     <t>Reservar Donation 2 (User A como voluntario)</t>
@@ -1168,7 +1189,7 @@
     <t>Verificar que la Donation pasa a estar reservada</t>
   </si>
   <si>
-    <t>D-08</t>
+    <t>D-09</t>
   </si>
   <si>
     <t>Confirmar reserva (User C como donante)</t>
@@ -1183,7 +1204,7 @@
     <t>Verificar que la Donation pasa a estar confirmada</t>
   </si>
   <si>
-    <t>D-09</t>
+    <t>D-10</t>
   </si>
   <si>
     <t>Marcar como recogida (User A)</t>
@@ -1198,7 +1219,7 @@
     <t>Verificar que la Donation pasa a estar recogida</t>
   </si>
   <si>
-    <t>D-10</t>
+    <t>D-11</t>
   </si>
   <si>
     <t>Completar donación (User A)</t>
@@ -1213,7 +1234,7 @@
     <t>Verificar que la Donation pasa a estar completa</t>
   </si>
   <si>
-    <t>D-11</t>
+    <t>D-12</t>
   </si>
   <si>
     <t>Cancelar Donation 1 (User C)</t>
@@ -1996,7 +2017,7 @@
       <alignment vertical="center"/>
     </xf>
     <xf borderId="1" fillId="10" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="10" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
@@ -3445,7 +3466,7 @@
   <sheetData>
     <row r="1" ht="24.0" customHeight="1">
       <c r="A1" s="27" t="s">
-        <v>441</v>
+        <v>448</v>
       </c>
       <c r="B1" s="28"/>
       <c r="C1" s="28"/>
@@ -3491,7 +3512,7 @@
     </row>
     <row r="3" ht="18.0" customHeight="1">
       <c r="A3" s="29" t="s">
-        <v>442</v>
+        <v>449</v>
       </c>
       <c r="B3" s="30"/>
       <c r="C3" s="30"/>
@@ -3505,16 +3526,16 @@
     </row>
     <row r="4" ht="42.0" customHeight="1">
       <c r="A4" s="23" t="s">
-        <v>443</v>
+        <v>450</v>
       </c>
       <c r="B4" s="21" t="s">
-        <v>444</v>
+        <v>451</v>
       </c>
       <c r="C4" s="32" t="s">
         <v>97</v>
       </c>
       <c r="D4" s="21" t="s">
-        <v>445</v>
+        <v>452</v>
       </c>
       <c r="E4" s="21" t="s">
         <v>198</v>
@@ -3524,28 +3545,28 @@
         <v>c7cf918d-7e04-4104-9790-fa5bb9d3756d, HELP_REQUEST</v>
       </c>
       <c r="G4" s="21" t="s">
-        <v>446</v>
+        <v>453</v>
       </c>
       <c r="H4" s="33" t="s">
         <v>70</v>
       </c>
       <c r="I4" s="21" t="s">
-        <v>447</v>
+        <v>454</v>
       </c>
       <c r="J4" s="23"/>
     </row>
     <row r="5" ht="42.0" customHeight="1">
       <c r="A5" s="34" t="s">
-        <v>448</v>
+        <v>455</v>
       </c>
       <c r="B5" s="20" t="s">
-        <v>449</v>
+        <v>456</v>
       </c>
       <c r="C5" s="36" t="s">
         <v>139</v>
       </c>
       <c r="D5" s="20" t="s">
-        <v>450</v>
+        <v>457</v>
       </c>
       <c r="E5" s="20" t="s">
         <v>198</v>
@@ -3554,28 +3575,28 @@
         <v>141</v>
       </c>
       <c r="G5" s="20" t="s">
-        <v>451</v>
+        <v>458</v>
       </c>
       <c r="H5" s="33" t="s">
         <v>70</v>
       </c>
       <c r="I5" s="20" t="s">
-        <v>452</v>
+        <v>459</v>
       </c>
       <c r="J5" s="34"/>
     </row>
     <row r="6" ht="42.0" customHeight="1">
       <c r="A6" s="23" t="s">
-        <v>453</v>
+        <v>460</v>
       </c>
       <c r="B6" s="21" t="s">
-        <v>454</v>
+        <v>461</v>
       </c>
       <c r="C6" s="32" t="s">
         <v>97</v>
       </c>
       <c r="D6" s="21" t="s">
-        <v>455</v>
+        <v>462</v>
       </c>
       <c r="E6" s="21" t="s">
         <v>198</v>
@@ -3585,28 +3606,28 @@
         <v>66cce1b2-c3f3-4c17-a0c2-1ab7c4292c37, {"content":"Hola, ¿a qué hora te va bien para la compra?"}</v>
       </c>
       <c r="G6" s="21" t="s">
-        <v>456</v>
+        <v>463</v>
       </c>
       <c r="H6" s="33" t="s">
         <v>70</v>
       </c>
       <c r="I6" s="21" t="s">
-        <v>457</v>
+        <v>464</v>
       </c>
       <c r="J6" s="23"/>
     </row>
     <row r="7" ht="42.0" customHeight="1">
       <c r="A7" s="34" t="s">
-        <v>458</v>
+        <v>465</v>
       </c>
       <c r="B7" s="20" t="s">
-        <v>459</v>
+        <v>466</v>
       </c>
       <c r="C7" s="35" t="s">
         <v>97</v>
       </c>
       <c r="D7" s="20" t="s">
-        <v>455</v>
+        <v>462</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>198</v>
@@ -3616,28 +3637,28 @@
         <v>66cce1b2-c3f3-4c17-a0c2-1ab7c4292c37, {"content":"Perfecto, me viene bien a las 10h"}</v>
       </c>
       <c r="G7" s="20" t="s">
-        <v>460</v>
+        <v>467</v>
       </c>
       <c r="H7" s="33" t="s">
         <v>70</v>
       </c>
       <c r="I7" s="21" t="s">
-        <v>461</v>
+        <v>468</v>
       </c>
       <c r="J7" s="34"/>
     </row>
     <row r="8" ht="42.0" customHeight="1">
       <c r="A8" s="23" t="s">
-        <v>462</v>
+        <v>469</v>
       </c>
       <c r="B8" s="21" t="s">
-        <v>463</v>
+        <v>470</v>
       </c>
       <c r="C8" s="43" t="s">
         <v>139</v>
       </c>
       <c r="D8" s="21" t="s">
-        <v>455</v>
+        <v>462</v>
       </c>
       <c r="E8" s="21" t="s">
         <v>198</v>
@@ -3647,28 +3668,28 @@
         <v>66cce1b2-c3f3-4c17-a0c2-1ab7c4292c37</v>
       </c>
       <c r="G8" s="21" t="s">
-        <v>464</v>
+        <v>471</v>
       </c>
       <c r="H8" s="33" t="s">
         <v>70</v>
       </c>
       <c r="I8" s="21" t="s">
-        <v>465</v>
+        <v>472</v>
       </c>
       <c r="J8" s="23"/>
     </row>
     <row r="9" ht="42.0" customHeight="1">
       <c r="A9" s="34" t="s">
-        <v>466</v>
+        <v>473</v>
       </c>
       <c r="B9" s="20" t="s">
-        <v>467</v>
+        <v>474</v>
       </c>
       <c r="C9" s="44" t="s">
         <v>211</v>
       </c>
       <c r="D9" s="20" t="s">
-        <v>468</v>
+        <v>475</v>
       </c>
       <c r="E9" s="20" t="s">
         <v>198</v>
@@ -3678,28 +3699,28 @@
         <v>66cce1b2-c3f3-4c17-a0c2-1ab7c4292c37</v>
       </c>
       <c r="G9" s="20" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="H9" s="33" t="s">
         <v>70</v>
       </c>
       <c r="I9" s="20" t="s">
-        <v>469</v>
+        <v>476</v>
       </c>
       <c r="J9" s="34"/>
     </row>
     <row r="10" ht="42.0" customHeight="1">
       <c r="A10" s="23" t="s">
-        <v>470</v>
+        <v>477</v>
       </c>
       <c r="B10" s="21" t="s">
-        <v>471</v>
+        <v>478</v>
       </c>
       <c r="C10" s="57" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="D10" s="21" t="s">
-        <v>472</v>
+        <v>479</v>
       </c>
       <c r="E10" s="21" t="s">
         <v>198</v>
@@ -3709,28 +3730,28 @@
         <v>66cce1b2-c3f3-4c17-a0c2-1ab7c4292c37</v>
       </c>
       <c r="G10" s="21" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="H10" s="33" t="s">
         <v>70</v>
       </c>
       <c r="I10" s="21" t="s">
-        <v>473</v>
+        <v>480</v>
       </c>
       <c r="J10" s="23"/>
     </row>
     <row r="11" ht="42.0" customHeight="1">
       <c r="A11" s="34" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
       <c r="B11" s="20" t="s">
-        <v>475</v>
+        <v>482</v>
       </c>
       <c r="C11" s="56" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="D11" s="20" t="s">
-        <v>472</v>
+        <v>479</v>
       </c>
       <c r="E11" s="20" t="s">
         <v>198</v>
@@ -3746,13 +3767,13 @@
         <v>70</v>
       </c>
       <c r="I11" s="20" t="s">
-        <v>476</v>
+        <v>483</v>
       </c>
       <c r="J11" s="34"/>
     </row>
     <row r="12" ht="18.0" customHeight="1">
       <c r="A12" s="29" t="s">
-        <v>477</v>
+        <v>484</v>
       </c>
       <c r="B12" s="30"/>
       <c r="C12" s="30"/>
@@ -3766,16 +3787,16 @@
     </row>
     <row r="13" ht="42.0" customHeight="1">
       <c r="A13" s="34" t="s">
-        <v>478</v>
+        <v>485</v>
       </c>
       <c r="B13" s="20" t="s">
-        <v>479</v>
+        <v>486</v>
       </c>
       <c r="C13" s="36" t="s">
         <v>139</v>
       </c>
       <c r="D13" s="20" t="s">
-        <v>480</v>
+        <v>487</v>
       </c>
       <c r="E13" s="20" t="s">
         <v>198</v>
@@ -3784,13 +3805,13 @@
         <v>141</v>
       </c>
       <c r="G13" s="20" t="s">
-        <v>481</v>
+        <v>488</v>
       </c>
       <c r="H13" s="33" t="s">
         <v>70</v>
       </c>
       <c r="I13" s="20" t="s">
-        <v>482</v>
+        <v>489</v>
       </c>
       <c r="J13" s="34"/>
     </row>
@@ -4828,7 +4849,7 @@
   <sheetData>
     <row r="1" ht="24.0" customHeight="1">
       <c r="A1" s="27" t="s">
-        <v>483</v>
+        <v>490</v>
       </c>
       <c r="B1" s="28"/>
       <c r="C1" s="28"/>
@@ -4874,7 +4895,7 @@
     </row>
     <row r="3" ht="18.0" customHeight="1">
       <c r="A3" s="29" t="s">
-        <v>484</v>
+        <v>491</v>
       </c>
       <c r="B3" s="30"/>
       <c r="C3" s="30"/>
@@ -4888,16 +4909,16 @@
     </row>
     <row r="4" ht="42.0" customHeight="1">
       <c r="A4" s="23" t="s">
-        <v>485</v>
+        <v>492</v>
       </c>
       <c r="B4" s="21" t="s">
-        <v>486</v>
+        <v>493</v>
       </c>
       <c r="C4" s="32" t="s">
         <v>97</v>
       </c>
       <c r="D4" s="21" t="s">
-        <v>487</v>
+        <v>494</v>
       </c>
       <c r="E4" s="21" t="s">
         <v>198</v>
@@ -4907,19 +4928,19 @@
         <v>c7cf918d-7e04-4104-9790-fa5bb9d3756d</v>
       </c>
       <c r="G4" s="21" t="s">
-        <v>488</v>
+        <v>495</v>
       </c>
       <c r="H4" s="33" t="s">
         <v>70</v>
       </c>
       <c r="I4" s="21" t="s">
-        <v>489</v>
+        <v>496</v>
       </c>
       <c r="J4" s="23"/>
     </row>
     <row r="5" ht="18.0" customHeight="1">
       <c r="A5" s="29" t="s">
-        <v>490</v>
+        <v>497</v>
       </c>
       <c r="B5" s="30"/>
       <c r="C5" s="30"/>
@@ -4933,16 +4954,16 @@
     </row>
     <row r="6" ht="42.0" customHeight="1">
       <c r="A6" s="23" t="s">
-        <v>491</v>
+        <v>498</v>
       </c>
       <c r="B6" s="21" t="s">
-        <v>492</v>
+        <v>499</v>
       </c>
       <c r="C6" s="32" t="s">
         <v>97</v>
       </c>
       <c r="D6" s="21" t="s">
-        <v>493</v>
+        <v>500</v>
       </c>
       <c r="E6" s="21" t="s">
         <v>198</v>
@@ -4952,28 +4973,28 @@
         <v>{"targetId":"69ad88c5-bd50-46e1-824a-0625dabf99ea","helpRequestId":"c7cf918d-7e04-4104-9790-fa5bb9d3756d","rating":5,"comment":"Excelente voluntario, muy puntual y atento"}</v>
       </c>
       <c r="G6" s="21" t="s">
-        <v>494</v>
+        <v>501</v>
       </c>
       <c r="H6" s="33" t="s">
         <v>70</v>
       </c>
       <c r="I6" s="21" t="s">
-        <v>495</v>
+        <v>502</v>
       </c>
       <c r="J6" s="23"/>
     </row>
     <row r="7" ht="42.0" customHeight="1">
       <c r="A7" s="34" t="s">
-        <v>496</v>
+        <v>503</v>
       </c>
       <c r="B7" s="20" t="s">
-        <v>497</v>
+        <v>504</v>
       </c>
       <c r="C7" s="35" t="s">
         <v>97</v>
       </c>
       <c r="D7" s="20" t="s">
-        <v>493</v>
+        <v>500</v>
       </c>
       <c r="E7" s="20" t="s">
         <v>198</v>
@@ -4983,28 +5004,28 @@
         <v>{"targetId":"f08371a0-756b-47d7-b714-533edd782035","helpRequestId":"c7cf918d-7e04-4104-9790-fa5bb9d3756d","rating":4,"comment":"Todo muy claro y organizado"}</v>
       </c>
       <c r="G7" s="20" t="s">
-        <v>498</v>
+        <v>505</v>
       </c>
       <c r="H7" s="33" t="s">
         <v>70</v>
       </c>
       <c r="I7" s="20" t="s">
-        <v>499</v>
+        <v>506</v>
       </c>
       <c r="J7" s="34"/>
     </row>
     <row r="8" ht="42.0" customHeight="1">
       <c r="A8" s="23" t="s">
-        <v>500</v>
+        <v>507</v>
       </c>
       <c r="B8" s="21" t="s">
-        <v>501</v>
+        <v>508</v>
       </c>
       <c r="C8" s="32" t="s">
         <v>97</v>
       </c>
       <c r="D8" s="21" t="s">
-        <v>493</v>
+        <v>500</v>
       </c>
       <c r="E8" s="21" t="s">
         <v>198</v>
@@ -5014,19 +5035,19 @@
         <v>{"targetId":"69ad88c5-bd50-46e1-824a-0625dabf99ea","donationId":"8396e74a-7bc5-4793-b7c4-bd79b3b7932b","rating":5,"comment":"Recogió la donación perfectamente"}</v>
       </c>
       <c r="G8" s="21" t="s">
-        <v>502</v>
+        <v>509</v>
       </c>
       <c r="H8" s="33" t="s">
         <v>70</v>
       </c>
       <c r="I8" s="21" t="s">
-        <v>499</v>
+        <v>506</v>
       </c>
       <c r="J8" s="23"/>
     </row>
     <row r="9" ht="18.0" customHeight="1">
       <c r="A9" s="29" t="s">
-        <v>503</v>
+        <v>510</v>
       </c>
       <c r="B9" s="30"/>
       <c r="C9" s="30"/>
@@ -5040,16 +5061,16 @@
     </row>
     <row r="10" ht="42.0" customHeight="1">
       <c r="A10" s="23" t="s">
-        <v>504</v>
+        <v>511</v>
       </c>
       <c r="B10" s="21" t="s">
-        <v>505</v>
+        <v>512</v>
       </c>
       <c r="C10" s="32" t="s">
         <v>97</v>
       </c>
       <c r="D10" s="21" t="s">
-        <v>493</v>
+        <v>500</v>
       </c>
       <c r="E10" s="21" t="s">
         <v>198</v>
@@ -5059,28 +5080,28 @@
         <v>{"targetId":"69ad88c5-bd50-46e1-824a-0625dabf99ea","helpRequestId":"c7cf918d-7e04-4104-9790-fa5bb9d3756d","rating":3,"comment":"Segunda review"}</v>
       </c>
       <c r="G10" s="21" t="s">
-        <v>506</v>
+        <v>513</v>
       </c>
       <c r="H10" s="33" t="s">
         <v>70</v>
       </c>
       <c r="I10" s="21" t="s">
-        <v>507</v>
+        <v>514</v>
       </c>
       <c r="J10" s="23"/>
     </row>
     <row r="11" ht="42.0" customHeight="1">
       <c r="A11" s="34" t="s">
-        <v>508</v>
+        <v>515</v>
       </c>
       <c r="B11" s="20" t="s">
-        <v>509</v>
+        <v>516</v>
       </c>
       <c r="C11" s="35" t="s">
         <v>97</v>
       </c>
       <c r="D11" s="20" t="s">
-        <v>493</v>
+        <v>500</v>
       </c>
       <c r="E11" s="20" t="s">
         <v>198</v>
@@ -5090,28 +5111,28 @@
         <v>{"targetId":"beeaa200-52c6-44fa-9333-b4f6f375e314","donationId":"4a2c7d53-9a34-4c40-9e8f-c8972db67211","rating":3,"comment":"Test"}</v>
       </c>
       <c r="G11" s="20" t="s">
-        <v>510</v>
+        <v>517</v>
       </c>
       <c r="H11" s="33" t="s">
         <v>70</v>
       </c>
       <c r="I11" s="20" t="s">
-        <v>511</v>
+        <v>518</v>
       </c>
       <c r="J11" s="34"/>
     </row>
     <row r="12" ht="42.0" customHeight="1">
       <c r="A12" s="23" t="s">
-        <v>512</v>
+        <v>519</v>
       </c>
       <c r="B12" s="21" t="s">
-        <v>513</v>
+        <v>520</v>
       </c>
       <c r="C12" s="32" t="s">
         <v>97</v>
       </c>
       <c r="D12" s="21" t="s">
-        <v>493</v>
+        <v>500</v>
       </c>
       <c r="E12" s="21" t="s">
         <v>198</v>
@@ -5121,13 +5142,13 @@
         <v>{"targetId":"69ad88c5-bd50-46e1-824a-0625dabf99ea","helpRequestId":"c7cf918d-7e04-4104-9790-fa5bb9d3756d","rating":4,"comment":"Test"}</v>
       </c>
       <c r="G12" s="21" t="s">
-        <v>514</v>
+        <v>521</v>
       </c>
       <c r="H12" s="33" t="s">
         <v>70</v>
       </c>
       <c r="I12" s="21" t="s">
-        <v>515</v>
+        <v>522</v>
       </c>
       <c r="J12" s="23"/>
     </row>
@@ -5147,16 +5168,16 @@
     </row>
     <row r="14" ht="42.0" customHeight="1">
       <c r="A14" s="23" t="s">
-        <v>516</v>
+        <v>523</v>
       </c>
       <c r="B14" s="21" t="s">
-        <v>517</v>
+        <v>524</v>
       </c>
       <c r="C14" s="43" t="s">
         <v>139</v>
       </c>
       <c r="D14" s="21" t="s">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="E14" s="21" t="s">
         <v>198</v>
@@ -5166,64 +5187,64 @@
         <v>69ad88c5-bd50-46e1-824a-0625dabf99ea</v>
       </c>
       <c r="G14" s="21" t="s">
-        <v>519</v>
+        <v>526</v>
       </c>
       <c r="H14" s="33" t="s">
         <v>70</v>
       </c>
       <c r="I14" s="21" t="s">
-        <v>520</v>
+        <v>527</v>
       </c>
       <c r="J14" s="23"/>
     </row>
     <row r="15" ht="42.0" customHeight="1">
       <c r="A15" s="34" t="s">
-        <v>521</v>
+        <v>528</v>
       </c>
       <c r="B15" s="20" t="s">
-        <v>522</v>
+        <v>529</v>
       </c>
       <c r="C15" s="44" t="s">
         <v>211</v>
       </c>
       <c r="D15" s="20" t="s">
-        <v>523</v>
+        <v>530</v>
       </c>
       <c r="E15" s="20" t="s">
         <v>198</v>
       </c>
       <c r="F15" s="20" t="s">
-        <v>524</v>
+        <v>531</v>
       </c>
       <c r="G15" s="20" t="s">
-        <v>525</v>
+        <v>532</v>
       </c>
       <c r="H15" s="33" t="s">
         <v>70</v>
       </c>
       <c r="I15" s="20" t="s">
-        <v>520</v>
+        <v>527</v>
       </c>
       <c r="J15" s="34"/>
     </row>
     <row r="16" ht="42.0" customHeight="1">
       <c r="A16" s="23" t="s">
-        <v>526</v>
+        <v>533</v>
       </c>
       <c r="B16" s="21" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="C16" s="45" t="s">
         <v>211</v>
       </c>
       <c r="D16" s="21" t="s">
-        <v>523</v>
+        <v>530</v>
       </c>
       <c r="E16" s="21" t="s">
         <v>198</v>
       </c>
       <c r="F16" s="21" t="s">
-        <v>528</v>
+        <v>535</v>
       </c>
       <c r="G16" s="21" t="s">
         <v>112</v>
@@ -5232,22 +5253,22 @@
         <v>70</v>
       </c>
       <c r="I16" s="21" t="s">
-        <v>529</v>
+        <v>536</v>
       </c>
       <c r="J16" s="23"/>
     </row>
     <row r="17" ht="42.0" customHeight="1">
       <c r="A17" s="34" t="s">
+        <v>537</v>
+      </c>
+      <c r="B17" s="20" t="s">
+        <v>538</v>
+      </c>
+      <c r="C17" s="56" t="s">
+        <v>344</v>
+      </c>
+      <c r="D17" s="20" t="s">
         <v>530</v>
-      </c>
-      <c r="B17" s="20" t="s">
-        <v>531</v>
-      </c>
-      <c r="C17" s="56" t="s">
-        <v>340</v>
-      </c>
-      <c r="D17" s="20" t="s">
-        <v>523</v>
       </c>
       <c r="E17" s="20" t="s">
         <v>198</v>
@@ -5256,13 +5277,13 @@
         <v>141</v>
       </c>
       <c r="G17" s="20" t="s">
-        <v>532</v>
+        <v>539</v>
       </c>
       <c r="H17" s="33" t="s">
         <v>70</v>
       </c>
       <c r="I17" s="20" t="s">
-        <v>533</v>
+        <v>540</v>
       </c>
       <c r="J17" s="34"/>
     </row>
@@ -7589,11 +7610,11 @@
       </c>
       <c r="C8" s="23">
         <f>COUNTIF('Help Requests'!A:A,"Hr-*")</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D8" s="23">
         <f>COUNTIF('Help Requests'!H:H,D4)</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E8" s="23">
         <f>COUNTIF('Help Requests'!H:H,E4)</f>
@@ -7614,11 +7635,11 @@
       </c>
       <c r="C9" s="23">
         <f>COUNTIF(Donations!A:A,"D-*")</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D9" s="23">
         <f>COUNTIF(Donations!H:H,D4)</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E9" s="23">
         <f>COUNTIF(Donations!H:H,E4)</f>
@@ -7714,11 +7735,11 @@
       </c>
       <c r="C13" s="25">
         <f t="shared" ref="C13:F13" si="2">SUM(C5:C12)</f>
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D13" s="25">
         <f t="shared" si="2"/>
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E13" s="25">
         <f t="shared" si="2"/>
@@ -13303,10 +13324,10 @@
       <c r="J5" s="34"/>
     </row>
     <row r="6" ht="42.0" customHeight="1">
-      <c r="A6" s="23" t="s">
+      <c r="A6" s="41" t="s">
         <v>276</v>
       </c>
-      <c r="B6" s="21" t="s">
+      <c r="B6" s="42" t="s">
         <v>277</v>
       </c>
       <c r="C6" s="32" t="s">
@@ -13319,246 +13340,230 @@
         <v>198</v>
       </c>
       <c r="F6" s="21" t="s">
+        <v>273</v>
+      </c>
+      <c r="G6" s="42" t="s">
         <v>278</v>
-      </c>
-      <c r="G6" s="21" t="s">
-        <v>117</v>
       </c>
       <c r="H6" s="33" t="s">
         <v>70</v>
       </c>
-      <c r="I6" s="21" t="s">
+      <c r="I6" s="42" t="s">
         <v>279</v>
       </c>
       <c r="J6" s="23"/>
     </row>
-    <row r="7" ht="18.0" customHeight="1">
-      <c r="A7" s="29" t="s">
+    <row r="7" ht="42.0" customHeight="1">
+      <c r="A7" s="38" t="s">
         <v>280</v>
       </c>
-      <c r="B7" s="30"/>
-      <c r="C7" s="30"/>
-      <c r="D7" s="30"/>
-      <c r="E7" s="30"/>
-      <c r="F7" s="30"/>
-      <c r="G7" s="30"/>
-      <c r="H7" s="30"/>
-      <c r="I7" s="30"/>
-      <c r="J7" s="31"/>
-    </row>
-    <row r="8" ht="42.0" customHeight="1">
-      <c r="A8" s="23" t="s">
+      <c r="B7" s="20" t="s">
         <v>281</v>
       </c>
-      <c r="B8" s="46" t="s">
+      <c r="C7" s="35" t="s">
+        <v>97</v>
+      </c>
+      <c r="D7" s="20" t="s">
+        <v>267</v>
+      </c>
+      <c r="E7" s="20" t="s">
+        <v>198</v>
+      </c>
+      <c r="F7" s="20" t="s">
         <v>282</v>
       </c>
-      <c r="C8" s="43" t="s">
+      <c r="G7" s="20" t="s">
+        <v>117</v>
+      </c>
+      <c r="H7" s="33" t="s">
+        <v>70</v>
+      </c>
+      <c r="I7" s="20" t="s">
+        <v>283</v>
+      </c>
+      <c r="J7" s="34"/>
+    </row>
+    <row r="8" ht="18.0" customHeight="1">
+      <c r="A8" s="29" t="s">
+        <v>284</v>
+      </c>
+      <c r="B8" s="30"/>
+      <c r="C8" s="30"/>
+      <c r="D8" s="30"/>
+      <c r="E8" s="30"/>
+      <c r="F8" s="30"/>
+      <c r="G8" s="30"/>
+      <c r="H8" s="30"/>
+      <c r="I8" s="30"/>
+      <c r="J8" s="31"/>
+    </row>
+    <row r="9" ht="42.0" customHeight="1">
+      <c r="A9" s="41" t="s">
+        <v>285</v>
+      </c>
+      <c r="B9" s="46" t="s">
+        <v>286</v>
+      </c>
+      <c r="C9" s="43" t="s">
         <v>139</v>
       </c>
-      <c r="D8" s="46" t="s">
+      <c r="D9" s="46" t="s">
         <v>267</v>
       </c>
-      <c r="E8" s="46" t="s">
+      <c r="E9" s="46" t="s">
         <v>198</v>
       </c>
-      <c r="F8" s="46" t="s">
+      <c r="F9" s="46" t="s">
         <v>141</v>
       </c>
-      <c r="G8" s="46" t="s">
-        <v>283</v>
-      </c>
-      <c r="H8" s="47" t="s">
+      <c r="G9" s="46" t="s">
+        <v>287</v>
+      </c>
+      <c r="H9" s="47" t="s">
         <v>70</v>
       </c>
-      <c r="I8" s="46" t="s">
-        <v>284</v>
-      </c>
-      <c r="J8" s="48"/>
-      <c r="K8" s="49"/>
-      <c r="L8" s="49"/>
-      <c r="M8" s="49"/>
-      <c r="N8" s="49"/>
-      <c r="O8" s="49"/>
-      <c r="P8" s="49"/>
-      <c r="Q8" s="49"/>
-      <c r="R8" s="49"/>
-      <c r="S8" s="49"/>
-      <c r="T8" s="49"/>
-      <c r="U8" s="49"/>
-      <c r="V8" s="49"/>
-      <c r="W8" s="49"/>
-      <c r="X8" s="49"/>
-      <c r="Y8" s="49"/>
-      <c r="Z8" s="49"/>
-    </row>
-    <row r="9" ht="42.0" customHeight="1">
-      <c r="A9" s="50" t="s">
-        <v>285</v>
-      </c>
-      <c r="B9" s="51" t="s">
-        <v>286</v>
-      </c>
-      <c r="C9" s="52" t="s">
+      <c r="I9" s="46" t="s">
+        <v>288</v>
+      </c>
+      <c r="J9" s="48"/>
+      <c r="K9" s="49"/>
+      <c r="L9" s="49"/>
+      <c r="M9" s="49"/>
+      <c r="N9" s="49"/>
+      <c r="O9" s="49"/>
+      <c r="P9" s="49"/>
+      <c r="Q9" s="49"/>
+      <c r="R9" s="49"/>
+      <c r="S9" s="49"/>
+      <c r="T9" s="49"/>
+      <c r="U9" s="49"/>
+      <c r="V9" s="49"/>
+      <c r="W9" s="49"/>
+      <c r="X9" s="49"/>
+      <c r="Y9" s="49"/>
+      <c r="Z9" s="49"/>
+    </row>
+    <row r="10" ht="42.0" customHeight="1">
+      <c r="A10" s="50" t="s">
+        <v>289</v>
+      </c>
+      <c r="B10" s="51" t="s">
+        <v>290</v>
+      </c>
+      <c r="C10" s="52" t="s">
         <v>139</v>
       </c>
-      <c r="D9" s="51" t="s">
-        <v>287</v>
-      </c>
-      <c r="E9" s="51" t="s">
+      <c r="D10" s="51" t="s">
+        <v>291</v>
+      </c>
+      <c r="E10" s="51" t="s">
         <v>198</v>
       </c>
-      <c r="F9" s="51" t="s">
+      <c r="F10" s="51" t="s">
         <v>141</v>
       </c>
-      <c r="G9" s="51" t="s">
-        <v>288</v>
-      </c>
-      <c r="H9" s="33" t="s">
+      <c r="G10" s="51" t="s">
+        <v>292</v>
+      </c>
+      <c r="H10" s="33" t="s">
         <v>70</v>
       </c>
-      <c r="I9" s="51" t="s">
-        <v>289</v>
-      </c>
-      <c r="J9" s="23"/>
-    </row>
-    <row r="10" ht="42.0" customHeight="1">
-      <c r="A10" s="23" t="s">
-        <v>290</v>
-      </c>
-      <c r="B10" s="21" t="s">
-        <v>291</v>
-      </c>
-      <c r="C10" s="43" t="s">
+      <c r="I10" s="51" t="s">
+        <v>293</v>
+      </c>
+      <c r="J10" s="23"/>
+    </row>
+    <row r="11" ht="42.0" customHeight="1">
+      <c r="A11" s="50" t="s">
+        <v>294</v>
+      </c>
+      <c r="B11" s="21" t="s">
+        <v>295</v>
+      </c>
+      <c r="C11" s="43" t="s">
         <v>139</v>
       </c>
-      <c r="D10" s="21" t="s">
-        <v>292</v>
-      </c>
-      <c r="E10" s="21" t="s">
+      <c r="D11" s="21" t="s">
+        <v>296</v>
+      </c>
+      <c r="E11" s="21" t="s">
         <v>198</v>
       </c>
-      <c r="F10" s="21" t="str">
+      <c r="F11" s="21" t="str">
         <f>Variables!C8</f>
         <v>c7cf918d-7e04-4104-9790-fa5bb9d3756d</v>
       </c>
-      <c r="G10" s="21" t="s">
-        <v>293</v>
-      </c>
-      <c r="H10" s="33" t="s">
-        <v>70</v>
-      </c>
-      <c r="I10" s="21" t="s">
-        <v>294</v>
-      </c>
-      <c r="J10" s="34"/>
-    </row>
-    <row r="11" ht="42.0" customHeight="1">
-      <c r="A11" s="34" t="s">
-        <v>295</v>
-      </c>
-      <c r="B11" s="20" t="s">
-        <v>296</v>
-      </c>
-      <c r="C11" s="36" t="s">
-        <v>139</v>
-      </c>
-      <c r="D11" s="20" t="s">
+      <c r="G11" s="21" t="s">
         <v>297</v>
-      </c>
-      <c r="E11" s="20" t="s">
-        <v>198</v>
-      </c>
-      <c r="F11" s="20" t="s">
-        <v>141</v>
-      </c>
-      <c r="G11" s="20" t="s">
-        <v>298</v>
       </c>
       <c r="H11" s="33" t="s">
         <v>70</v>
       </c>
-      <c r="I11" s="20" t="s">
+      <c r="I11" s="21" t="s">
+        <v>298</v>
+      </c>
+      <c r="J11" s="34"/>
+    </row>
+    <row r="12" ht="42.0" customHeight="1">
+      <c r="A12" s="50" t="s">
         <v>299</v>
       </c>
-      <c r="J11" s="34"/>
-    </row>
-    <row r="12" ht="42.0" customHeight="1">
-      <c r="A12" s="23" t="s">
+      <c r="B12" s="20" t="s">
         <v>300</v>
       </c>
-      <c r="B12" s="46" t="s">
+      <c r="C12" s="36" t="s">
+        <v>139</v>
+      </c>
+      <c r="D12" s="20" t="s">
         <v>301</v>
       </c>
-      <c r="C12" s="43" t="s">
+      <c r="E12" s="20" t="s">
+        <v>198</v>
+      </c>
+      <c r="F12" s="20" t="s">
+        <v>141</v>
+      </c>
+      <c r="G12" s="20" t="s">
+        <v>302</v>
+      </c>
+      <c r="H12" s="33" t="s">
+        <v>70</v>
+      </c>
+      <c r="I12" s="20" t="s">
+        <v>303</v>
+      </c>
+      <c r="J12" s="34"/>
+    </row>
+    <row r="13" ht="42.0" customHeight="1">
+      <c r="A13" s="50" t="s">
+        <v>304</v>
+      </c>
+      <c r="B13" s="46" t="s">
+        <v>305</v>
+      </c>
+      <c r="C13" s="43" t="s">
         <v>139</v>
       </c>
-      <c r="D12" s="46" t="s">
-        <v>302</v>
-      </c>
-      <c r="E12" s="46" t="s">
+      <c r="D13" s="46" t="s">
+        <v>306</v>
+      </c>
+      <c r="E13" s="46" t="s">
         <v>198</v>
       </c>
-      <c r="F12" s="21" t="str">
+      <c r="F13" s="21" t="str">
         <f>Variables!C8</f>
         <v>c7cf918d-7e04-4104-9790-fa5bb9d3756d</v>
       </c>
-      <c r="G12" s="46" t="s">
-        <v>303</v>
-      </c>
-      <c r="H12" s="47" t="s">
-        <v>70</v>
-      </c>
-      <c r="I12" s="46" t="s">
-        <v>304</v>
-      </c>
-      <c r="J12" s="48"/>
-      <c r="K12" s="49"/>
-      <c r="L12" s="49"/>
-      <c r="M12" s="49"/>
-      <c r="N12" s="49"/>
-      <c r="O12" s="49"/>
-      <c r="P12" s="49"/>
-      <c r="Q12" s="49"/>
-      <c r="R12" s="49"/>
-      <c r="S12" s="49"/>
-      <c r="T12" s="49"/>
-      <c r="U12" s="49"/>
-      <c r="V12" s="49"/>
-      <c r="W12" s="49"/>
-      <c r="X12" s="49"/>
-      <c r="Y12" s="49"/>
-      <c r="Z12" s="49"/>
-    </row>
-    <row r="13" ht="42.0" customHeight="1">
-      <c r="A13" s="34" t="s">
-        <v>305</v>
-      </c>
-      <c r="B13" s="53" t="s">
-        <v>306</v>
-      </c>
-      <c r="C13" s="36" t="s">
-        <v>139</v>
-      </c>
-      <c r="D13" s="53" t="s">
+      <c r="G13" s="46" t="s">
         <v>307</v>
-      </c>
-      <c r="E13" s="53" t="s">
-        <v>198</v>
-      </c>
-      <c r="F13" s="53" t="s">
-        <v>308</v>
-      </c>
-      <c r="G13" s="53" t="s">
-        <v>309</v>
       </c>
       <c r="H13" s="47" t="s">
         <v>70</v>
       </c>
-      <c r="I13" s="53" t="s">
-        <v>310</v>
-      </c>
-      <c r="J13" s="54"/>
+      <c r="I13" s="46" t="s">
+        <v>308</v>
+      </c>
+      <c r="J13" s="48"/>
       <c r="K13" s="49"/>
       <c r="L13" s="49"/>
       <c r="M13" s="49"/>
@@ -13577,34 +13582,34 @@
       <c r="Z13" s="49"/>
     </row>
     <row r="14" ht="42.0" customHeight="1">
-      <c r="A14" s="23" t="s">
+      <c r="A14" s="50" t="s">
+        <v>309</v>
+      </c>
+      <c r="B14" s="53" t="s">
+        <v>310</v>
+      </c>
+      <c r="C14" s="36" t="s">
+        <v>139</v>
+      </c>
+      <c r="D14" s="53" t="s">
         <v>311</v>
       </c>
-      <c r="B14" s="46" t="s">
+      <c r="E14" s="53" t="s">
+        <v>198</v>
+      </c>
+      <c r="F14" s="53" t="s">
         <v>312</v>
       </c>
-      <c r="C14" s="43" t="s">
-        <v>139</v>
-      </c>
-      <c r="D14" s="46" t="s">
+      <c r="G14" s="53" t="s">
         <v>313</v>
-      </c>
-      <c r="E14" s="46" t="s">
-        <v>198</v>
-      </c>
-      <c r="F14" s="46" t="s">
-        <v>141</v>
-      </c>
-      <c r="G14" s="46" t="s">
-        <v>298</v>
       </c>
       <c r="H14" s="47" t="s">
         <v>70</v>
       </c>
-      <c r="I14" s="46" t="s">
+      <c r="I14" s="53" t="s">
         <v>314</v>
       </c>
-      <c r="J14" s="48"/>
+      <c r="J14" s="54"/>
       <c r="K14" s="49"/>
       <c r="L14" s="49"/>
       <c r="M14" s="49"/>
@@ -13623,35 +13628,34 @@
       <c r="Z14" s="49"/>
     </row>
     <row r="15" ht="42.0" customHeight="1">
-      <c r="A15" s="34" t="s">
+      <c r="A15" s="50" t="s">
         <v>315</v>
       </c>
-      <c r="B15" s="53" t="s">
+      <c r="B15" s="46" t="s">
         <v>316</v>
       </c>
-      <c r="C15" s="36" t="s">
+      <c r="C15" s="43" t="s">
         <v>139</v>
       </c>
-      <c r="D15" s="53" t="s">
-        <v>292</v>
-      </c>
-      <c r="E15" s="53" t="s">
+      <c r="D15" s="46" t="s">
+        <v>317</v>
+      </c>
+      <c r="E15" s="46" t="s">
         <v>198</v>
       </c>
-      <c r="F15" s="53" t="str">
-        <f>Variables!C8</f>
-        <v>c7cf918d-7e04-4104-9790-fa5bb9d3756d</v>
-      </c>
-      <c r="G15" s="53" t="s">
-        <v>317</v>
+      <c r="F15" s="46" t="s">
+        <v>141</v>
+      </c>
+      <c r="G15" s="46" t="s">
+        <v>302</v>
       </c>
       <c r="H15" s="47" t="s">
         <v>70</v>
       </c>
-      <c r="I15" s="53" t="s">
-        <v>224</v>
-      </c>
-      <c r="J15" s="54"/>
+      <c r="I15" s="46" t="s">
+        <v>318</v>
+      </c>
+      <c r="J15" s="48"/>
       <c r="K15" s="49"/>
       <c r="L15" s="49"/>
       <c r="M15" s="49"/>
@@ -13670,34 +13674,35 @@
       <c r="Z15" s="49"/>
     </row>
     <row r="16" ht="42.0" customHeight="1">
-      <c r="A16" s="41" t="s">
-        <v>318</v>
-      </c>
-      <c r="B16" s="55" t="s">
+      <c r="A16" s="50" t="s">
         <v>319</v>
       </c>
-      <c r="C16" s="43" t="s">
+      <c r="B16" s="53" t="s">
+        <v>320</v>
+      </c>
+      <c r="C16" s="36" t="s">
         <v>139</v>
       </c>
-      <c r="D16" s="55" t="s">
-        <v>320</v>
-      </c>
-      <c r="E16" s="46" t="s">
+      <c r="D16" s="53" t="s">
+        <v>296</v>
+      </c>
+      <c r="E16" s="53" t="s">
         <v>198</v>
       </c>
-      <c r="F16" s="55" t="s">
+      <c r="F16" s="53" t="str">
+        <f>Variables!C8</f>
+        <v>c7cf918d-7e04-4104-9790-fa5bb9d3756d</v>
+      </c>
+      <c r="G16" s="53" t="s">
         <v>321</v>
-      </c>
-      <c r="G16" s="55" t="s">
-        <v>148</v>
       </c>
       <c r="H16" s="47" t="s">
         <v>70</v>
       </c>
-      <c r="I16" s="55" t="s">
-        <v>322</v>
-      </c>
-      <c r="J16" s="48"/>
+      <c r="I16" s="53" t="s">
+        <v>224</v>
+      </c>
+      <c r="J16" s="54"/>
       <c r="K16" s="49"/>
       <c r="L16" s="49"/>
       <c r="M16" s="49"/>
@@ -13715,154 +13720,1687 @@
       <c r="Y16" s="49"/>
       <c r="Z16" s="49"/>
     </row>
-    <row r="17" ht="18.0" customHeight="1">
-      <c r="A17" s="29" t="s">
+    <row r="17" ht="42.0" customHeight="1">
+      <c r="A17" s="50" t="s">
+        <v>322</v>
+      </c>
+      <c r="B17" s="55" t="s">
         <v>323</v>
       </c>
-      <c r="B17" s="30"/>
-      <c r="C17" s="30"/>
-      <c r="D17" s="30"/>
-      <c r="E17" s="30"/>
-      <c r="F17" s="30"/>
-      <c r="G17" s="30"/>
-      <c r="H17" s="30"/>
-      <c r="I17" s="30"/>
-      <c r="J17" s="31"/>
-    </row>
-    <row r="18" ht="42.0" customHeight="1">
-      <c r="A18" s="38" t="s">
+      <c r="C17" s="43" t="s">
+        <v>139</v>
+      </c>
+      <c r="D17" s="55" t="s">
         <v>324</v>
       </c>
-      <c r="B18" s="20" t="s">
+      <c r="E17" s="46" t="s">
+        <v>198</v>
+      </c>
+      <c r="F17" s="55" t="s">
         <v>325</v>
       </c>
-      <c r="C18" s="44" t="s">
+      <c r="G17" s="55" t="s">
+        <v>148</v>
+      </c>
+      <c r="H17" s="47" t="s">
+        <v>70</v>
+      </c>
+      <c r="I17" s="55" t="s">
+        <v>326</v>
+      </c>
+      <c r="J17" s="48"/>
+      <c r="K17" s="49"/>
+      <c r="L17" s="49"/>
+      <c r="M17" s="49"/>
+      <c r="N17" s="49"/>
+      <c r="O17" s="49"/>
+      <c r="P17" s="49"/>
+      <c r="Q17" s="49"/>
+      <c r="R17" s="49"/>
+      <c r="S17" s="49"/>
+      <c r="T17" s="49"/>
+      <c r="U17" s="49"/>
+      <c r="V17" s="49"/>
+      <c r="W17" s="49"/>
+      <c r="X17" s="49"/>
+      <c r="Y17" s="49"/>
+      <c r="Z17" s="49"/>
+    </row>
+    <row r="18" ht="18.0" customHeight="1">
+      <c r="A18" s="29" t="s">
+        <v>327</v>
+      </c>
+      <c r="B18" s="30"/>
+      <c r="C18" s="30"/>
+      <c r="D18" s="30"/>
+      <c r="E18" s="30"/>
+      <c r="F18" s="30"/>
+      <c r="G18" s="30"/>
+      <c r="H18" s="30"/>
+      <c r="I18" s="30"/>
+      <c r="J18" s="31"/>
+    </row>
+    <row r="19" ht="42.0" customHeight="1">
+      <c r="A19" s="38" t="s">
+        <v>328</v>
+      </c>
+      <c r="B19" s="20" t="s">
+        <v>329</v>
+      </c>
+      <c r="C19" s="44" t="s">
         <v>211</v>
       </c>
-      <c r="D18" s="20" t="s">
-        <v>326</v>
-      </c>
-      <c r="E18" s="20" t="s">
+      <c r="D19" s="20" t="s">
+        <v>330</v>
+      </c>
+      <c r="E19" s="20" t="s">
         <v>198</v>
       </c>
-      <c r="F18" s="20" t="str">
+      <c r="F19" s="20" t="str">
         <f>Variables!C8 &amp; ", {""title"":""Compra en supermercado — URGENTE""}"</f>
         <v>c7cf918d-7e04-4104-9790-fa5bb9d3756d, {"title":"Compra en supermercado — URGENTE"}</v>
       </c>
-      <c r="G18" s="20" t="s">
-        <v>327</v>
-      </c>
-      <c r="H18" s="33" t="s">
-        <v>70</v>
-      </c>
-      <c r="I18" s="20" t="s">
-        <v>328</v>
-      </c>
-      <c r="J18" s="34"/>
-    </row>
-    <row r="19" ht="42.0" customHeight="1">
-      <c r="A19" s="41" t="s">
-        <v>329</v>
-      </c>
-      <c r="B19" s="21" t="s">
-        <v>330</v>
-      </c>
-      <c r="C19" s="45" t="s">
-        <v>211</v>
-      </c>
-      <c r="D19" s="21" t="s">
-        <v>326</v>
-      </c>
-      <c r="E19" s="21" t="s">
-        <v>198</v>
-      </c>
-      <c r="F19" s="21" t="s">
+      <c r="G19" s="20" t="s">
         <v>331</v>
-      </c>
-      <c r="G19" s="21" t="s">
-        <v>223</v>
       </c>
       <c r="H19" s="33" t="s">
         <v>70</v>
       </c>
-      <c r="I19" s="46" t="s">
+      <c r="I19" s="20" t="s">
+        <v>332</v>
+      </c>
+      <c r="J19" s="34"/>
+    </row>
+    <row r="20" ht="42.0" customHeight="1">
+      <c r="A20" s="41" t="s">
+        <v>333</v>
+      </c>
+      <c r="B20" s="21" t="s">
+        <v>334</v>
+      </c>
+      <c r="C20" s="45" t="s">
+        <v>211</v>
+      </c>
+      <c r="D20" s="21" t="s">
+        <v>330</v>
+      </c>
+      <c r="E20" s="21" t="s">
+        <v>198</v>
+      </c>
+      <c r="F20" s="21" t="s">
+        <v>335</v>
+      </c>
+      <c r="G20" s="21" t="s">
+        <v>223</v>
+      </c>
+      <c r="H20" s="33" t="s">
+        <v>70</v>
+      </c>
+      <c r="I20" s="46" t="s">
         <v>224</v>
       </c>
-      <c r="J19" s="23"/>
-    </row>
-    <row r="20" ht="18.0" customHeight="1">
-      <c r="A20" s="29" t="s">
-        <v>332</v>
-      </c>
-      <c r="B20" s="30"/>
-      <c r="C20" s="30"/>
-      <c r="D20" s="30"/>
-      <c r="E20" s="30"/>
-      <c r="F20" s="30"/>
-      <c r="G20" s="30"/>
-      <c r="H20" s="30"/>
-      <c r="I20" s="30"/>
-      <c r="J20" s="31"/>
-    </row>
-    <row r="21" ht="42.0" customHeight="1">
-      <c r="A21" s="41" t="s">
-        <v>333</v>
-      </c>
-      <c r="B21" s="21" t="s">
-        <v>334</v>
-      </c>
-      <c r="C21" s="32" t="s">
+      <c r="J20" s="23"/>
+    </row>
+    <row r="21" ht="18.0" customHeight="1">
+      <c r="A21" s="29" t="s">
+        <v>336</v>
+      </c>
+      <c r="B21" s="30"/>
+      <c r="C21" s="30"/>
+      <c r="D21" s="30"/>
+      <c r="E21" s="30"/>
+      <c r="F21" s="30"/>
+      <c r="G21" s="30"/>
+      <c r="H21" s="30"/>
+      <c r="I21" s="30"/>
+      <c r="J21" s="31"/>
+    </row>
+    <row r="22" ht="42.0" customHeight="1">
+      <c r="A22" s="41" t="s">
+        <v>337</v>
+      </c>
+      <c r="B22" s="21" t="s">
+        <v>338</v>
+      </c>
+      <c r="C22" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="D21" s="21" t="s">
-        <v>335</v>
-      </c>
-      <c r="E21" s="21" t="s">
+      <c r="D22" s="21" t="s">
+        <v>339</v>
+      </c>
+      <c r="E22" s="21" t="s">
         <v>198</v>
       </c>
-      <c r="F21" s="21" t="s">
+      <c r="F22" s="21" t="s">
         <v>141</v>
       </c>
-      <c r="G21" s="21" t="s">
-        <v>336</v>
-      </c>
-      <c r="H21" s="33" t="s">
-        <v>70</v>
-      </c>
-      <c r="I21" s="21" t="s">
-        <v>337</v>
-      </c>
-      <c r="J21" s="23"/>
-    </row>
-    <row r="22" ht="42.0" customHeight="1">
-      <c r="A22" s="38" t="s">
-        <v>338</v>
-      </c>
-      <c r="B22" s="20" t="s">
-        <v>339</v>
-      </c>
-      <c r="C22" s="56" t="s">
+      <c r="G22" s="21" t="s">
         <v>340</v>
-      </c>
-      <c r="D22" s="20" t="s">
-        <v>341</v>
-      </c>
-      <c r="E22" s="20" t="s">
-        <v>198</v>
-      </c>
-      <c r="F22" s="20" t="s">
-        <v>141</v>
-      </c>
-      <c r="G22" s="20" t="s">
-        <v>342</v>
       </c>
       <c r="H22" s="33" t="s">
         <v>70</v>
       </c>
-      <c r="I22" s="20" t="s">
+      <c r="I22" s="21" t="s">
+        <v>341</v>
+      </c>
+      <c r="J22" s="23"/>
+    </row>
+    <row r="23" ht="42.0" customHeight="1">
+      <c r="A23" s="38" t="s">
+        <v>342</v>
+      </c>
+      <c r="B23" s="20" t="s">
         <v>343</v>
       </c>
-      <c r="J22" s="34"/>
+      <c r="C23" s="56" t="s">
+        <v>344</v>
+      </c>
+      <c r="D23" s="20" t="s">
+        <v>345</v>
+      </c>
+      <c r="E23" s="20" t="s">
+        <v>198</v>
+      </c>
+      <c r="F23" s="20" t="s">
+        <v>141</v>
+      </c>
+      <c r="G23" s="20" t="s">
+        <v>346</v>
+      </c>
+      <c r="H23" s="33" t="s">
+        <v>70</v>
+      </c>
+      <c r="I23" s="20" t="s">
+        <v>347</v>
+      </c>
+      <c r="J23" s="34"/>
+    </row>
+    <row r="24" ht="15.75" customHeight="1"/>
+    <row r="25" ht="15.75" customHeight="1"/>
+    <row r="26" ht="15.75" customHeight="1"/>
+    <row r="27" ht="15.75" customHeight="1"/>
+    <row r="28" ht="15.75" customHeight="1"/>
+    <row r="29" ht="15.75" customHeight="1"/>
+    <row r="30" ht="15.75" customHeight="1"/>
+    <row r="31" ht="15.75" customHeight="1"/>
+    <row r="32" ht="15.75" customHeight="1"/>
+    <row r="33" ht="15.75" customHeight="1"/>
+    <row r="34" ht="15.75" customHeight="1"/>
+    <row r="35" ht="15.75" customHeight="1"/>
+    <row r="36" ht="15.75" customHeight="1"/>
+    <row r="37" ht="15.75" customHeight="1"/>
+    <row r="38" ht="15.75" customHeight="1"/>
+    <row r="39" ht="15.75" customHeight="1"/>
+    <row r="40" ht="15.75" customHeight="1"/>
+    <row r="41" ht="15.75" customHeight="1"/>
+    <row r="42" ht="15.75" customHeight="1"/>
+    <row r="43" ht="15.75" customHeight="1"/>
+    <row r="44" ht="15.75" customHeight="1"/>
+    <row r="45" ht="15.75" customHeight="1"/>
+    <row r="46" ht="15.75" customHeight="1"/>
+    <row r="47" ht="15.75" customHeight="1"/>
+    <row r="48" ht="15.75" customHeight="1"/>
+    <row r="49" ht="15.75" customHeight="1"/>
+    <row r="50" ht="15.75" customHeight="1"/>
+    <row r="51" ht="15.75" customHeight="1"/>
+    <row r="52" ht="15.75" customHeight="1"/>
+    <row r="53" ht="15.75" customHeight="1"/>
+    <row r="54" ht="15.75" customHeight="1"/>
+    <row r="55" ht="15.75" customHeight="1"/>
+    <row r="56" ht="15.75" customHeight="1"/>
+    <row r="57" ht="15.75" customHeight="1"/>
+    <row r="58" ht="15.75" customHeight="1"/>
+    <row r="59" ht="15.75" customHeight="1"/>
+    <row r="60" ht="15.75" customHeight="1"/>
+    <row r="61" ht="15.75" customHeight="1"/>
+    <row r="62" ht="15.75" customHeight="1"/>
+    <row r="63" ht="15.75" customHeight="1"/>
+    <row r="64" ht="15.75" customHeight="1"/>
+    <row r="65" ht="15.75" customHeight="1"/>
+    <row r="66" ht="15.75" customHeight="1"/>
+    <row r="67" ht="15.75" customHeight="1"/>
+    <row r="68" ht="15.75" customHeight="1"/>
+    <row r="69" ht="15.75" customHeight="1"/>
+    <row r="70" ht="15.75" customHeight="1"/>
+    <row r="71" ht="15.75" customHeight="1"/>
+    <row r="72" ht="15.75" customHeight="1"/>
+    <row r="73" ht="15.75" customHeight="1"/>
+    <row r="74" ht="15.75" customHeight="1"/>
+    <row r="75" ht="15.75" customHeight="1"/>
+    <row r="76" ht="15.75" customHeight="1"/>
+    <row r="77" ht="15.75" customHeight="1"/>
+    <row r="78" ht="15.75" customHeight="1"/>
+    <row r="79" ht="15.75" customHeight="1"/>
+    <row r="80" ht="15.75" customHeight="1"/>
+    <row r="81" ht="15.75" customHeight="1"/>
+    <row r="82" ht="15.75" customHeight="1"/>
+    <row r="83" ht="15.75" customHeight="1"/>
+    <row r="84" ht="15.75" customHeight="1"/>
+    <row r="85" ht="15.75" customHeight="1"/>
+    <row r="86" ht="15.75" customHeight="1"/>
+    <row r="87" ht="15.75" customHeight="1"/>
+    <row r="88" ht="15.75" customHeight="1"/>
+    <row r="89" ht="15.75" customHeight="1"/>
+    <row r="90" ht="15.75" customHeight="1"/>
+    <row r="91" ht="15.75" customHeight="1"/>
+    <row r="92" ht="15.75" customHeight="1"/>
+    <row r="93" ht="15.75" customHeight="1"/>
+    <row r="94" ht="15.75" customHeight="1"/>
+    <row r="95" ht="15.75" customHeight="1"/>
+    <row r="96" ht="15.75" customHeight="1"/>
+    <row r="97" ht="15.75" customHeight="1"/>
+    <row r="98" ht="15.75" customHeight="1"/>
+    <row r="99" ht="15.75" customHeight="1"/>
+    <row r="100" ht="15.75" customHeight="1"/>
+    <row r="101" ht="15.75" customHeight="1"/>
+    <row r="102" ht="15.75" customHeight="1"/>
+    <row r="103" ht="15.75" customHeight="1"/>
+    <row r="104" ht="15.75" customHeight="1"/>
+    <row r="105" ht="15.75" customHeight="1"/>
+    <row r="106" ht="15.75" customHeight="1"/>
+    <row r="107" ht="15.75" customHeight="1"/>
+    <row r="108" ht="15.75" customHeight="1"/>
+    <row r="109" ht="15.75" customHeight="1"/>
+    <row r="110" ht="15.75" customHeight="1"/>
+    <row r="111" ht="15.75" customHeight="1"/>
+    <row r="112" ht="15.75" customHeight="1"/>
+    <row r="113" ht="15.75" customHeight="1"/>
+    <row r="114" ht="15.75" customHeight="1"/>
+    <row r="115" ht="15.75" customHeight="1"/>
+    <row r="116" ht="15.75" customHeight="1"/>
+    <row r="117" ht="15.75" customHeight="1"/>
+    <row r="118" ht="15.75" customHeight="1"/>
+    <row r="119" ht="15.75" customHeight="1"/>
+    <row r="120" ht="15.75" customHeight="1"/>
+    <row r="121" ht="15.75" customHeight="1"/>
+    <row r="122" ht="15.75" customHeight="1"/>
+    <row r="123" ht="15.75" customHeight="1"/>
+    <row r="124" ht="15.75" customHeight="1"/>
+    <row r="125" ht="15.75" customHeight="1"/>
+    <row r="126" ht="15.75" customHeight="1"/>
+    <row r="127" ht="15.75" customHeight="1"/>
+    <row r="128" ht="15.75" customHeight="1"/>
+    <row r="129" ht="15.75" customHeight="1"/>
+    <row r="130" ht="15.75" customHeight="1"/>
+    <row r="131" ht="15.75" customHeight="1"/>
+    <row r="132" ht="15.75" customHeight="1"/>
+    <row r="133" ht="15.75" customHeight="1"/>
+    <row r="134" ht="15.75" customHeight="1"/>
+    <row r="135" ht="15.75" customHeight="1"/>
+    <row r="136" ht="15.75" customHeight="1"/>
+    <row r="137" ht="15.75" customHeight="1"/>
+    <row r="138" ht="15.75" customHeight="1"/>
+    <row r="139" ht="15.75" customHeight="1"/>
+    <row r="140" ht="15.75" customHeight="1"/>
+    <row r="141" ht="15.75" customHeight="1"/>
+    <row r="142" ht="15.75" customHeight="1"/>
+    <row r="143" ht="15.75" customHeight="1"/>
+    <row r="144" ht="15.75" customHeight="1"/>
+    <row r="145" ht="15.75" customHeight="1"/>
+    <row r="146" ht="15.75" customHeight="1"/>
+    <row r="147" ht="15.75" customHeight="1"/>
+    <row r="148" ht="15.75" customHeight="1"/>
+    <row r="149" ht="15.75" customHeight="1"/>
+    <row r="150" ht="15.75" customHeight="1"/>
+    <row r="151" ht="15.75" customHeight="1"/>
+    <row r="152" ht="15.75" customHeight="1"/>
+    <row r="153" ht="15.75" customHeight="1"/>
+    <row r="154" ht="15.75" customHeight="1"/>
+    <row r="155" ht="15.75" customHeight="1"/>
+    <row r="156" ht="15.75" customHeight="1"/>
+    <row r="157" ht="15.75" customHeight="1"/>
+    <row r="158" ht="15.75" customHeight="1"/>
+    <row r="159" ht="15.75" customHeight="1"/>
+    <row r="160" ht="15.75" customHeight="1"/>
+    <row r="161" ht="15.75" customHeight="1"/>
+    <row r="162" ht="15.75" customHeight="1"/>
+    <row r="163" ht="15.75" customHeight="1"/>
+    <row r="164" ht="15.75" customHeight="1"/>
+    <row r="165" ht="15.75" customHeight="1"/>
+    <row r="166" ht="15.75" customHeight="1"/>
+    <row r="167" ht="15.75" customHeight="1"/>
+    <row r="168" ht="15.75" customHeight="1"/>
+    <row r="169" ht="15.75" customHeight="1"/>
+    <row r="170" ht="15.75" customHeight="1"/>
+    <row r="171" ht="15.75" customHeight="1"/>
+    <row r="172" ht="15.75" customHeight="1"/>
+    <row r="173" ht="15.75" customHeight="1"/>
+    <row r="174" ht="15.75" customHeight="1"/>
+    <row r="175" ht="15.75" customHeight="1"/>
+    <row r="176" ht="15.75" customHeight="1"/>
+    <row r="177" ht="15.75" customHeight="1"/>
+    <row r="178" ht="15.75" customHeight="1"/>
+    <row r="179" ht="15.75" customHeight="1"/>
+    <row r="180" ht="15.75" customHeight="1"/>
+    <row r="181" ht="15.75" customHeight="1"/>
+    <row r="182" ht="15.75" customHeight="1"/>
+    <row r="183" ht="15.75" customHeight="1"/>
+    <row r="184" ht="15.75" customHeight="1"/>
+    <row r="185" ht="15.75" customHeight="1"/>
+    <row r="186" ht="15.75" customHeight="1"/>
+    <row r="187" ht="15.75" customHeight="1"/>
+    <row r="188" ht="15.75" customHeight="1"/>
+    <row r="189" ht="15.75" customHeight="1"/>
+    <row r="190" ht="15.75" customHeight="1"/>
+    <row r="191" ht="15.75" customHeight="1"/>
+    <row r="192" ht="15.75" customHeight="1"/>
+    <row r="193" ht="15.75" customHeight="1"/>
+    <row r="194" ht="15.75" customHeight="1"/>
+    <row r="195" ht="15.75" customHeight="1"/>
+    <row r="196" ht="15.75" customHeight="1"/>
+    <row r="197" ht="15.75" customHeight="1"/>
+    <row r="198" ht="15.75" customHeight="1"/>
+    <row r="199" ht="15.75" customHeight="1"/>
+    <row r="200" ht="15.75" customHeight="1"/>
+    <row r="201" ht="15.75" customHeight="1"/>
+    <row r="202" ht="15.75" customHeight="1"/>
+    <row r="203" ht="15.75" customHeight="1"/>
+    <row r="204" ht="15.75" customHeight="1"/>
+    <row r="205" ht="15.75" customHeight="1"/>
+    <row r="206" ht="15.75" customHeight="1"/>
+    <row r="207" ht="15.75" customHeight="1"/>
+    <row r="208" ht="15.75" customHeight="1"/>
+    <row r="209" ht="15.75" customHeight="1"/>
+    <row r="210" ht="15.75" customHeight="1"/>
+    <row r="211" ht="15.75" customHeight="1"/>
+    <row r="212" ht="15.75" customHeight="1"/>
+    <row r="213" ht="15.75" customHeight="1"/>
+    <row r="214" ht="15.75" customHeight="1"/>
+    <row r="215" ht="15.75" customHeight="1"/>
+    <row r="216" ht="15.75" customHeight="1"/>
+    <row r="217" ht="15.75" customHeight="1"/>
+    <row r="218" ht="15.75" customHeight="1"/>
+    <row r="219" ht="15.75" customHeight="1"/>
+    <row r="220" ht="15.75" customHeight="1"/>
+    <row r="221" ht="15.75" customHeight="1"/>
+    <row r="222" ht="15.75" customHeight="1"/>
+    <row r="223" ht="15.75" customHeight="1"/>
+    <row r="224" ht="15.75" customHeight="1"/>
+    <row r="225" ht="15.75" customHeight="1"/>
+    <row r="226" ht="15.75" customHeight="1"/>
+    <row r="227" ht="15.75" customHeight="1"/>
+    <row r="228" ht="15.75" customHeight="1"/>
+    <row r="229" ht="15.75" customHeight="1"/>
+    <row r="230" ht="15.75" customHeight="1"/>
+    <row r="231" ht="15.75" customHeight="1"/>
+    <row r="232" ht="15.75" customHeight="1"/>
+    <row r="233" ht="15.75" customHeight="1"/>
+    <row r="234" ht="15.75" customHeight="1"/>
+    <row r="235" ht="15.75" customHeight="1"/>
+    <row r="236" ht="15.75" customHeight="1"/>
+    <row r="237" ht="15.75" customHeight="1"/>
+    <row r="238" ht="15.75" customHeight="1"/>
+    <row r="239" ht="15.75" customHeight="1"/>
+    <row r="240" ht="15.75" customHeight="1"/>
+    <row r="241" ht="15.75" customHeight="1"/>
+    <row r="242" ht="15.75" customHeight="1"/>
+    <row r="243" ht="15.75" customHeight="1"/>
+    <row r="244" ht="15.75" customHeight="1"/>
+    <row r="245" ht="15.75" customHeight="1"/>
+    <row r="246" ht="15.75" customHeight="1"/>
+    <row r="247" ht="15.75" customHeight="1"/>
+    <row r="248" ht="15.75" customHeight="1"/>
+    <row r="249" ht="15.75" customHeight="1"/>
+    <row r="250" ht="15.75" customHeight="1"/>
+    <row r="251" ht="15.75" customHeight="1"/>
+    <row r="252" ht="15.75" customHeight="1"/>
+    <row r="253" ht="15.75" customHeight="1"/>
+    <row r="254" ht="15.75" customHeight="1"/>
+    <row r="255" ht="15.75" customHeight="1"/>
+    <row r="256" ht="15.75" customHeight="1"/>
+    <row r="257" ht="15.75" customHeight="1"/>
+    <row r="258" ht="15.75" customHeight="1"/>
+    <row r="259" ht="15.75" customHeight="1"/>
+    <row r="260" ht="15.75" customHeight="1"/>
+    <row r="261" ht="15.75" customHeight="1"/>
+    <row r="262" ht="15.75" customHeight="1"/>
+    <row r="263" ht="15.75" customHeight="1"/>
+    <row r="264" ht="15.75" customHeight="1"/>
+    <row r="265" ht="15.75" customHeight="1"/>
+    <row r="266" ht="15.75" customHeight="1"/>
+    <row r="267" ht="15.75" customHeight="1"/>
+    <row r="268" ht="15.75" customHeight="1"/>
+    <row r="269" ht="15.75" customHeight="1"/>
+    <row r="270" ht="15.75" customHeight="1"/>
+    <row r="271" ht="15.75" customHeight="1"/>
+    <row r="272" ht="15.75" customHeight="1"/>
+    <row r="273" ht="15.75" customHeight="1"/>
+    <row r="274" ht="15.75" customHeight="1"/>
+    <row r="275" ht="15.75" customHeight="1"/>
+    <row r="276" ht="15.75" customHeight="1"/>
+    <row r="277" ht="15.75" customHeight="1"/>
+    <row r="278" ht="15.75" customHeight="1"/>
+    <row r="279" ht="15.75" customHeight="1"/>
+    <row r="280" ht="15.75" customHeight="1"/>
+    <row r="281" ht="15.75" customHeight="1"/>
+    <row r="282" ht="15.75" customHeight="1"/>
+    <row r="283" ht="15.75" customHeight="1"/>
+    <row r="284" ht="15.75" customHeight="1"/>
+    <row r="285" ht="15.75" customHeight="1"/>
+    <row r="286" ht="15.75" customHeight="1"/>
+    <row r="287" ht="15.75" customHeight="1"/>
+    <row r="288" ht="15.75" customHeight="1"/>
+    <row r="289" ht="15.75" customHeight="1"/>
+    <row r="290" ht="15.75" customHeight="1"/>
+    <row r="291" ht="15.75" customHeight="1"/>
+    <row r="292" ht="15.75" customHeight="1"/>
+    <row r="293" ht="15.75" customHeight="1"/>
+    <row r="294" ht="15.75" customHeight="1"/>
+    <row r="295" ht="15.75" customHeight="1"/>
+    <row r="296" ht="15.75" customHeight="1"/>
+    <row r="297" ht="15.75" customHeight="1"/>
+    <row r="298" ht="15.75" customHeight="1"/>
+    <row r="299" ht="15.75" customHeight="1"/>
+    <row r="300" ht="15.75" customHeight="1"/>
+    <row r="301" ht="15.75" customHeight="1"/>
+    <row r="302" ht="15.75" customHeight="1"/>
+    <row r="303" ht="15.75" customHeight="1"/>
+    <row r="304" ht="15.75" customHeight="1"/>
+    <row r="305" ht="15.75" customHeight="1"/>
+    <row r="306" ht="15.75" customHeight="1"/>
+    <row r="307" ht="15.75" customHeight="1"/>
+    <row r="308" ht="15.75" customHeight="1"/>
+    <row r="309" ht="15.75" customHeight="1"/>
+    <row r="310" ht="15.75" customHeight="1"/>
+    <row r="311" ht="15.75" customHeight="1"/>
+    <row r="312" ht="15.75" customHeight="1"/>
+    <row r="313" ht="15.75" customHeight="1"/>
+    <row r="314" ht="15.75" customHeight="1"/>
+    <row r="315" ht="15.75" customHeight="1"/>
+    <row r="316" ht="15.75" customHeight="1"/>
+    <row r="317" ht="15.75" customHeight="1"/>
+    <row r="318" ht="15.75" customHeight="1"/>
+    <row r="319" ht="15.75" customHeight="1"/>
+    <row r="320" ht="15.75" customHeight="1"/>
+    <row r="321" ht="15.75" customHeight="1"/>
+    <row r="322" ht="15.75" customHeight="1"/>
+    <row r="323" ht="15.75" customHeight="1"/>
+    <row r="324" ht="15.75" customHeight="1"/>
+    <row r="325" ht="15.75" customHeight="1"/>
+    <row r="326" ht="15.75" customHeight="1"/>
+    <row r="327" ht="15.75" customHeight="1"/>
+    <row r="328" ht="15.75" customHeight="1"/>
+    <row r="329" ht="15.75" customHeight="1"/>
+    <row r="330" ht="15.75" customHeight="1"/>
+    <row r="331" ht="15.75" customHeight="1"/>
+    <row r="332" ht="15.75" customHeight="1"/>
+    <row r="333" ht="15.75" customHeight="1"/>
+    <row r="334" ht="15.75" customHeight="1"/>
+    <row r="335" ht="15.75" customHeight="1"/>
+    <row r="336" ht="15.75" customHeight="1"/>
+    <row r="337" ht="15.75" customHeight="1"/>
+    <row r="338" ht="15.75" customHeight="1"/>
+    <row r="339" ht="15.75" customHeight="1"/>
+    <row r="340" ht="15.75" customHeight="1"/>
+    <row r="341" ht="15.75" customHeight="1"/>
+    <row r="342" ht="15.75" customHeight="1"/>
+    <row r="343" ht="15.75" customHeight="1"/>
+    <row r="344" ht="15.75" customHeight="1"/>
+    <row r="345" ht="15.75" customHeight="1"/>
+    <row r="346" ht="15.75" customHeight="1"/>
+    <row r="347" ht="15.75" customHeight="1"/>
+    <row r="348" ht="15.75" customHeight="1"/>
+    <row r="349" ht="15.75" customHeight="1"/>
+    <row r="350" ht="15.75" customHeight="1"/>
+    <row r="351" ht="15.75" customHeight="1"/>
+    <row r="352" ht="15.75" customHeight="1"/>
+    <row r="353" ht="15.75" customHeight="1"/>
+    <row r="354" ht="15.75" customHeight="1"/>
+    <row r="355" ht="15.75" customHeight="1"/>
+    <row r="356" ht="15.75" customHeight="1"/>
+    <row r="357" ht="15.75" customHeight="1"/>
+    <row r="358" ht="15.75" customHeight="1"/>
+    <row r="359" ht="15.75" customHeight="1"/>
+    <row r="360" ht="15.75" customHeight="1"/>
+    <row r="361" ht="15.75" customHeight="1"/>
+    <row r="362" ht="15.75" customHeight="1"/>
+    <row r="363" ht="15.75" customHeight="1"/>
+    <row r="364" ht="15.75" customHeight="1"/>
+    <row r="365" ht="15.75" customHeight="1"/>
+    <row r="366" ht="15.75" customHeight="1"/>
+    <row r="367" ht="15.75" customHeight="1"/>
+    <row r="368" ht="15.75" customHeight="1"/>
+    <row r="369" ht="15.75" customHeight="1"/>
+    <row r="370" ht="15.75" customHeight="1"/>
+    <row r="371" ht="15.75" customHeight="1"/>
+    <row r="372" ht="15.75" customHeight="1"/>
+    <row r="373" ht="15.75" customHeight="1"/>
+    <row r="374" ht="15.75" customHeight="1"/>
+    <row r="375" ht="15.75" customHeight="1"/>
+    <row r="376" ht="15.75" customHeight="1"/>
+    <row r="377" ht="15.75" customHeight="1"/>
+    <row r="378" ht="15.75" customHeight="1"/>
+    <row r="379" ht="15.75" customHeight="1"/>
+    <row r="380" ht="15.75" customHeight="1"/>
+    <row r="381" ht="15.75" customHeight="1"/>
+    <row r="382" ht="15.75" customHeight="1"/>
+    <row r="383" ht="15.75" customHeight="1"/>
+    <row r="384" ht="15.75" customHeight="1"/>
+    <row r="385" ht="15.75" customHeight="1"/>
+    <row r="386" ht="15.75" customHeight="1"/>
+    <row r="387" ht="15.75" customHeight="1"/>
+    <row r="388" ht="15.75" customHeight="1"/>
+    <row r="389" ht="15.75" customHeight="1"/>
+    <row r="390" ht="15.75" customHeight="1"/>
+    <row r="391" ht="15.75" customHeight="1"/>
+    <row r="392" ht="15.75" customHeight="1"/>
+    <row r="393" ht="15.75" customHeight="1"/>
+    <row r="394" ht="15.75" customHeight="1"/>
+    <row r="395" ht="15.75" customHeight="1"/>
+    <row r="396" ht="15.75" customHeight="1"/>
+    <row r="397" ht="15.75" customHeight="1"/>
+    <row r="398" ht="15.75" customHeight="1"/>
+    <row r="399" ht="15.75" customHeight="1"/>
+    <row r="400" ht="15.75" customHeight="1"/>
+    <row r="401" ht="15.75" customHeight="1"/>
+    <row r="402" ht="15.75" customHeight="1"/>
+    <row r="403" ht="15.75" customHeight="1"/>
+    <row r="404" ht="15.75" customHeight="1"/>
+    <row r="405" ht="15.75" customHeight="1"/>
+    <row r="406" ht="15.75" customHeight="1"/>
+    <row r="407" ht="15.75" customHeight="1"/>
+    <row r="408" ht="15.75" customHeight="1"/>
+    <row r="409" ht="15.75" customHeight="1"/>
+    <row r="410" ht="15.75" customHeight="1"/>
+    <row r="411" ht="15.75" customHeight="1"/>
+    <row r="412" ht="15.75" customHeight="1"/>
+    <row r="413" ht="15.75" customHeight="1"/>
+    <row r="414" ht="15.75" customHeight="1"/>
+    <row r="415" ht="15.75" customHeight="1"/>
+    <row r="416" ht="15.75" customHeight="1"/>
+    <row r="417" ht="15.75" customHeight="1"/>
+    <row r="418" ht="15.75" customHeight="1"/>
+    <row r="419" ht="15.75" customHeight="1"/>
+    <row r="420" ht="15.75" customHeight="1"/>
+    <row r="421" ht="15.75" customHeight="1"/>
+    <row r="422" ht="15.75" customHeight="1"/>
+    <row r="423" ht="15.75" customHeight="1"/>
+    <row r="424" ht="15.75" customHeight="1"/>
+    <row r="425" ht="15.75" customHeight="1"/>
+    <row r="426" ht="15.75" customHeight="1"/>
+    <row r="427" ht="15.75" customHeight="1"/>
+    <row r="428" ht="15.75" customHeight="1"/>
+    <row r="429" ht="15.75" customHeight="1"/>
+    <row r="430" ht="15.75" customHeight="1"/>
+    <row r="431" ht="15.75" customHeight="1"/>
+    <row r="432" ht="15.75" customHeight="1"/>
+    <row r="433" ht="15.75" customHeight="1"/>
+    <row r="434" ht="15.75" customHeight="1"/>
+    <row r="435" ht="15.75" customHeight="1"/>
+    <row r="436" ht="15.75" customHeight="1"/>
+    <row r="437" ht="15.75" customHeight="1"/>
+    <row r="438" ht="15.75" customHeight="1"/>
+    <row r="439" ht="15.75" customHeight="1"/>
+    <row r="440" ht="15.75" customHeight="1"/>
+    <row r="441" ht="15.75" customHeight="1"/>
+    <row r="442" ht="15.75" customHeight="1"/>
+    <row r="443" ht="15.75" customHeight="1"/>
+    <row r="444" ht="15.75" customHeight="1"/>
+    <row r="445" ht="15.75" customHeight="1"/>
+    <row r="446" ht="15.75" customHeight="1"/>
+    <row r="447" ht="15.75" customHeight="1"/>
+    <row r="448" ht="15.75" customHeight="1"/>
+    <row r="449" ht="15.75" customHeight="1"/>
+    <row r="450" ht="15.75" customHeight="1"/>
+    <row r="451" ht="15.75" customHeight="1"/>
+    <row r="452" ht="15.75" customHeight="1"/>
+    <row r="453" ht="15.75" customHeight="1"/>
+    <row r="454" ht="15.75" customHeight="1"/>
+    <row r="455" ht="15.75" customHeight="1"/>
+    <row r="456" ht="15.75" customHeight="1"/>
+    <row r="457" ht="15.75" customHeight="1"/>
+    <row r="458" ht="15.75" customHeight="1"/>
+    <row r="459" ht="15.75" customHeight="1"/>
+    <row r="460" ht="15.75" customHeight="1"/>
+    <row r="461" ht="15.75" customHeight="1"/>
+    <row r="462" ht="15.75" customHeight="1"/>
+    <row r="463" ht="15.75" customHeight="1"/>
+    <row r="464" ht="15.75" customHeight="1"/>
+    <row r="465" ht="15.75" customHeight="1"/>
+    <row r="466" ht="15.75" customHeight="1"/>
+    <row r="467" ht="15.75" customHeight="1"/>
+    <row r="468" ht="15.75" customHeight="1"/>
+    <row r="469" ht="15.75" customHeight="1"/>
+    <row r="470" ht="15.75" customHeight="1"/>
+    <row r="471" ht="15.75" customHeight="1"/>
+    <row r="472" ht="15.75" customHeight="1"/>
+    <row r="473" ht="15.75" customHeight="1"/>
+    <row r="474" ht="15.75" customHeight="1"/>
+    <row r="475" ht="15.75" customHeight="1"/>
+    <row r="476" ht="15.75" customHeight="1"/>
+    <row r="477" ht="15.75" customHeight="1"/>
+    <row r="478" ht="15.75" customHeight="1"/>
+    <row r="479" ht="15.75" customHeight="1"/>
+    <row r="480" ht="15.75" customHeight="1"/>
+    <row r="481" ht="15.75" customHeight="1"/>
+    <row r="482" ht="15.75" customHeight="1"/>
+    <row r="483" ht="15.75" customHeight="1"/>
+    <row r="484" ht="15.75" customHeight="1"/>
+    <row r="485" ht="15.75" customHeight="1"/>
+    <row r="486" ht="15.75" customHeight="1"/>
+    <row r="487" ht="15.75" customHeight="1"/>
+    <row r="488" ht="15.75" customHeight="1"/>
+    <row r="489" ht="15.75" customHeight="1"/>
+    <row r="490" ht="15.75" customHeight="1"/>
+    <row r="491" ht="15.75" customHeight="1"/>
+    <row r="492" ht="15.75" customHeight="1"/>
+    <row r="493" ht="15.75" customHeight="1"/>
+    <row r="494" ht="15.75" customHeight="1"/>
+    <row r="495" ht="15.75" customHeight="1"/>
+    <row r="496" ht="15.75" customHeight="1"/>
+    <row r="497" ht="15.75" customHeight="1"/>
+    <row r="498" ht="15.75" customHeight="1"/>
+    <row r="499" ht="15.75" customHeight="1"/>
+    <row r="500" ht="15.75" customHeight="1"/>
+    <row r="501" ht="15.75" customHeight="1"/>
+    <row r="502" ht="15.75" customHeight="1"/>
+    <row r="503" ht="15.75" customHeight="1"/>
+    <row r="504" ht="15.75" customHeight="1"/>
+    <row r="505" ht="15.75" customHeight="1"/>
+    <row r="506" ht="15.75" customHeight="1"/>
+    <row r="507" ht="15.75" customHeight="1"/>
+    <row r="508" ht="15.75" customHeight="1"/>
+    <row r="509" ht="15.75" customHeight="1"/>
+    <row r="510" ht="15.75" customHeight="1"/>
+    <row r="511" ht="15.75" customHeight="1"/>
+    <row r="512" ht="15.75" customHeight="1"/>
+    <row r="513" ht="15.75" customHeight="1"/>
+    <row r="514" ht="15.75" customHeight="1"/>
+    <row r="515" ht="15.75" customHeight="1"/>
+    <row r="516" ht="15.75" customHeight="1"/>
+    <row r="517" ht="15.75" customHeight="1"/>
+    <row r="518" ht="15.75" customHeight="1"/>
+    <row r="519" ht="15.75" customHeight="1"/>
+    <row r="520" ht="15.75" customHeight="1"/>
+    <row r="521" ht="15.75" customHeight="1"/>
+    <row r="522" ht="15.75" customHeight="1"/>
+    <row r="523" ht="15.75" customHeight="1"/>
+    <row r="524" ht="15.75" customHeight="1"/>
+    <row r="525" ht="15.75" customHeight="1"/>
+    <row r="526" ht="15.75" customHeight="1"/>
+    <row r="527" ht="15.75" customHeight="1"/>
+    <row r="528" ht="15.75" customHeight="1"/>
+    <row r="529" ht="15.75" customHeight="1"/>
+    <row r="530" ht="15.75" customHeight="1"/>
+    <row r="531" ht="15.75" customHeight="1"/>
+    <row r="532" ht="15.75" customHeight="1"/>
+    <row r="533" ht="15.75" customHeight="1"/>
+    <row r="534" ht="15.75" customHeight="1"/>
+    <row r="535" ht="15.75" customHeight="1"/>
+    <row r="536" ht="15.75" customHeight="1"/>
+    <row r="537" ht="15.75" customHeight="1"/>
+    <row r="538" ht="15.75" customHeight="1"/>
+    <row r="539" ht="15.75" customHeight="1"/>
+    <row r="540" ht="15.75" customHeight="1"/>
+    <row r="541" ht="15.75" customHeight="1"/>
+    <row r="542" ht="15.75" customHeight="1"/>
+    <row r="543" ht="15.75" customHeight="1"/>
+    <row r="544" ht="15.75" customHeight="1"/>
+    <row r="545" ht="15.75" customHeight="1"/>
+    <row r="546" ht="15.75" customHeight="1"/>
+    <row r="547" ht="15.75" customHeight="1"/>
+    <row r="548" ht="15.75" customHeight="1"/>
+    <row r="549" ht="15.75" customHeight="1"/>
+    <row r="550" ht="15.75" customHeight="1"/>
+    <row r="551" ht="15.75" customHeight="1"/>
+    <row r="552" ht="15.75" customHeight="1"/>
+    <row r="553" ht="15.75" customHeight="1"/>
+    <row r="554" ht="15.75" customHeight="1"/>
+    <row r="555" ht="15.75" customHeight="1"/>
+    <row r="556" ht="15.75" customHeight="1"/>
+    <row r="557" ht="15.75" customHeight="1"/>
+    <row r="558" ht="15.75" customHeight="1"/>
+    <row r="559" ht="15.75" customHeight="1"/>
+    <row r="560" ht="15.75" customHeight="1"/>
+    <row r="561" ht="15.75" customHeight="1"/>
+    <row r="562" ht="15.75" customHeight="1"/>
+    <row r="563" ht="15.75" customHeight="1"/>
+    <row r="564" ht="15.75" customHeight="1"/>
+    <row r="565" ht="15.75" customHeight="1"/>
+    <row r="566" ht="15.75" customHeight="1"/>
+    <row r="567" ht="15.75" customHeight="1"/>
+    <row r="568" ht="15.75" customHeight="1"/>
+    <row r="569" ht="15.75" customHeight="1"/>
+    <row r="570" ht="15.75" customHeight="1"/>
+    <row r="571" ht="15.75" customHeight="1"/>
+    <row r="572" ht="15.75" customHeight="1"/>
+    <row r="573" ht="15.75" customHeight="1"/>
+    <row r="574" ht="15.75" customHeight="1"/>
+    <row r="575" ht="15.75" customHeight="1"/>
+    <row r="576" ht="15.75" customHeight="1"/>
+    <row r="577" ht="15.75" customHeight="1"/>
+    <row r="578" ht="15.75" customHeight="1"/>
+    <row r="579" ht="15.75" customHeight="1"/>
+    <row r="580" ht="15.75" customHeight="1"/>
+    <row r="581" ht="15.75" customHeight="1"/>
+    <row r="582" ht="15.75" customHeight="1"/>
+    <row r="583" ht="15.75" customHeight="1"/>
+    <row r="584" ht="15.75" customHeight="1"/>
+    <row r="585" ht="15.75" customHeight="1"/>
+    <row r="586" ht="15.75" customHeight="1"/>
+    <row r="587" ht="15.75" customHeight="1"/>
+    <row r="588" ht="15.75" customHeight="1"/>
+    <row r="589" ht="15.75" customHeight="1"/>
+    <row r="590" ht="15.75" customHeight="1"/>
+    <row r="591" ht="15.75" customHeight="1"/>
+    <row r="592" ht="15.75" customHeight="1"/>
+    <row r="593" ht="15.75" customHeight="1"/>
+    <row r="594" ht="15.75" customHeight="1"/>
+    <row r="595" ht="15.75" customHeight="1"/>
+    <row r="596" ht="15.75" customHeight="1"/>
+    <row r="597" ht="15.75" customHeight="1"/>
+    <row r="598" ht="15.75" customHeight="1"/>
+    <row r="599" ht="15.75" customHeight="1"/>
+    <row r="600" ht="15.75" customHeight="1"/>
+    <row r="601" ht="15.75" customHeight="1"/>
+    <row r="602" ht="15.75" customHeight="1"/>
+    <row r="603" ht="15.75" customHeight="1"/>
+    <row r="604" ht="15.75" customHeight="1"/>
+    <row r="605" ht="15.75" customHeight="1"/>
+    <row r="606" ht="15.75" customHeight="1"/>
+    <row r="607" ht="15.75" customHeight="1"/>
+    <row r="608" ht="15.75" customHeight="1"/>
+    <row r="609" ht="15.75" customHeight="1"/>
+    <row r="610" ht="15.75" customHeight="1"/>
+    <row r="611" ht="15.75" customHeight="1"/>
+    <row r="612" ht="15.75" customHeight="1"/>
+    <row r="613" ht="15.75" customHeight="1"/>
+    <row r="614" ht="15.75" customHeight="1"/>
+    <row r="615" ht="15.75" customHeight="1"/>
+    <row r="616" ht="15.75" customHeight="1"/>
+    <row r="617" ht="15.75" customHeight="1"/>
+    <row r="618" ht="15.75" customHeight="1"/>
+    <row r="619" ht="15.75" customHeight="1"/>
+    <row r="620" ht="15.75" customHeight="1"/>
+    <row r="621" ht="15.75" customHeight="1"/>
+    <row r="622" ht="15.75" customHeight="1"/>
+    <row r="623" ht="15.75" customHeight="1"/>
+    <row r="624" ht="15.75" customHeight="1"/>
+    <row r="625" ht="15.75" customHeight="1"/>
+    <row r="626" ht="15.75" customHeight="1"/>
+    <row r="627" ht="15.75" customHeight="1"/>
+    <row r="628" ht="15.75" customHeight="1"/>
+    <row r="629" ht="15.75" customHeight="1"/>
+    <row r="630" ht="15.75" customHeight="1"/>
+    <row r="631" ht="15.75" customHeight="1"/>
+    <row r="632" ht="15.75" customHeight="1"/>
+    <row r="633" ht="15.75" customHeight="1"/>
+    <row r="634" ht="15.75" customHeight="1"/>
+    <row r="635" ht="15.75" customHeight="1"/>
+    <row r="636" ht="15.75" customHeight="1"/>
+    <row r="637" ht="15.75" customHeight="1"/>
+    <row r="638" ht="15.75" customHeight="1"/>
+    <row r="639" ht="15.75" customHeight="1"/>
+    <row r="640" ht="15.75" customHeight="1"/>
+    <row r="641" ht="15.75" customHeight="1"/>
+    <row r="642" ht="15.75" customHeight="1"/>
+    <row r="643" ht="15.75" customHeight="1"/>
+    <row r="644" ht="15.75" customHeight="1"/>
+    <row r="645" ht="15.75" customHeight="1"/>
+    <row r="646" ht="15.75" customHeight="1"/>
+    <row r="647" ht="15.75" customHeight="1"/>
+    <row r="648" ht="15.75" customHeight="1"/>
+    <row r="649" ht="15.75" customHeight="1"/>
+    <row r="650" ht="15.75" customHeight="1"/>
+    <row r="651" ht="15.75" customHeight="1"/>
+    <row r="652" ht="15.75" customHeight="1"/>
+    <row r="653" ht="15.75" customHeight="1"/>
+    <row r="654" ht="15.75" customHeight="1"/>
+    <row r="655" ht="15.75" customHeight="1"/>
+    <row r="656" ht="15.75" customHeight="1"/>
+    <row r="657" ht="15.75" customHeight="1"/>
+    <row r="658" ht="15.75" customHeight="1"/>
+    <row r="659" ht="15.75" customHeight="1"/>
+    <row r="660" ht="15.75" customHeight="1"/>
+    <row r="661" ht="15.75" customHeight="1"/>
+    <row r="662" ht="15.75" customHeight="1"/>
+    <row r="663" ht="15.75" customHeight="1"/>
+    <row r="664" ht="15.75" customHeight="1"/>
+    <row r="665" ht="15.75" customHeight="1"/>
+    <row r="666" ht="15.75" customHeight="1"/>
+    <row r="667" ht="15.75" customHeight="1"/>
+    <row r="668" ht="15.75" customHeight="1"/>
+    <row r="669" ht="15.75" customHeight="1"/>
+    <row r="670" ht="15.75" customHeight="1"/>
+    <row r="671" ht="15.75" customHeight="1"/>
+    <row r="672" ht="15.75" customHeight="1"/>
+    <row r="673" ht="15.75" customHeight="1"/>
+    <row r="674" ht="15.75" customHeight="1"/>
+    <row r="675" ht="15.75" customHeight="1"/>
+    <row r="676" ht="15.75" customHeight="1"/>
+    <row r="677" ht="15.75" customHeight="1"/>
+    <row r="678" ht="15.75" customHeight="1"/>
+    <row r="679" ht="15.75" customHeight="1"/>
+    <row r="680" ht="15.75" customHeight="1"/>
+    <row r="681" ht="15.75" customHeight="1"/>
+    <row r="682" ht="15.75" customHeight="1"/>
+    <row r="683" ht="15.75" customHeight="1"/>
+    <row r="684" ht="15.75" customHeight="1"/>
+    <row r="685" ht="15.75" customHeight="1"/>
+    <row r="686" ht="15.75" customHeight="1"/>
+    <row r="687" ht="15.75" customHeight="1"/>
+    <row r="688" ht="15.75" customHeight="1"/>
+    <row r="689" ht="15.75" customHeight="1"/>
+    <row r="690" ht="15.75" customHeight="1"/>
+    <row r="691" ht="15.75" customHeight="1"/>
+    <row r="692" ht="15.75" customHeight="1"/>
+    <row r="693" ht="15.75" customHeight="1"/>
+    <row r="694" ht="15.75" customHeight="1"/>
+    <row r="695" ht="15.75" customHeight="1"/>
+    <row r="696" ht="15.75" customHeight="1"/>
+    <row r="697" ht="15.75" customHeight="1"/>
+    <row r="698" ht="15.75" customHeight="1"/>
+    <row r="699" ht="15.75" customHeight="1"/>
+    <row r="700" ht="15.75" customHeight="1"/>
+    <row r="701" ht="15.75" customHeight="1"/>
+    <row r="702" ht="15.75" customHeight="1"/>
+    <row r="703" ht="15.75" customHeight="1"/>
+    <row r="704" ht="15.75" customHeight="1"/>
+    <row r="705" ht="15.75" customHeight="1"/>
+    <row r="706" ht="15.75" customHeight="1"/>
+    <row r="707" ht="15.75" customHeight="1"/>
+    <row r="708" ht="15.75" customHeight="1"/>
+    <row r="709" ht="15.75" customHeight="1"/>
+    <row r="710" ht="15.75" customHeight="1"/>
+    <row r="711" ht="15.75" customHeight="1"/>
+    <row r="712" ht="15.75" customHeight="1"/>
+    <row r="713" ht="15.75" customHeight="1"/>
+    <row r="714" ht="15.75" customHeight="1"/>
+    <row r="715" ht="15.75" customHeight="1"/>
+    <row r="716" ht="15.75" customHeight="1"/>
+    <row r="717" ht="15.75" customHeight="1"/>
+    <row r="718" ht="15.75" customHeight="1"/>
+    <row r="719" ht="15.75" customHeight="1"/>
+    <row r="720" ht="15.75" customHeight="1"/>
+    <row r="721" ht="15.75" customHeight="1"/>
+    <row r="722" ht="15.75" customHeight="1"/>
+    <row r="723" ht="15.75" customHeight="1"/>
+    <row r="724" ht="15.75" customHeight="1"/>
+    <row r="725" ht="15.75" customHeight="1"/>
+    <row r="726" ht="15.75" customHeight="1"/>
+    <row r="727" ht="15.75" customHeight="1"/>
+    <row r="728" ht="15.75" customHeight="1"/>
+    <row r="729" ht="15.75" customHeight="1"/>
+    <row r="730" ht="15.75" customHeight="1"/>
+    <row r="731" ht="15.75" customHeight="1"/>
+    <row r="732" ht="15.75" customHeight="1"/>
+    <row r="733" ht="15.75" customHeight="1"/>
+    <row r="734" ht="15.75" customHeight="1"/>
+    <row r="735" ht="15.75" customHeight="1"/>
+    <row r="736" ht="15.75" customHeight="1"/>
+    <row r="737" ht="15.75" customHeight="1"/>
+    <row r="738" ht="15.75" customHeight="1"/>
+    <row r="739" ht="15.75" customHeight="1"/>
+    <row r="740" ht="15.75" customHeight="1"/>
+    <row r="741" ht="15.75" customHeight="1"/>
+    <row r="742" ht="15.75" customHeight="1"/>
+    <row r="743" ht="15.75" customHeight="1"/>
+    <row r="744" ht="15.75" customHeight="1"/>
+    <row r="745" ht="15.75" customHeight="1"/>
+    <row r="746" ht="15.75" customHeight="1"/>
+    <row r="747" ht="15.75" customHeight="1"/>
+    <row r="748" ht="15.75" customHeight="1"/>
+    <row r="749" ht="15.75" customHeight="1"/>
+    <row r="750" ht="15.75" customHeight="1"/>
+    <row r="751" ht="15.75" customHeight="1"/>
+    <row r="752" ht="15.75" customHeight="1"/>
+    <row r="753" ht="15.75" customHeight="1"/>
+    <row r="754" ht="15.75" customHeight="1"/>
+    <row r="755" ht="15.75" customHeight="1"/>
+    <row r="756" ht="15.75" customHeight="1"/>
+    <row r="757" ht="15.75" customHeight="1"/>
+    <row r="758" ht="15.75" customHeight="1"/>
+    <row r="759" ht="15.75" customHeight="1"/>
+    <row r="760" ht="15.75" customHeight="1"/>
+    <row r="761" ht="15.75" customHeight="1"/>
+    <row r="762" ht="15.75" customHeight="1"/>
+    <row r="763" ht="15.75" customHeight="1"/>
+    <row r="764" ht="15.75" customHeight="1"/>
+    <row r="765" ht="15.75" customHeight="1"/>
+    <row r="766" ht="15.75" customHeight="1"/>
+    <row r="767" ht="15.75" customHeight="1"/>
+    <row r="768" ht="15.75" customHeight="1"/>
+    <row r="769" ht="15.75" customHeight="1"/>
+    <row r="770" ht="15.75" customHeight="1"/>
+    <row r="771" ht="15.75" customHeight="1"/>
+    <row r="772" ht="15.75" customHeight="1"/>
+    <row r="773" ht="15.75" customHeight="1"/>
+    <row r="774" ht="15.75" customHeight="1"/>
+    <row r="775" ht="15.75" customHeight="1"/>
+    <row r="776" ht="15.75" customHeight="1"/>
+    <row r="777" ht="15.75" customHeight="1"/>
+    <row r="778" ht="15.75" customHeight="1"/>
+    <row r="779" ht="15.75" customHeight="1"/>
+    <row r="780" ht="15.75" customHeight="1"/>
+    <row r="781" ht="15.75" customHeight="1"/>
+    <row r="782" ht="15.75" customHeight="1"/>
+    <row r="783" ht="15.75" customHeight="1"/>
+    <row r="784" ht="15.75" customHeight="1"/>
+    <row r="785" ht="15.75" customHeight="1"/>
+    <row r="786" ht="15.75" customHeight="1"/>
+    <row r="787" ht="15.75" customHeight="1"/>
+    <row r="788" ht="15.75" customHeight="1"/>
+    <row r="789" ht="15.75" customHeight="1"/>
+    <row r="790" ht="15.75" customHeight="1"/>
+    <row r="791" ht="15.75" customHeight="1"/>
+    <row r="792" ht="15.75" customHeight="1"/>
+    <row r="793" ht="15.75" customHeight="1"/>
+    <row r="794" ht="15.75" customHeight="1"/>
+    <row r="795" ht="15.75" customHeight="1"/>
+    <row r="796" ht="15.75" customHeight="1"/>
+    <row r="797" ht="15.75" customHeight="1"/>
+    <row r="798" ht="15.75" customHeight="1"/>
+    <row r="799" ht="15.75" customHeight="1"/>
+    <row r="800" ht="15.75" customHeight="1"/>
+    <row r="801" ht="15.75" customHeight="1"/>
+    <row r="802" ht="15.75" customHeight="1"/>
+    <row r="803" ht="15.75" customHeight="1"/>
+    <row r="804" ht="15.75" customHeight="1"/>
+    <row r="805" ht="15.75" customHeight="1"/>
+    <row r="806" ht="15.75" customHeight="1"/>
+    <row r="807" ht="15.75" customHeight="1"/>
+    <row r="808" ht="15.75" customHeight="1"/>
+    <row r="809" ht="15.75" customHeight="1"/>
+    <row r="810" ht="15.75" customHeight="1"/>
+    <row r="811" ht="15.75" customHeight="1"/>
+    <row r="812" ht="15.75" customHeight="1"/>
+    <row r="813" ht="15.75" customHeight="1"/>
+    <row r="814" ht="15.75" customHeight="1"/>
+    <row r="815" ht="15.75" customHeight="1"/>
+    <row r="816" ht="15.75" customHeight="1"/>
+    <row r="817" ht="15.75" customHeight="1"/>
+    <row r="818" ht="15.75" customHeight="1"/>
+    <row r="819" ht="15.75" customHeight="1"/>
+    <row r="820" ht="15.75" customHeight="1"/>
+    <row r="821" ht="15.75" customHeight="1"/>
+    <row r="822" ht="15.75" customHeight="1"/>
+    <row r="823" ht="15.75" customHeight="1"/>
+    <row r="824" ht="15.75" customHeight="1"/>
+    <row r="825" ht="15.75" customHeight="1"/>
+    <row r="826" ht="15.75" customHeight="1"/>
+    <row r="827" ht="15.75" customHeight="1"/>
+    <row r="828" ht="15.75" customHeight="1"/>
+    <row r="829" ht="15.75" customHeight="1"/>
+    <row r="830" ht="15.75" customHeight="1"/>
+    <row r="831" ht="15.75" customHeight="1"/>
+    <row r="832" ht="15.75" customHeight="1"/>
+    <row r="833" ht="15.75" customHeight="1"/>
+    <row r="834" ht="15.75" customHeight="1"/>
+    <row r="835" ht="15.75" customHeight="1"/>
+    <row r="836" ht="15.75" customHeight="1"/>
+    <row r="837" ht="15.75" customHeight="1"/>
+    <row r="838" ht="15.75" customHeight="1"/>
+    <row r="839" ht="15.75" customHeight="1"/>
+    <row r="840" ht="15.75" customHeight="1"/>
+    <row r="841" ht="15.75" customHeight="1"/>
+    <row r="842" ht="15.75" customHeight="1"/>
+    <row r="843" ht="15.75" customHeight="1"/>
+    <row r="844" ht="15.75" customHeight="1"/>
+    <row r="845" ht="15.75" customHeight="1"/>
+    <row r="846" ht="15.75" customHeight="1"/>
+    <row r="847" ht="15.75" customHeight="1"/>
+    <row r="848" ht="15.75" customHeight="1"/>
+    <row r="849" ht="15.75" customHeight="1"/>
+    <row r="850" ht="15.75" customHeight="1"/>
+    <row r="851" ht="15.75" customHeight="1"/>
+    <row r="852" ht="15.75" customHeight="1"/>
+    <row r="853" ht="15.75" customHeight="1"/>
+    <row r="854" ht="15.75" customHeight="1"/>
+    <row r="855" ht="15.75" customHeight="1"/>
+    <row r="856" ht="15.75" customHeight="1"/>
+    <row r="857" ht="15.75" customHeight="1"/>
+    <row r="858" ht="15.75" customHeight="1"/>
+    <row r="859" ht="15.75" customHeight="1"/>
+    <row r="860" ht="15.75" customHeight="1"/>
+    <row r="861" ht="15.75" customHeight="1"/>
+    <row r="862" ht="15.75" customHeight="1"/>
+    <row r="863" ht="15.75" customHeight="1"/>
+    <row r="864" ht="15.75" customHeight="1"/>
+    <row r="865" ht="15.75" customHeight="1"/>
+    <row r="866" ht="15.75" customHeight="1"/>
+    <row r="867" ht="15.75" customHeight="1"/>
+    <row r="868" ht="15.75" customHeight="1"/>
+    <row r="869" ht="15.75" customHeight="1"/>
+    <row r="870" ht="15.75" customHeight="1"/>
+    <row r="871" ht="15.75" customHeight="1"/>
+    <row r="872" ht="15.75" customHeight="1"/>
+    <row r="873" ht="15.75" customHeight="1"/>
+    <row r="874" ht="15.75" customHeight="1"/>
+    <row r="875" ht="15.75" customHeight="1"/>
+    <row r="876" ht="15.75" customHeight="1"/>
+    <row r="877" ht="15.75" customHeight="1"/>
+    <row r="878" ht="15.75" customHeight="1"/>
+    <row r="879" ht="15.75" customHeight="1"/>
+    <row r="880" ht="15.75" customHeight="1"/>
+    <row r="881" ht="15.75" customHeight="1"/>
+    <row r="882" ht="15.75" customHeight="1"/>
+    <row r="883" ht="15.75" customHeight="1"/>
+    <row r="884" ht="15.75" customHeight="1"/>
+    <row r="885" ht="15.75" customHeight="1"/>
+    <row r="886" ht="15.75" customHeight="1"/>
+    <row r="887" ht="15.75" customHeight="1"/>
+    <row r="888" ht="15.75" customHeight="1"/>
+    <row r="889" ht="15.75" customHeight="1"/>
+    <row r="890" ht="15.75" customHeight="1"/>
+    <row r="891" ht="15.75" customHeight="1"/>
+    <row r="892" ht="15.75" customHeight="1"/>
+    <row r="893" ht="15.75" customHeight="1"/>
+    <row r="894" ht="15.75" customHeight="1"/>
+    <row r="895" ht="15.75" customHeight="1"/>
+    <row r="896" ht="15.75" customHeight="1"/>
+    <row r="897" ht="15.75" customHeight="1"/>
+    <row r="898" ht="15.75" customHeight="1"/>
+    <row r="899" ht="15.75" customHeight="1"/>
+    <row r="900" ht="15.75" customHeight="1"/>
+    <row r="901" ht="15.75" customHeight="1"/>
+    <row r="902" ht="15.75" customHeight="1"/>
+    <row r="903" ht="15.75" customHeight="1"/>
+    <row r="904" ht="15.75" customHeight="1"/>
+    <row r="905" ht="15.75" customHeight="1"/>
+    <row r="906" ht="15.75" customHeight="1"/>
+    <row r="907" ht="15.75" customHeight="1"/>
+    <row r="908" ht="15.75" customHeight="1"/>
+    <row r="909" ht="15.75" customHeight="1"/>
+    <row r="910" ht="15.75" customHeight="1"/>
+    <row r="911" ht="15.75" customHeight="1"/>
+    <row r="912" ht="15.75" customHeight="1"/>
+    <row r="913" ht="15.75" customHeight="1"/>
+    <row r="914" ht="15.75" customHeight="1"/>
+    <row r="915" ht="15.75" customHeight="1"/>
+    <row r="916" ht="15.75" customHeight="1"/>
+    <row r="917" ht="15.75" customHeight="1"/>
+    <row r="918" ht="15.75" customHeight="1"/>
+    <row r="919" ht="15.75" customHeight="1"/>
+    <row r="920" ht="15.75" customHeight="1"/>
+    <row r="921" ht="15.75" customHeight="1"/>
+    <row r="922" ht="15.75" customHeight="1"/>
+    <row r="923" ht="15.75" customHeight="1"/>
+    <row r="924" ht="15.75" customHeight="1"/>
+    <row r="925" ht="15.75" customHeight="1"/>
+    <row r="926" ht="15.75" customHeight="1"/>
+    <row r="927" ht="15.75" customHeight="1"/>
+    <row r="928" ht="15.75" customHeight="1"/>
+    <row r="929" ht="15.75" customHeight="1"/>
+    <row r="930" ht="15.75" customHeight="1"/>
+    <row r="931" ht="15.75" customHeight="1"/>
+    <row r="932" ht="15.75" customHeight="1"/>
+    <row r="933" ht="15.75" customHeight="1"/>
+    <row r="934" ht="15.75" customHeight="1"/>
+    <row r="935" ht="15.75" customHeight="1"/>
+    <row r="936" ht="15.75" customHeight="1"/>
+    <row r="937" ht="15.75" customHeight="1"/>
+    <row r="938" ht="15.75" customHeight="1"/>
+    <row r="939" ht="15.75" customHeight="1"/>
+    <row r="940" ht="15.75" customHeight="1"/>
+    <row r="941" ht="15.75" customHeight="1"/>
+    <row r="942" ht="15.75" customHeight="1"/>
+    <row r="943" ht="15.75" customHeight="1"/>
+    <row r="944" ht="15.75" customHeight="1"/>
+    <row r="945" ht="15.75" customHeight="1"/>
+    <row r="946" ht="15.75" customHeight="1"/>
+    <row r="947" ht="15.75" customHeight="1"/>
+    <row r="948" ht="15.75" customHeight="1"/>
+    <row r="949" ht="15.75" customHeight="1"/>
+    <row r="950" ht="15.75" customHeight="1"/>
+    <row r="951" ht="15.75" customHeight="1"/>
+    <row r="952" ht="15.75" customHeight="1"/>
+    <row r="953" ht="15.75" customHeight="1"/>
+    <row r="954" ht="15.75" customHeight="1"/>
+    <row r="955" ht="15.75" customHeight="1"/>
+    <row r="956" ht="15.75" customHeight="1"/>
+    <row r="957" ht="15.75" customHeight="1"/>
+    <row r="958" ht="15.75" customHeight="1"/>
+    <row r="959" ht="15.75" customHeight="1"/>
+    <row r="960" ht="15.75" customHeight="1"/>
+    <row r="961" ht="15.75" customHeight="1"/>
+    <row r="962" ht="15.75" customHeight="1"/>
+    <row r="963" ht="15.75" customHeight="1"/>
+    <row r="964" ht="15.75" customHeight="1"/>
+    <row r="965" ht="15.75" customHeight="1"/>
+    <row r="966" ht="15.75" customHeight="1"/>
+    <row r="967" ht="15.75" customHeight="1"/>
+    <row r="968" ht="15.75" customHeight="1"/>
+    <row r="969" ht="15.75" customHeight="1"/>
+    <row r="970" ht="15.75" customHeight="1"/>
+    <row r="971" ht="15.75" customHeight="1"/>
+    <row r="972" ht="15.75" customHeight="1"/>
+    <row r="973" ht="15.75" customHeight="1"/>
+    <row r="974" ht="15.75" customHeight="1"/>
+    <row r="975" ht="15.75" customHeight="1"/>
+    <row r="976" ht="15.75" customHeight="1"/>
+    <row r="977" ht="15.75" customHeight="1"/>
+    <row r="978" ht="15.75" customHeight="1"/>
+    <row r="979" ht="15.75" customHeight="1"/>
+    <row r="980" ht="15.75" customHeight="1"/>
+    <row r="981" ht="15.75" customHeight="1"/>
+    <row r="982" ht="15.75" customHeight="1"/>
+    <row r="983" ht="15.75" customHeight="1"/>
+    <row r="984" ht="15.75" customHeight="1"/>
+    <row r="985" ht="15.75" customHeight="1"/>
+    <row r="986" ht="15.75" customHeight="1"/>
+    <row r="987" ht="15.75" customHeight="1"/>
+    <row r="988" ht="15.75" customHeight="1"/>
+    <row r="989" ht="15.75" customHeight="1"/>
+    <row r="990" ht="15.75" customHeight="1"/>
+    <row r="991" ht="15.75" customHeight="1"/>
+    <row r="992" ht="15.75" customHeight="1"/>
+    <row r="993" ht="15.75" customHeight="1"/>
+    <row r="994" ht="15.75" customHeight="1"/>
+    <row r="995" ht="15.75" customHeight="1"/>
+    <row r="996" ht="15.75" customHeight="1"/>
+    <row r="997" ht="15.75" customHeight="1"/>
+    <row r="998" ht="15.75" customHeight="1"/>
+    <row r="999" ht="15.75" customHeight="1"/>
+    <row r="1000" ht="15.75" customHeight="1"/>
+    <row r="1001" ht="15.75" customHeight="1"/>
+    <row r="1002" ht="15.75" customHeight="1"/>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A3:J3"/>
+    <mergeCell ref="A8:J8"/>
+    <mergeCell ref="A18:J18"/>
+    <mergeCell ref="A21:J21"/>
+  </mergeCells>
+  <conditionalFormatting sqref="H4:H7 H9:H17 H19:H20 H22:H23">
+    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="✅ PASS">
+      <formula>NOT(ISERROR(SEARCH(("✅ PASS"),(H4))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H4:H7 H9:H17 H19:H20 H22:H23">
+    <cfRule type="containsText" dxfId="4" priority="2" operator="containsText" text="❌ FAIL">
+      <formula>NOT(ISERROR(SEARCH(("❌ FAIL"),(H4))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H4:H7 H9:H17 H19:H20 H22:H23">
+    <cfRule type="containsText" dxfId="2" priority="3" operator="containsText" text="⏳ PENDING">
+      <formula>NOT(ISERROR(SEARCH(("⏳ PENDING"),(H4))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="H4:H7 H9:H17 H19:H20 H22:H23">
+      <formula1>"⏳ PENDIENTE,✅ PASS,❌ FAIL"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <printOptions/>
+  <pageMargins bottom="1.0" footer="0.0" header="0.0" left="0.75" right="0.75" top="1.0"/>
+  <pageSetup orientation="landscape"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <pageSetUpPr/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="6.0"/>
+    <col customWidth="1" min="2" max="2" width="38.0"/>
+    <col customWidth="1" min="3" max="3" width="9.0"/>
+    <col customWidth="1" min="4" max="4" width="42.0"/>
+    <col customWidth="1" min="5" max="5" width="18.0"/>
+    <col customWidth="1" min="6" max="6" width="55.0"/>
+    <col customWidth="1" min="7" max="7" width="45.0"/>
+    <col customWidth="1" min="8" max="8" width="16.0"/>
+    <col customWidth="1" min="9" max="9" width="40.0"/>
+    <col customWidth="1" min="10" max="10" width="14.0"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24.0" customHeight="1">
+      <c r="A1" s="27" t="s">
+        <v>348</v>
+      </c>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+      <c r="H1" s="28"/>
+      <c r="I1" s="28"/>
+      <c r="J1" s="28"/>
+    </row>
+    <row r="2" ht="21.75" customHeight="1">
+      <c r="A2" s="22" t="s">
+        <v>85</v>
+      </c>
+      <c r="B2" s="22" t="s">
+        <v>86</v>
+      </c>
+      <c r="C2" s="22" t="s">
+        <v>87</v>
+      </c>
+      <c r="D2" s="22" t="s">
+        <v>88</v>
+      </c>
+      <c r="E2" s="22" t="s">
+        <v>89</v>
+      </c>
+      <c r="F2" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="G2" s="22" t="s">
+        <v>90</v>
+      </c>
+      <c r="H2" s="22" t="s">
+        <v>91</v>
+      </c>
+      <c r="I2" s="22" t="s">
+        <v>92</v>
+      </c>
+      <c r="J2" s="22" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="3" ht="18.0" customHeight="1">
+      <c r="A3" s="29" t="s">
+        <v>264</v>
+      </c>
+      <c r="B3" s="30"/>
+      <c r="C3" s="30"/>
+      <c r="D3" s="30"/>
+      <c r="E3" s="30"/>
+      <c r="F3" s="30"/>
+      <c r="G3" s="30"/>
+      <c r="H3" s="30"/>
+      <c r="I3" s="30"/>
+      <c r="J3" s="31"/>
+    </row>
+    <row r="4" ht="42.0" customHeight="1">
+      <c r="A4" s="23" t="s">
+        <v>349</v>
+      </c>
+      <c r="B4" s="21" t="s">
+        <v>350</v>
+      </c>
+      <c r="C4" s="32" t="s">
+        <v>97</v>
+      </c>
+      <c r="D4" s="21" t="s">
+        <v>351</v>
+      </c>
+      <c r="E4" s="21" t="s">
+        <v>198</v>
+      </c>
+      <c r="F4" s="21" t="s">
+        <v>352</v>
+      </c>
+      <c r="G4" s="21" t="s">
+        <v>353</v>
+      </c>
+      <c r="H4" s="33" t="s">
+        <v>70</v>
+      </c>
+      <c r="I4" s="21" t="s">
+        <v>354</v>
+      </c>
+      <c r="J4" s="23"/>
+    </row>
+    <row r="5" ht="42.0" customHeight="1">
+      <c r="A5" s="34" t="s">
+        <v>355</v>
+      </c>
+      <c r="B5" s="20" t="s">
+        <v>356</v>
+      </c>
+      <c r="C5" s="35" t="s">
+        <v>97</v>
+      </c>
+      <c r="D5" s="20" t="s">
+        <v>351</v>
+      </c>
+      <c r="E5" s="20" t="s">
+        <v>198</v>
+      </c>
+      <c r="F5" s="20" t="s">
+        <v>357</v>
+      </c>
+      <c r="G5" s="20" t="s">
+        <v>358</v>
+      </c>
+      <c r="H5" s="33" t="s">
+        <v>70</v>
+      </c>
+      <c r="I5" s="20" t="s">
+        <v>359</v>
+      </c>
+      <c r="J5" s="34"/>
+    </row>
+    <row r="6" ht="42.0" customHeight="1">
+      <c r="A6" s="41" t="s">
+        <v>360</v>
+      </c>
+      <c r="B6" s="42" t="s">
+        <v>361</v>
+      </c>
+      <c r="C6" s="32" t="s">
+        <v>97</v>
+      </c>
+      <c r="D6" s="21" t="s">
+        <v>351</v>
+      </c>
+      <c r="E6" s="21" t="s">
+        <v>198</v>
+      </c>
+      <c r="F6" s="21" t="s">
+        <v>357</v>
+      </c>
+      <c r="G6" s="42" t="s">
+        <v>278</v>
+      </c>
+      <c r="H6" s="33" t="s">
+        <v>70</v>
+      </c>
+      <c r="I6" s="42" t="s">
+        <v>362</v>
+      </c>
+      <c r="J6" s="23"/>
+    </row>
+    <row r="7" ht="18.0" customHeight="1">
+      <c r="A7" s="29" t="s">
+        <v>284</v>
+      </c>
+      <c r="B7" s="30"/>
+      <c r="C7" s="30"/>
+      <c r="D7" s="30"/>
+      <c r="E7" s="30"/>
+      <c r="F7" s="30"/>
+      <c r="G7" s="30"/>
+      <c r="H7" s="30"/>
+      <c r="I7" s="30"/>
+      <c r="J7" s="31"/>
+    </row>
+    <row r="8" ht="42.0" customHeight="1">
+      <c r="A8" s="38" t="s">
+        <v>363</v>
+      </c>
+      <c r="B8" s="20" t="s">
+        <v>364</v>
+      </c>
+      <c r="C8" s="36" t="s">
+        <v>139</v>
+      </c>
+      <c r="D8" s="20" t="s">
+        <v>365</v>
+      </c>
+      <c r="E8" s="20" t="s">
+        <v>198</v>
+      </c>
+      <c r="F8" s="20" t="s">
+        <v>141</v>
+      </c>
+      <c r="G8" s="20" t="s">
+        <v>366</v>
+      </c>
+      <c r="H8" s="33" t="s">
+        <v>70</v>
+      </c>
+      <c r="I8" s="20" t="s">
+        <v>367</v>
+      </c>
+      <c r="J8" s="34"/>
+    </row>
+    <row r="9" ht="42.0" customHeight="1">
+      <c r="A9" s="38" t="s">
+        <v>368</v>
+      </c>
+      <c r="B9" s="21" t="s">
+        <v>369</v>
+      </c>
+      <c r="C9" s="43" t="s">
+        <v>139</v>
+      </c>
+      <c r="D9" s="21" t="s">
+        <v>370</v>
+      </c>
+      <c r="E9" s="21" t="s">
+        <v>198</v>
+      </c>
+      <c r="F9" s="21" t="str">
+        <f>Variables!C10</f>
+        <v>4a2c7d53-9a34-4c40-9e8f-c8972db67211</v>
+      </c>
+      <c r="G9" s="21" t="s">
+        <v>371</v>
+      </c>
+      <c r="H9" s="33" t="s">
+        <v>70</v>
+      </c>
+      <c r="I9" s="21" t="s">
+        <v>372</v>
+      </c>
+      <c r="J9" s="23"/>
+    </row>
+    <row r="10" ht="42.0" customHeight="1">
+      <c r="A10" s="38" t="s">
+        <v>373</v>
+      </c>
+      <c r="B10" s="20" t="s">
+        <v>374</v>
+      </c>
+      <c r="C10" s="36" t="s">
+        <v>139</v>
+      </c>
+      <c r="D10" s="20" t="s">
+        <v>375</v>
+      </c>
+      <c r="E10" s="20" t="s">
+        <v>198</v>
+      </c>
+      <c r="F10" s="20" t="s">
+        <v>141</v>
+      </c>
+      <c r="G10" s="20" t="s">
+        <v>376</v>
+      </c>
+      <c r="H10" s="33" t="s">
+        <v>70</v>
+      </c>
+      <c r="I10" s="20" t="s">
+        <v>377</v>
+      </c>
+      <c r="J10" s="34"/>
+    </row>
+    <row r="11" ht="42.0" customHeight="1">
+      <c r="A11" s="41" t="s">
+        <v>378</v>
+      </c>
+      <c r="B11" s="42" t="s">
+        <v>379</v>
+      </c>
+      <c r="C11" s="43" t="s">
+        <v>139</v>
+      </c>
+      <c r="D11" s="42" t="s">
+        <v>380</v>
+      </c>
+      <c r="E11" s="21" t="s">
+        <v>198</v>
+      </c>
+      <c r="F11" s="42" t="s">
+        <v>381</v>
+      </c>
+      <c r="G11" s="42" t="s">
+        <v>148</v>
+      </c>
+      <c r="H11" s="33" t="s">
+        <v>70</v>
+      </c>
+      <c r="I11" s="42" t="s">
+        <v>326</v>
+      </c>
+      <c r="J11" s="23"/>
+    </row>
+    <row r="12" ht="18.0" customHeight="1">
+      <c r="A12" s="29" t="s">
+        <v>382</v>
+      </c>
+      <c r="B12" s="30"/>
+      <c r="C12" s="30"/>
+      <c r="D12" s="30"/>
+      <c r="E12" s="30"/>
+      <c r="F12" s="30"/>
+      <c r="G12" s="30"/>
+      <c r="H12" s="30"/>
+      <c r="I12" s="30"/>
+      <c r="J12" s="31"/>
+    </row>
+    <row r="13" ht="42.0" customHeight="1">
+      <c r="A13" s="38" t="s">
+        <v>383</v>
+      </c>
+      <c r="B13" s="20" t="s">
+        <v>384</v>
+      </c>
+      <c r="C13" s="35" t="s">
+        <v>97</v>
+      </c>
+      <c r="D13" s="20" t="s">
+        <v>385</v>
+      </c>
+      <c r="E13" s="20" t="s">
+        <v>198</v>
+      </c>
+      <c r="F13" s="20" t="str">
+        <f>Variables!C11</f>
+        <v>8396e74a-7bc5-4793-b7c4-bd79b3b7932b</v>
+      </c>
+      <c r="G13" s="20" t="s">
+        <v>386</v>
+      </c>
+      <c r="H13" s="33" t="s">
+        <v>70</v>
+      </c>
+      <c r="I13" s="20" t="s">
+        <v>387</v>
+      </c>
+      <c r="J13" s="34"/>
+    </row>
+    <row r="14" ht="42.0" customHeight="1">
+      <c r="A14" s="41" t="s">
+        <v>388</v>
+      </c>
+      <c r="B14" s="21" t="s">
+        <v>389</v>
+      </c>
+      <c r="C14" s="32" t="s">
+        <v>97</v>
+      </c>
+      <c r="D14" s="21" t="s">
+        <v>390</v>
+      </c>
+      <c r="E14" s="21" t="s">
+        <v>198</v>
+      </c>
+      <c r="F14" s="21" t="str">
+        <f>Variables!C11</f>
+        <v>8396e74a-7bc5-4793-b7c4-bd79b3b7932b</v>
+      </c>
+      <c r="G14" s="21" t="s">
+        <v>391</v>
+      </c>
+      <c r="H14" s="33" t="s">
+        <v>70</v>
+      </c>
+      <c r="I14" s="21" t="s">
+        <v>392</v>
+      </c>
+      <c r="J14" s="23"/>
+    </row>
+    <row r="15" ht="42.0" customHeight="1">
+      <c r="A15" s="38" t="s">
+        <v>393</v>
+      </c>
+      <c r="B15" s="20" t="s">
+        <v>394</v>
+      </c>
+      <c r="C15" s="35" t="s">
+        <v>97</v>
+      </c>
+      <c r="D15" s="20" t="s">
+        <v>395</v>
+      </c>
+      <c r="E15" s="20" t="s">
+        <v>198</v>
+      </c>
+      <c r="F15" s="20" t="str">
+        <f>Variables!C11</f>
+        <v>8396e74a-7bc5-4793-b7c4-bd79b3b7932b</v>
+      </c>
+      <c r="G15" s="20" t="s">
+        <v>396</v>
+      </c>
+      <c r="H15" s="33" t="s">
+        <v>70</v>
+      </c>
+      <c r="I15" s="20" t="s">
+        <v>397</v>
+      </c>
+      <c r="J15" s="34"/>
+    </row>
+    <row r="16" ht="42.0" customHeight="1">
+      <c r="A16" s="41" t="s">
+        <v>398</v>
+      </c>
+      <c r="B16" s="21" t="s">
+        <v>399</v>
+      </c>
+      <c r="C16" s="32" t="s">
+        <v>97</v>
+      </c>
+      <c r="D16" s="21" t="s">
+        <v>400</v>
+      </c>
+      <c r="E16" s="21" t="s">
+        <v>198</v>
+      </c>
+      <c r="F16" s="21" t="str">
+        <f>Variables!C11</f>
+        <v>8396e74a-7bc5-4793-b7c4-bd79b3b7932b</v>
+      </c>
+      <c r="G16" s="21" t="s">
+        <v>401</v>
+      </c>
+      <c r="H16" s="33" t="s">
+        <v>70</v>
+      </c>
+      <c r="I16" s="21" t="s">
+        <v>402</v>
+      </c>
+      <c r="J16" s="23"/>
+    </row>
+    <row r="17" ht="42.0" customHeight="1">
+      <c r="A17" s="38" t="s">
+        <v>403</v>
+      </c>
+      <c r="B17" s="20" t="s">
+        <v>404</v>
+      </c>
+      <c r="C17" s="35" t="s">
+        <v>97</v>
+      </c>
+      <c r="D17" s="20" t="s">
+        <v>405</v>
+      </c>
+      <c r="E17" s="20" t="s">
+        <v>198</v>
+      </c>
+      <c r="F17" s="20" t="str">
+        <f>Variables!C10</f>
+        <v>4a2c7d53-9a34-4c40-9e8f-c8972db67211</v>
+      </c>
+      <c r="G17" s="20" t="s">
+        <v>340</v>
+      </c>
+      <c r="H17" s="33" t="s">
+        <v>70</v>
+      </c>
+      <c r="I17" s="20" t="s">
+        <v>406</v>
+      </c>
+      <c r="J17" s="34"/>
     </row>
     <row r="23" ht="15.75" customHeight="1"/>
     <row r="24" ht="15.75" customHeight="1"/>
@@ -14843,1488 +16381,31 @@
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
     <row r="1001" ht="15.75" customHeight="1"/>
+    <row r="1002" ht="15.75" customHeight="1"/>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="4">
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A3:J3"/>
     <mergeCell ref="A7:J7"/>
-    <mergeCell ref="A17:J17"/>
-    <mergeCell ref="A20:J20"/>
+    <mergeCell ref="A12:J12"/>
   </mergeCells>
-  <conditionalFormatting sqref="H4:H6 H8:H16 H18:H19 H21:H22">
+  <conditionalFormatting sqref="H4:H6 H8:H11 H13:H17">
     <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="✅ PASS">
       <formula>NOT(ISERROR(SEARCH(("✅ PASS"),(H4))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H4:H6 H8:H16 H18:H19 H21:H22">
+  <conditionalFormatting sqref="H4:H6 H8:H11 H13:H17">
     <cfRule type="containsText" dxfId="4" priority="2" operator="containsText" text="❌ FAIL">
       <formula>NOT(ISERROR(SEARCH(("❌ FAIL"),(H4))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H4:H6 H8:H16 H18:H19 H21:H22">
+  <conditionalFormatting sqref="H4:H6 H8:H11 H13:H17">
     <cfRule type="containsText" dxfId="2" priority="3" operator="containsText" text="⏳ PENDING">
       <formula>NOT(ISERROR(SEARCH(("⏳ PENDING"),(H4))))</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="H4:H6 H8:H16 H18:H19 H21:H22">
-      <formula1>"⏳ PENDIENTE,✅ PASS,❌ FAIL"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <printOptions/>
-  <pageMargins bottom="1.0" footer="0.0" header="0.0" left="0.75" right="0.75" top="1.0"/>
-  <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
-  <cols>
-    <col customWidth="1" min="1" max="1" width="6.0"/>
-    <col customWidth="1" min="2" max="2" width="38.0"/>
-    <col customWidth="1" min="3" max="3" width="9.0"/>
-    <col customWidth="1" min="4" max="4" width="42.0"/>
-    <col customWidth="1" min="5" max="5" width="18.0"/>
-    <col customWidth="1" min="6" max="6" width="55.0"/>
-    <col customWidth="1" min="7" max="7" width="45.0"/>
-    <col customWidth="1" min="8" max="8" width="16.0"/>
-    <col customWidth="1" min="9" max="9" width="40.0"/>
-    <col customWidth="1" min="10" max="10" width="14.0"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="24.0" customHeight="1">
-      <c r="A1" s="27" t="s">
-        <v>344</v>
-      </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
-      <c r="H1" s="28"/>
-      <c r="I1" s="28"/>
-      <c r="J1" s="28"/>
-    </row>
-    <row r="2" ht="21.75" customHeight="1">
-      <c r="A2" s="22" t="s">
-        <v>85</v>
-      </c>
-      <c r="B2" s="22" t="s">
-        <v>86</v>
-      </c>
-      <c r="C2" s="22" t="s">
-        <v>87</v>
-      </c>
-      <c r="D2" s="22" t="s">
-        <v>88</v>
-      </c>
-      <c r="E2" s="22" t="s">
-        <v>89</v>
-      </c>
-      <c r="F2" s="22" t="s">
-        <v>26</v>
-      </c>
-      <c r="G2" s="22" t="s">
-        <v>90</v>
-      </c>
-      <c r="H2" s="22" t="s">
-        <v>91</v>
-      </c>
-      <c r="I2" s="22" t="s">
-        <v>92</v>
-      </c>
-      <c r="J2" s="22" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="3" ht="18.0" customHeight="1">
-      <c r="A3" s="29" t="s">
-        <v>264</v>
-      </c>
-      <c r="B3" s="30"/>
-      <c r="C3" s="30"/>
-      <c r="D3" s="30"/>
-      <c r="E3" s="30"/>
-      <c r="F3" s="30"/>
-      <c r="G3" s="30"/>
-      <c r="H3" s="30"/>
-      <c r="I3" s="30"/>
-      <c r="J3" s="31"/>
-    </row>
-    <row r="4" ht="42.0" customHeight="1">
-      <c r="A4" s="23" t="s">
-        <v>345</v>
-      </c>
-      <c r="B4" s="21" t="s">
-        <v>346</v>
-      </c>
-      <c r="C4" s="32" t="s">
-        <v>97</v>
-      </c>
-      <c r="D4" s="21" t="s">
-        <v>347</v>
-      </c>
-      <c r="E4" s="21" t="s">
-        <v>198</v>
-      </c>
-      <c r="F4" s="21" t="s">
-        <v>348</v>
-      </c>
-      <c r="G4" s="21" t="s">
-        <v>349</v>
-      </c>
-      <c r="H4" s="33" t="s">
-        <v>70</v>
-      </c>
-      <c r="I4" s="21" t="s">
-        <v>350</v>
-      </c>
-      <c r="J4" s="23"/>
-    </row>
-    <row r="5" ht="42.0" customHeight="1">
-      <c r="A5" s="34" t="s">
-        <v>351</v>
-      </c>
-      <c r="B5" s="20" t="s">
-        <v>352</v>
-      </c>
-      <c r="C5" s="35" t="s">
-        <v>97</v>
-      </c>
-      <c r="D5" s="20" t="s">
-        <v>347</v>
-      </c>
-      <c r="E5" s="20" t="s">
-        <v>198</v>
-      </c>
-      <c r="F5" s="20" t="s">
-        <v>353</v>
-      </c>
-      <c r="G5" s="20" t="s">
-        <v>354</v>
-      </c>
-      <c r="H5" s="33" t="s">
-        <v>70</v>
-      </c>
-      <c r="I5" s="20" t="s">
-        <v>355</v>
-      </c>
-      <c r="J5" s="34"/>
-    </row>
-    <row r="6" ht="18.0" customHeight="1">
-      <c r="A6" s="29" t="s">
-        <v>280</v>
-      </c>
-      <c r="B6" s="30"/>
-      <c r="C6" s="30"/>
-      <c r="D6" s="30"/>
-      <c r="E6" s="30"/>
-      <c r="F6" s="30"/>
-      <c r="G6" s="30"/>
-      <c r="H6" s="30"/>
-      <c r="I6" s="30"/>
-      <c r="J6" s="31"/>
-    </row>
-    <row r="7" ht="42.0" customHeight="1">
-      <c r="A7" s="34" t="s">
-        <v>356</v>
-      </c>
-      <c r="B7" s="20" t="s">
-        <v>357</v>
-      </c>
-      <c r="C7" s="36" t="s">
-        <v>139</v>
-      </c>
-      <c r="D7" s="20" t="s">
-        <v>358</v>
-      </c>
-      <c r="E7" s="20" t="s">
-        <v>198</v>
-      </c>
-      <c r="F7" s="20" t="s">
-        <v>141</v>
-      </c>
-      <c r="G7" s="20" t="s">
-        <v>359</v>
-      </c>
-      <c r="H7" s="33" t="s">
-        <v>70</v>
-      </c>
-      <c r="I7" s="20" t="s">
-        <v>360</v>
-      </c>
-      <c r="J7" s="34"/>
-    </row>
-    <row r="8" ht="42.0" customHeight="1">
-      <c r="A8" s="23" t="s">
-        <v>361</v>
-      </c>
-      <c r="B8" s="21" t="s">
-        <v>362</v>
-      </c>
-      <c r="C8" s="43" t="s">
-        <v>139</v>
-      </c>
-      <c r="D8" s="21" t="s">
-        <v>363</v>
-      </c>
-      <c r="E8" s="21" t="s">
-        <v>198</v>
-      </c>
-      <c r="F8" s="21" t="str">
-        <f>Variables!C10</f>
-        <v>4a2c7d53-9a34-4c40-9e8f-c8972db67211</v>
-      </c>
-      <c r="G8" s="21" t="s">
-        <v>364</v>
-      </c>
-      <c r="H8" s="33" t="s">
-        <v>70</v>
-      </c>
-      <c r="I8" s="21" t="s">
-        <v>365</v>
-      </c>
-      <c r="J8" s="23"/>
-    </row>
-    <row r="9" ht="42.0" customHeight="1">
-      <c r="A9" s="34" t="s">
-        <v>366</v>
-      </c>
-      <c r="B9" s="20" t="s">
-        <v>367</v>
-      </c>
-      <c r="C9" s="36" t="s">
-        <v>139</v>
-      </c>
-      <c r="D9" s="20" t="s">
-        <v>368</v>
-      </c>
-      <c r="E9" s="20" t="s">
-        <v>198</v>
-      </c>
-      <c r="F9" s="20" t="s">
-        <v>141</v>
-      </c>
-      <c r="G9" s="20" t="s">
-        <v>369</v>
-      </c>
-      <c r="H9" s="33" t="s">
-        <v>70</v>
-      </c>
-      <c r="I9" s="20" t="s">
-        <v>370</v>
-      </c>
-      <c r="J9" s="34"/>
-    </row>
-    <row r="10" ht="42.0" customHeight="1">
-      <c r="A10" s="41" t="s">
-        <v>371</v>
-      </c>
-      <c r="B10" s="42" t="s">
-        <v>372</v>
-      </c>
-      <c r="C10" s="43" t="s">
-        <v>139</v>
-      </c>
-      <c r="D10" s="42" t="s">
-        <v>373</v>
-      </c>
-      <c r="E10" s="21" t="s">
-        <v>198</v>
-      </c>
-      <c r="F10" s="42" t="s">
-        <v>374</v>
-      </c>
-      <c r="G10" s="42" t="s">
-        <v>148</v>
-      </c>
-      <c r="H10" s="33" t="s">
-        <v>70</v>
-      </c>
-      <c r="I10" s="42" t="s">
-        <v>322</v>
-      </c>
-      <c r="J10" s="23"/>
-    </row>
-    <row r="11" ht="18.0" customHeight="1">
-      <c r="A11" s="29" t="s">
-        <v>375</v>
-      </c>
-      <c r="B11" s="30"/>
-      <c r="C11" s="30"/>
-      <c r="D11" s="30"/>
-      <c r="E11" s="30"/>
-      <c r="F11" s="30"/>
-      <c r="G11" s="30"/>
-      <c r="H11" s="30"/>
-      <c r="I11" s="30"/>
-      <c r="J11" s="31"/>
-    </row>
-    <row r="12" ht="42.0" customHeight="1">
-      <c r="A12" s="38" t="s">
-        <v>376</v>
-      </c>
-      <c r="B12" s="20" t="s">
-        <v>377</v>
-      </c>
-      <c r="C12" s="35" t="s">
-        <v>97</v>
-      </c>
-      <c r="D12" s="20" t="s">
-        <v>378</v>
-      </c>
-      <c r="E12" s="20" t="s">
-        <v>198</v>
-      </c>
-      <c r="F12" s="20" t="str">
-        <f>Variables!C11</f>
-        <v>8396e74a-7bc5-4793-b7c4-bd79b3b7932b</v>
-      </c>
-      <c r="G12" s="20" t="s">
-        <v>379</v>
-      </c>
-      <c r="H12" s="33" t="s">
-        <v>70</v>
-      </c>
-      <c r="I12" s="20" t="s">
-        <v>380</v>
-      </c>
-      <c r="J12" s="34"/>
-    </row>
-    <row r="13" ht="42.0" customHeight="1">
-      <c r="A13" s="41" t="s">
-        <v>381</v>
-      </c>
-      <c r="B13" s="21" t="s">
-        <v>382</v>
-      </c>
-      <c r="C13" s="32" t="s">
-        <v>97</v>
-      </c>
-      <c r="D13" s="21" t="s">
-        <v>383</v>
-      </c>
-      <c r="E13" s="21" t="s">
-        <v>198</v>
-      </c>
-      <c r="F13" s="21" t="str">
-        <f>Variables!C11</f>
-        <v>8396e74a-7bc5-4793-b7c4-bd79b3b7932b</v>
-      </c>
-      <c r="G13" s="21" t="s">
-        <v>384</v>
-      </c>
-      <c r="H13" s="33" t="s">
-        <v>70</v>
-      </c>
-      <c r="I13" s="21" t="s">
-        <v>385</v>
-      </c>
-      <c r="J13" s="23"/>
-    </row>
-    <row r="14" ht="42.0" customHeight="1">
-      <c r="A14" s="38" t="s">
-        <v>386</v>
-      </c>
-      <c r="B14" s="20" t="s">
-        <v>387</v>
-      </c>
-      <c r="C14" s="35" t="s">
-        <v>97</v>
-      </c>
-      <c r="D14" s="20" t="s">
-        <v>388</v>
-      </c>
-      <c r="E14" s="20" t="s">
-        <v>198</v>
-      </c>
-      <c r="F14" s="20" t="str">
-        <f>Variables!C11</f>
-        <v>8396e74a-7bc5-4793-b7c4-bd79b3b7932b</v>
-      </c>
-      <c r="G14" s="20" t="s">
-        <v>389</v>
-      </c>
-      <c r="H14" s="33" t="s">
-        <v>70</v>
-      </c>
-      <c r="I14" s="20" t="s">
-        <v>390</v>
-      </c>
-      <c r="J14" s="34"/>
-    </row>
-    <row r="15" ht="42.0" customHeight="1">
-      <c r="A15" s="41" t="s">
-        <v>391</v>
-      </c>
-      <c r="B15" s="21" t="s">
-        <v>392</v>
-      </c>
-      <c r="C15" s="32" t="s">
-        <v>97</v>
-      </c>
-      <c r="D15" s="21" t="s">
-        <v>393</v>
-      </c>
-      <c r="E15" s="21" t="s">
-        <v>198</v>
-      </c>
-      <c r="F15" s="21" t="str">
-        <f>Variables!C11</f>
-        <v>8396e74a-7bc5-4793-b7c4-bd79b3b7932b</v>
-      </c>
-      <c r="G15" s="21" t="s">
-        <v>394</v>
-      </c>
-      <c r="H15" s="33" t="s">
-        <v>70</v>
-      </c>
-      <c r="I15" s="21" t="s">
-        <v>395</v>
-      </c>
-      <c r="J15" s="23"/>
-    </row>
-    <row r="16" ht="42.0" customHeight="1">
-      <c r="A16" s="38" t="s">
-        <v>396</v>
-      </c>
-      <c r="B16" s="20" t="s">
-        <v>397</v>
-      </c>
-      <c r="C16" s="35" t="s">
-        <v>97</v>
-      </c>
-      <c r="D16" s="20" t="s">
-        <v>398</v>
-      </c>
-      <c r="E16" s="20" t="s">
-        <v>198</v>
-      </c>
-      <c r="F16" s="20" t="str">
-        <f>Variables!C10</f>
-        <v>4a2c7d53-9a34-4c40-9e8f-c8972db67211</v>
-      </c>
-      <c r="G16" s="20" t="s">
-        <v>336</v>
-      </c>
-      <c r="H16" s="33" t="s">
-        <v>70</v>
-      </c>
-      <c r="I16" s="20" t="s">
-        <v>399</v>
-      </c>
-      <c r="J16" s="34"/>
-    </row>
-    <row r="22" ht="15.75" customHeight="1"/>
-    <row r="23" ht="15.75" customHeight="1"/>
-    <row r="24" ht="15.75" customHeight="1"/>
-    <row r="25" ht="15.75" customHeight="1"/>
-    <row r="26" ht="15.75" customHeight="1"/>
-    <row r="27" ht="15.75" customHeight="1"/>
-    <row r="28" ht="15.75" customHeight="1"/>
-    <row r="29" ht="15.75" customHeight="1"/>
-    <row r="30" ht="15.75" customHeight="1"/>
-    <row r="31" ht="15.75" customHeight="1"/>
-    <row r="32" ht="15.75" customHeight="1"/>
-    <row r="33" ht="15.75" customHeight="1"/>
-    <row r="34" ht="15.75" customHeight="1"/>
-    <row r="35" ht="15.75" customHeight="1"/>
-    <row r="36" ht="15.75" customHeight="1"/>
-    <row r="37" ht="15.75" customHeight="1"/>
-    <row r="38" ht="15.75" customHeight="1"/>
-    <row r="39" ht="15.75" customHeight="1"/>
-    <row r="40" ht="15.75" customHeight="1"/>
-    <row r="41" ht="15.75" customHeight="1"/>
-    <row r="42" ht="15.75" customHeight="1"/>
-    <row r="43" ht="15.75" customHeight="1"/>
-    <row r="44" ht="15.75" customHeight="1"/>
-    <row r="45" ht="15.75" customHeight="1"/>
-    <row r="46" ht="15.75" customHeight="1"/>
-    <row r="47" ht="15.75" customHeight="1"/>
-    <row r="48" ht="15.75" customHeight="1"/>
-    <row r="49" ht="15.75" customHeight="1"/>
-    <row r="50" ht="15.75" customHeight="1"/>
-    <row r="51" ht="15.75" customHeight="1"/>
-    <row r="52" ht="15.75" customHeight="1"/>
-    <row r="53" ht="15.75" customHeight="1"/>
-    <row r="54" ht="15.75" customHeight="1"/>
-    <row r="55" ht="15.75" customHeight="1"/>
-    <row r="56" ht="15.75" customHeight="1"/>
-    <row r="57" ht="15.75" customHeight="1"/>
-    <row r="58" ht="15.75" customHeight="1"/>
-    <row r="59" ht="15.75" customHeight="1"/>
-    <row r="60" ht="15.75" customHeight="1"/>
-    <row r="61" ht="15.75" customHeight="1"/>
-    <row r="62" ht="15.75" customHeight="1"/>
-    <row r="63" ht="15.75" customHeight="1"/>
-    <row r="64" ht="15.75" customHeight="1"/>
-    <row r="65" ht="15.75" customHeight="1"/>
-    <row r="66" ht="15.75" customHeight="1"/>
-    <row r="67" ht="15.75" customHeight="1"/>
-    <row r="68" ht="15.75" customHeight="1"/>
-    <row r="69" ht="15.75" customHeight="1"/>
-    <row r="70" ht="15.75" customHeight="1"/>
-    <row r="71" ht="15.75" customHeight="1"/>
-    <row r="72" ht="15.75" customHeight="1"/>
-    <row r="73" ht="15.75" customHeight="1"/>
-    <row r="74" ht="15.75" customHeight="1"/>
-    <row r="75" ht="15.75" customHeight="1"/>
-    <row r="76" ht="15.75" customHeight="1"/>
-    <row r="77" ht="15.75" customHeight="1"/>
-    <row r="78" ht="15.75" customHeight="1"/>
-    <row r="79" ht="15.75" customHeight="1"/>
-    <row r="80" ht="15.75" customHeight="1"/>
-    <row r="81" ht="15.75" customHeight="1"/>
-    <row r="82" ht="15.75" customHeight="1"/>
-    <row r="83" ht="15.75" customHeight="1"/>
-    <row r="84" ht="15.75" customHeight="1"/>
-    <row r="85" ht="15.75" customHeight="1"/>
-    <row r="86" ht="15.75" customHeight="1"/>
-    <row r="87" ht="15.75" customHeight="1"/>
-    <row r="88" ht="15.75" customHeight="1"/>
-    <row r="89" ht="15.75" customHeight="1"/>
-    <row r="90" ht="15.75" customHeight="1"/>
-    <row r="91" ht="15.75" customHeight="1"/>
-    <row r="92" ht="15.75" customHeight="1"/>
-    <row r="93" ht="15.75" customHeight="1"/>
-    <row r="94" ht="15.75" customHeight="1"/>
-    <row r="95" ht="15.75" customHeight="1"/>
-    <row r="96" ht="15.75" customHeight="1"/>
-    <row r="97" ht="15.75" customHeight="1"/>
-    <row r="98" ht="15.75" customHeight="1"/>
-    <row r="99" ht="15.75" customHeight="1"/>
-    <row r="100" ht="15.75" customHeight="1"/>
-    <row r="101" ht="15.75" customHeight="1"/>
-    <row r="102" ht="15.75" customHeight="1"/>
-    <row r="103" ht="15.75" customHeight="1"/>
-    <row r="104" ht="15.75" customHeight="1"/>
-    <row r="105" ht="15.75" customHeight="1"/>
-    <row r="106" ht="15.75" customHeight="1"/>
-    <row r="107" ht="15.75" customHeight="1"/>
-    <row r="108" ht="15.75" customHeight="1"/>
-    <row r="109" ht="15.75" customHeight="1"/>
-    <row r="110" ht="15.75" customHeight="1"/>
-    <row r="111" ht="15.75" customHeight="1"/>
-    <row r="112" ht="15.75" customHeight="1"/>
-    <row r="113" ht="15.75" customHeight="1"/>
-    <row r="114" ht="15.75" customHeight="1"/>
-    <row r="115" ht="15.75" customHeight="1"/>
-    <row r="116" ht="15.75" customHeight="1"/>
-    <row r="117" ht="15.75" customHeight="1"/>
-    <row r="118" ht="15.75" customHeight="1"/>
-    <row r="119" ht="15.75" customHeight="1"/>
-    <row r="120" ht="15.75" customHeight="1"/>
-    <row r="121" ht="15.75" customHeight="1"/>
-    <row r="122" ht="15.75" customHeight="1"/>
-    <row r="123" ht="15.75" customHeight="1"/>
-    <row r="124" ht="15.75" customHeight="1"/>
-    <row r="125" ht="15.75" customHeight="1"/>
-    <row r="126" ht="15.75" customHeight="1"/>
-    <row r="127" ht="15.75" customHeight="1"/>
-    <row r="128" ht="15.75" customHeight="1"/>
-    <row r="129" ht="15.75" customHeight="1"/>
-    <row r="130" ht="15.75" customHeight="1"/>
-    <row r="131" ht="15.75" customHeight="1"/>
-    <row r="132" ht="15.75" customHeight="1"/>
-    <row r="133" ht="15.75" customHeight="1"/>
-    <row r="134" ht="15.75" customHeight="1"/>
-    <row r="135" ht="15.75" customHeight="1"/>
-    <row r="136" ht="15.75" customHeight="1"/>
-    <row r="137" ht="15.75" customHeight="1"/>
-    <row r="138" ht="15.75" customHeight="1"/>
-    <row r="139" ht="15.75" customHeight="1"/>
-    <row r="140" ht="15.75" customHeight="1"/>
-    <row r="141" ht="15.75" customHeight="1"/>
-    <row r="142" ht="15.75" customHeight="1"/>
-    <row r="143" ht="15.75" customHeight="1"/>
-    <row r="144" ht="15.75" customHeight="1"/>
-    <row r="145" ht="15.75" customHeight="1"/>
-    <row r="146" ht="15.75" customHeight="1"/>
-    <row r="147" ht="15.75" customHeight="1"/>
-    <row r="148" ht="15.75" customHeight="1"/>
-    <row r="149" ht="15.75" customHeight="1"/>
-    <row r="150" ht="15.75" customHeight="1"/>
-    <row r="151" ht="15.75" customHeight="1"/>
-    <row r="152" ht="15.75" customHeight="1"/>
-    <row r="153" ht="15.75" customHeight="1"/>
-    <row r="154" ht="15.75" customHeight="1"/>
-    <row r="155" ht="15.75" customHeight="1"/>
-    <row r="156" ht="15.75" customHeight="1"/>
-    <row r="157" ht="15.75" customHeight="1"/>
-    <row r="158" ht="15.75" customHeight="1"/>
-    <row r="159" ht="15.75" customHeight="1"/>
-    <row r="160" ht="15.75" customHeight="1"/>
-    <row r="161" ht="15.75" customHeight="1"/>
-    <row r="162" ht="15.75" customHeight="1"/>
-    <row r="163" ht="15.75" customHeight="1"/>
-    <row r="164" ht="15.75" customHeight="1"/>
-    <row r="165" ht="15.75" customHeight="1"/>
-    <row r="166" ht="15.75" customHeight="1"/>
-    <row r="167" ht="15.75" customHeight="1"/>
-    <row r="168" ht="15.75" customHeight="1"/>
-    <row r="169" ht="15.75" customHeight="1"/>
-    <row r="170" ht="15.75" customHeight="1"/>
-    <row r="171" ht="15.75" customHeight="1"/>
-    <row r="172" ht="15.75" customHeight="1"/>
-    <row r="173" ht="15.75" customHeight="1"/>
-    <row r="174" ht="15.75" customHeight="1"/>
-    <row r="175" ht="15.75" customHeight="1"/>
-    <row r="176" ht="15.75" customHeight="1"/>
-    <row r="177" ht="15.75" customHeight="1"/>
-    <row r="178" ht="15.75" customHeight="1"/>
-    <row r="179" ht="15.75" customHeight="1"/>
-    <row r="180" ht="15.75" customHeight="1"/>
-    <row r="181" ht="15.75" customHeight="1"/>
-    <row r="182" ht="15.75" customHeight="1"/>
-    <row r="183" ht="15.75" customHeight="1"/>
-    <row r="184" ht="15.75" customHeight="1"/>
-    <row r="185" ht="15.75" customHeight="1"/>
-    <row r="186" ht="15.75" customHeight="1"/>
-    <row r="187" ht="15.75" customHeight="1"/>
-    <row r="188" ht="15.75" customHeight="1"/>
-    <row r="189" ht="15.75" customHeight="1"/>
-    <row r="190" ht="15.75" customHeight="1"/>
-    <row r="191" ht="15.75" customHeight="1"/>
-    <row r="192" ht="15.75" customHeight="1"/>
-    <row r="193" ht="15.75" customHeight="1"/>
-    <row r="194" ht="15.75" customHeight="1"/>
-    <row r="195" ht="15.75" customHeight="1"/>
-    <row r="196" ht="15.75" customHeight="1"/>
-    <row r="197" ht="15.75" customHeight="1"/>
-    <row r="198" ht="15.75" customHeight="1"/>
-    <row r="199" ht="15.75" customHeight="1"/>
-    <row r="200" ht="15.75" customHeight="1"/>
-    <row r="201" ht="15.75" customHeight="1"/>
-    <row r="202" ht="15.75" customHeight="1"/>
-    <row r="203" ht="15.75" customHeight="1"/>
-    <row r="204" ht="15.75" customHeight="1"/>
-    <row r="205" ht="15.75" customHeight="1"/>
-    <row r="206" ht="15.75" customHeight="1"/>
-    <row r="207" ht="15.75" customHeight="1"/>
-    <row r="208" ht="15.75" customHeight="1"/>
-    <row r="209" ht="15.75" customHeight="1"/>
-    <row r="210" ht="15.75" customHeight="1"/>
-    <row r="211" ht="15.75" customHeight="1"/>
-    <row r="212" ht="15.75" customHeight="1"/>
-    <row r="213" ht="15.75" customHeight="1"/>
-    <row r="214" ht="15.75" customHeight="1"/>
-    <row r="215" ht="15.75" customHeight="1"/>
-    <row r="216" ht="15.75" customHeight="1"/>
-    <row r="217" ht="15.75" customHeight="1"/>
-    <row r="218" ht="15.75" customHeight="1"/>
-    <row r="219" ht="15.75" customHeight="1"/>
-    <row r="220" ht="15.75" customHeight="1"/>
-    <row r="221" ht="15.75" customHeight="1"/>
-    <row r="222" ht="15.75" customHeight="1"/>
-    <row r="223" ht="15.75" customHeight="1"/>
-    <row r="224" ht="15.75" customHeight="1"/>
-    <row r="225" ht="15.75" customHeight="1"/>
-    <row r="226" ht="15.75" customHeight="1"/>
-    <row r="227" ht="15.75" customHeight="1"/>
-    <row r="228" ht="15.75" customHeight="1"/>
-    <row r="229" ht="15.75" customHeight="1"/>
-    <row r="230" ht="15.75" customHeight="1"/>
-    <row r="231" ht="15.75" customHeight="1"/>
-    <row r="232" ht="15.75" customHeight="1"/>
-    <row r="233" ht="15.75" customHeight="1"/>
-    <row r="234" ht="15.75" customHeight="1"/>
-    <row r="235" ht="15.75" customHeight="1"/>
-    <row r="236" ht="15.75" customHeight="1"/>
-    <row r="237" ht="15.75" customHeight="1"/>
-    <row r="238" ht="15.75" customHeight="1"/>
-    <row r="239" ht="15.75" customHeight="1"/>
-    <row r="240" ht="15.75" customHeight="1"/>
-    <row r="241" ht="15.75" customHeight="1"/>
-    <row r="242" ht="15.75" customHeight="1"/>
-    <row r="243" ht="15.75" customHeight="1"/>
-    <row r="244" ht="15.75" customHeight="1"/>
-    <row r="245" ht="15.75" customHeight="1"/>
-    <row r="246" ht="15.75" customHeight="1"/>
-    <row r="247" ht="15.75" customHeight="1"/>
-    <row r="248" ht="15.75" customHeight="1"/>
-    <row r="249" ht="15.75" customHeight="1"/>
-    <row r="250" ht="15.75" customHeight="1"/>
-    <row r="251" ht="15.75" customHeight="1"/>
-    <row r="252" ht="15.75" customHeight="1"/>
-    <row r="253" ht="15.75" customHeight="1"/>
-    <row r="254" ht="15.75" customHeight="1"/>
-    <row r="255" ht="15.75" customHeight="1"/>
-    <row r="256" ht="15.75" customHeight="1"/>
-    <row r="257" ht="15.75" customHeight="1"/>
-    <row r="258" ht="15.75" customHeight="1"/>
-    <row r="259" ht="15.75" customHeight="1"/>
-    <row r="260" ht="15.75" customHeight="1"/>
-    <row r="261" ht="15.75" customHeight="1"/>
-    <row r="262" ht="15.75" customHeight="1"/>
-    <row r="263" ht="15.75" customHeight="1"/>
-    <row r="264" ht="15.75" customHeight="1"/>
-    <row r="265" ht="15.75" customHeight="1"/>
-    <row r="266" ht="15.75" customHeight="1"/>
-    <row r="267" ht="15.75" customHeight="1"/>
-    <row r="268" ht="15.75" customHeight="1"/>
-    <row r="269" ht="15.75" customHeight="1"/>
-    <row r="270" ht="15.75" customHeight="1"/>
-    <row r="271" ht="15.75" customHeight="1"/>
-    <row r="272" ht="15.75" customHeight="1"/>
-    <row r="273" ht="15.75" customHeight="1"/>
-    <row r="274" ht="15.75" customHeight="1"/>
-    <row r="275" ht="15.75" customHeight="1"/>
-    <row r="276" ht="15.75" customHeight="1"/>
-    <row r="277" ht="15.75" customHeight="1"/>
-    <row r="278" ht="15.75" customHeight="1"/>
-    <row r="279" ht="15.75" customHeight="1"/>
-    <row r="280" ht="15.75" customHeight="1"/>
-    <row r="281" ht="15.75" customHeight="1"/>
-    <row r="282" ht="15.75" customHeight="1"/>
-    <row r="283" ht="15.75" customHeight="1"/>
-    <row r="284" ht="15.75" customHeight="1"/>
-    <row r="285" ht="15.75" customHeight="1"/>
-    <row r="286" ht="15.75" customHeight="1"/>
-    <row r="287" ht="15.75" customHeight="1"/>
-    <row r="288" ht="15.75" customHeight="1"/>
-    <row r="289" ht="15.75" customHeight="1"/>
-    <row r="290" ht="15.75" customHeight="1"/>
-    <row r="291" ht="15.75" customHeight="1"/>
-    <row r="292" ht="15.75" customHeight="1"/>
-    <row r="293" ht="15.75" customHeight="1"/>
-    <row r="294" ht="15.75" customHeight="1"/>
-    <row r="295" ht="15.75" customHeight="1"/>
-    <row r="296" ht="15.75" customHeight="1"/>
-    <row r="297" ht="15.75" customHeight="1"/>
-    <row r="298" ht="15.75" customHeight="1"/>
-    <row r="299" ht="15.75" customHeight="1"/>
-    <row r="300" ht="15.75" customHeight="1"/>
-    <row r="301" ht="15.75" customHeight="1"/>
-    <row r="302" ht="15.75" customHeight="1"/>
-    <row r="303" ht="15.75" customHeight="1"/>
-    <row r="304" ht="15.75" customHeight="1"/>
-    <row r="305" ht="15.75" customHeight="1"/>
-    <row r="306" ht="15.75" customHeight="1"/>
-    <row r="307" ht="15.75" customHeight="1"/>
-    <row r="308" ht="15.75" customHeight="1"/>
-    <row r="309" ht="15.75" customHeight="1"/>
-    <row r="310" ht="15.75" customHeight="1"/>
-    <row r="311" ht="15.75" customHeight="1"/>
-    <row r="312" ht="15.75" customHeight="1"/>
-    <row r="313" ht="15.75" customHeight="1"/>
-    <row r="314" ht="15.75" customHeight="1"/>
-    <row r="315" ht="15.75" customHeight="1"/>
-    <row r="316" ht="15.75" customHeight="1"/>
-    <row r="317" ht="15.75" customHeight="1"/>
-    <row r="318" ht="15.75" customHeight="1"/>
-    <row r="319" ht="15.75" customHeight="1"/>
-    <row r="320" ht="15.75" customHeight="1"/>
-    <row r="321" ht="15.75" customHeight="1"/>
-    <row r="322" ht="15.75" customHeight="1"/>
-    <row r="323" ht="15.75" customHeight="1"/>
-    <row r="324" ht="15.75" customHeight="1"/>
-    <row r="325" ht="15.75" customHeight="1"/>
-    <row r="326" ht="15.75" customHeight="1"/>
-    <row r="327" ht="15.75" customHeight="1"/>
-    <row r="328" ht="15.75" customHeight="1"/>
-    <row r="329" ht="15.75" customHeight="1"/>
-    <row r="330" ht="15.75" customHeight="1"/>
-    <row r="331" ht="15.75" customHeight="1"/>
-    <row r="332" ht="15.75" customHeight="1"/>
-    <row r="333" ht="15.75" customHeight="1"/>
-    <row r="334" ht="15.75" customHeight="1"/>
-    <row r="335" ht="15.75" customHeight="1"/>
-    <row r="336" ht="15.75" customHeight="1"/>
-    <row r="337" ht="15.75" customHeight="1"/>
-    <row r="338" ht="15.75" customHeight="1"/>
-    <row r="339" ht="15.75" customHeight="1"/>
-    <row r="340" ht="15.75" customHeight="1"/>
-    <row r="341" ht="15.75" customHeight="1"/>
-    <row r="342" ht="15.75" customHeight="1"/>
-    <row r="343" ht="15.75" customHeight="1"/>
-    <row r="344" ht="15.75" customHeight="1"/>
-    <row r="345" ht="15.75" customHeight="1"/>
-    <row r="346" ht="15.75" customHeight="1"/>
-    <row r="347" ht="15.75" customHeight="1"/>
-    <row r="348" ht="15.75" customHeight="1"/>
-    <row r="349" ht="15.75" customHeight="1"/>
-    <row r="350" ht="15.75" customHeight="1"/>
-    <row r="351" ht="15.75" customHeight="1"/>
-    <row r="352" ht="15.75" customHeight="1"/>
-    <row r="353" ht="15.75" customHeight="1"/>
-    <row r="354" ht="15.75" customHeight="1"/>
-    <row r="355" ht="15.75" customHeight="1"/>
-    <row r="356" ht="15.75" customHeight="1"/>
-    <row r="357" ht="15.75" customHeight="1"/>
-    <row r="358" ht="15.75" customHeight="1"/>
-    <row r="359" ht="15.75" customHeight="1"/>
-    <row r="360" ht="15.75" customHeight="1"/>
-    <row r="361" ht="15.75" customHeight="1"/>
-    <row r="362" ht="15.75" customHeight="1"/>
-    <row r="363" ht="15.75" customHeight="1"/>
-    <row r="364" ht="15.75" customHeight="1"/>
-    <row r="365" ht="15.75" customHeight="1"/>
-    <row r="366" ht="15.75" customHeight="1"/>
-    <row r="367" ht="15.75" customHeight="1"/>
-    <row r="368" ht="15.75" customHeight="1"/>
-    <row r="369" ht="15.75" customHeight="1"/>
-    <row r="370" ht="15.75" customHeight="1"/>
-    <row r="371" ht="15.75" customHeight="1"/>
-    <row r="372" ht="15.75" customHeight="1"/>
-    <row r="373" ht="15.75" customHeight="1"/>
-    <row r="374" ht="15.75" customHeight="1"/>
-    <row r="375" ht="15.75" customHeight="1"/>
-    <row r="376" ht="15.75" customHeight="1"/>
-    <row r="377" ht="15.75" customHeight="1"/>
-    <row r="378" ht="15.75" customHeight="1"/>
-    <row r="379" ht="15.75" customHeight="1"/>
-    <row r="380" ht="15.75" customHeight="1"/>
-    <row r="381" ht="15.75" customHeight="1"/>
-    <row r="382" ht="15.75" customHeight="1"/>
-    <row r="383" ht="15.75" customHeight="1"/>
-    <row r="384" ht="15.75" customHeight="1"/>
-    <row r="385" ht="15.75" customHeight="1"/>
-    <row r="386" ht="15.75" customHeight="1"/>
-    <row r="387" ht="15.75" customHeight="1"/>
-    <row r="388" ht="15.75" customHeight="1"/>
-    <row r="389" ht="15.75" customHeight="1"/>
-    <row r="390" ht="15.75" customHeight="1"/>
-    <row r="391" ht="15.75" customHeight="1"/>
-    <row r="392" ht="15.75" customHeight="1"/>
-    <row r="393" ht="15.75" customHeight="1"/>
-    <row r="394" ht="15.75" customHeight="1"/>
-    <row r="395" ht="15.75" customHeight="1"/>
-    <row r="396" ht="15.75" customHeight="1"/>
-    <row r="397" ht="15.75" customHeight="1"/>
-    <row r="398" ht="15.75" customHeight="1"/>
-    <row r="399" ht="15.75" customHeight="1"/>
-    <row r="400" ht="15.75" customHeight="1"/>
-    <row r="401" ht="15.75" customHeight="1"/>
-    <row r="402" ht="15.75" customHeight="1"/>
-    <row r="403" ht="15.75" customHeight="1"/>
-    <row r="404" ht="15.75" customHeight="1"/>
-    <row r="405" ht="15.75" customHeight="1"/>
-    <row r="406" ht="15.75" customHeight="1"/>
-    <row r="407" ht="15.75" customHeight="1"/>
-    <row r="408" ht="15.75" customHeight="1"/>
-    <row r="409" ht="15.75" customHeight="1"/>
-    <row r="410" ht="15.75" customHeight="1"/>
-    <row r="411" ht="15.75" customHeight="1"/>
-    <row r="412" ht="15.75" customHeight="1"/>
-    <row r="413" ht="15.75" customHeight="1"/>
-    <row r="414" ht="15.75" customHeight="1"/>
-    <row r="415" ht="15.75" customHeight="1"/>
-    <row r="416" ht="15.75" customHeight="1"/>
-    <row r="417" ht="15.75" customHeight="1"/>
-    <row r="418" ht="15.75" customHeight="1"/>
-    <row r="419" ht="15.75" customHeight="1"/>
-    <row r="420" ht="15.75" customHeight="1"/>
-    <row r="421" ht="15.75" customHeight="1"/>
-    <row r="422" ht="15.75" customHeight="1"/>
-    <row r="423" ht="15.75" customHeight="1"/>
-    <row r="424" ht="15.75" customHeight="1"/>
-    <row r="425" ht="15.75" customHeight="1"/>
-    <row r="426" ht="15.75" customHeight="1"/>
-    <row r="427" ht="15.75" customHeight="1"/>
-    <row r="428" ht="15.75" customHeight="1"/>
-    <row r="429" ht="15.75" customHeight="1"/>
-    <row r="430" ht="15.75" customHeight="1"/>
-    <row r="431" ht="15.75" customHeight="1"/>
-    <row r="432" ht="15.75" customHeight="1"/>
-    <row r="433" ht="15.75" customHeight="1"/>
-    <row r="434" ht="15.75" customHeight="1"/>
-    <row r="435" ht="15.75" customHeight="1"/>
-    <row r="436" ht="15.75" customHeight="1"/>
-    <row r="437" ht="15.75" customHeight="1"/>
-    <row r="438" ht="15.75" customHeight="1"/>
-    <row r="439" ht="15.75" customHeight="1"/>
-    <row r="440" ht="15.75" customHeight="1"/>
-    <row r="441" ht="15.75" customHeight="1"/>
-    <row r="442" ht="15.75" customHeight="1"/>
-    <row r="443" ht="15.75" customHeight="1"/>
-    <row r="444" ht="15.75" customHeight="1"/>
-    <row r="445" ht="15.75" customHeight="1"/>
-    <row r="446" ht="15.75" customHeight="1"/>
-    <row r="447" ht="15.75" customHeight="1"/>
-    <row r="448" ht="15.75" customHeight="1"/>
-    <row r="449" ht="15.75" customHeight="1"/>
-    <row r="450" ht="15.75" customHeight="1"/>
-    <row r="451" ht="15.75" customHeight="1"/>
-    <row r="452" ht="15.75" customHeight="1"/>
-    <row r="453" ht="15.75" customHeight="1"/>
-    <row r="454" ht="15.75" customHeight="1"/>
-    <row r="455" ht="15.75" customHeight="1"/>
-    <row r="456" ht="15.75" customHeight="1"/>
-    <row r="457" ht="15.75" customHeight="1"/>
-    <row r="458" ht="15.75" customHeight="1"/>
-    <row r="459" ht="15.75" customHeight="1"/>
-    <row r="460" ht="15.75" customHeight="1"/>
-    <row r="461" ht="15.75" customHeight="1"/>
-    <row r="462" ht="15.75" customHeight="1"/>
-    <row r="463" ht="15.75" customHeight="1"/>
-    <row r="464" ht="15.75" customHeight="1"/>
-    <row r="465" ht="15.75" customHeight="1"/>
-    <row r="466" ht="15.75" customHeight="1"/>
-    <row r="467" ht="15.75" customHeight="1"/>
-    <row r="468" ht="15.75" customHeight="1"/>
-    <row r="469" ht="15.75" customHeight="1"/>
-    <row r="470" ht="15.75" customHeight="1"/>
-    <row r="471" ht="15.75" customHeight="1"/>
-    <row r="472" ht="15.75" customHeight="1"/>
-    <row r="473" ht="15.75" customHeight="1"/>
-    <row r="474" ht="15.75" customHeight="1"/>
-    <row r="475" ht="15.75" customHeight="1"/>
-    <row r="476" ht="15.75" customHeight="1"/>
-    <row r="477" ht="15.75" customHeight="1"/>
-    <row r="478" ht="15.75" customHeight="1"/>
-    <row r="479" ht="15.75" customHeight="1"/>
-    <row r="480" ht="15.75" customHeight="1"/>
-    <row r="481" ht="15.75" customHeight="1"/>
-    <row r="482" ht="15.75" customHeight="1"/>
-    <row r="483" ht="15.75" customHeight="1"/>
-    <row r="484" ht="15.75" customHeight="1"/>
-    <row r="485" ht="15.75" customHeight="1"/>
-    <row r="486" ht="15.75" customHeight="1"/>
-    <row r="487" ht="15.75" customHeight="1"/>
-    <row r="488" ht="15.75" customHeight="1"/>
-    <row r="489" ht="15.75" customHeight="1"/>
-    <row r="490" ht="15.75" customHeight="1"/>
-    <row r="491" ht="15.75" customHeight="1"/>
-    <row r="492" ht="15.75" customHeight="1"/>
-    <row r="493" ht="15.75" customHeight="1"/>
-    <row r="494" ht="15.75" customHeight="1"/>
-    <row r="495" ht="15.75" customHeight="1"/>
-    <row r="496" ht="15.75" customHeight="1"/>
-    <row r="497" ht="15.75" customHeight="1"/>
-    <row r="498" ht="15.75" customHeight="1"/>
-    <row r="499" ht="15.75" customHeight="1"/>
-    <row r="500" ht="15.75" customHeight="1"/>
-    <row r="501" ht="15.75" customHeight="1"/>
-    <row r="502" ht="15.75" customHeight="1"/>
-    <row r="503" ht="15.75" customHeight="1"/>
-    <row r="504" ht="15.75" customHeight="1"/>
-    <row r="505" ht="15.75" customHeight="1"/>
-    <row r="506" ht="15.75" customHeight="1"/>
-    <row r="507" ht="15.75" customHeight="1"/>
-    <row r="508" ht="15.75" customHeight="1"/>
-    <row r="509" ht="15.75" customHeight="1"/>
-    <row r="510" ht="15.75" customHeight="1"/>
-    <row r="511" ht="15.75" customHeight="1"/>
-    <row r="512" ht="15.75" customHeight="1"/>
-    <row r="513" ht="15.75" customHeight="1"/>
-    <row r="514" ht="15.75" customHeight="1"/>
-    <row r="515" ht="15.75" customHeight="1"/>
-    <row r="516" ht="15.75" customHeight="1"/>
-    <row r="517" ht="15.75" customHeight="1"/>
-    <row r="518" ht="15.75" customHeight="1"/>
-    <row r="519" ht="15.75" customHeight="1"/>
-    <row r="520" ht="15.75" customHeight="1"/>
-    <row r="521" ht="15.75" customHeight="1"/>
-    <row r="522" ht="15.75" customHeight="1"/>
-    <row r="523" ht="15.75" customHeight="1"/>
-    <row r="524" ht="15.75" customHeight="1"/>
-    <row r="525" ht="15.75" customHeight="1"/>
-    <row r="526" ht="15.75" customHeight="1"/>
-    <row r="527" ht="15.75" customHeight="1"/>
-    <row r="528" ht="15.75" customHeight="1"/>
-    <row r="529" ht="15.75" customHeight="1"/>
-    <row r="530" ht="15.75" customHeight="1"/>
-    <row r="531" ht="15.75" customHeight="1"/>
-    <row r="532" ht="15.75" customHeight="1"/>
-    <row r="533" ht="15.75" customHeight="1"/>
-    <row r="534" ht="15.75" customHeight="1"/>
-    <row r="535" ht="15.75" customHeight="1"/>
-    <row r="536" ht="15.75" customHeight="1"/>
-    <row r="537" ht="15.75" customHeight="1"/>
-    <row r="538" ht="15.75" customHeight="1"/>
-    <row r="539" ht="15.75" customHeight="1"/>
-    <row r="540" ht="15.75" customHeight="1"/>
-    <row r="541" ht="15.75" customHeight="1"/>
-    <row r="542" ht="15.75" customHeight="1"/>
-    <row r="543" ht="15.75" customHeight="1"/>
-    <row r="544" ht="15.75" customHeight="1"/>
-    <row r="545" ht="15.75" customHeight="1"/>
-    <row r="546" ht="15.75" customHeight="1"/>
-    <row r="547" ht="15.75" customHeight="1"/>
-    <row r="548" ht="15.75" customHeight="1"/>
-    <row r="549" ht="15.75" customHeight="1"/>
-    <row r="550" ht="15.75" customHeight="1"/>
-    <row r="551" ht="15.75" customHeight="1"/>
-    <row r="552" ht="15.75" customHeight="1"/>
-    <row r="553" ht="15.75" customHeight="1"/>
-    <row r="554" ht="15.75" customHeight="1"/>
-    <row r="555" ht="15.75" customHeight="1"/>
-    <row r="556" ht="15.75" customHeight="1"/>
-    <row r="557" ht="15.75" customHeight="1"/>
-    <row r="558" ht="15.75" customHeight="1"/>
-    <row r="559" ht="15.75" customHeight="1"/>
-    <row r="560" ht="15.75" customHeight="1"/>
-    <row r="561" ht="15.75" customHeight="1"/>
-    <row r="562" ht="15.75" customHeight="1"/>
-    <row r="563" ht="15.75" customHeight="1"/>
-    <row r="564" ht="15.75" customHeight="1"/>
-    <row r="565" ht="15.75" customHeight="1"/>
-    <row r="566" ht="15.75" customHeight="1"/>
-    <row r="567" ht="15.75" customHeight="1"/>
-    <row r="568" ht="15.75" customHeight="1"/>
-    <row r="569" ht="15.75" customHeight="1"/>
-    <row r="570" ht="15.75" customHeight="1"/>
-    <row r="571" ht="15.75" customHeight="1"/>
-    <row r="572" ht="15.75" customHeight="1"/>
-    <row r="573" ht="15.75" customHeight="1"/>
-    <row r="574" ht="15.75" customHeight="1"/>
-    <row r="575" ht="15.75" customHeight="1"/>
-    <row r="576" ht="15.75" customHeight="1"/>
-    <row r="577" ht="15.75" customHeight="1"/>
-    <row r="578" ht="15.75" customHeight="1"/>
-    <row r="579" ht="15.75" customHeight="1"/>
-    <row r="580" ht="15.75" customHeight="1"/>
-    <row r="581" ht="15.75" customHeight="1"/>
-    <row r="582" ht="15.75" customHeight="1"/>
-    <row r="583" ht="15.75" customHeight="1"/>
-    <row r="584" ht="15.75" customHeight="1"/>
-    <row r="585" ht="15.75" customHeight="1"/>
-    <row r="586" ht="15.75" customHeight="1"/>
-    <row r="587" ht="15.75" customHeight="1"/>
-    <row r="588" ht="15.75" customHeight="1"/>
-    <row r="589" ht="15.75" customHeight="1"/>
-    <row r="590" ht="15.75" customHeight="1"/>
-    <row r="591" ht="15.75" customHeight="1"/>
-    <row r="592" ht="15.75" customHeight="1"/>
-    <row r="593" ht="15.75" customHeight="1"/>
-    <row r="594" ht="15.75" customHeight="1"/>
-    <row r="595" ht="15.75" customHeight="1"/>
-    <row r="596" ht="15.75" customHeight="1"/>
-    <row r="597" ht="15.75" customHeight="1"/>
-    <row r="598" ht="15.75" customHeight="1"/>
-    <row r="599" ht="15.75" customHeight="1"/>
-    <row r="600" ht="15.75" customHeight="1"/>
-    <row r="601" ht="15.75" customHeight="1"/>
-    <row r="602" ht="15.75" customHeight="1"/>
-    <row r="603" ht="15.75" customHeight="1"/>
-    <row r="604" ht="15.75" customHeight="1"/>
-    <row r="605" ht="15.75" customHeight="1"/>
-    <row r="606" ht="15.75" customHeight="1"/>
-    <row r="607" ht="15.75" customHeight="1"/>
-    <row r="608" ht="15.75" customHeight="1"/>
-    <row r="609" ht="15.75" customHeight="1"/>
-    <row r="610" ht="15.75" customHeight="1"/>
-    <row r="611" ht="15.75" customHeight="1"/>
-    <row r="612" ht="15.75" customHeight="1"/>
-    <row r="613" ht="15.75" customHeight="1"/>
-    <row r="614" ht="15.75" customHeight="1"/>
-    <row r="615" ht="15.75" customHeight="1"/>
-    <row r="616" ht="15.75" customHeight="1"/>
-    <row r="617" ht="15.75" customHeight="1"/>
-    <row r="618" ht="15.75" customHeight="1"/>
-    <row r="619" ht="15.75" customHeight="1"/>
-    <row r="620" ht="15.75" customHeight="1"/>
-    <row r="621" ht="15.75" customHeight="1"/>
-    <row r="622" ht="15.75" customHeight="1"/>
-    <row r="623" ht="15.75" customHeight="1"/>
-    <row r="624" ht="15.75" customHeight="1"/>
-    <row r="625" ht="15.75" customHeight="1"/>
-    <row r="626" ht="15.75" customHeight="1"/>
-    <row r="627" ht="15.75" customHeight="1"/>
-    <row r="628" ht="15.75" customHeight="1"/>
-    <row r="629" ht="15.75" customHeight="1"/>
-    <row r="630" ht="15.75" customHeight="1"/>
-    <row r="631" ht="15.75" customHeight="1"/>
-    <row r="632" ht="15.75" customHeight="1"/>
-    <row r="633" ht="15.75" customHeight="1"/>
-    <row r="634" ht="15.75" customHeight="1"/>
-    <row r="635" ht="15.75" customHeight="1"/>
-    <row r="636" ht="15.75" customHeight="1"/>
-    <row r="637" ht="15.75" customHeight="1"/>
-    <row r="638" ht="15.75" customHeight="1"/>
-    <row r="639" ht="15.75" customHeight="1"/>
-    <row r="640" ht="15.75" customHeight="1"/>
-    <row r="641" ht="15.75" customHeight="1"/>
-    <row r="642" ht="15.75" customHeight="1"/>
-    <row r="643" ht="15.75" customHeight="1"/>
-    <row r="644" ht="15.75" customHeight="1"/>
-    <row r="645" ht="15.75" customHeight="1"/>
-    <row r="646" ht="15.75" customHeight="1"/>
-    <row r="647" ht="15.75" customHeight="1"/>
-    <row r="648" ht="15.75" customHeight="1"/>
-    <row r="649" ht="15.75" customHeight="1"/>
-    <row r="650" ht="15.75" customHeight="1"/>
-    <row r="651" ht="15.75" customHeight="1"/>
-    <row r="652" ht="15.75" customHeight="1"/>
-    <row r="653" ht="15.75" customHeight="1"/>
-    <row r="654" ht="15.75" customHeight="1"/>
-    <row r="655" ht="15.75" customHeight="1"/>
-    <row r="656" ht="15.75" customHeight="1"/>
-    <row r="657" ht="15.75" customHeight="1"/>
-    <row r="658" ht="15.75" customHeight="1"/>
-    <row r="659" ht="15.75" customHeight="1"/>
-    <row r="660" ht="15.75" customHeight="1"/>
-    <row r="661" ht="15.75" customHeight="1"/>
-    <row r="662" ht="15.75" customHeight="1"/>
-    <row r="663" ht="15.75" customHeight="1"/>
-    <row r="664" ht="15.75" customHeight="1"/>
-    <row r="665" ht="15.75" customHeight="1"/>
-    <row r="666" ht="15.75" customHeight="1"/>
-    <row r="667" ht="15.75" customHeight="1"/>
-    <row r="668" ht="15.75" customHeight="1"/>
-    <row r="669" ht="15.75" customHeight="1"/>
-    <row r="670" ht="15.75" customHeight="1"/>
-    <row r="671" ht="15.75" customHeight="1"/>
-    <row r="672" ht="15.75" customHeight="1"/>
-    <row r="673" ht="15.75" customHeight="1"/>
-    <row r="674" ht="15.75" customHeight="1"/>
-    <row r="675" ht="15.75" customHeight="1"/>
-    <row r="676" ht="15.75" customHeight="1"/>
-    <row r="677" ht="15.75" customHeight="1"/>
-    <row r="678" ht="15.75" customHeight="1"/>
-    <row r="679" ht="15.75" customHeight="1"/>
-    <row r="680" ht="15.75" customHeight="1"/>
-    <row r="681" ht="15.75" customHeight="1"/>
-    <row r="682" ht="15.75" customHeight="1"/>
-    <row r="683" ht="15.75" customHeight="1"/>
-    <row r="684" ht="15.75" customHeight="1"/>
-    <row r="685" ht="15.75" customHeight="1"/>
-    <row r="686" ht="15.75" customHeight="1"/>
-    <row r="687" ht="15.75" customHeight="1"/>
-    <row r="688" ht="15.75" customHeight="1"/>
-    <row r="689" ht="15.75" customHeight="1"/>
-    <row r="690" ht="15.75" customHeight="1"/>
-    <row r="691" ht="15.75" customHeight="1"/>
-    <row r="692" ht="15.75" customHeight="1"/>
-    <row r="693" ht="15.75" customHeight="1"/>
-    <row r="694" ht="15.75" customHeight="1"/>
-    <row r="695" ht="15.75" customHeight="1"/>
-    <row r="696" ht="15.75" customHeight="1"/>
-    <row r="697" ht="15.75" customHeight="1"/>
-    <row r="698" ht="15.75" customHeight="1"/>
-    <row r="699" ht="15.75" customHeight="1"/>
-    <row r="700" ht="15.75" customHeight="1"/>
-    <row r="701" ht="15.75" customHeight="1"/>
-    <row r="702" ht="15.75" customHeight="1"/>
-    <row r="703" ht="15.75" customHeight="1"/>
-    <row r="704" ht="15.75" customHeight="1"/>
-    <row r="705" ht="15.75" customHeight="1"/>
-    <row r="706" ht="15.75" customHeight="1"/>
-    <row r="707" ht="15.75" customHeight="1"/>
-    <row r="708" ht="15.75" customHeight="1"/>
-    <row r="709" ht="15.75" customHeight="1"/>
-    <row r="710" ht="15.75" customHeight="1"/>
-    <row r="711" ht="15.75" customHeight="1"/>
-    <row r="712" ht="15.75" customHeight="1"/>
-    <row r="713" ht="15.75" customHeight="1"/>
-    <row r="714" ht="15.75" customHeight="1"/>
-    <row r="715" ht="15.75" customHeight="1"/>
-    <row r="716" ht="15.75" customHeight="1"/>
-    <row r="717" ht="15.75" customHeight="1"/>
-    <row r="718" ht="15.75" customHeight="1"/>
-    <row r="719" ht="15.75" customHeight="1"/>
-    <row r="720" ht="15.75" customHeight="1"/>
-    <row r="721" ht="15.75" customHeight="1"/>
-    <row r="722" ht="15.75" customHeight="1"/>
-    <row r="723" ht="15.75" customHeight="1"/>
-    <row r="724" ht="15.75" customHeight="1"/>
-    <row r="725" ht="15.75" customHeight="1"/>
-    <row r="726" ht="15.75" customHeight="1"/>
-    <row r="727" ht="15.75" customHeight="1"/>
-    <row r="728" ht="15.75" customHeight="1"/>
-    <row r="729" ht="15.75" customHeight="1"/>
-    <row r="730" ht="15.75" customHeight="1"/>
-    <row r="731" ht="15.75" customHeight="1"/>
-    <row r="732" ht="15.75" customHeight="1"/>
-    <row r="733" ht="15.75" customHeight="1"/>
-    <row r="734" ht="15.75" customHeight="1"/>
-    <row r="735" ht="15.75" customHeight="1"/>
-    <row r="736" ht="15.75" customHeight="1"/>
-    <row r="737" ht="15.75" customHeight="1"/>
-    <row r="738" ht="15.75" customHeight="1"/>
-    <row r="739" ht="15.75" customHeight="1"/>
-    <row r="740" ht="15.75" customHeight="1"/>
-    <row r="741" ht="15.75" customHeight="1"/>
-    <row r="742" ht="15.75" customHeight="1"/>
-    <row r="743" ht="15.75" customHeight="1"/>
-    <row r="744" ht="15.75" customHeight="1"/>
-    <row r="745" ht="15.75" customHeight="1"/>
-    <row r="746" ht="15.75" customHeight="1"/>
-    <row r="747" ht="15.75" customHeight="1"/>
-    <row r="748" ht="15.75" customHeight="1"/>
-    <row r="749" ht="15.75" customHeight="1"/>
-    <row r="750" ht="15.75" customHeight="1"/>
-    <row r="751" ht="15.75" customHeight="1"/>
-    <row r="752" ht="15.75" customHeight="1"/>
-    <row r="753" ht="15.75" customHeight="1"/>
-    <row r="754" ht="15.75" customHeight="1"/>
-    <row r="755" ht="15.75" customHeight="1"/>
-    <row r="756" ht="15.75" customHeight="1"/>
-    <row r="757" ht="15.75" customHeight="1"/>
-    <row r="758" ht="15.75" customHeight="1"/>
-    <row r="759" ht="15.75" customHeight="1"/>
-    <row r="760" ht="15.75" customHeight="1"/>
-    <row r="761" ht="15.75" customHeight="1"/>
-    <row r="762" ht="15.75" customHeight="1"/>
-    <row r="763" ht="15.75" customHeight="1"/>
-    <row r="764" ht="15.75" customHeight="1"/>
-    <row r="765" ht="15.75" customHeight="1"/>
-    <row r="766" ht="15.75" customHeight="1"/>
-    <row r="767" ht="15.75" customHeight="1"/>
-    <row r="768" ht="15.75" customHeight="1"/>
-    <row r="769" ht="15.75" customHeight="1"/>
-    <row r="770" ht="15.75" customHeight="1"/>
-    <row r="771" ht="15.75" customHeight="1"/>
-    <row r="772" ht="15.75" customHeight="1"/>
-    <row r="773" ht="15.75" customHeight="1"/>
-    <row r="774" ht="15.75" customHeight="1"/>
-    <row r="775" ht="15.75" customHeight="1"/>
-    <row r="776" ht="15.75" customHeight="1"/>
-    <row r="777" ht="15.75" customHeight="1"/>
-    <row r="778" ht="15.75" customHeight="1"/>
-    <row r="779" ht="15.75" customHeight="1"/>
-    <row r="780" ht="15.75" customHeight="1"/>
-    <row r="781" ht="15.75" customHeight="1"/>
-    <row r="782" ht="15.75" customHeight="1"/>
-    <row r="783" ht="15.75" customHeight="1"/>
-    <row r="784" ht="15.75" customHeight="1"/>
-    <row r="785" ht="15.75" customHeight="1"/>
-    <row r="786" ht="15.75" customHeight="1"/>
-    <row r="787" ht="15.75" customHeight="1"/>
-    <row r="788" ht="15.75" customHeight="1"/>
-    <row r="789" ht="15.75" customHeight="1"/>
-    <row r="790" ht="15.75" customHeight="1"/>
-    <row r="791" ht="15.75" customHeight="1"/>
-    <row r="792" ht="15.75" customHeight="1"/>
-    <row r="793" ht="15.75" customHeight="1"/>
-    <row r="794" ht="15.75" customHeight="1"/>
-    <row r="795" ht="15.75" customHeight="1"/>
-    <row r="796" ht="15.75" customHeight="1"/>
-    <row r="797" ht="15.75" customHeight="1"/>
-    <row r="798" ht="15.75" customHeight="1"/>
-    <row r="799" ht="15.75" customHeight="1"/>
-    <row r="800" ht="15.75" customHeight="1"/>
-    <row r="801" ht="15.75" customHeight="1"/>
-    <row r="802" ht="15.75" customHeight="1"/>
-    <row r="803" ht="15.75" customHeight="1"/>
-    <row r="804" ht="15.75" customHeight="1"/>
-    <row r="805" ht="15.75" customHeight="1"/>
-    <row r="806" ht="15.75" customHeight="1"/>
-    <row r="807" ht="15.75" customHeight="1"/>
-    <row r="808" ht="15.75" customHeight="1"/>
-    <row r="809" ht="15.75" customHeight="1"/>
-    <row r="810" ht="15.75" customHeight="1"/>
-    <row r="811" ht="15.75" customHeight="1"/>
-    <row r="812" ht="15.75" customHeight="1"/>
-    <row r="813" ht="15.75" customHeight="1"/>
-    <row r="814" ht="15.75" customHeight="1"/>
-    <row r="815" ht="15.75" customHeight="1"/>
-    <row r="816" ht="15.75" customHeight="1"/>
-    <row r="817" ht="15.75" customHeight="1"/>
-    <row r="818" ht="15.75" customHeight="1"/>
-    <row r="819" ht="15.75" customHeight="1"/>
-    <row r="820" ht="15.75" customHeight="1"/>
-    <row r="821" ht="15.75" customHeight="1"/>
-    <row r="822" ht="15.75" customHeight="1"/>
-    <row r="823" ht="15.75" customHeight="1"/>
-    <row r="824" ht="15.75" customHeight="1"/>
-    <row r="825" ht="15.75" customHeight="1"/>
-    <row r="826" ht="15.75" customHeight="1"/>
-    <row r="827" ht="15.75" customHeight="1"/>
-    <row r="828" ht="15.75" customHeight="1"/>
-    <row r="829" ht="15.75" customHeight="1"/>
-    <row r="830" ht="15.75" customHeight="1"/>
-    <row r="831" ht="15.75" customHeight="1"/>
-    <row r="832" ht="15.75" customHeight="1"/>
-    <row r="833" ht="15.75" customHeight="1"/>
-    <row r="834" ht="15.75" customHeight="1"/>
-    <row r="835" ht="15.75" customHeight="1"/>
-    <row r="836" ht="15.75" customHeight="1"/>
-    <row r="837" ht="15.75" customHeight="1"/>
-    <row r="838" ht="15.75" customHeight="1"/>
-    <row r="839" ht="15.75" customHeight="1"/>
-    <row r="840" ht="15.75" customHeight="1"/>
-    <row r="841" ht="15.75" customHeight="1"/>
-    <row r="842" ht="15.75" customHeight="1"/>
-    <row r="843" ht="15.75" customHeight="1"/>
-    <row r="844" ht="15.75" customHeight="1"/>
-    <row r="845" ht="15.75" customHeight="1"/>
-    <row r="846" ht="15.75" customHeight="1"/>
-    <row r="847" ht="15.75" customHeight="1"/>
-    <row r="848" ht="15.75" customHeight="1"/>
-    <row r="849" ht="15.75" customHeight="1"/>
-    <row r="850" ht="15.75" customHeight="1"/>
-    <row r="851" ht="15.75" customHeight="1"/>
-    <row r="852" ht="15.75" customHeight="1"/>
-    <row r="853" ht="15.75" customHeight="1"/>
-    <row r="854" ht="15.75" customHeight="1"/>
-    <row r="855" ht="15.75" customHeight="1"/>
-    <row r="856" ht="15.75" customHeight="1"/>
-    <row r="857" ht="15.75" customHeight="1"/>
-    <row r="858" ht="15.75" customHeight="1"/>
-    <row r="859" ht="15.75" customHeight="1"/>
-    <row r="860" ht="15.75" customHeight="1"/>
-    <row r="861" ht="15.75" customHeight="1"/>
-    <row r="862" ht="15.75" customHeight="1"/>
-    <row r="863" ht="15.75" customHeight="1"/>
-    <row r="864" ht="15.75" customHeight="1"/>
-    <row r="865" ht="15.75" customHeight="1"/>
-    <row r="866" ht="15.75" customHeight="1"/>
-    <row r="867" ht="15.75" customHeight="1"/>
-    <row r="868" ht="15.75" customHeight="1"/>
-    <row r="869" ht="15.75" customHeight="1"/>
-    <row r="870" ht="15.75" customHeight="1"/>
-    <row r="871" ht="15.75" customHeight="1"/>
-    <row r="872" ht="15.75" customHeight="1"/>
-    <row r="873" ht="15.75" customHeight="1"/>
-    <row r="874" ht="15.75" customHeight="1"/>
-    <row r="875" ht="15.75" customHeight="1"/>
-    <row r="876" ht="15.75" customHeight="1"/>
-    <row r="877" ht="15.75" customHeight="1"/>
-    <row r="878" ht="15.75" customHeight="1"/>
-    <row r="879" ht="15.75" customHeight="1"/>
-    <row r="880" ht="15.75" customHeight="1"/>
-    <row r="881" ht="15.75" customHeight="1"/>
-    <row r="882" ht="15.75" customHeight="1"/>
-    <row r="883" ht="15.75" customHeight="1"/>
-    <row r="884" ht="15.75" customHeight="1"/>
-    <row r="885" ht="15.75" customHeight="1"/>
-    <row r="886" ht="15.75" customHeight="1"/>
-    <row r="887" ht="15.75" customHeight="1"/>
-    <row r="888" ht="15.75" customHeight="1"/>
-    <row r="889" ht="15.75" customHeight="1"/>
-    <row r="890" ht="15.75" customHeight="1"/>
-    <row r="891" ht="15.75" customHeight="1"/>
-    <row r="892" ht="15.75" customHeight="1"/>
-    <row r="893" ht="15.75" customHeight="1"/>
-    <row r="894" ht="15.75" customHeight="1"/>
-    <row r="895" ht="15.75" customHeight="1"/>
-    <row r="896" ht="15.75" customHeight="1"/>
-    <row r="897" ht="15.75" customHeight="1"/>
-    <row r="898" ht="15.75" customHeight="1"/>
-    <row r="899" ht="15.75" customHeight="1"/>
-    <row r="900" ht="15.75" customHeight="1"/>
-    <row r="901" ht="15.75" customHeight="1"/>
-    <row r="902" ht="15.75" customHeight="1"/>
-    <row r="903" ht="15.75" customHeight="1"/>
-    <row r="904" ht="15.75" customHeight="1"/>
-    <row r="905" ht="15.75" customHeight="1"/>
-    <row r="906" ht="15.75" customHeight="1"/>
-    <row r="907" ht="15.75" customHeight="1"/>
-    <row r="908" ht="15.75" customHeight="1"/>
-    <row r="909" ht="15.75" customHeight="1"/>
-    <row r="910" ht="15.75" customHeight="1"/>
-    <row r="911" ht="15.75" customHeight="1"/>
-    <row r="912" ht="15.75" customHeight="1"/>
-    <row r="913" ht="15.75" customHeight="1"/>
-    <row r="914" ht="15.75" customHeight="1"/>
-    <row r="915" ht="15.75" customHeight="1"/>
-    <row r="916" ht="15.75" customHeight="1"/>
-    <row r="917" ht="15.75" customHeight="1"/>
-    <row r="918" ht="15.75" customHeight="1"/>
-    <row r="919" ht="15.75" customHeight="1"/>
-    <row r="920" ht="15.75" customHeight="1"/>
-    <row r="921" ht="15.75" customHeight="1"/>
-    <row r="922" ht="15.75" customHeight="1"/>
-    <row r="923" ht="15.75" customHeight="1"/>
-    <row r="924" ht="15.75" customHeight="1"/>
-    <row r="925" ht="15.75" customHeight="1"/>
-    <row r="926" ht="15.75" customHeight="1"/>
-    <row r="927" ht="15.75" customHeight="1"/>
-    <row r="928" ht="15.75" customHeight="1"/>
-    <row r="929" ht="15.75" customHeight="1"/>
-    <row r="930" ht="15.75" customHeight="1"/>
-    <row r="931" ht="15.75" customHeight="1"/>
-    <row r="932" ht="15.75" customHeight="1"/>
-    <row r="933" ht="15.75" customHeight="1"/>
-    <row r="934" ht="15.75" customHeight="1"/>
-    <row r="935" ht="15.75" customHeight="1"/>
-    <row r="936" ht="15.75" customHeight="1"/>
-    <row r="937" ht="15.75" customHeight="1"/>
-    <row r="938" ht="15.75" customHeight="1"/>
-    <row r="939" ht="15.75" customHeight="1"/>
-    <row r="940" ht="15.75" customHeight="1"/>
-    <row r="941" ht="15.75" customHeight="1"/>
-    <row r="942" ht="15.75" customHeight="1"/>
-    <row r="943" ht="15.75" customHeight="1"/>
-    <row r="944" ht="15.75" customHeight="1"/>
-    <row r="945" ht="15.75" customHeight="1"/>
-    <row r="946" ht="15.75" customHeight="1"/>
-    <row r="947" ht="15.75" customHeight="1"/>
-    <row r="948" ht="15.75" customHeight="1"/>
-    <row r="949" ht="15.75" customHeight="1"/>
-    <row r="950" ht="15.75" customHeight="1"/>
-    <row r="951" ht="15.75" customHeight="1"/>
-    <row r="952" ht="15.75" customHeight="1"/>
-    <row r="953" ht="15.75" customHeight="1"/>
-    <row r="954" ht="15.75" customHeight="1"/>
-    <row r="955" ht="15.75" customHeight="1"/>
-    <row r="956" ht="15.75" customHeight="1"/>
-    <row r="957" ht="15.75" customHeight="1"/>
-    <row r="958" ht="15.75" customHeight="1"/>
-    <row r="959" ht="15.75" customHeight="1"/>
-    <row r="960" ht="15.75" customHeight="1"/>
-    <row r="961" ht="15.75" customHeight="1"/>
-    <row r="962" ht="15.75" customHeight="1"/>
-    <row r="963" ht="15.75" customHeight="1"/>
-    <row r="964" ht="15.75" customHeight="1"/>
-    <row r="965" ht="15.75" customHeight="1"/>
-    <row r="966" ht="15.75" customHeight="1"/>
-    <row r="967" ht="15.75" customHeight="1"/>
-    <row r="968" ht="15.75" customHeight="1"/>
-    <row r="969" ht="15.75" customHeight="1"/>
-    <row r="970" ht="15.75" customHeight="1"/>
-    <row r="971" ht="15.75" customHeight="1"/>
-    <row r="972" ht="15.75" customHeight="1"/>
-    <row r="973" ht="15.75" customHeight="1"/>
-    <row r="974" ht="15.75" customHeight="1"/>
-    <row r="975" ht="15.75" customHeight="1"/>
-    <row r="976" ht="15.75" customHeight="1"/>
-    <row r="977" ht="15.75" customHeight="1"/>
-    <row r="978" ht="15.75" customHeight="1"/>
-    <row r="979" ht="15.75" customHeight="1"/>
-    <row r="980" ht="15.75" customHeight="1"/>
-    <row r="981" ht="15.75" customHeight="1"/>
-    <row r="982" ht="15.75" customHeight="1"/>
-    <row r="983" ht="15.75" customHeight="1"/>
-    <row r="984" ht="15.75" customHeight="1"/>
-    <row r="985" ht="15.75" customHeight="1"/>
-    <row r="986" ht="15.75" customHeight="1"/>
-    <row r="987" ht="15.75" customHeight="1"/>
-    <row r="988" ht="15.75" customHeight="1"/>
-    <row r="989" ht="15.75" customHeight="1"/>
-    <row r="990" ht="15.75" customHeight="1"/>
-    <row r="991" ht="15.75" customHeight="1"/>
-    <row r="992" ht="15.75" customHeight="1"/>
-    <row r="993" ht="15.75" customHeight="1"/>
-    <row r="994" ht="15.75" customHeight="1"/>
-    <row r="995" ht="15.75" customHeight="1"/>
-    <row r="996" ht="15.75" customHeight="1"/>
-    <row r="997" ht="15.75" customHeight="1"/>
-    <row r="998" ht="15.75" customHeight="1"/>
-    <row r="999" ht="15.75" customHeight="1"/>
-    <row r="1000" ht="15.75" customHeight="1"/>
-    <row r="1001" ht="15.75" customHeight="1"/>
-  </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A3:J3"/>
-    <mergeCell ref="A6:J6"/>
-    <mergeCell ref="A11:J11"/>
-  </mergeCells>
-  <conditionalFormatting sqref="H4:H5 H7:H10 H12:H16">
-    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="✅ PASS">
-      <formula>NOT(ISERROR(SEARCH(("✅ PASS"),(H4))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H4:H5 H7:H10 H12:H16">
-    <cfRule type="containsText" dxfId="4" priority="2" operator="containsText" text="❌ FAIL">
-      <formula>NOT(ISERROR(SEARCH(("❌ FAIL"),(H4))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H4:H5 H7:H10 H12:H16">
-    <cfRule type="containsText" dxfId="2" priority="3" operator="containsText" text="⏳ PENDING">
-      <formula>NOT(ISERROR(SEARCH(("⏳ PENDING"),(H4))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <dataValidations>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="H4:H5 H7:H10 H12:H16">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="H4:H6 H8:H11 H13:H17">
       <formula1>"⏳ PENDIENTE,✅ PASS,❌ FAIL"</formula1>
     </dataValidation>
   </dataValidations>
@@ -16356,7 +16437,7 @@
   <sheetData>
     <row r="1" ht="24.0" customHeight="1">
       <c r="A1" s="27" t="s">
-        <v>400</v>
+        <v>407</v>
       </c>
       <c r="B1" s="28"/>
       <c r="C1" s="28"/>
@@ -16402,7 +16483,7 @@
     </row>
     <row r="3" ht="18.0" customHeight="1">
       <c r="A3" s="29" t="s">
-        <v>401</v>
+        <v>408</v>
       </c>
       <c r="B3" s="30"/>
       <c r="C3" s="30"/>
@@ -16416,16 +16497,16 @@
     </row>
     <row r="4" ht="42.0" customHeight="1">
       <c r="A4" s="23" t="s">
-        <v>402</v>
+        <v>409</v>
       </c>
       <c r="B4" s="21" t="s">
-        <v>403</v>
+        <v>410</v>
       </c>
       <c r="C4" s="43" t="s">
         <v>139</v>
       </c>
       <c r="D4" s="21" t="s">
-        <v>404</v>
+        <v>411</v>
       </c>
       <c r="E4" s="21" t="s">
         <v>198</v>
@@ -16434,28 +16515,28 @@
         <v>141</v>
       </c>
       <c r="G4" s="21" t="s">
-        <v>405</v>
+        <v>412</v>
       </c>
       <c r="H4" s="33" t="s">
         <v>70</v>
       </c>
       <c r="I4" s="21" t="s">
-        <v>406</v>
+        <v>413</v>
       </c>
       <c r="J4" s="23"/>
     </row>
     <row r="5" ht="42.0" customHeight="1">
       <c r="A5" s="34" t="s">
-        <v>407</v>
+        <v>414</v>
       </c>
       <c r="B5" s="20" t="s">
-        <v>408</v>
+        <v>415</v>
       </c>
       <c r="C5" s="36" t="s">
         <v>139</v>
       </c>
       <c r="D5" s="20" t="s">
-        <v>404</v>
+        <v>411</v>
       </c>
       <c r="E5" s="20" t="s">
         <v>198</v>
@@ -16464,19 +16545,19 @@
         <v>141</v>
       </c>
       <c r="G5" s="20" t="s">
-        <v>409</v>
+        <v>416</v>
       </c>
       <c r="H5" s="33" t="s">
         <v>70</v>
       </c>
       <c r="I5" s="20" t="s">
-        <v>410</v>
+        <v>417</v>
       </c>
       <c r="J5" s="34"/>
     </row>
     <row r="6" ht="18.0" customHeight="1">
       <c r="A6" s="29" t="s">
-        <v>411</v>
+        <v>418</v>
       </c>
       <c r="B6" s="30"/>
       <c r="C6" s="30"/>
@@ -16490,16 +16571,16 @@
     </row>
     <row r="7" ht="42.0" customHeight="1">
       <c r="A7" s="23" t="s">
-        <v>412</v>
+        <v>419</v>
       </c>
       <c r="B7" s="21" t="s">
-        <v>413</v>
+        <v>420</v>
       </c>
       <c r="C7" s="32" t="s">
         <v>97</v>
       </c>
       <c r="D7" s="21" t="s">
-        <v>414</v>
+        <v>421</v>
       </c>
       <c r="E7" s="21" t="s">
         <v>198</v>
@@ -16509,28 +16590,28 @@
         <v>967092f8-fb6a-4db2-af08-d77fa4540610</v>
       </c>
       <c r="G7" s="21" t="s">
-        <v>415</v>
+        <v>422</v>
       </c>
       <c r="H7" s="33" t="s">
         <v>70</v>
       </c>
       <c r="I7" s="21" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="J7" s="23"/>
     </row>
     <row r="8" ht="42.0" customHeight="1">
       <c r="A8" s="34" t="s">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="B8" s="20" t="s">
-        <v>418</v>
+        <v>425</v>
       </c>
       <c r="C8" s="35" t="s">
         <v>97</v>
       </c>
       <c r="D8" s="20" t="s">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="E8" s="20" t="s">
         <v>198</v>
@@ -16540,28 +16621,28 @@
         <v>5df1bedc-a8b4-4cb2-9a9a-7b3d60252582</v>
       </c>
       <c r="G8" s="20" t="s">
-        <v>420</v>
+        <v>427</v>
       </c>
       <c r="H8" s="33" t="s">
         <v>70</v>
       </c>
       <c r="I8" s="20" t="s">
-        <v>421</v>
+        <v>428</v>
       </c>
       <c r="J8" s="34"/>
     </row>
     <row r="9" ht="42.0" customHeight="1">
       <c r="A9" s="23" t="s">
-        <v>422</v>
+        <v>429</v>
       </c>
       <c r="B9" s="21" t="s">
-        <v>423</v>
+        <v>430</v>
       </c>
       <c r="C9" s="32" t="s">
         <v>97</v>
       </c>
       <c r="D9" s="21" t="s">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="E9" s="21" t="s">
         <v>198</v>
@@ -16571,7 +16652,7 @@
         <v>5df1bedc-a8b4-4cb2-9a9a-7b3d60252582</v>
       </c>
       <c r="G9" s="21" t="s">
-        <v>424</v>
+        <v>431</v>
       </c>
       <c r="H9" s="33" t="s">
         <v>70</v>
@@ -16581,16 +16662,16 @@
     </row>
     <row r="10" ht="42.0" customHeight="1">
       <c r="A10" s="34" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="B10" s="20" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="C10" s="35" t="s">
         <v>97</v>
       </c>
       <c r="D10" s="20" t="s">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="E10" s="20" t="s">
         <v>198</v>
@@ -16600,7 +16681,7 @@
         <v>967092f8-fb6a-4db2-af08-d77fa4540610</v>
       </c>
       <c r="G10" s="20" t="s">
-        <v>424</v>
+        <v>431</v>
       </c>
       <c r="H10" s="33" t="s">
         <v>70</v>
@@ -16610,7 +16691,7 @@
     </row>
     <row r="11" ht="18.0" customHeight="1">
       <c r="A11" s="29" t="s">
-        <v>427</v>
+        <v>434</v>
       </c>
       <c r="B11" s="30"/>
       <c r="C11" s="30"/>
@@ -16624,16 +16705,16 @@
     </row>
     <row r="12" ht="42.0" customHeight="1">
       <c r="A12" s="23" t="s">
-        <v>428</v>
+        <v>435</v>
       </c>
       <c r="B12" s="21" t="s">
-        <v>429</v>
+        <v>436</v>
       </c>
       <c r="C12" s="43" t="s">
         <v>139</v>
       </c>
       <c r="D12" s="21" t="s">
-        <v>430</v>
+        <v>437</v>
       </c>
       <c r="E12" s="21" t="s">
         <v>198</v>
@@ -16643,7 +16724,7 @@
         <v>c7cf918d-7e04-4104-9790-fa5bb9d3756d</v>
       </c>
       <c r="G12" s="21" t="s">
-        <v>431</v>
+        <v>438</v>
       </c>
       <c r="H12" s="33" t="s">
         <v>70</v>
@@ -16653,16 +16734,16 @@
     </row>
     <row r="13" ht="42.0" customHeight="1">
       <c r="A13" s="34" t="s">
-        <v>432</v>
+        <v>439</v>
       </c>
       <c r="B13" s="20" t="s">
-        <v>433</v>
+        <v>440</v>
       </c>
       <c r="C13" s="36" t="s">
         <v>139</v>
       </c>
       <c r="D13" s="20" t="s">
-        <v>434</v>
+        <v>441</v>
       </c>
       <c r="E13" s="20" t="s">
         <v>198</v>
@@ -16671,7 +16752,7 @@
         <v>141</v>
       </c>
       <c r="G13" s="20" t="s">
-        <v>435</v>
+        <v>442</v>
       </c>
       <c r="H13" s="33" t="s">
         <v>70</v>
@@ -16681,16 +16762,16 @@
     </row>
     <row r="14" ht="42.0" customHeight="1">
       <c r="A14" s="23" t="s">
-        <v>436</v>
+        <v>443</v>
       </c>
       <c r="B14" s="21" t="s">
-        <v>437</v>
+        <v>444</v>
       </c>
       <c r="C14" s="32" t="s">
         <v>97</v>
       </c>
       <c r="D14" s="21" t="s">
-        <v>438</v>
+        <v>445</v>
       </c>
       <c r="E14" s="21" t="s">
         <v>198</v>
@@ -16700,13 +16781,13 @@
         <v>c7cf918d-7e04-4104-9790-fa5bb9d3756d</v>
       </c>
       <c r="G14" s="21" t="s">
-        <v>439</v>
+        <v>446</v>
       </c>
       <c r="H14" s="33" t="s">
         <v>70</v>
       </c>
       <c r="I14" s="21" t="s">
-        <v>440</v>
+        <v>447</v>
       </c>
       <c r="J14" s="23"/>
     </row>
